--- a/2026_B题/outputs/task_candidates.xlsx
+++ b/2026_B题/outputs/task_candidates.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,47 +417,47 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>target_id</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>task</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>prep_start_s</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>exec_time_s</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>distance_m</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>speed_m_s</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>accel_m_s2</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>angle_deg</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>expected_success</t>
         </is>
@@ -493,16 +481,16 @@
         <v>477</v>
       </c>
       <c r="E2" t="n">
-        <v>26.71633608228954</v>
+        <v>26.71633608228991</v>
       </c>
       <c r="F2" t="n">
-        <v>1.089397535081516</v>
+        <v>1.089397535081515</v>
       </c>
       <c r="G2" t="n">
-        <v>0.3652891506876635</v>
+        <v>0.3652891506872737</v>
       </c>
       <c r="H2" t="n">
-        <v>147.2343787012731</v>
+        <v>147.2343787012737</v>
       </c>
       <c r="I2" t="n">
         <v>1</v>
@@ -526,16 +514,16 @@
         <v>477</v>
       </c>
       <c r="E3" t="n">
-        <v>25.88567667433599</v>
+        <v>25.88567667433622</v>
       </c>
       <c r="F3" t="n">
-        <v>1.089397535081516</v>
+        <v>1.089397535081515</v>
       </c>
       <c r="G3" t="n">
-        <v>0.3652891506876635</v>
+        <v>0.3652891506872737</v>
       </c>
       <c r="H3" t="n">
-        <v>122.3876809210369</v>
+        <v>122.3876809210378</v>
       </c>
       <c r="I3" t="n">
         <v>1</v>
@@ -559,16 +547,16 @@
         <v>477</v>
       </c>
       <c r="E4" t="n">
-        <v>18.4410683947705</v>
+        <v>18.4410683947704</v>
       </c>
       <c r="F4" t="n">
-        <v>1.089397535081516</v>
+        <v>1.089397535081515</v>
       </c>
       <c r="G4" t="n">
-        <v>0.3652891506876635</v>
+        <v>0.3652891506872737</v>
       </c>
       <c r="H4" t="n">
-        <v>78.31635261010109</v>
+        <v>78.31635261010246</v>
       </c>
       <c r="I4" t="n">
         <v>1</v>
@@ -592,16 +580,16 @@
         <v>477</v>
       </c>
       <c r="E5" t="n">
-        <v>29.37029946649339</v>
+        <v>29.37029946649321</v>
       </c>
       <c r="F5" t="n">
-        <v>1.089397535081516</v>
+        <v>1.089397535081515</v>
       </c>
       <c r="G5" t="n">
-        <v>0.3652891506876635</v>
+        <v>0.3652891506872737</v>
       </c>
       <c r="H5" t="n">
-        <v>68.14268028657978</v>
+        <v>68.14268028658057</v>
       </c>
       <c r="I5" t="n">
         <v>1</v>
@@ -625,16 +613,16 @@
         <v>477</v>
       </c>
       <c r="E6" t="n">
-        <v>20.38745436775327</v>
+        <v>20.38745436775285</v>
       </c>
       <c r="F6" t="n">
-        <v>1.089397535081516</v>
+        <v>1.089397535081515</v>
       </c>
       <c r="G6" t="n">
-        <v>0.3652891506876635</v>
+        <v>0.3652891506872737</v>
       </c>
       <c r="H6" t="n">
-        <v>19.36145406858014</v>
+        <v>19.36145406858054</v>
       </c>
       <c r="I6" t="n">
         <v>1</v>
@@ -658,16 +646,16 @@
         <v>477</v>
       </c>
       <c r="E7" t="n">
-        <v>33.92637958590459</v>
+        <v>33.92637958590421</v>
       </c>
       <c r="F7" t="n">
-        <v>1.089397535081516</v>
+        <v>1.089397535081515</v>
       </c>
       <c r="G7" t="n">
-        <v>0.3652891506876635</v>
+        <v>0.3652891506872737</v>
       </c>
       <c r="H7" t="n">
-        <v>33.36594655209029</v>
+        <v>33.36594655209069</v>
       </c>
       <c r="I7" t="n">
         <v>1</v>
@@ -691,16 +679,16 @@
         <v>477</v>
       </c>
       <c r="E8" t="n">
-        <v>24.27930391464074</v>
+        <v>24.27930391464108</v>
       </c>
       <c r="F8" t="n">
-        <v>1.089397535081516</v>
+        <v>1.089397535081515</v>
       </c>
       <c r="G8" t="n">
-        <v>0.3652891506876635</v>
+        <v>0.3652891506872737</v>
       </c>
       <c r="H8" t="n">
-        <v>222.6222568976733</v>
+        <v>222.6222568976726</v>
       </c>
       <c r="I8" t="n">
         <v>1</v>
@@ -724,16 +712,16 @@
         <v>477</v>
       </c>
       <c r="E9" t="n">
-        <v>18.99200284537356</v>
+        <v>18.99200284537343</v>
       </c>
       <c r="F9" t="n">
-        <v>1.089397535081516</v>
+        <v>1.089397535081515</v>
       </c>
       <c r="G9" t="n">
-        <v>0.3652891506876635</v>
+        <v>0.3652891506872737</v>
       </c>
       <c r="H9" t="n">
-        <v>288.2082402663081</v>
+        <v>288.2082402663068</v>
       </c>
       <c r="I9" t="n">
         <v>1</v>
@@ -757,16 +745,16 @@
         <v>477</v>
       </c>
       <c r="E10" t="n">
-        <v>16.50916702272726</v>
+        <v>16.50916702272687</v>
       </c>
       <c r="F10" t="n">
-        <v>1.089397535081516</v>
+        <v>1.089397535081515</v>
       </c>
       <c r="G10" t="n">
-        <v>0.3652891506876635</v>
+        <v>0.3652891506872737</v>
       </c>
       <c r="H10" t="n">
-        <v>332.4298100159656</v>
+        <v>332.4298100159648</v>
       </c>
       <c r="I10" t="n">
         <v>1</v>
@@ -790,16 +778,16 @@
         <v>477</v>
       </c>
       <c r="E11" t="n">
-        <v>30.58054313454867</v>
+        <v>30.58054313454835</v>
       </c>
       <c r="F11" t="n">
-        <v>1.089397535081516</v>
+        <v>1.089397535081515</v>
       </c>
       <c r="G11" t="n">
-        <v>0.3652891506876635</v>
+        <v>0.3652891506872737</v>
       </c>
       <c r="H11" t="n">
-        <v>318.3052367610168</v>
+        <v>318.3052367610163</v>
       </c>
       <c r="I11" t="n">
         <v>1</v>
@@ -823,16 +811,16 @@
         <v>477</v>
       </c>
       <c r="E12" t="n">
-        <v>33.35513989423738</v>
+        <v>33.35513989423695</v>
       </c>
       <c r="F12" t="n">
-        <v>1.089397535081516</v>
+        <v>1.089397535081515</v>
       </c>
       <c r="G12" t="n">
-        <v>0.3652891506876635</v>
+        <v>0.3652891506872737</v>
       </c>
       <c r="H12" t="n">
-        <v>344.4514275353555</v>
+        <v>344.4514275353553</v>
       </c>
       <c r="I12" t="n">
         <v>1</v>
@@ -856,16 +844,16 @@
         <v>477.1</v>
       </c>
       <c r="E13" t="n">
-        <v>24.27015625162585</v>
+        <v>24.27015625162618</v>
       </c>
       <c r="F13" t="n">
-        <v>1.015715699352925</v>
+        <v>1.015715699352924</v>
       </c>
       <c r="G13" t="n">
-        <v>0.3307581721744901</v>
+        <v>0.3307581721741226</v>
       </c>
       <c r="H13" t="n">
-        <v>223.1177554867222</v>
+        <v>223.1177554867215</v>
       </c>
       <c r="I13" t="n">
         <v>1</v>
@@ -889,13 +877,13 @@
         <v>477.5</v>
       </c>
       <c r="E14" t="n">
-        <v>18.14300171259512</v>
+        <v>18.1430017125955</v>
       </c>
       <c r="F14" t="n">
-        <v>0.8653356928561711</v>
+        <v>0.8653356928561704</v>
       </c>
       <c r="G14" t="n">
-        <v>0.4177629005766424</v>
+        <v>0.4177629005766074</v>
       </c>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="n">
@@ -920,13 +908,13 @@
         <v>477.5</v>
       </c>
       <c r="E15" t="n">
-        <v>9.918062381431817</v>
+        <v>9.918062381432213</v>
       </c>
       <c r="F15" t="n">
-        <v>0.8653356928561711</v>
+        <v>0.8653356928561704</v>
       </c>
       <c r="G15" t="n">
-        <v>0.4177629005766424</v>
+        <v>0.4177629005766074</v>
       </c>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="n">
@@ -951,13 +939,13 @@
         <v>477.5</v>
       </c>
       <c r="E16" t="n">
-        <v>13.73399760388541</v>
+        <v>13.73399760388551</v>
       </c>
       <c r="F16" t="n">
-        <v>0.8653356928561711</v>
+        <v>0.8653356928561704</v>
       </c>
       <c r="G16" t="n">
-        <v>0.4177629005766424</v>
+        <v>0.4177629005766074</v>
       </c>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="n">
@@ -982,13 +970,13 @@
         <v>477.5</v>
       </c>
       <c r="E17" t="n">
-        <v>17.53655404330096</v>
+        <v>17.53655404330063</v>
       </c>
       <c r="F17" t="n">
-        <v>0.8653356928561711</v>
+        <v>0.8653356928561704</v>
       </c>
       <c r="G17" t="n">
-        <v>0.4177629005766424</v>
+        <v>0.4177629005766074</v>
       </c>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="n">
@@ -1013,13 +1001,13 @@
         <v>477.5</v>
       </c>
       <c r="E18" t="n">
-        <v>22.37383532872388</v>
+        <v>22.37383532872347</v>
       </c>
       <c r="F18" t="n">
-        <v>0.8653356928561711</v>
+        <v>0.8653356928561704</v>
       </c>
       <c r="G18" t="n">
-        <v>0.4177629005766424</v>
+        <v>0.4177629005766074</v>
       </c>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="n">
@@ -1044,16 +1032,16 @@
         <v>477.5</v>
       </c>
       <c r="E19" t="n">
-        <v>25.7918297526355</v>
+        <v>25.79182975263586</v>
       </c>
       <c r="F19" t="n">
-        <v>0.8653356928561711</v>
+        <v>0.8653356928561704</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4177629005766424</v>
+        <v>0.4177629005766074</v>
       </c>
       <c r="H19" t="n">
-        <v>147.7517613986253</v>
+        <v>147.7517613986258</v>
       </c>
       <c r="I19" t="n">
         <v>1</v>
@@ -1077,16 +1065,16 @@
         <v>477.5</v>
       </c>
       <c r="E20" t="n">
-        <v>24.9485629439128</v>
+        <v>24.94856294391301</v>
       </c>
       <c r="F20" t="n">
-        <v>0.8653356928561711</v>
+        <v>0.8653356928561704</v>
       </c>
       <c r="G20" t="n">
-        <v>0.4177629005766424</v>
+        <v>0.4177629005766074</v>
       </c>
       <c r="H20" t="n">
-        <v>121.9798731864513</v>
+        <v>121.9798731864522</v>
       </c>
       <c r="I20" t="n">
         <v>1</v>
@@ -1110,16 +1098,16 @@
         <v>477.5</v>
       </c>
       <c r="E21" t="n">
-        <v>17.90782072399248</v>
+        <v>17.90782072399234</v>
       </c>
       <c r="F21" t="n">
-        <v>0.8653356928561711</v>
+        <v>0.8653356928561704</v>
       </c>
       <c r="G21" t="n">
-        <v>0.4177629005766424</v>
+        <v>0.4177629005766074</v>
       </c>
       <c r="H21" t="n">
-        <v>75.82049994013005</v>
+        <v>75.82049994013141</v>
       </c>
       <c r="I21" t="n">
         <v>1</v>
@@ -1143,16 +1131,16 @@
         <v>477.5</v>
       </c>
       <c r="E22" t="n">
-        <v>28.97936466000711</v>
+        <v>28.97936466000692</v>
       </c>
       <c r="F22" t="n">
-        <v>0.8653356928561711</v>
+        <v>0.8653356928561704</v>
       </c>
       <c r="G22" t="n">
-        <v>0.4177629005766424</v>
+        <v>0.4177629005766074</v>
       </c>
       <c r="H22" t="n">
-        <v>66.43268687355504</v>
+        <v>66.43268687355578</v>
       </c>
       <c r="I22" t="n">
         <v>1</v>
@@ -1176,16 +1164,16 @@
         <v>477.5</v>
       </c>
       <c r="E23" t="n">
-        <v>20.7901840605558</v>
+        <v>20.79018406055537</v>
       </c>
       <c r="F23" t="n">
-        <v>0.8653356928561711</v>
+        <v>0.8653356928561704</v>
       </c>
       <c r="G23" t="n">
-        <v>0.4177629005766424</v>
+        <v>0.4177629005766074</v>
       </c>
       <c r="H23" t="n">
-        <v>16.95321247974726</v>
+        <v>16.95321247974755</v>
       </c>
       <c r="I23" t="n">
         <v>1</v>
@@ -1209,16 +1197,16 @@
         <v>477.5</v>
       </c>
       <c r="E24" t="n">
-        <v>34.10089134694379</v>
+        <v>34.1008913469434</v>
       </c>
       <c r="F24" t="n">
-        <v>0.8653356928561711</v>
+        <v>0.8653356928561704</v>
       </c>
       <c r="G24" t="n">
-        <v>0.4177629005766424</v>
+        <v>0.4177629005766074</v>
       </c>
       <c r="H24" t="n">
-        <v>31.78529639469366</v>
+        <v>31.78529639469406</v>
       </c>
       <c r="I24" t="n">
         <v>1</v>
@@ -1242,16 +1230,16 @@
         <v>477.5</v>
       </c>
       <c r="E25" t="n">
-        <v>24.28993105277934</v>
+        <v>24.28993105277967</v>
       </c>
       <c r="F25" t="n">
-        <v>0.8653356928561711</v>
+        <v>0.8653356928561704</v>
       </c>
       <c r="G25" t="n">
-        <v>0.4177629005766424</v>
+        <v>0.4177629005766074</v>
       </c>
       <c r="H25" t="n">
-        <v>224.8740447202403</v>
+        <v>224.8740447202396</v>
       </c>
       <c r="I25" t="n">
         <v>1</v>
@@ -1275,16 +1263,16 @@
         <v>477.5</v>
       </c>
       <c r="E26" t="n">
-        <v>19.86174658809819</v>
+        <v>19.86174658809807</v>
       </c>
       <c r="F26" t="n">
-        <v>0.8653356928561711</v>
+        <v>0.8653356928561704</v>
       </c>
       <c r="G26" t="n">
-        <v>0.4177629005766424</v>
+        <v>0.4177629005766074</v>
       </c>
       <c r="H26" t="n">
-        <v>289.3676109952581</v>
+        <v>289.3676109952569</v>
       </c>
       <c r="I26" t="n">
         <v>1</v>
@@ -1308,16 +1296,16 @@
         <v>477.5</v>
       </c>
       <c r="E27" t="n">
-        <v>17.41269580752055</v>
+        <v>17.41269580752018</v>
       </c>
       <c r="F27" t="n">
-        <v>0.8653356928561711</v>
+        <v>0.8653356928561704</v>
       </c>
       <c r="G27" t="n">
-        <v>0.4177629005766424</v>
+        <v>0.4177629005766074</v>
       </c>
       <c r="H27" t="n">
-        <v>331.3907796590553</v>
+        <v>331.3907796590545</v>
       </c>
       <c r="I27" t="n">
         <v>1</v>
@@ -1341,16 +1329,16 @@
         <v>477.5</v>
       </c>
       <c r="E28" t="n">
-        <v>31.5311513850021</v>
+        <v>31.53115138500179</v>
       </c>
       <c r="F28" t="n">
-        <v>0.8653356928561711</v>
+        <v>0.8653356928561704</v>
       </c>
       <c r="G28" t="n">
-        <v>0.4177629005766424</v>
+        <v>0.4177629005766074</v>
       </c>
       <c r="H28" t="n">
-        <v>318.1482069711444</v>
+        <v>318.1482069711439</v>
       </c>
       <c r="I28" t="n">
         <v>1</v>
@@ -1374,16 +1362,16 @@
         <v>477.5</v>
       </c>
       <c r="E29" t="n">
-        <v>34.17389360971303</v>
+        <v>34.17389360971261</v>
       </c>
       <c r="F29" t="n">
-        <v>0.8653356928561711</v>
+        <v>0.8653356928561704</v>
       </c>
       <c r="G29" t="n">
-        <v>0.4177629005766424</v>
+        <v>0.4177629005766074</v>
       </c>
       <c r="H29" t="n">
-        <v>343.619103322943</v>
+        <v>343.6191033229427</v>
       </c>
       <c r="I29" t="n">
         <v>1</v>
@@ -1407,16 +1395,16 @@
         <v>477.6</v>
       </c>
       <c r="E30" t="n">
-        <v>17.90025067678558</v>
+        <v>17.90025067678545</v>
       </c>
       <c r="F30" t="n">
-        <v>0.9408419365202229</v>
+        <v>0.9408419365202224</v>
       </c>
       <c r="G30" t="n">
-        <v>0.4300317607196878</v>
+        <v>0.4300317607196872</v>
       </c>
       <c r="H30" t="n">
-        <v>75.29635873490736</v>
+        <v>75.29635873490867</v>
       </c>
       <c r="I30" t="n">
         <v>1</v>
@@ -1440,16 +1428,16 @@
         <v>477.9</v>
       </c>
       <c r="E31" t="n">
-        <v>25.26132500201643</v>
+        <v>25.26132500201677</v>
       </c>
       <c r="F31" t="n">
-        <v>1.420377470650887</v>
+        <v>1.420377470650886</v>
       </c>
       <c r="G31" t="n">
-        <v>0.4969312263433484</v>
+        <v>0.4969312263434795</v>
       </c>
       <c r="H31" t="n">
-        <v>147.4549318375722</v>
+        <v>147.4549318375729</v>
       </c>
       <c r="I31" t="n">
         <v>1</v>
@@ -1473,16 +1461,16 @@
         <v>477.9</v>
       </c>
       <c r="E32" t="n">
-        <v>24.52989970630669</v>
+        <v>24.52989970630689</v>
       </c>
       <c r="F32" t="n">
-        <v>1.420377470650887</v>
+        <v>1.420377470650886</v>
       </c>
       <c r="G32" t="n">
-        <v>0.4969312263433484</v>
+        <v>0.4969312263434795</v>
       </c>
       <c r="H32" t="n">
-        <v>121.1654681667918</v>
+        <v>121.1654681667927</v>
       </c>
       <c r="I32" t="n">
         <v>1</v>
@@ -1506,16 +1494,16 @@
         <v>477.9</v>
       </c>
       <c r="E33" t="n">
-        <v>17.87590886484232</v>
+        <v>17.87590886484217</v>
       </c>
       <c r="F33" t="n">
-        <v>1.420377470650887</v>
+        <v>1.420377470650886</v>
       </c>
       <c r="G33" t="n">
-        <v>0.4969312263433484</v>
+        <v>0.4969312263434795</v>
       </c>
       <c r="H33" t="n">
-        <v>74.07257858952551</v>
+        <v>74.07257858952681</v>
       </c>
       <c r="I33" t="n">
         <v>1</v>
@@ -1539,16 +1527,16 @@
         <v>477.9</v>
       </c>
       <c r="E34" t="n">
-        <v>29.03372037559205</v>
+        <v>29.03372037559184</v>
       </c>
       <c r="F34" t="n">
-        <v>1.420377470650887</v>
+        <v>1.420377470650886</v>
       </c>
       <c r="G34" t="n">
-        <v>0.4969312263433484</v>
+        <v>0.4969312263434795</v>
       </c>
       <c r="H34" t="n">
-        <v>65.35806629896359</v>
+        <v>65.35806629896433</v>
       </c>
       <c r="I34" t="n">
         <v>1</v>
@@ -1572,16 +1560,16 @@
         <v>477.9</v>
       </c>
       <c r="E35" t="n">
-        <v>21.2384640019492</v>
+        <v>21.23846400194878</v>
       </c>
       <c r="F35" t="n">
-        <v>1.420377470650887</v>
+        <v>1.420377470650886</v>
       </c>
       <c r="G35" t="n">
-        <v>0.4969312263433484</v>
+        <v>0.4969312263434795</v>
       </c>
       <c r="H35" t="n">
-        <v>16.09976679946851</v>
+        <v>16.09976679946874</v>
       </c>
       <c r="I35" t="n">
         <v>1</v>
@@ -1605,16 +1593,16 @@
         <v>477.9</v>
       </c>
       <c r="E36" t="n">
-        <v>34.45353650084634</v>
+        <v>34.45353650084596</v>
       </c>
       <c r="F36" t="n">
-        <v>1.420377470650887</v>
+        <v>1.420377470650886</v>
       </c>
       <c r="G36" t="n">
-        <v>0.4969312263433484</v>
+        <v>0.4969312263434795</v>
       </c>
       <c r="H36" t="n">
-        <v>31.08689989402114</v>
+        <v>31.08689989402149</v>
       </c>
       <c r="I36" t="n">
         <v>1</v>
@@ -1638,16 +1626,16 @@
         <v>477.9</v>
       </c>
       <c r="E37" t="n">
-        <v>24.04900176882343</v>
+        <v>24.04900176882375</v>
       </c>
       <c r="F37" t="n">
-        <v>1.420377470650887</v>
+        <v>1.420377470650886</v>
       </c>
       <c r="G37" t="n">
-        <v>0.4969312263433484</v>
+        <v>0.4969312263434795</v>
       </c>
       <c r="H37" t="n">
-        <v>226.0375391238844</v>
+        <v>226.0375391238837</v>
       </c>
       <c r="I37" t="n">
         <v>1</v>
@@ -1671,16 +1659,16 @@
         <v>477.9</v>
       </c>
       <c r="E38" t="n">
-        <v>20.20121954783743</v>
+        <v>20.2012195478373</v>
       </c>
       <c r="F38" t="n">
-        <v>1.420377470650887</v>
+        <v>1.420377470650886</v>
       </c>
       <c r="G38" t="n">
-        <v>0.4969312263433484</v>
+        <v>0.4969312263434795</v>
       </c>
       <c r="H38" t="n">
-        <v>290.5935373616379</v>
+        <v>290.5935373616367</v>
       </c>
       <c r="I38" t="n">
         <v>1</v>
@@ -1704,16 +1692,16 @@
         <v>477.9</v>
       </c>
       <c r="E39" t="n">
-        <v>17.95103715182181</v>
+        <v>17.95103715182144</v>
       </c>
       <c r="F39" t="n">
-        <v>1.420377470650887</v>
+        <v>1.420377470650886</v>
       </c>
       <c r="G39" t="n">
-        <v>0.4969312263433484</v>
+        <v>0.4969312263434795</v>
       </c>
       <c r="H39" t="n">
-        <v>331.7001061507138</v>
+        <v>331.7001061507131</v>
       </c>
       <c r="I39" t="n">
         <v>1</v>
@@ -1737,16 +1725,16 @@
         <v>477.9</v>
       </c>
       <c r="E40" t="n">
-        <v>32.03346181131509</v>
+        <v>32.03346181131479</v>
       </c>
       <c r="F40" t="n">
-        <v>1.420377470650887</v>
+        <v>1.420377470650886</v>
       </c>
       <c r="G40" t="n">
-        <v>0.4969312263433484</v>
+        <v>0.4969312263434795</v>
       </c>
       <c r="H40" t="n">
-        <v>318.5374073903427</v>
+        <v>318.5374073903421</v>
       </c>
       <c r="I40" t="n">
         <v>1</v>
@@ -1770,16 +1758,16 @@
         <v>477.9</v>
       </c>
       <c r="E41" t="n">
-        <v>34.72029730030896</v>
+        <v>34.72029730030856</v>
       </c>
       <c r="F41" t="n">
-        <v>1.420377470650887</v>
+        <v>1.420377470650886</v>
       </c>
       <c r="G41" t="n">
-        <v>0.4969312263433484</v>
+        <v>0.4969312263434795</v>
       </c>
       <c r="H41" t="n">
-        <v>343.5873278360241</v>
+        <v>343.5873278360239</v>
       </c>
       <c r="I41" t="n">
         <v>1</v>
@@ -1803,13 +1791,13 @@
         <v>478</v>
       </c>
       <c r="E42" t="n">
-        <v>17.68870318639376</v>
+        <v>17.68870318639411</v>
       </c>
       <c r="F42" t="n">
-        <v>1.627062111739188</v>
+        <v>1.627062111739187</v>
       </c>
       <c r="G42" t="n">
-        <v>0.5092526391113109</v>
+        <v>0.5092526391114468</v>
       </c>
       <c r="H42" t="inlineStr"/>
       <c r="I42" t="n">
@@ -1834,13 +1822,13 @@
         <v>478</v>
       </c>
       <c r="E43" t="n">
-        <v>9.422440001332792</v>
+        <v>9.422440001333166</v>
       </c>
       <c r="F43" t="n">
-        <v>1.627062111739188</v>
+        <v>1.627062111739187</v>
       </c>
       <c r="G43" t="n">
-        <v>0.5092526391113109</v>
+        <v>0.5092526391114468</v>
       </c>
       <c r="H43" t="inlineStr"/>
       <c r="I43" t="n">
@@ -1865,13 +1853,13 @@
         <v>478</v>
       </c>
       <c r="E44" t="n">
-        <v>13.83264722079083</v>
+        <v>13.83264722079091</v>
       </c>
       <c r="F44" t="n">
-        <v>1.627062111739188</v>
+        <v>1.627062111739187</v>
       </c>
       <c r="G44" t="n">
-        <v>0.5092526391113109</v>
+        <v>0.5092526391114468</v>
       </c>
       <c r="H44" t="inlineStr"/>
       <c r="I44" t="n">
@@ -1896,13 +1884,13 @@
         <v>478</v>
       </c>
       <c r="E45" t="n">
-        <v>7.462014441860378</v>
+        <v>7.462014441860013</v>
       </c>
       <c r="F45" t="n">
-        <v>1.627062111739188</v>
+        <v>1.627062111739187</v>
       </c>
       <c r="G45" t="n">
-        <v>0.5092526391113109</v>
+        <v>0.5092526391114468</v>
       </c>
       <c r="H45" t="inlineStr"/>
       <c r="I45" t="n">
@@ -1927,13 +1915,13 @@
         <v>478</v>
       </c>
       <c r="E46" t="n">
-        <v>18.20216343866621</v>
+        <v>18.20216343866589</v>
       </c>
       <c r="F46" t="n">
-        <v>1.627062111739188</v>
+        <v>1.627062111739187</v>
       </c>
       <c r="G46" t="n">
-        <v>0.5092526391113109</v>
+        <v>0.5092526391114468</v>
       </c>
       <c r="H46" t="inlineStr"/>
       <c r="I46" t="n">
@@ -1958,13 +1946,13 @@
         <v>478</v>
       </c>
       <c r="E47" t="n">
-        <v>23.08973432969071</v>
+        <v>23.08973432969031</v>
       </c>
       <c r="F47" t="n">
-        <v>1.627062111739188</v>
+        <v>1.627062111739187</v>
       </c>
       <c r="G47" t="n">
-        <v>0.5092526391113109</v>
+        <v>0.5092526391114468</v>
       </c>
       <c r="H47" t="inlineStr"/>
       <c r="I47" t="n">
@@ -1989,13 +1977,13 @@
         <v>478.4</v>
       </c>
       <c r="E48" t="n">
-        <v>13.67579887027014</v>
+        <v>13.6757988702702</v>
       </c>
       <c r="F48" t="n">
-        <v>1.743556963523517</v>
+        <v>1.743556963523515</v>
       </c>
       <c r="G48" t="n">
-        <v>0.4414627908934557</v>
+        <v>0.4414627908935818</v>
       </c>
       <c r="H48" t="inlineStr"/>
       <c r="I48" t="n">
@@ -2020,13 +2008,13 @@
         <v>478.5</v>
       </c>
       <c r="E49" t="n">
-        <v>16.89961213527365</v>
+        <v>16.899612135274</v>
       </c>
       <c r="F49" t="n">
-        <v>1.870284641620085</v>
+        <v>1.870284641620083</v>
       </c>
       <c r="G49" t="n">
-        <v>0.4687649567322231</v>
+        <v>0.4687649567323425</v>
       </c>
       <c r="H49" t="inlineStr"/>
       <c r="I49" t="n">
@@ -2051,13 +2039,13 @@
         <v>478.5</v>
       </c>
       <c r="E50" t="n">
-        <v>8.607828367614268</v>
+        <v>8.607828367614619</v>
       </c>
       <c r="F50" t="n">
-        <v>1.870284641620085</v>
+        <v>1.870284641620083</v>
       </c>
       <c r="G50" t="n">
-        <v>0.4687649567322231</v>
+        <v>0.4687649567323425</v>
       </c>
       <c r="H50" t="inlineStr"/>
       <c r="I50" t="n">
@@ -2082,13 +2070,13 @@
         <v>478.5</v>
       </c>
       <c r="E51" t="n">
-        <v>13.6768595062743</v>
+        <v>13.67685950627434</v>
       </c>
       <c r="F51" t="n">
-        <v>1.870284641620085</v>
+        <v>1.870284641620083</v>
       </c>
       <c r="G51" t="n">
-        <v>0.4687649567322231</v>
+        <v>0.4687649567323425</v>
       </c>
       <c r="H51" t="inlineStr"/>
       <c r="I51" t="n">
@@ -2113,13 +2101,13 @@
         <v>478.5</v>
       </c>
       <c r="E52" t="n">
-        <v>8.264087415958681</v>
+        <v>8.264087415958315</v>
       </c>
       <c r="F52" t="n">
-        <v>1.870284641620085</v>
+        <v>1.870284641620083</v>
       </c>
       <c r="G52" t="n">
-        <v>0.4687649567322231</v>
+        <v>0.4687649567323425</v>
       </c>
       <c r="H52" t="inlineStr"/>
       <c r="I52" t="n">
@@ -2144,13 +2132,13 @@
         <v>478.5</v>
       </c>
       <c r="E53" t="n">
-        <v>18.89662582982199</v>
+        <v>18.89662582982167</v>
       </c>
       <c r="F53" t="n">
-        <v>1.870284641620085</v>
+        <v>1.870284641620083</v>
       </c>
       <c r="G53" t="n">
-        <v>0.4687649567322231</v>
+        <v>0.4687649567323425</v>
       </c>
       <c r="H53" t="inlineStr"/>
       <c r="I53" t="n">
@@ -2175,13 +2163,13 @@
         <v>478.5</v>
       </c>
       <c r="E54" t="n">
-        <v>23.95387404239118</v>
+        <v>23.95387404239079</v>
       </c>
       <c r="F54" t="n">
-        <v>1.870284641620085</v>
+        <v>1.870284641620083</v>
       </c>
       <c r="G54" t="n">
-        <v>0.4687649567322231</v>
+        <v>0.4687649567323425</v>
       </c>
       <c r="H54" t="inlineStr"/>
       <c r="I54" t="n">
@@ -2206,16 +2194,16 @@
         <v>481.5</v>
       </c>
       <c r="E55" t="n">
-        <v>20.92972497808368</v>
+        <v>20.9297249780839</v>
       </c>
       <c r="F55" t="n">
-        <v>0.8367785158010671</v>
+        <v>0.8367785158010662</v>
       </c>
       <c r="G55" t="n">
-        <v>0.3160018881791601</v>
+        <v>0.3160018881789212</v>
       </c>
       <c r="H55" t="n">
-        <v>133.4379746372997</v>
+        <v>133.4379746373003</v>
       </c>
       <c r="I55" t="n">
         <v>1</v>
@@ -2239,16 +2227,16 @@
         <v>481.5</v>
       </c>
       <c r="E56" t="n">
-        <v>23.32760568583381</v>
+        <v>23.32760568583388</v>
       </c>
       <c r="F56" t="n">
-        <v>0.8367785158010671</v>
+        <v>0.8367785158010662</v>
       </c>
       <c r="G56" t="n">
-        <v>0.3160018881791601</v>
+        <v>0.3160018881789212</v>
       </c>
       <c r="H56" t="n">
-        <v>104.3728401307449</v>
+        <v>104.3728401307456</v>
       </c>
       <c r="I56" t="n">
         <v>1</v>
@@ -2272,16 +2260,16 @@
         <v>481.5</v>
       </c>
       <c r="E57" t="n">
-        <v>22.19924025791583</v>
+        <v>22.19924025791566</v>
       </c>
       <c r="F57" t="n">
-        <v>0.8367785158010671</v>
+        <v>0.8367785158010662</v>
       </c>
       <c r="G57" t="n">
-        <v>0.3160018881791601</v>
+        <v>0.3160018881789212</v>
       </c>
       <c r="H57" t="n">
-        <v>57.86121608955295</v>
+        <v>57.86121608955364</v>
       </c>
       <c r="I57" t="n">
         <v>1</v>
@@ -2305,16 +2293,16 @@
         <v>481.5</v>
       </c>
       <c r="E58" t="n">
-        <v>33.84102143328688</v>
+        <v>33.8410214332867</v>
       </c>
       <c r="F58" t="n">
-        <v>0.8367785158010671</v>
+        <v>0.8367785158010662</v>
       </c>
       <c r="G58" t="n">
-        <v>0.3160018881791601</v>
+        <v>0.3160018881789212</v>
       </c>
       <c r="H58" t="n">
-        <v>55.82477412786636</v>
+        <v>55.82477412786682</v>
       </c>
       <c r="I58" t="n">
         <v>1</v>
@@ -2338,16 +2326,16 @@
         <v>481.5</v>
       </c>
       <c r="E59" t="n">
-        <v>28.3198496736475</v>
+        <v>28.31984967364719</v>
       </c>
       <c r="F59" t="n">
-        <v>0.8367785158010671</v>
+        <v>0.8367785158010662</v>
       </c>
       <c r="G59" t="n">
-        <v>0.3160018881791601</v>
+        <v>0.3160018881789212</v>
       </c>
       <c r="H59" t="n">
-        <v>15.35166467246108</v>
+        <v>15.35166467246125</v>
       </c>
       <c r="I59" t="n">
         <v>1</v>
@@ -2371,16 +2359,16 @@
         <v>481.5</v>
       </c>
       <c r="E60" t="n">
-        <v>18.50474918945561</v>
+        <v>18.50474918945577</v>
       </c>
       <c r="F60" t="n">
-        <v>0.8367785158010671</v>
+        <v>0.8367785158010662</v>
       </c>
       <c r="G60" t="n">
-        <v>0.3160018881791601</v>
+        <v>0.3160018881789212</v>
       </c>
       <c r="H60" t="n">
-        <v>238.0561896146499</v>
+        <v>238.0561896146491</v>
       </c>
       <c r="I60" t="n">
         <v>1</v>
@@ -2404,16 +2392,16 @@
         <v>481.5</v>
       </c>
       <c r="E61" t="n">
-        <v>22.26297182994274</v>
+        <v>22.26297182994254</v>
       </c>
       <c r="F61" t="n">
-        <v>0.8367785158010671</v>
+        <v>0.8367785158010662</v>
       </c>
       <c r="G61" t="n">
-        <v>0.3160018881791601</v>
+        <v>0.3160018881789212</v>
       </c>
       <c r="H61" t="n">
-        <v>308.9961237089955</v>
+        <v>308.9961237089948</v>
       </c>
       <c r="I61" t="n">
         <v>1</v>
@@ -2437,16 +2425,16 @@
         <v>481.5</v>
       </c>
       <c r="E62" t="n">
-        <v>23.73521496692213</v>
+        <v>23.73521496692182</v>
       </c>
       <c r="F62" t="n">
-        <v>0.8367785158010671</v>
+        <v>0.8367785158010662</v>
       </c>
       <c r="G62" t="n">
-        <v>0.3160018881791601</v>
+        <v>0.3160018881789212</v>
       </c>
       <c r="H62" t="n">
-        <v>343.0933206699129</v>
+        <v>343.0933206699127</v>
       </c>
       <c r="I62" t="n">
         <v>1</v>
@@ -2470,16 +2458,16 @@
         <v>481.5</v>
       </c>
       <c r="E63" t="n">
-        <v>36.60120621023719</v>
+        <v>36.60120621023692</v>
       </c>
       <c r="F63" t="n">
-        <v>0.8367785158010671</v>
+        <v>0.8367785158010662</v>
       </c>
       <c r="G63" t="n">
-        <v>0.3160018881791601</v>
+        <v>0.3160018881789212</v>
       </c>
       <c r="H63" t="n">
-        <v>327.6173900974943</v>
+        <v>327.617390097494</v>
       </c>
       <c r="I63" t="n">
         <v>1</v>
@@ -2503,16 +2491,16 @@
         <v>482</v>
       </c>
       <c r="E64" t="n">
-        <v>20.75981765389583</v>
+        <v>20.75981765389604</v>
       </c>
       <c r="F64" t="n">
-        <v>1.03671884114252</v>
+        <v>1.036718841142519</v>
       </c>
       <c r="G64" t="n">
-        <v>0.3756347989096224</v>
+        <v>0.3756347989098908</v>
       </c>
       <c r="H64" t="n">
-        <v>133.4183896924487</v>
+        <v>133.4183896924493</v>
       </c>
       <c r="I64" t="n">
         <v>1</v>
@@ -2536,16 +2524,16 @@
         <v>482</v>
       </c>
       <c r="E65" t="n">
-        <v>23.18271126906961</v>
+        <v>23.18271126906969</v>
       </c>
       <c r="F65" t="n">
-        <v>1.03671884114252</v>
+        <v>1.036718841142519</v>
       </c>
       <c r="G65" t="n">
-        <v>0.3756347989096224</v>
+        <v>0.3756347989098908</v>
       </c>
       <c r="H65" t="n">
-        <v>104.1535081830747</v>
+        <v>104.1535081830755</v>
       </c>
       <c r="I65" t="n">
         <v>1</v>
@@ -2569,16 +2557,16 @@
         <v>482</v>
       </c>
       <c r="E66" t="n">
-        <v>22.16441551408801</v>
+        <v>22.16441551408784</v>
       </c>
       <c r="F66" t="n">
-        <v>1.03671884114252</v>
+        <v>1.036718841142519</v>
       </c>
       <c r="G66" t="n">
-        <v>0.3756347989096224</v>
+        <v>0.3756347989098908</v>
       </c>
       <c r="H66" t="n">
-        <v>57.43126672044662</v>
+        <v>57.4312667204473</v>
       </c>
       <c r="I66" t="n">
         <v>1</v>
@@ -2602,16 +2590,16 @@
         <v>482</v>
       </c>
       <c r="E67" t="n">
-        <v>33.81192004107114</v>
+        <v>33.81192004107096</v>
       </c>
       <c r="F67" t="n">
-        <v>1.03671884114252</v>
+        <v>1.036718841142519</v>
       </c>
       <c r="G67" t="n">
-        <v>0.3756347989096224</v>
+        <v>0.3756347989098908</v>
       </c>
       <c r="H67" t="n">
-        <v>55.54097829811269</v>
+        <v>55.54097829811315</v>
       </c>
       <c r="I67" t="n">
         <v>1</v>
@@ -2635,16 +2623,16 @@
         <v>482</v>
       </c>
       <c r="E68" t="n">
-        <v>28.40648138645804</v>
+        <v>28.40648138645773</v>
       </c>
       <c r="F68" t="n">
-        <v>1.03671884114252</v>
+        <v>1.036718841142519</v>
       </c>
       <c r="G68" t="n">
-        <v>0.3756347989096224</v>
+        <v>0.3756347989098908</v>
       </c>
       <c r="H68" t="n">
-        <v>15.05605408987014</v>
+        <v>15.05605408987032</v>
       </c>
       <c r="I68" t="n">
         <v>1</v>
@@ -2668,16 +2656,16 @@
         <v>482</v>
       </c>
       <c r="E69" t="n">
-        <v>18.54150863722302</v>
+        <v>18.54150863722319</v>
       </c>
       <c r="F69" t="n">
-        <v>1.03671884114252</v>
+        <v>1.036718841142519</v>
       </c>
       <c r="G69" t="n">
-        <v>0.3756347989096224</v>
+        <v>0.3756347989098908</v>
       </c>
       <c r="H69" t="n">
-        <v>238.5697749977384</v>
+        <v>238.5697749977376</v>
       </c>
       <c r="I69" t="n">
         <v>1</v>
@@ -2701,16 +2689,16 @@
         <v>482</v>
       </c>
       <c r="E70" t="n">
-        <v>22.43182958519165</v>
+        <v>22.43182958519145</v>
       </c>
       <c r="F70" t="n">
-        <v>1.03671884114252</v>
+        <v>1.036718841142519</v>
       </c>
       <c r="G70" t="n">
-        <v>0.3756347989096224</v>
+        <v>0.3756347989098908</v>
       </c>
       <c r="H70" t="n">
-        <v>309.0478052485814</v>
+        <v>309.0478052485808</v>
       </c>
       <c r="I70" t="n">
         <v>1</v>
@@ -2734,16 +2722,16 @@
         <v>482</v>
       </c>
       <c r="E71" t="n">
-        <v>23.88650651740105</v>
+        <v>23.88650651740075</v>
       </c>
       <c r="F71" t="n">
-        <v>1.03671884114252</v>
+        <v>1.036718841142519</v>
       </c>
       <c r="G71" t="n">
-        <v>0.3756347989096224</v>
+        <v>0.3756347989098908</v>
       </c>
       <c r="H71" t="n">
-        <v>342.9064619486972</v>
+        <v>342.906461948697</v>
       </c>
       <c r="I71" t="n">
         <v>1</v>
@@ -2767,16 +2755,16 @@
         <v>482</v>
       </c>
       <c r="E72" t="n">
-        <v>36.76769289585154</v>
+        <v>36.76769289585128</v>
       </c>
       <c r="F72" t="n">
-        <v>1.03671884114252</v>
+        <v>1.036718841142519</v>
       </c>
       <c r="G72" t="n">
-        <v>0.3756347989096224</v>
+        <v>0.3756347989098908</v>
       </c>
       <c r="H72" t="n">
-        <v>327.5632530465594</v>
+        <v>327.5632530465591</v>
       </c>
       <c r="I72" t="n">
         <v>1</v>
@@ -2800,16 +2788,16 @@
         <v>482.1</v>
       </c>
       <c r="E73" t="n">
-        <v>23.15245267049934</v>
+        <v>23.15245267049941</v>
       </c>
       <c r="F73" t="n">
-        <v>1.212867546144009</v>
+        <v>1.212867546144007</v>
       </c>
       <c r="G73" t="n">
-        <v>0.4730106066637481</v>
+        <v>0.4730106066640166</v>
       </c>
       <c r="H73" t="n">
-        <v>104.0376031703317</v>
+        <v>104.0376031703324</v>
       </c>
       <c r="I73" t="n">
         <v>1</v>
@@ -2833,16 +2821,16 @@
         <v>482.1</v>
       </c>
       <c r="E74" t="n">
-        <v>28.45285075726409</v>
+        <v>28.45285075726379</v>
       </c>
       <c r="F74" t="n">
-        <v>1.212867546144009</v>
+        <v>1.212867546144007</v>
       </c>
       <c r="G74" t="n">
-        <v>0.4730106066637481</v>
+        <v>0.4730106066640166</v>
       </c>
       <c r="H74" t="n">
-        <v>14.99354862339902</v>
+        <v>14.99354862339914</v>
       </c>
       <c r="I74" t="n">
         <v>1</v>
@@ -2866,13 +2854,13 @@
         <v>482.2</v>
       </c>
       <c r="E75" t="n">
-        <v>11.42659916431426</v>
+        <v>11.42659916431446</v>
       </c>
       <c r="F75" t="n">
-        <v>1.383708317324046</v>
+        <v>1.383708317324045</v>
       </c>
       <c r="G75" t="n">
-        <v>0.5309158474560929</v>
+        <v>0.5309158474563628</v>
       </c>
       <c r="H75" t="inlineStr"/>
       <c r="I75" t="n">
@@ -2897,13 +2885,13 @@
         <v>482.2</v>
       </c>
       <c r="E76" t="n">
-        <v>13.34124097449744</v>
+        <v>13.34124097449731</v>
       </c>
       <c r="F76" t="n">
-        <v>1.383708317324046</v>
+        <v>1.383708317324045</v>
       </c>
       <c r="G76" t="n">
-        <v>0.5309158474560929</v>
+        <v>0.5309158474563628</v>
       </c>
       <c r="H76" t="inlineStr"/>
       <c r="I76" t="n">
@@ -2928,13 +2916,13 @@
         <v>482.2</v>
       </c>
       <c r="E77" t="n">
-        <v>13.81248584398659</v>
+        <v>13.81248584398628</v>
       </c>
       <c r="F77" t="n">
-        <v>1.383708317324046</v>
+        <v>1.383708317324045</v>
       </c>
       <c r="G77" t="n">
-        <v>0.5309158474560929</v>
+        <v>0.5309158474563628</v>
       </c>
       <c r="H77" t="inlineStr"/>
       <c r="I77" t="n">
@@ -2959,13 +2947,13 @@
         <v>482.2</v>
       </c>
       <c r="E78" t="n">
-        <v>23.5010370431981</v>
+        <v>23.50103704319782</v>
       </c>
       <c r="F78" t="n">
-        <v>1.383708317324046</v>
+        <v>1.383708317324045</v>
       </c>
       <c r="G78" t="n">
-        <v>0.5309158474560929</v>
+        <v>0.5309158474563628</v>
       </c>
       <c r="H78" t="inlineStr"/>
       <c r="I78" t="n">
@@ -2990,13 +2978,13 @@
         <v>482.2</v>
       </c>
       <c r="E79" t="n">
-        <v>29.60311909971402</v>
+        <v>29.60311909971372</v>
       </c>
       <c r="F79" t="n">
-        <v>1.383708317324046</v>
+        <v>1.383708317324045</v>
       </c>
       <c r="G79" t="n">
-        <v>0.5309158474560929</v>
+        <v>0.5309158474563628</v>
       </c>
       <c r="H79" t="inlineStr"/>
       <c r="I79" t="n">
@@ -3021,16 +3009,16 @@
         <v>482.2</v>
       </c>
       <c r="E80" t="n">
-        <v>20.6619599050663</v>
+        <v>20.66195990506651</v>
       </c>
       <c r="F80" t="n">
-        <v>1.383708317324046</v>
+        <v>1.383708317324045</v>
       </c>
       <c r="G80" t="n">
-        <v>0.5309158474560929</v>
+        <v>0.5309158474563628</v>
       </c>
       <c r="H80" t="n">
-        <v>133.0536431093598</v>
+        <v>133.0536431093605</v>
       </c>
       <c r="I80" t="n">
         <v>1</v>
@@ -3054,16 +3042,16 @@
         <v>482.2</v>
       </c>
       <c r="E81" t="n">
-        <v>23.16185001138283</v>
+        <v>23.1618500113829</v>
       </c>
       <c r="F81" t="n">
-        <v>1.383708317324046</v>
+        <v>1.383708317324045</v>
       </c>
       <c r="G81" t="n">
-        <v>0.5309158474560929</v>
+        <v>0.5309158474563628</v>
       </c>
       <c r="H81" t="n">
-        <v>103.7508135432297</v>
+        <v>103.7508135432305</v>
       </c>
       <c r="I81" t="n">
         <v>1</v>
@@ -3087,16 +3075,16 @@
         <v>482.2</v>
       </c>
       <c r="E82" t="n">
-        <v>22.268601638396</v>
+        <v>22.26860163839583</v>
       </c>
       <c r="F82" t="n">
-        <v>1.383708317324046</v>
+        <v>1.383708317324045</v>
       </c>
       <c r="G82" t="n">
-        <v>0.5309158474560929</v>
+        <v>0.5309158474563628</v>
       </c>
       <c r="H82" t="n">
-        <v>57.103983288476</v>
+        <v>57.10398328847668</v>
       </c>
       <c r="I82" t="n">
         <v>1</v>
@@ -3120,16 +3108,16 @@
         <v>482.2</v>
       </c>
       <c r="E83" t="n">
-        <v>33.92010778816255</v>
+        <v>33.92010778816237</v>
       </c>
       <c r="F83" t="n">
-        <v>1.383708317324046</v>
+        <v>1.383708317324045</v>
       </c>
       <c r="G83" t="n">
-        <v>0.5309158474560929</v>
+        <v>0.5309158474563628</v>
       </c>
       <c r="H83" t="n">
-        <v>55.33201861621063</v>
+        <v>55.33201861621103</v>
       </c>
       <c r="I83" t="n">
         <v>1</v>
@@ -3153,16 +3141,16 @@
         <v>482.2</v>
       </c>
       <c r="E84" t="n">
-        <v>28.56892184097429</v>
+        <v>28.56892184097399</v>
       </c>
       <c r="F84" t="n">
-        <v>1.383708317324046</v>
+        <v>1.383708317324045</v>
       </c>
       <c r="G84" t="n">
-        <v>0.5309158474560929</v>
+        <v>0.5309158474563628</v>
       </c>
       <c r="H84" t="n">
-        <v>15.00793170474134</v>
+        <v>15.00793170474151</v>
       </c>
       <c r="I84" t="n">
         <v>1</v>
@@ -3186,16 +3174,16 @@
         <v>482.2</v>
       </c>
       <c r="E85" t="n">
-        <v>18.4406866096638</v>
+        <v>18.44068660966396</v>
       </c>
       <c r="F85" t="n">
-        <v>1.383708317324046</v>
+        <v>1.383708317324045</v>
       </c>
       <c r="G85" t="n">
-        <v>0.5309158474560929</v>
+        <v>0.5309158474563628</v>
       </c>
       <c r="H85" t="n">
-        <v>238.9713284804441</v>
+        <v>238.9713284804433</v>
       </c>
       <c r="I85" t="n">
         <v>1</v>
@@ -3219,16 +3207,16 @@
         <v>482.2</v>
       </c>
       <c r="E86" t="n">
-        <v>22.52022317139449</v>
+        <v>22.5202231713943</v>
       </c>
       <c r="F86" t="n">
-        <v>1.383708317324046</v>
+        <v>1.383708317324045</v>
       </c>
       <c r="G86" t="n">
-        <v>0.5309158474560929</v>
+        <v>0.5309158474563628</v>
       </c>
       <c r="H86" t="n">
-        <v>309.4005358536373</v>
+        <v>309.4005358536368</v>
       </c>
       <c r="I86" t="n">
         <v>1</v>
@@ -3252,16 +3240,16 @@
         <v>482.2</v>
       </c>
       <c r="E87" t="n">
-        <v>24.03688945329548</v>
+        <v>24.03688945329518</v>
       </c>
       <c r="F87" t="n">
-        <v>1.383708317324046</v>
+        <v>1.383708317324045</v>
       </c>
       <c r="G87" t="n">
-        <v>0.5309158474560929</v>
+        <v>0.5309158474563628</v>
       </c>
       <c r="H87" t="n">
-        <v>343.0640669198602</v>
+        <v>343.06406691986</v>
       </c>
       <c r="I87" t="n">
         <v>1</v>
@@ -3285,16 +3273,16 @@
         <v>482.2</v>
       </c>
       <c r="E88" t="n">
-        <v>36.89527840199128</v>
+        <v>36.89527840199102</v>
       </c>
       <c r="F88" t="n">
-        <v>1.383708317324046</v>
+        <v>1.383708317324045</v>
       </c>
       <c r="G88" t="n">
-        <v>0.5309158474560929</v>
+        <v>0.5309158474563628</v>
       </c>
       <c r="H88" t="n">
-        <v>327.7240273546831</v>
+        <v>327.7240273546828</v>
       </c>
       <c r="I88" t="n">
         <v>1</v>
@@ -3318,13 +3306,13 @@
         <v>482.3</v>
       </c>
       <c r="E89" t="n">
-        <v>13.33444379751264</v>
+        <v>13.33444379751251</v>
       </c>
       <c r="F89" t="n">
-        <v>1.54626222800448</v>
+        <v>1.546262228004478</v>
       </c>
       <c r="G89" t="n">
-        <v>0.5374693795255316</v>
+        <v>0.5374693795257891</v>
       </c>
       <c r="H89" t="inlineStr"/>
       <c r="I89" t="n">
@@ -3349,13 +3337,13 @@
         <v>482.3</v>
       </c>
       <c r="E90" t="n">
-        <v>29.77524198003879</v>
+        <v>29.77524198003848</v>
       </c>
       <c r="F90" t="n">
-        <v>1.54626222800448</v>
+        <v>1.546262228004478</v>
       </c>
       <c r="G90" t="n">
-        <v>0.5374693795255316</v>
+        <v>0.5374693795257891</v>
       </c>
       <c r="H90" t="inlineStr"/>
       <c r="I90" t="n">
@@ -3380,13 +3368,13 @@
         <v>482.6</v>
       </c>
       <c r="E91" t="n">
-        <v>10.55954111022697</v>
+        <v>10.55954111022715</v>
       </c>
       <c r="F91" t="n">
-        <v>1.931303128554924</v>
+        <v>1.931303128554921</v>
       </c>
       <c r="G91" t="n">
-        <v>0.564073027878179</v>
+        <v>0.564073027878374</v>
       </c>
       <c r="H91" t="inlineStr"/>
       <c r="I91" t="n">
@@ -3411,13 +3399,13 @@
         <v>482.6</v>
       </c>
       <c r="E92" t="n">
-        <v>13.35330283495814</v>
+        <v>13.35330283495799</v>
       </c>
       <c r="F92" t="n">
-        <v>1.931303128554924</v>
+        <v>1.931303128554921</v>
       </c>
       <c r="G92" t="n">
-        <v>0.564073027878179</v>
+        <v>0.564073027878374</v>
       </c>
       <c r="H92" t="inlineStr"/>
       <c r="I92" t="n">
@@ -3442,13 +3430,13 @@
         <v>482.6</v>
       </c>
       <c r="E93" t="n">
-        <v>14.62993796661925</v>
+        <v>14.62993796661895</v>
       </c>
       <c r="F93" t="n">
-        <v>1.931303128554924</v>
+        <v>1.931303128554921</v>
       </c>
       <c r="G93" t="n">
-        <v>0.564073027878179</v>
+        <v>0.564073027878374</v>
       </c>
       <c r="H93" t="inlineStr"/>
       <c r="I93" t="n">
@@ -3473,13 +3461,13 @@
         <v>482.6</v>
       </c>
       <c r="E94" t="n">
-        <v>24.1414661362187</v>
+        <v>24.14146613621842</v>
       </c>
       <c r="F94" t="n">
-        <v>1.931303128554924</v>
+        <v>1.931303128554921</v>
       </c>
       <c r="G94" t="n">
-        <v>0.564073027878179</v>
+        <v>0.564073027878374</v>
       </c>
       <c r="H94" t="inlineStr"/>
       <c r="I94" t="n">
@@ -3504,16 +3492,16 @@
         <v>488.9</v>
       </c>
       <c r="E95" t="n">
-        <v>14.78983151306694</v>
+        <v>14.78983151306692</v>
       </c>
       <c r="F95" t="n">
-        <v>1.29036660785675</v>
+        <v>1.290366607856749</v>
       </c>
       <c r="G95" t="n">
-        <v>1.268558534998172</v>
+        <v>1.268558534998151</v>
       </c>
       <c r="H95" t="n">
-        <v>70.92942721815609</v>
+        <v>70.92942721815615</v>
       </c>
       <c r="I95" t="n">
         <v>1</v>
@@ -3537,16 +3525,16 @@
         <v>488.9</v>
       </c>
       <c r="E96" t="n">
-        <v>25.24779522880866</v>
+        <v>25.24779522880863</v>
       </c>
       <c r="F96" t="n">
-        <v>1.29036660785675</v>
+        <v>1.290366607856749</v>
       </c>
       <c r="G96" t="n">
-        <v>1.268558534998172</v>
+        <v>1.268558534998151</v>
       </c>
       <c r="H96" t="n">
-        <v>57.85799481306179</v>
+        <v>57.85799481306174</v>
       </c>
       <c r="I96" t="n">
         <v>1</v>
@@ -3570,16 +3558,16 @@
         <v>488.9</v>
       </c>
       <c r="E97" t="n">
-        <v>22.85592830373207</v>
+        <v>22.85592830373205</v>
       </c>
       <c r="F97" t="n">
-        <v>1.29036660785675</v>
+        <v>1.290366607856749</v>
       </c>
       <c r="G97" t="n">
-        <v>1.268558534998172</v>
+        <v>1.268558534998151</v>
       </c>
       <c r="H97" t="n">
-        <v>18.0401974717056</v>
+        <v>18.04019747170554</v>
       </c>
       <c r="I97" t="n">
         <v>1</v>
@@ -3603,13 +3591,13 @@
         <v>488.9</v>
       </c>
       <c r="E98" t="n">
-        <v>35.66504017085249</v>
+        <v>35.66504017085246</v>
       </c>
       <c r="F98" t="n">
-        <v>1.29036660785675</v>
+        <v>1.290366607856749</v>
       </c>
       <c r="G98" t="n">
-        <v>1.268558534998172</v>
+        <v>1.268558534998151</v>
       </c>
       <c r="H98" t="n">
         <v>29.52919151888773</v>
@@ -3636,16 +3624,16 @@
         <v>488.9</v>
       </c>
       <c r="E99" t="n">
-        <v>19.37314381993712</v>
+        <v>19.37314381993713</v>
       </c>
       <c r="F99" t="n">
-        <v>1.29036660785675</v>
+        <v>1.290366607856749</v>
       </c>
       <c r="G99" t="n">
-        <v>1.268558534998172</v>
+        <v>1.268558534998151</v>
       </c>
       <c r="H99" t="n">
-        <v>299.135457028298</v>
+        <v>299.1354570282979</v>
       </c>
       <c r="I99" t="n">
         <v>1</v>
@@ -3672,10 +3660,10 @@
         <v>21.7641531384655</v>
       </c>
       <c r="F100" t="n">
-        <v>1.29036660785675</v>
+        <v>1.290366607856749</v>
       </c>
       <c r="G100" t="n">
-        <v>1.268558534998172</v>
+        <v>1.268558534998151</v>
       </c>
       <c r="H100" t="n">
         <v>342.2865722605958</v>
@@ -3705,10 +3693,10 @@
         <v>38.04532963953353</v>
       </c>
       <c r="F101" t="n">
-        <v>1.29036660785675</v>
+        <v>1.290366607856749</v>
       </c>
       <c r="G101" t="n">
-        <v>1.268558534998172</v>
+        <v>1.268558534998151</v>
       </c>
       <c r="H101" t="n">
         <v>330.8670901537202</v>
@@ -3735,13 +3723,13 @@
         <v>489.1</v>
       </c>
       <c r="E102" t="n">
-        <v>14.69965605746296</v>
+        <v>14.69965605746293</v>
       </c>
       <c r="F102" t="n">
-        <v>1.471166673582187</v>
+        <v>1.471166673582186</v>
       </c>
       <c r="G102" t="n">
-        <v>1.348976596362693</v>
+        <v>1.348976596362673</v>
       </c>
       <c r="H102" t="n">
         <v>69.336817380453</v>
@@ -3768,16 +3756,16 @@
         <v>489.1</v>
       </c>
       <c r="E103" t="n">
-        <v>25.2503107625063</v>
+        <v>25.25031076250628</v>
       </c>
       <c r="F103" t="n">
-        <v>1.471166673582187</v>
+        <v>1.471166673582186</v>
       </c>
       <c r="G103" t="n">
-        <v>1.348976596362693</v>
+        <v>1.348976596362673</v>
       </c>
       <c r="H103" t="n">
-        <v>56.9057494120093</v>
+        <v>56.90574941200924</v>
       </c>
       <c r="I103" t="n">
         <v>1</v>
@@ -3801,16 +3789,16 @@
         <v>489.1</v>
       </c>
       <c r="E104" t="n">
-        <v>23.12615022428574</v>
+        <v>23.12615022428573</v>
       </c>
       <c r="F104" t="n">
-        <v>1.471166673582187</v>
+        <v>1.471166673582186</v>
       </c>
       <c r="G104" t="n">
-        <v>1.348976596362693</v>
+        <v>1.348976596362673</v>
       </c>
       <c r="H104" t="n">
-        <v>17.24008128333855</v>
+        <v>17.2400812833385</v>
       </c>
       <c r="I104" t="n">
         <v>1</v>
@@ -3834,13 +3822,13 @@
         <v>489.1</v>
       </c>
       <c r="E105" t="n">
-        <v>35.86522211269629</v>
+        <v>35.86522211269627</v>
       </c>
       <c r="F105" t="n">
-        <v>1.471166673582187</v>
+        <v>1.471166673582186</v>
       </c>
       <c r="G105" t="n">
-        <v>1.348976596362693</v>
+        <v>1.348976596362673</v>
       </c>
       <c r="H105" t="n">
         <v>28.93834845409856</v>
@@ -3867,13 +3855,13 @@
         <v>489.1</v>
       </c>
       <c r="E106" t="n">
-        <v>19.74263510347247</v>
+        <v>19.74263510347248</v>
       </c>
       <c r="F106" t="n">
-        <v>1.471166673582187</v>
+        <v>1.471166673582186</v>
       </c>
       <c r="G106" t="n">
-        <v>1.348976596362693</v>
+        <v>1.348976596362673</v>
       </c>
       <c r="H106" t="n">
         <v>299.7182499827078</v>
@@ -3900,13 +3888,13 @@
         <v>489.1</v>
       </c>
       <c r="E107" t="n">
-        <v>22.17056254321642</v>
+        <v>22.17056254321643</v>
       </c>
       <c r="F107" t="n">
-        <v>1.471166673582187</v>
+        <v>1.471166673582186</v>
       </c>
       <c r="G107" t="n">
-        <v>1.348976596362693</v>
+        <v>1.348976596362673</v>
       </c>
       <c r="H107" t="n">
         <v>342.0139178471612</v>
@@ -3936,13 +3924,13 @@
         <v>38.46434315719667</v>
       </c>
       <c r="F108" t="n">
-        <v>1.471166673582187</v>
+        <v>1.471166673582186</v>
       </c>
       <c r="G108" t="n">
-        <v>1.348976596362693</v>
+        <v>1.348976596362673</v>
       </c>
       <c r="H108" t="n">
-        <v>330.8328313639825</v>
+        <v>330.8328313639824</v>
       </c>
       <c r="I108" t="n">
         <v>1</v>
@@ -3966,16 +3954,16 @@
         <v>493.1</v>
       </c>
       <c r="E109" t="n">
-        <v>19.07499382263313</v>
+        <v>19.07499382263304</v>
       </c>
       <c r="F109" t="n">
-        <v>0.3855700571420326</v>
+        <v>0.3855700571420329</v>
       </c>
       <c r="G109" t="n">
-        <v>0.4931096392336043</v>
+        <v>0.4931096392337408</v>
       </c>
       <c r="H109" t="n">
-        <v>37.46615836196793</v>
+        <v>37.46615836196747</v>
       </c>
       <c r="I109" t="n">
         <v>1</v>
@@ -3999,16 +3987,16 @@
         <v>493.1</v>
       </c>
       <c r="E110" t="n">
-        <v>23.59469297401813</v>
+        <v>23.59469297401816</v>
       </c>
       <c r="F110" t="n">
-        <v>0.3855700571420326</v>
+        <v>0.3855700571420329</v>
       </c>
       <c r="G110" t="n">
-        <v>0.4931096392336043</v>
+        <v>0.4931096392337408</v>
       </c>
       <c r="H110" t="n">
-        <v>353.4368789435915</v>
+        <v>353.4368789435911</v>
       </c>
       <c r="I110" t="n">
         <v>1</v>
@@ -4032,16 +4020,16 @@
         <v>493.1</v>
       </c>
       <c r="E111" t="n">
-        <v>33.65711733847974</v>
+        <v>33.65711733847971</v>
       </c>
       <c r="F111" t="n">
-        <v>0.3855700571420326</v>
+        <v>0.3855700571420329</v>
       </c>
       <c r="G111" t="n">
-        <v>0.4931096392336043</v>
+        <v>0.4931096392337408</v>
       </c>
       <c r="H111" t="n">
-        <v>13.40562395961297</v>
+        <v>13.40562395961268</v>
       </c>
       <c r="I111" t="n">
         <v>1</v>
@@ -4065,16 +4053,16 @@
         <v>493.1</v>
       </c>
       <c r="E112" t="n">
-        <v>28.9278631595823</v>
+        <v>28.92786315958246</v>
       </c>
       <c r="F112" t="n">
-        <v>0.3855700571420326</v>
+        <v>0.3855700571420329</v>
       </c>
       <c r="G112" t="n">
-        <v>0.4931096392336043</v>
+        <v>0.4931096392337408</v>
       </c>
       <c r="H112" t="n">
-        <v>292.6498326275607</v>
+        <v>292.6498326275606</v>
       </c>
       <c r="I112" t="n">
         <v>1</v>
@@ -4098,16 +4086,16 @@
         <v>493.1</v>
       </c>
       <c r="E113" t="n">
-        <v>27.7923059560073</v>
+        <v>27.79230595600742</v>
       </c>
       <c r="F113" t="n">
-        <v>0.3855700571420326</v>
+        <v>0.3855700571420329</v>
       </c>
       <c r="G113" t="n">
-        <v>0.4931096392336043</v>
+        <v>0.4931096392337408</v>
       </c>
       <c r="H113" t="n">
-        <v>323.8446274128528</v>
+        <v>323.8446274128526</v>
       </c>
       <c r="I113" t="n">
         <v>1</v>
@@ -4131,16 +4119,16 @@
         <v>493.6</v>
       </c>
       <c r="E114" t="n">
-        <v>19.15443455205088</v>
+        <v>19.15443455205079</v>
       </c>
       <c r="F114" t="n">
-        <v>0.3075480024199045</v>
+        <v>0.3075480024199032</v>
       </c>
       <c r="G114" t="n">
-        <v>0.6050145883315989</v>
+        <v>0.6050145883316765</v>
       </c>
       <c r="H114" t="n">
-        <v>35.3087823412576</v>
+        <v>35.30878234125709</v>
       </c>
       <c r="I114" t="n">
         <v>1</v>
@@ -4164,16 +4152,16 @@
         <v>493.6</v>
       </c>
       <c r="E115" t="n">
-        <v>24.14782797060088</v>
+        <v>24.14782797060092</v>
       </c>
       <c r="F115" t="n">
-        <v>0.3075480024199045</v>
+        <v>0.3075480024199032</v>
       </c>
       <c r="G115" t="n">
-        <v>0.6050145883315989</v>
+        <v>0.6050145883316765</v>
       </c>
       <c r="H115" t="n">
-        <v>352.3153410881819</v>
+        <v>352.3153410881815</v>
       </c>
       <c r="I115" t="n">
         <v>1</v>
@@ -4197,16 +4185,16 @@
         <v>493.6</v>
       </c>
       <c r="E116" t="n">
-        <v>34.01709827711349</v>
+        <v>34.01709827711348</v>
       </c>
       <c r="F116" t="n">
-        <v>0.3075480024199045</v>
+        <v>0.3075480024199032</v>
       </c>
       <c r="G116" t="n">
-        <v>0.6050145883315989</v>
+        <v>0.6050145883316765</v>
       </c>
       <c r="H116" t="n">
-        <v>12.34181899237228</v>
+        <v>12.341818992372</v>
       </c>
       <c r="I116" t="n">
         <v>1</v>
@@ -4230,16 +4218,16 @@
         <v>493.6</v>
       </c>
       <c r="E117" t="n">
-        <v>29.60914226697632</v>
+        <v>29.60914226697651</v>
       </c>
       <c r="F117" t="n">
-        <v>0.3075480024199045</v>
+        <v>0.3075480024199032</v>
       </c>
       <c r="G117" t="n">
-        <v>0.6050145883315989</v>
+        <v>0.6050145883316765</v>
       </c>
       <c r="H117" t="n">
-        <v>293.1298592065637</v>
+        <v>293.1298592065635</v>
       </c>
       <c r="I117" t="n">
         <v>1</v>
@@ -4263,16 +4251,16 @@
         <v>493.6</v>
       </c>
       <c r="E118" t="n">
-        <v>28.50301986722604</v>
+        <v>28.50301986722616</v>
       </c>
       <c r="F118" t="n">
-        <v>0.3075480024199045</v>
+        <v>0.3075480024199032</v>
       </c>
       <c r="G118" t="n">
-        <v>0.6050145883315989</v>
+        <v>0.6050145883316765</v>
       </c>
       <c r="H118" t="n">
-        <v>323.562935344753</v>
+        <v>323.5629353447528</v>
       </c>
       <c r="I118" t="n">
         <v>1</v>
@@ -4296,13 +4284,13 @@
         <v>494</v>
       </c>
       <c r="E119" t="n">
-        <v>24.42413912086602</v>
+        <v>24.42413912086619</v>
       </c>
       <c r="F119" t="n">
-        <v>0.5428364720993621</v>
+        <v>0.5428364720993618</v>
       </c>
       <c r="G119" t="n">
-        <v>0.3515540270933211</v>
+        <v>0.3515540270933099</v>
       </c>
       <c r="H119" t="inlineStr"/>
       <c r="I119" t="n">
@@ -4327,13 +4315,13 @@
         <v>494</v>
       </c>
       <c r="E120" t="n">
-        <v>24.94242666808485</v>
+        <v>24.94242666808497</v>
       </c>
       <c r="F120" t="n">
-        <v>0.5428364720993621</v>
+        <v>0.5428364720993618</v>
       </c>
       <c r="G120" t="n">
-        <v>0.3515540270933211</v>
+        <v>0.3515540270933099</v>
       </c>
       <c r="H120" t="inlineStr"/>
       <c r="I120" t="n">
@@ -4358,16 +4346,16 @@
         <v>494.1</v>
       </c>
       <c r="E121" t="n">
-        <v>18.72619773433351</v>
+        <v>18.72619773433341</v>
       </c>
       <c r="F121" t="n">
-        <v>0.6401969386332381</v>
+        <v>0.6401969386332378</v>
       </c>
       <c r="G121" t="n">
-        <v>0.3327167018905053</v>
+        <v>0.33271670189047</v>
       </c>
       <c r="H121" t="n">
-        <v>35.02490904267245</v>
+        <v>35.02490904267194</v>
       </c>
       <c r="I121" t="n">
         <v>1</v>
@@ -4391,16 +4379,16 @@
         <v>494.1</v>
       </c>
       <c r="E122" t="n">
-        <v>23.90041320776886</v>
+        <v>23.90041320776891</v>
       </c>
       <c r="F122" t="n">
-        <v>0.6401969386332381</v>
+        <v>0.6401969386332378</v>
       </c>
       <c r="G122" t="n">
-        <v>0.3327167018905053</v>
+        <v>0.33271670189047</v>
       </c>
       <c r="H122" t="n">
-        <v>351.4521967262634</v>
+        <v>351.452196726263</v>
       </c>
       <c r="I122" t="n">
         <v>1</v>
@@ -4424,16 +4412,16 @@
         <v>494.1</v>
       </c>
       <c r="E123" t="n">
-        <v>33.65974649821377</v>
+        <v>33.65974649821376</v>
       </c>
       <c r="F123" t="n">
-        <v>0.6401969386332381</v>
+        <v>0.6401969386332378</v>
       </c>
       <c r="G123" t="n">
-        <v>0.3327167018905053</v>
+        <v>0.33271670189047</v>
       </c>
       <c r="H123" t="n">
-        <v>11.91181721216878</v>
+        <v>11.91181721216844</v>
       </c>
       <c r="I123" t="n">
         <v>1</v>
@@ -4457,16 +4445,16 @@
         <v>494.1</v>
       </c>
       <c r="E124" t="n">
-        <v>29.79289998687277</v>
+        <v>29.79289998687295</v>
       </c>
       <c r="F124" t="n">
-        <v>0.6401969386332381</v>
+        <v>0.6401969386332378</v>
       </c>
       <c r="G124" t="n">
-        <v>0.3327167018905053</v>
+        <v>0.33271670189047</v>
       </c>
       <c r="H124" t="n">
-        <v>292.3620239412362</v>
+        <v>292.3620239412361</v>
       </c>
       <c r="I124" t="n">
         <v>1</v>
@@ -4490,16 +4478,16 @@
         <v>494.1</v>
       </c>
       <c r="E125" t="n">
-        <v>28.46025951461028</v>
+        <v>28.46025951461041</v>
       </c>
       <c r="F125" t="n">
-        <v>0.6401969386332381</v>
+        <v>0.6401969386332378</v>
       </c>
       <c r="G125" t="n">
-        <v>0.3327167018905053</v>
+        <v>0.33271670189047</v>
       </c>
       <c r="H125" t="n">
-        <v>322.6852204259091</v>
+        <v>322.6852204259088</v>
       </c>
       <c r="I125" t="n">
         <v>1</v>
@@ -4523,13 +4511,13 @@
         <v>494.5</v>
       </c>
       <c r="E126" t="n">
-        <v>24.53715780365136</v>
+        <v>24.53715780365153</v>
       </c>
       <c r="F126" t="n">
-        <v>0.7615344654707419</v>
+        <v>0.7615344654707416</v>
       </c>
       <c r="G126" t="n">
-        <v>0.3533133288922095</v>
+        <v>0.3533133288920607</v>
       </c>
       <c r="H126" t="inlineStr"/>
       <c r="I126" t="n">
@@ -4554,13 +4542,13 @@
         <v>494.5</v>
       </c>
       <c r="E127" t="n">
-        <v>24.90848137171105</v>
+        <v>24.90848137171118</v>
       </c>
       <c r="F127" t="n">
-        <v>0.7615344654707419</v>
+        <v>0.7615344654707416</v>
       </c>
       <c r="G127" t="n">
-        <v>0.3533133288922095</v>
+        <v>0.3533133288920607</v>
       </c>
       <c r="H127" t="inlineStr"/>
       <c r="I127" t="n">
@@ -4585,16 +4573,16 @@
         <v>494.6</v>
       </c>
       <c r="E128" t="n">
-        <v>18.29895519695118</v>
+        <v>18.29895519695108</v>
       </c>
       <c r="F128" t="n">
-        <v>0.7802312732734344</v>
+        <v>0.7802312732734343</v>
       </c>
       <c r="G128" t="n">
-        <v>0.4997692472107983</v>
+        <v>0.4997692472106314</v>
       </c>
       <c r="H128" t="n">
-        <v>35.34125195653371</v>
+        <v>35.34125195653326</v>
       </c>
       <c r="I128" t="n">
         <v>1</v>
@@ -4618,16 +4606,16 @@
         <v>494.6</v>
       </c>
       <c r="E129" t="n">
-        <v>23.52207768816949</v>
+        <v>23.52207768816953</v>
       </c>
       <c r="F129" t="n">
-        <v>0.7802312732734344</v>
+        <v>0.7802312732734343</v>
       </c>
       <c r="G129" t="n">
-        <v>0.4997692472107983</v>
+        <v>0.4997692472106314</v>
       </c>
       <c r="H129" t="n">
-        <v>350.912696638499</v>
+        <v>350.9126966384986</v>
       </c>
       <c r="I129" t="n">
         <v>1</v>
@@ -4651,16 +4639,16 @@
         <v>494.6</v>
       </c>
       <c r="E130" t="n">
-        <v>33.22696594182381</v>
+        <v>33.22696594182378</v>
       </c>
       <c r="F130" t="n">
-        <v>0.7802312732734344</v>
+        <v>0.7802312732734343</v>
       </c>
       <c r="G130" t="n">
-        <v>0.4997692472107983</v>
+        <v>0.4997692472106314</v>
       </c>
       <c r="H130" t="n">
-        <v>11.78266151127076</v>
+        <v>11.78266151127042</v>
       </c>
       <c r="I130" t="n">
         <v>1</v>
@@ -4684,16 +4672,16 @@
         <v>494.6</v>
       </c>
       <c r="E131" t="n">
-        <v>29.79128274077858</v>
+        <v>29.79128274077876</v>
       </c>
       <c r="F131" t="n">
-        <v>0.7802312732734344</v>
+        <v>0.7802312732734343</v>
       </c>
       <c r="G131" t="n">
-        <v>0.4997692472107983</v>
+        <v>0.4997692472106314</v>
       </c>
       <c r="H131" t="n">
-        <v>291.5171709854189</v>
+        <v>291.5171709854188</v>
       </c>
       <c r="I131" t="n">
         <v>1</v>
@@ -4717,16 +4705,16 @@
         <v>494.6</v>
       </c>
       <c r="E132" t="n">
-        <v>28.23680347364129</v>
+        <v>28.23680347364141</v>
       </c>
       <c r="F132" t="n">
-        <v>0.7802312732734344</v>
+        <v>0.7802312732734343</v>
       </c>
       <c r="G132" t="n">
-        <v>0.4997692472107983</v>
+        <v>0.4997692472106314</v>
       </c>
       <c r="H132" t="n">
-        <v>321.9207832436755</v>
+        <v>321.9207832436752</v>
       </c>
       <c r="I132" t="n">
         <v>1</v>
@@ -4750,13 +4738,13 @@
         <v>494.9</v>
       </c>
       <c r="E133" t="n">
-        <v>24.25602915976911</v>
+        <v>24.25602915976928</v>
       </c>
       <c r="F133" t="n">
-        <v>1.219979737545301</v>
+        <v>1.2199797375453</v>
       </c>
       <c r="G133" t="n">
-        <v>0.8092765675138153</v>
+        <v>0.8092765675136508</v>
       </c>
       <c r="H133" t="inlineStr"/>
       <c r="I133" t="n">
@@ -4781,13 +4769,13 @@
         <v>495</v>
       </c>
       <c r="E134" t="n">
-        <v>24.30642746544959</v>
+        <v>24.30642746544975</v>
       </c>
       <c r="F134" t="n">
         <v>1.350514415016634</v>
       </c>
       <c r="G134" t="n">
-        <v>0.8423792496590908</v>
+        <v>0.8423792496589299</v>
       </c>
       <c r="H134" t="inlineStr"/>
       <c r="I134" t="n">
@@ -4812,13 +4800,13 @@
         <v>495</v>
       </c>
       <c r="E135" t="n">
-        <v>24.49466566246795</v>
+        <v>24.49466566246807</v>
       </c>
       <c r="F135" t="n">
         <v>1.350514415016634</v>
       </c>
       <c r="G135" t="n">
-        <v>0.8423792496590908</v>
+        <v>0.8423792496589299</v>
       </c>
       <c r="H135" t="inlineStr"/>
       <c r="I135" t="n">
@@ -4843,16 +4831,16 @@
         <v>495.1</v>
       </c>
       <c r="E136" t="n">
-        <v>17.62147171996645</v>
+        <v>17.62147171996634</v>
       </c>
       <c r="F136" t="n">
-        <v>1.475419714988617</v>
+        <v>1.475419714988615</v>
       </c>
       <c r="G136" t="n">
-        <v>0.8210450087327569</v>
+        <v>0.821045008732599</v>
       </c>
       <c r="H136" t="n">
-        <v>35.31709983016162</v>
+        <v>35.31709983016111</v>
       </c>
       <c r="I136" t="n">
         <v>1</v>
@@ -4876,16 +4864,16 @@
         <v>495.1</v>
       </c>
       <c r="E137" t="n">
-        <v>23.04845870128828</v>
+        <v>23.04845870128831</v>
       </c>
       <c r="F137" t="n">
-        <v>1.475419714988617</v>
+        <v>1.475419714988615</v>
       </c>
       <c r="G137" t="n">
-        <v>0.8210450087327569</v>
+        <v>0.821045008732599</v>
       </c>
       <c r="H137" t="n">
-        <v>349.7204874075622</v>
+        <v>349.7204874075617</v>
       </c>
       <c r="I137" t="n">
         <v>1</v>
@@ -4909,16 +4897,16 @@
         <v>495.1</v>
       </c>
       <c r="E138" t="n">
-        <v>32.61009843155624</v>
+        <v>32.6100984315562</v>
       </c>
       <c r="F138" t="n">
-        <v>1.475419714988617</v>
+        <v>1.475419714988615</v>
       </c>
       <c r="G138" t="n">
-        <v>0.8210450087327569</v>
+        <v>0.821045008732599</v>
       </c>
       <c r="H138" t="n">
-        <v>11.29493022428414</v>
+        <v>11.2949302242838</v>
       </c>
       <c r="I138" t="n">
         <v>1</v>
@@ -4942,16 +4930,16 @@
         <v>495.1</v>
       </c>
       <c r="E139" t="n">
-        <v>29.96755776556725</v>
+        <v>29.96755776556743</v>
       </c>
       <c r="F139" t="n">
-        <v>1.475419714988617</v>
+        <v>1.475419714988615</v>
       </c>
       <c r="G139" t="n">
-        <v>0.8210450087327569</v>
+        <v>0.821045008732599</v>
       </c>
       <c r="H139" t="n">
-        <v>290.2626820998633</v>
+        <v>290.2626820998632</v>
       </c>
       <c r="I139" t="n">
         <v>1</v>
@@ -4975,16 +4963,16 @@
         <v>495.1</v>
       </c>
       <c r="E140" t="n">
-        <v>28.0581684273994</v>
+        <v>28.05816842739953</v>
       </c>
       <c r="F140" t="n">
-        <v>1.475419714988617</v>
+        <v>1.475419714988615</v>
       </c>
       <c r="G140" t="n">
-        <v>0.8210450087327569</v>
+        <v>0.821045008732599</v>
       </c>
       <c r="H140" t="n">
-        <v>320.5904043470812</v>
+        <v>320.5904043470809</v>
       </c>
       <c r="I140" t="n">
         <v>1</v>
@@ -5008,13 +4996,13 @@
         <v>495.3</v>
       </c>
       <c r="E141" t="n">
-        <v>24.82773173264021</v>
+        <v>24.82773173264038</v>
       </c>
       <c r="F141" t="n">
-        <v>1.809741037192209</v>
+        <v>1.809741037192208</v>
       </c>
       <c r="G141" t="n">
-        <v>0.7068384646860416</v>
+        <v>0.7068384646858787</v>
       </c>
       <c r="H141" t="inlineStr"/>
       <c r="I141" t="n">
@@ -5039,13 +5027,13 @@
         <v>495.3</v>
       </c>
       <c r="E142" t="n">
-        <v>24.85612021312745</v>
+        <v>24.85612021312759</v>
       </c>
       <c r="F142" t="n">
-        <v>1.809741037192209</v>
+        <v>1.809741037192208</v>
       </c>
       <c r="G142" t="n">
-        <v>0.7068384646860416</v>
+        <v>0.7068384646858787</v>
       </c>
       <c r="H142" t="inlineStr"/>
       <c r="I142" t="n">
@@ -5070,16 +5058,16 @@
         <v>508.3</v>
       </c>
       <c r="E143" t="n">
-        <v>32.19087659855808</v>
+        <v>32.1908765985588</v>
       </c>
       <c r="F143" t="n">
-        <v>0.6951059843008373</v>
+        <v>0.6951059843008366</v>
       </c>
       <c r="G143" t="n">
-        <v>0.3711854024758574</v>
+        <v>0.3711854024764962</v>
       </c>
       <c r="H143" t="n">
-        <v>279.3770924106739</v>
+        <v>279.3770924106737</v>
       </c>
       <c r="I143" t="n">
         <v>1</v>
@@ -5103,16 +5091,16 @@
         <v>508.3</v>
       </c>
       <c r="E144" t="n">
-        <v>28.020104644159</v>
+        <v>28.02010464415964</v>
       </c>
       <c r="F144" t="n">
-        <v>0.6951059843008373</v>
+        <v>0.6951059843008366</v>
       </c>
       <c r="G144" t="n">
-        <v>0.3711854024758574</v>
+        <v>0.3711854024764962</v>
       </c>
       <c r="H144" t="n">
-        <v>299.6108306819174</v>
+        <v>299.6108306819167</v>
       </c>
       <c r="I144" t="n">
         <v>1</v>
@@ -5136,13 +5124,13 @@
         <v>508.7</v>
       </c>
       <c r="E145" t="n">
-        <v>9.918058955415294</v>
+        <v>9.918058955414905</v>
       </c>
       <c r="F145" t="n">
-        <v>0.7632986234973324</v>
+        <v>0.7632986234973314</v>
       </c>
       <c r="G145" t="n">
-        <v>0.2360869225073451</v>
+        <v>0.2360869225076145</v>
       </c>
       <c r="H145" t="inlineStr"/>
       <c r="I145" t="n">
@@ -5167,13 +5155,13 @@
         <v>508.7</v>
       </c>
       <c r="E146" t="n">
-        <v>16.09187826862355</v>
+        <v>16.09187826862361</v>
       </c>
       <c r="F146" t="n">
-        <v>0.7632986234973324</v>
+        <v>0.7632986234973314</v>
       </c>
       <c r="G146" t="n">
-        <v>0.2360869225073451</v>
+        <v>0.2360869225076145</v>
       </c>
       <c r="H146" t="inlineStr"/>
       <c r="I146" t="n">
@@ -5198,13 +5186,13 @@
         <v>508.7</v>
       </c>
       <c r="E147" t="n">
-        <v>26.77180753151245</v>
+        <v>26.77180753151214</v>
       </c>
       <c r="F147" t="n">
-        <v>0.7632986234973324</v>
+        <v>0.7632986234973314</v>
       </c>
       <c r="G147" t="n">
-        <v>0.2360869225073451</v>
+        <v>0.2360869225076145</v>
       </c>
       <c r="H147" t="inlineStr"/>
       <c r="I147" t="n">
@@ -5229,16 +5217,16 @@
         <v>508.8</v>
       </c>
       <c r="E148" t="n">
-        <v>32.49537904551172</v>
+        <v>32.49537904551246</v>
       </c>
       <c r="F148" t="n">
-        <v>1.041968106976509</v>
+        <v>1.041968106976508</v>
       </c>
       <c r="G148" t="n">
-        <v>0.1995177761908223</v>
+        <v>0.1995177761912379</v>
       </c>
       <c r="H148" t="n">
-        <v>279.4269931078693</v>
+        <v>279.4269931078691</v>
       </c>
       <c r="I148" t="n">
         <v>1</v>
@@ -5262,16 +5250,16 @@
         <v>508.8</v>
       </c>
       <c r="E149" t="n">
-        <v>28.31570206347525</v>
+        <v>28.3157020634759</v>
       </c>
       <c r="F149" t="n">
-        <v>1.041968106976509</v>
+        <v>1.041968106976508</v>
       </c>
       <c r="G149" t="n">
-        <v>0.1995177761908223</v>
+        <v>0.1995177761912379</v>
       </c>
       <c r="H149" t="n">
-        <v>299.4514759138168</v>
+        <v>299.4514759138161</v>
       </c>
       <c r="I149" t="n">
         <v>1</v>
@@ -5295,13 +5283,13 @@
         <v>509.2</v>
       </c>
       <c r="E150" t="n">
-        <v>10.05294011404404</v>
+        <v>10.05294011404369</v>
       </c>
       <c r="F150" t="n">
-        <v>1.185672884682118</v>
+        <v>1.185672884682117</v>
       </c>
       <c r="G150" t="n">
-        <v>0.134777543903531</v>
+        <v>0.1347775439041639</v>
       </c>
       <c r="H150" t="inlineStr"/>
       <c r="I150" t="n">
@@ -5326,13 +5314,13 @@
         <v>509.2</v>
       </c>
       <c r="E151" t="n">
-        <v>16.60573691356583</v>
+        <v>16.60573691356593</v>
       </c>
       <c r="F151" t="n">
-        <v>1.185672884682118</v>
+        <v>1.185672884682117</v>
       </c>
       <c r="G151" t="n">
-        <v>0.134777543903531</v>
+        <v>0.1347775439041639</v>
       </c>
       <c r="H151" t="inlineStr"/>
       <c r="I151" t="n">
@@ -5357,13 +5345,13 @@
         <v>509.2</v>
       </c>
       <c r="E152" t="n">
-        <v>26.97124870095701</v>
+        <v>26.97124870095671</v>
       </c>
       <c r="F152" t="n">
-        <v>1.185672884682118</v>
+        <v>1.185672884682117</v>
       </c>
       <c r="G152" t="n">
-        <v>0.134777543903531</v>
+        <v>0.1347775439041639</v>
       </c>
       <c r="H152" t="inlineStr"/>
       <c r="I152" t="n">
@@ -5388,16 +5376,16 @@
         <v>509.3</v>
       </c>
       <c r="E153" t="n">
-        <v>32.99986572350814</v>
+        <v>32.99986572350888</v>
       </c>
       <c r="F153" t="n">
-        <v>1.10284844547316</v>
+        <v>1.102848445473159</v>
       </c>
       <c r="G153" t="n">
-        <v>0.1109048808462759</v>
+        <v>0.110904880846821</v>
       </c>
       <c r="H153" t="n">
-        <v>279.9932985228343</v>
+        <v>279.993298522834</v>
       </c>
       <c r="I153" t="n">
         <v>1</v>
@@ -5421,16 +5409,16 @@
         <v>509.3</v>
       </c>
       <c r="E154" t="n">
-        <v>28.90017295275549</v>
+        <v>28.90017295275615</v>
       </c>
       <c r="F154" t="n">
-        <v>1.10284844547316</v>
+        <v>1.102848445473159</v>
       </c>
       <c r="G154" t="n">
-        <v>0.1109048808462759</v>
+        <v>0.110904880846821</v>
       </c>
       <c r="H154" t="n">
-        <v>299.7176310038869</v>
+        <v>299.7176310038861</v>
       </c>
       <c r="I154" t="n">
         <v>1</v>
@@ -5454,13 +5442,13 @@
         <v>509.7</v>
       </c>
       <c r="E155" t="n">
-        <v>10.03407636903677</v>
+        <v>10.03407636903645</v>
       </c>
       <c r="F155" t="n">
-        <v>0.6932377746155652</v>
+        <v>0.6932377746155653</v>
       </c>
       <c r="G155" t="n">
-        <v>0.03676819793808372</v>
+        <v>0.03676819793870069</v>
       </c>
       <c r="H155" t="inlineStr"/>
       <c r="I155" t="n">
@@ -5485,13 +5473,13 @@
         <v>509.7</v>
       </c>
       <c r="E156" t="n">
-        <v>16.80370803106747</v>
+        <v>16.80370803106758</v>
       </c>
       <c r="F156" t="n">
-        <v>0.6932377746155652</v>
+        <v>0.6932377746155653</v>
       </c>
       <c r="G156" t="n">
-        <v>0.03676819793808372</v>
+        <v>0.03676819793870069</v>
       </c>
       <c r="H156" t="inlineStr"/>
       <c r="I156" t="n">
@@ -5516,13 +5504,13 @@
         <v>509.7</v>
       </c>
       <c r="E157" t="n">
-        <v>26.97530734079103</v>
+        <v>26.97530734079075</v>
       </c>
       <c r="F157" t="n">
-        <v>0.6932377746155652</v>
+        <v>0.6932377746155653</v>
       </c>
       <c r="G157" t="n">
-        <v>0.03676819793808372</v>
+        <v>0.03676819793870069</v>
       </c>
       <c r="H157" t="inlineStr"/>
       <c r="I157" t="n">
@@ -5547,16 +5535,16 @@
         <v>509.8</v>
       </c>
       <c r="E158" t="n">
-        <v>33.23924710940759</v>
+        <v>33.23924710940834</v>
       </c>
       <c r="F158" t="n">
-        <v>0.5982877841336045</v>
+        <v>0.5982877841336044</v>
       </c>
       <c r="G158" t="n">
-        <v>0.1344980702678082</v>
+        <v>0.1344980702672017</v>
       </c>
       <c r="H158" t="n">
-        <v>280.2389315442544</v>
+        <v>280.2389315442542</v>
       </c>
       <c r="I158" t="n">
         <v>1</v>
@@ -5580,16 +5568,16 @@
         <v>509.8</v>
       </c>
       <c r="E159" t="n">
-        <v>29.17336356608179</v>
+        <v>29.17336356608245</v>
       </c>
       <c r="F159" t="n">
-        <v>0.5982877841336045</v>
+        <v>0.5982877841336044</v>
       </c>
       <c r="G159" t="n">
-        <v>0.1344980702678082</v>
+        <v>0.1344980702672017</v>
       </c>
       <c r="H159" t="n">
-        <v>299.8226093374229</v>
+        <v>299.8226093374223</v>
       </c>
       <c r="I159" t="n">
         <v>1</v>
@@ -5613,16 +5601,16 @@
         <v>509.9</v>
       </c>
       <c r="E160" t="n">
-        <v>29.15074509928239</v>
+        <v>29.15074509928304</v>
       </c>
       <c r="F160" t="n">
         <v>0.6212614757832813</v>
       </c>
       <c r="G160" t="n">
-        <v>0.2980972624476169</v>
+        <v>0.2980972624470007</v>
       </c>
       <c r="H160" t="n">
-        <v>300.1003228290468</v>
+        <v>300.100322829046</v>
       </c>
       <c r="I160" t="n">
         <v>1</v>
@@ -5646,13 +5634,13 @@
         <v>510.2</v>
       </c>
       <c r="E161" t="n">
-        <v>10.19851857711685</v>
+        <v>10.19851857711656</v>
       </c>
       <c r="F161" t="n">
-        <v>0.6872818345299919</v>
+        <v>0.6872818345299915</v>
       </c>
       <c r="G161" t="n">
-        <v>0.2871565425382101</v>
+        <v>0.2871565425375567</v>
       </c>
       <c r="H161" t="inlineStr"/>
       <c r="I161" t="n">
@@ -5677,13 +5665,13 @@
         <v>510.2</v>
       </c>
       <c r="E162" t="n">
-        <v>17.06377583553678</v>
+        <v>17.06377583553691</v>
       </c>
       <c r="F162" t="n">
-        <v>0.6872818345299919</v>
+        <v>0.6872818345299915</v>
       </c>
       <c r="G162" t="n">
-        <v>0.2871565425382101</v>
+        <v>0.2871565425375567</v>
       </c>
       <c r="H162" t="inlineStr"/>
       <c r="I162" t="n">
@@ -5708,13 +5696,13 @@
         <v>510.2</v>
       </c>
       <c r="E163" t="n">
-        <v>27.14872732576319</v>
+        <v>27.14872732576292</v>
       </c>
       <c r="F163" t="n">
-        <v>0.6872818345299919</v>
+        <v>0.6872818345299915</v>
       </c>
       <c r="G163" t="n">
-        <v>0.2871565425382101</v>
+        <v>0.2871565425375567</v>
       </c>
       <c r="H163" t="inlineStr"/>
       <c r="I163" t="n">
@@ -5739,16 +5727,16 @@
         <v>510.3</v>
       </c>
       <c r="E164" t="n">
-        <v>33.65891011670148</v>
+        <v>33.65891011670226</v>
       </c>
       <c r="F164" t="n">
-        <v>0.5922106949472203</v>
+        <v>0.59221069494722</v>
       </c>
       <c r="G164" t="n">
-        <v>0.2458718330875971</v>
+        <v>0.2458718330869303</v>
       </c>
       <c r="H164" t="n">
-        <v>280.3478433564286</v>
+        <v>280.3478433564284</v>
       </c>
       <c r="I164" t="n">
         <v>1</v>
@@ -5772,16 +5760,16 @@
         <v>510.3</v>
       </c>
       <c r="E165" t="n">
-        <v>29.59024756499733</v>
+        <v>29.59024756499801</v>
       </c>
       <c r="F165" t="n">
-        <v>0.5922106949472203</v>
+        <v>0.59221069494722</v>
       </c>
       <c r="G165" t="n">
-        <v>0.2458718330875971</v>
+        <v>0.2458718330869303</v>
       </c>
       <c r="H165" t="n">
-        <v>299.6670006932845</v>
+        <v>299.6670006932838</v>
       </c>
       <c r="I165" t="n">
         <v>1</v>
@@ -5805,13 +5793,13 @@
         <v>510.7</v>
       </c>
       <c r="E166" t="n">
-        <v>10.28930901235274</v>
+        <v>10.2893090123525</v>
       </c>
       <c r="F166" t="n">
-        <v>0.9409000630411641</v>
+        <v>0.9409000630411644</v>
       </c>
       <c r="G166" t="n">
-        <v>0.2656867683529419</v>
+        <v>0.2656867683524544</v>
       </c>
       <c r="H166" t="inlineStr"/>
       <c r="I166" t="n">
@@ -5836,13 +5824,13 @@
         <v>510.7</v>
       </c>
       <c r="E167" t="n">
-        <v>17.55369586832758</v>
+        <v>17.55369586832774</v>
       </c>
       <c r="F167" t="n">
-        <v>0.9409000630411641</v>
+        <v>0.9409000630411644</v>
       </c>
       <c r="G167" t="n">
-        <v>0.2656867683529419</v>
+        <v>0.2656867683524544</v>
       </c>
       <c r="H167" t="inlineStr"/>
       <c r="I167" t="n">
@@ -5867,13 +5855,13 @@
         <v>510.7</v>
       </c>
       <c r="E168" t="n">
-        <v>27.24680499490193</v>
+        <v>27.24680499490168</v>
       </c>
       <c r="F168" t="n">
-        <v>0.9409000630411641</v>
+        <v>0.9409000630411644</v>
       </c>
       <c r="G168" t="n">
-        <v>0.2656867683529419</v>
+        <v>0.2656867683524544</v>
       </c>
       <c r="H168" t="inlineStr"/>
       <c r="I168" t="n">
@@ -5898,16 +5886,16 @@
         <v>510.8</v>
       </c>
       <c r="E169" t="n">
-        <v>34.35272744260759</v>
+        <v>34.35272744260833</v>
       </c>
       <c r="F169" t="n">
         <v>1.066926510142702</v>
       </c>
       <c r="G169" t="n">
-        <v>0.3425309975106969</v>
+        <v>0.3425309975102418</v>
       </c>
       <c r="H169" t="n">
-        <v>280.9828001406468</v>
+        <v>280.9828001406465</v>
       </c>
       <c r="I169" t="n">
         <v>1</v>
@@ -5931,16 +5919,16 @@
         <v>510.8</v>
       </c>
       <c r="E170" t="n">
-        <v>30.36923001797918</v>
+        <v>30.36923001797985</v>
       </c>
       <c r="F170" t="n">
         <v>1.066926510142702</v>
       </c>
       <c r="G170" t="n">
-        <v>0.3425309975106969</v>
+        <v>0.3425309975102418</v>
       </c>
       <c r="H170" t="n">
-        <v>299.913052790098</v>
+        <v>299.9130527900974</v>
       </c>
       <c r="I170" t="n">
         <v>1</v>
@@ -5964,13 +5952,13 @@
         <v>511.2</v>
       </c>
       <c r="E171" t="n">
-        <v>10.42209940367371</v>
+        <v>10.42209940367351</v>
       </c>
       <c r="F171" t="n">
-        <v>1.327504207095133</v>
+        <v>1.327504207095132</v>
       </c>
       <c r="G171" t="n">
-        <v>0.416028609492486</v>
+        <v>0.4160286094920612</v>
       </c>
       <c r="H171" t="inlineStr"/>
       <c r="I171" t="n">
@@ -5995,13 +5983,13 @@
         <v>511.2</v>
       </c>
       <c r="E172" t="n">
-        <v>17.93800954463276</v>
+        <v>17.93800954463294</v>
       </c>
       <c r="F172" t="n">
-        <v>1.327504207095133</v>
+        <v>1.327504207095132</v>
       </c>
       <c r="G172" t="n">
-        <v>0.416028609492486</v>
+        <v>0.4160286094920612</v>
       </c>
       <c r="H172" t="inlineStr"/>
       <c r="I172" t="n">
@@ -6026,13 +6014,13 @@
         <v>511.2</v>
       </c>
       <c r="E173" t="n">
-        <v>27.36214444769929</v>
+        <v>27.36214444769906</v>
       </c>
       <c r="F173" t="n">
-        <v>1.327504207095133</v>
+        <v>1.327504207095132</v>
       </c>
       <c r="G173" t="n">
-        <v>0.416028609492486</v>
+        <v>0.4160286094920612</v>
       </c>
       <c r="H173" t="inlineStr"/>
       <c r="I173" t="n">
@@ -6057,16 +6045,16 @@
         <v>511.3</v>
       </c>
       <c r="E174" t="n">
-        <v>34.88834105212323</v>
+        <v>34.88834105212401</v>
       </c>
       <c r="F174" t="n">
-        <v>1.267644037405673</v>
+        <v>1.267644037405672</v>
       </c>
       <c r="G174" t="n">
-        <v>0.3876677236122157</v>
+        <v>0.3876677236117305</v>
       </c>
       <c r="H174" t="n">
-        <v>281.0478490530766</v>
+        <v>281.0478490530764</v>
       </c>
       <c r="I174" t="n">
         <v>1</v>
@@ -6090,16 +6078,16 @@
         <v>511.3</v>
       </c>
       <c r="E175" t="n">
-        <v>30.88900387130364</v>
+        <v>30.88900387130434</v>
       </c>
       <c r="F175" t="n">
-        <v>1.267644037405673</v>
+        <v>1.267644037405672</v>
       </c>
       <c r="G175" t="n">
-        <v>0.3876677236122157</v>
+        <v>0.3876677236117305</v>
       </c>
       <c r="H175" t="n">
-        <v>299.6602527971614</v>
+        <v>299.6602527971607</v>
       </c>
       <c r="I175" t="n">
         <v>1</v>
@@ -6123,16 +6111,16 @@
         <v>511.6</v>
       </c>
       <c r="E176" t="n">
-        <v>35.25651124010034</v>
+        <v>35.25651124010113</v>
       </c>
       <c r="F176" t="n">
-        <v>1.470132789251904</v>
+        <v>1.470132789251903</v>
       </c>
       <c r="G176" t="n">
-        <v>0.4911868906510909</v>
+        <v>0.4911868906506509</v>
       </c>
       <c r="H176" t="n">
-        <v>281.3007985178697</v>
+        <v>281.3007985178695</v>
       </c>
       <c r="I176" t="n">
         <v>1</v>
@@ -6156,16 +6144,16 @@
         <v>511.6</v>
       </c>
       <c r="E177" t="n">
-        <v>31.28728533594916</v>
+        <v>31.28728533594985</v>
       </c>
       <c r="F177" t="n">
-        <v>1.470132789251904</v>
+        <v>1.470132789251903</v>
       </c>
       <c r="G177" t="n">
-        <v>0.4911868906510909</v>
+        <v>0.4911868906506509</v>
       </c>
       <c r="H177" t="n">
-        <v>299.71539665877</v>
+        <v>299.7153966587693</v>
       </c>
       <c r="I177" t="n">
         <v>1</v>
@@ -6189,13 +6177,13 @@
         <v>511.7</v>
       </c>
       <c r="E178" t="n">
-        <v>10.52020741219233</v>
+        <v>10.52020741219217</v>
       </c>
       <c r="F178" t="n">
         <v>1.602191966144515</v>
       </c>
       <c r="G178" t="n">
-        <v>0.5386540864605069</v>
+        <v>0.538654086460041</v>
       </c>
       <c r="H178" t="inlineStr"/>
       <c r="I178" t="n">
@@ -6220,13 +6208,13 @@
         <v>511.7</v>
       </c>
       <c r="E179" t="n">
-        <v>18.27362565451604</v>
+        <v>18.27362565451625</v>
       </c>
       <c r="F179" t="n">
         <v>1.602191966144515</v>
       </c>
       <c r="G179" t="n">
-        <v>0.5386540864605069</v>
+        <v>0.538654086460041</v>
       </c>
       <c r="H179" t="inlineStr"/>
       <c r="I179" t="n">
@@ -6251,13 +6239,13 @@
         <v>511.7</v>
       </c>
       <c r="E180" t="n">
-        <v>27.42574168610331</v>
+        <v>27.42574168610309</v>
       </c>
       <c r="F180" t="n">
         <v>1.602191966144515</v>
       </c>
       <c r="G180" t="n">
-        <v>0.5386540864605069</v>
+        <v>0.538654086460041</v>
       </c>
       <c r="H180" t="inlineStr"/>
       <c r="I180" t="n">
@@ -6282,13 +6270,13 @@
         <v>512.1</v>
       </c>
       <c r="E181" t="n">
-        <v>10.19933608780398</v>
+        <v>10.19933608780385</v>
       </c>
       <c r="F181" t="n">
-        <v>1.917472070147218</v>
+        <v>1.917472070147217</v>
       </c>
       <c r="G181" t="n">
-        <v>0.4765618512524499</v>
+        <v>0.4765618512518291</v>
       </c>
       <c r="H181" t="inlineStr"/>
       <c r="I181" t="n">
@@ -6313,13 +6301,13 @@
         <v>512.1</v>
       </c>
       <c r="E182" t="n">
-        <v>18.16482596416989</v>
+        <v>18.16482596417011</v>
       </c>
       <c r="F182" t="n">
-        <v>1.917472070147218</v>
+        <v>1.917472070147217</v>
       </c>
       <c r="G182" t="n">
-        <v>0.4765618512524499</v>
+        <v>0.4765618512518291</v>
       </c>
       <c r="H182" t="inlineStr"/>
       <c r="I182" t="n">
@@ -6344,13 +6332,13 @@
         <v>512.1</v>
       </c>
       <c r="E183" t="n">
-        <v>27.06932512186492</v>
+        <v>27.06932512186471</v>
       </c>
       <c r="F183" t="n">
-        <v>1.917472070147218</v>
+        <v>1.917472070147217</v>
       </c>
       <c r="G183" t="n">
-        <v>0.4765618512524499</v>
+        <v>0.4765618512518291</v>
       </c>
       <c r="H183" t="inlineStr"/>
       <c r="I183" t="n">
@@ -6375,16 +6363,16 @@
         <v>514.5</v>
       </c>
       <c r="E184" t="n">
-        <v>35.57068201475736</v>
+        <v>35.57068201475816</v>
       </c>
       <c r="F184" t="n">
         <v>1.251747950292333</v>
       </c>
       <c r="G184" t="n">
-        <v>0.4155408662486358</v>
+        <v>0.4155408662491613</v>
       </c>
       <c r="H184" t="n">
-        <v>295.2226292848125</v>
+        <v>295.2226292848119</v>
       </c>
       <c r="I184" t="n">
         <v>1</v>
@@ -6408,16 +6396,16 @@
         <v>514.7</v>
       </c>
       <c r="E185" t="n">
-        <v>35.65913990407224</v>
+        <v>35.65913990407305</v>
       </c>
       <c r="F185" t="n">
-        <v>1.441833937068555</v>
+        <v>1.441833937068554</v>
       </c>
       <c r="G185" t="n">
-        <v>0.343123677189617</v>
+        <v>0.3431236771900188</v>
       </c>
       <c r="H185" t="n">
-        <v>295.0088309347191</v>
+        <v>295.0088309347185</v>
       </c>
       <c r="I185" t="n">
         <v>1</v>
@@ -6441,13 +6429,13 @@
         <v>514.9</v>
       </c>
       <c r="E186" t="n">
-        <v>10.04439516364714</v>
+        <v>10.0443951636474</v>
       </c>
       <c r="F186" t="n">
         <v>1.605993802428558</v>
       </c>
       <c r="G186" t="n">
-        <v>0.2681630642047913</v>
+        <v>0.2681630642051849</v>
       </c>
       <c r="H186" t="inlineStr"/>
       <c r="I186" t="n">
@@ -6472,13 +6460,13 @@
         <v>514.9</v>
       </c>
       <c r="E187" t="n">
-        <v>19.62531133000576</v>
+        <v>19.6253113300062</v>
       </c>
       <c r="F187" t="n">
         <v>1.605993802428558</v>
       </c>
       <c r="G187" t="n">
-        <v>0.2681630642047913</v>
+        <v>0.2681630642051849</v>
       </c>
       <c r="H187" t="inlineStr"/>
       <c r="I187" t="n">
@@ -6503,13 +6491,13 @@
         <v>514.9</v>
       </c>
       <c r="E188" t="n">
-        <v>25.69177271173442</v>
+        <v>25.69177271173433</v>
       </c>
       <c r="F188" t="n">
         <v>1.605993802428558</v>
       </c>
       <c r="G188" t="n">
-        <v>0.2681630642047913</v>
+        <v>0.2681630642051849</v>
       </c>
       <c r="H188" t="inlineStr"/>
       <c r="I188" t="n">
@@ -6534,13 +6522,13 @@
         <v>515.3</v>
       </c>
       <c r="E189" t="n">
-        <v>9.75931773904118</v>
+        <v>9.759317739041499</v>
       </c>
       <c r="F189" t="n">
         <v>1.126298627120343</v>
       </c>
       <c r="G189" t="n">
-        <v>0.2231316765138373</v>
+        <v>0.2231316765146018</v>
       </c>
       <c r="H189" t="inlineStr"/>
       <c r="I189" t="n">
@@ -6565,13 +6553,13 @@
         <v>515.3</v>
       </c>
       <c r="E190" t="n">
-        <v>19.4919711050263</v>
+        <v>19.49197110502676</v>
       </c>
       <c r="F190" t="n">
         <v>1.126298627120343</v>
       </c>
       <c r="G190" t="n">
-        <v>0.2231316765138373</v>
+        <v>0.2231316765146018</v>
       </c>
       <c r="H190" t="inlineStr"/>
       <c r="I190" t="n">
@@ -6596,13 +6584,13 @@
         <v>515.4</v>
       </c>
       <c r="E191" t="n">
-        <v>9.774842006463755</v>
+        <v>9.774842006464082</v>
       </c>
       <c r="F191" t="n">
         <v>1.13312767227287</v>
       </c>
       <c r="G191" t="n">
-        <v>0.2125330513015744</v>
+        <v>0.212533051302341</v>
       </c>
       <c r="H191" t="inlineStr"/>
       <c r="I191" t="n">
@@ -6627,13 +6615,13 @@
         <v>515.4</v>
       </c>
       <c r="E192" t="n">
-        <v>19.5283751029016</v>
+        <v>19.52837510290206</v>
       </c>
       <c r="F192" t="n">
         <v>1.13312767227287</v>
       </c>
       <c r="G192" t="n">
-        <v>0.2125330513015744</v>
+        <v>0.212533051302341</v>
       </c>
       <c r="H192" t="inlineStr"/>
       <c r="I192" t="n">
@@ -6658,13 +6646,13 @@
         <v>515.4</v>
       </c>
       <c r="E193" t="n">
-        <v>25.08598236462019</v>
+        <v>25.08598236462012</v>
       </c>
       <c r="F193" t="n">
         <v>1.13312767227287</v>
       </c>
       <c r="G193" t="n">
-        <v>0.2125330513015744</v>
+        <v>0.212533051302341</v>
       </c>
       <c r="H193" t="inlineStr"/>
       <c r="I193" t="n">
@@ -6689,16 +6677,16 @@
         <v>515.6</v>
       </c>
       <c r="E194" t="n">
-        <v>36.55650913449314</v>
+        <v>36.55650913449396</v>
       </c>
       <c r="F194" t="n">
         <v>1.22959500231105</v>
       </c>
       <c r="G194" t="n">
-        <v>0.3221524724761381</v>
+        <v>0.3221524724769121</v>
       </c>
       <c r="H194" t="n">
-        <v>293.1935211254461</v>
+        <v>293.1935211254455</v>
       </c>
       <c r="I194" t="n">
         <v>1</v>
@@ -6722,13 +6710,13 @@
         <v>515.9</v>
       </c>
       <c r="E195" t="n">
-        <v>9.939040812961759</v>
+        <v>9.939040812962153</v>
       </c>
       <c r="F195" t="n">
-        <v>1.142449240988915</v>
+        <v>1.142449240988914</v>
       </c>
       <c r="G195" t="n">
-        <v>0.3407608330125673</v>
+        <v>0.3407608330133383</v>
       </c>
       <c r="H195" t="inlineStr"/>
       <c r="I195" t="n">
@@ -6753,13 +6741,13 @@
         <v>515.9</v>
       </c>
       <c r="E196" t="n">
-        <v>19.81006249540336</v>
+        <v>19.81006249540386</v>
       </c>
       <c r="F196" t="n">
-        <v>1.142449240988915</v>
+        <v>1.142449240988914</v>
       </c>
       <c r="G196" t="n">
-        <v>0.3407608330125673</v>
+        <v>0.3407608330133383</v>
       </c>
       <c r="H196" t="inlineStr"/>
       <c r="I196" t="n">
@@ -6784,13 +6772,13 @@
         <v>515.9</v>
       </c>
       <c r="E197" t="n">
-        <v>24.86896312802939</v>
+        <v>24.86896312802933</v>
       </c>
       <c r="F197" t="n">
-        <v>1.142449240988915</v>
+        <v>1.142449240988914</v>
       </c>
       <c r="G197" t="n">
-        <v>0.3407608330125673</v>
+        <v>0.3407608330133383</v>
       </c>
       <c r="H197" t="inlineStr"/>
       <c r="I197" t="n">
@@ -6815,16 +6803,16 @@
         <v>516.1</v>
       </c>
       <c r="E198" t="n">
-        <v>36.75005325406521</v>
+        <v>36.75005325406603</v>
       </c>
       <c r="F198" t="n">
-        <v>0.9419331483563665</v>
+        <v>0.9419331483563657</v>
       </c>
       <c r="G198" t="n">
-        <v>0.20844313011166</v>
+        <v>0.2084431301122369</v>
       </c>
       <c r="H198" t="n">
-        <v>292.4657199144577</v>
+        <v>292.4657199144572</v>
       </c>
       <c r="I198" t="n">
         <v>1</v>
@@ -6848,13 +6836,13 @@
         <v>516.4</v>
       </c>
       <c r="E199" t="n">
-        <v>9.77486582099044</v>
+        <v>9.774865820990851</v>
       </c>
       <c r="F199" t="n">
-        <v>0.7857925277137408</v>
+        <v>0.7857925277137406</v>
       </c>
       <c r="G199" t="n">
-        <v>0.07822117000643611</v>
+        <v>0.07822117000616881</v>
       </c>
       <c r="H199" t="inlineStr"/>
       <c r="I199" t="n">
@@ -6879,13 +6867,13 @@
         <v>516.4</v>
       </c>
       <c r="E200" t="n">
-        <v>19.668412533283</v>
+        <v>19.66841253328352</v>
       </c>
       <c r="F200" t="n">
-        <v>0.7857925277137408</v>
+        <v>0.7857925277137406</v>
       </c>
       <c r="G200" t="n">
-        <v>0.07822117000643611</v>
+        <v>0.07822117000616881</v>
       </c>
       <c r="H200" t="inlineStr"/>
       <c r="I200" t="n">
@@ -6910,13 +6898,13 @@
         <v>516.4</v>
       </c>
       <c r="E201" t="n">
-        <v>24.64780447306638</v>
+        <v>24.64780447306633</v>
       </c>
       <c r="F201" t="n">
-        <v>0.7857925277137408</v>
+        <v>0.7857925277137406</v>
       </c>
       <c r="G201" t="n">
-        <v>0.07822117000643611</v>
+        <v>0.07822117000616881</v>
       </c>
       <c r="H201" t="inlineStr"/>
       <c r="I201" t="n">
@@ -6941,16 +6929,16 @@
         <v>516.6</v>
       </c>
       <c r="E202" t="n">
-        <v>36.89360908696355</v>
+        <v>36.89360908696437</v>
       </c>
       <c r="F202" t="n">
-        <v>0.9880308413166523</v>
+        <v>0.9880308413166521</v>
       </c>
       <c r="G202" t="n">
-        <v>0.1168909839243275</v>
+        <v>0.1168909839235565</v>
       </c>
       <c r="H202" t="n">
-        <v>292.2739596385342</v>
+        <v>292.2739596385337</v>
       </c>
       <c r="I202" t="n">
         <v>1</v>
@@ -6974,13 +6962,13 @@
         <v>516.9</v>
       </c>
       <c r="E203" t="n">
-        <v>9.869422849475686</v>
+        <v>9.869422849476122</v>
       </c>
       <c r="F203" t="n">
-        <v>0.9423114166542358</v>
+        <v>0.9423114166542356</v>
       </c>
       <c r="G203" t="n">
-        <v>0.1160548280988571</v>
+        <v>0.1160548280980668</v>
       </c>
       <c r="H203" t="inlineStr"/>
       <c r="I203" t="n">
@@ -7005,13 +6993,13 @@
         <v>516.9</v>
       </c>
       <c r="E204" t="n">
-        <v>19.80971123869344</v>
+        <v>19.80971123869395</v>
       </c>
       <c r="F204" t="n">
-        <v>0.9423114166542358</v>
+        <v>0.9423114166542356</v>
       </c>
       <c r="G204" t="n">
-        <v>0.1160548280988571</v>
+        <v>0.1160548280980668</v>
       </c>
       <c r="H204" t="inlineStr"/>
       <c r="I204" t="n">
@@ -7036,13 +7024,13 @@
         <v>516.9</v>
       </c>
       <c r="E205" t="n">
-        <v>24.52336879333062</v>
+        <v>24.52336879333057</v>
       </c>
       <c r="F205" t="n">
-        <v>0.9423114166542358</v>
+        <v>0.9423114166542356</v>
       </c>
       <c r="G205" t="n">
-        <v>0.1160548280988571</v>
+        <v>0.1160548280980668</v>
       </c>
       <c r="H205" t="inlineStr"/>
       <c r="I205" t="n">
@@ -7067,16 +7055,16 @@
         <v>517.1</v>
       </c>
       <c r="E206" t="n">
-        <v>37.23301647826592</v>
+        <v>37.23301647826676</v>
       </c>
       <c r="F206" t="n">
-        <v>0.6664570037040677</v>
+        <v>0.6664570037040674</v>
       </c>
       <c r="G206" t="n">
-        <v>0.1953008046814398</v>
+        <v>0.1953008046807689</v>
       </c>
       <c r="H206" t="n">
-        <v>291.6214016647764</v>
+        <v>291.6214016647759</v>
       </c>
       <c r="I206" t="n">
         <v>1</v>
@@ -7100,13 +7088,13 @@
         <v>517.4</v>
       </c>
       <c r="E207" t="n">
-        <v>9.987186466777608</v>
+        <v>9.987186466778113</v>
       </c>
       <c r="F207" t="n">
         <v>1.082507370603079</v>
       </c>
       <c r="G207" t="n">
-        <v>0.1416013353810314</v>
+        <v>0.1416013353807315</v>
       </c>
       <c r="H207" t="inlineStr"/>
       <c r="I207" t="n">
@@ -7131,13 +7119,13 @@
         <v>517.4</v>
       </c>
       <c r="E208" t="n">
-        <v>19.99345273810552</v>
+        <v>19.99345273810608</v>
       </c>
       <c r="F208" t="n">
         <v>1.082507370603079</v>
       </c>
       <c r="G208" t="n">
-        <v>0.1416013353810314</v>
+        <v>0.1416013353807315</v>
       </c>
       <c r="H208" t="inlineStr"/>
       <c r="I208" t="n">
@@ -7162,13 +7150,13 @@
         <v>517.4</v>
       </c>
       <c r="E209" t="n">
-        <v>24.21809875305543</v>
+        <v>24.21809875305541</v>
       </c>
       <c r="F209" t="n">
         <v>1.082507370603079</v>
       </c>
       <c r="G209" t="n">
-        <v>0.1416013353810314</v>
+        <v>0.1416013353807315</v>
       </c>
       <c r="H209" t="inlineStr"/>
       <c r="I209" t="n">
@@ -7193,16 +7181,16 @@
         <v>517.6</v>
       </c>
       <c r="E210" t="n">
-        <v>37.88510111126232</v>
+        <v>37.88510111126318</v>
       </c>
       <c r="F210" t="n">
         <v>1.313053084473911</v>
       </c>
       <c r="G210" t="n">
-        <v>0.130934221944196</v>
+        <v>0.1309342219437797</v>
       </c>
       <c r="H210" t="n">
-        <v>291.0838330438966</v>
+        <v>291.083833043896</v>
       </c>
       <c r="I210" t="n">
         <v>1</v>
@@ -7226,13 +7214,13 @@
         <v>517.9</v>
       </c>
       <c r="E211" t="n">
-        <v>10.04234515906757</v>
+        <v>10.04234515906811</v>
       </c>
       <c r="F211" t="n">
         <v>1.238225262681231</v>
       </c>
       <c r="G211" t="n">
-        <v>0.3601204103332641</v>
+        <v>0.360120410333039</v>
       </c>
       <c r="H211" t="inlineStr"/>
       <c r="I211" t="n">
@@ -7257,13 +7245,13 @@
         <v>517.9</v>
       </c>
       <c r="E212" t="n">
-        <v>20.08161374098554</v>
+        <v>20.08161374098611</v>
       </c>
       <c r="F212" t="n">
         <v>1.238225262681231</v>
       </c>
       <c r="G212" t="n">
-        <v>0.3601204103332641</v>
+        <v>0.360120410333039</v>
       </c>
       <c r="H212" t="inlineStr"/>
       <c r="I212" t="n">
@@ -7288,13 +7276,13 @@
         <v>517.9</v>
       </c>
       <c r="E213" t="n">
-        <v>23.92230780810067</v>
+        <v>23.92230780810066</v>
       </c>
       <c r="F213" t="n">
         <v>1.238225262681231</v>
       </c>
       <c r="G213" t="n">
-        <v>0.3601204103332641</v>
+        <v>0.360120410333039</v>
       </c>
       <c r="H213" t="inlineStr"/>
       <c r="I213" t="n">
@@ -7325,7 +7313,7 @@
         <v>1.307449226032096</v>
       </c>
       <c r="G214" t="n">
-        <v>0.435328424659263</v>
+        <v>0.435328424659043</v>
       </c>
       <c r="H214" t="inlineStr"/>
       <c r="I214" t="n">
@@ -7350,16 +7338,16 @@
         <v>518.1</v>
       </c>
       <c r="E215" t="n">
-        <v>38.19873930694772</v>
+        <v>38.19873930694859</v>
       </c>
       <c r="F215" t="n">
         <v>1.307449226032096</v>
       </c>
       <c r="G215" t="n">
-        <v>0.435328424659263</v>
+        <v>0.435328424659043</v>
       </c>
       <c r="H215" t="n">
-        <v>290.2389309136113</v>
+        <v>290.2389309136108</v>
       </c>
       <c r="I215" t="n">
         <v>1</v>
@@ -7383,13 +7371,13 @@
         <v>518.4</v>
       </c>
       <c r="E216" t="n">
-        <v>10.41102763068922</v>
+        <v>10.41102763068979</v>
       </c>
       <c r="F216" t="n">
-        <v>1.367168580081151</v>
+        <v>1.367168580081149</v>
       </c>
       <c r="G216" t="n">
-        <v>0.3002968321451143</v>
+        <v>0.3002968321446201</v>
       </c>
       <c r="H216" t="inlineStr"/>
       <c r="I216" t="n">
@@ -7414,13 +7402,13 @@
         <v>518.4</v>
       </c>
       <c r="E217" t="n">
-        <v>20.46000040823033</v>
+        <v>20.46000040823092</v>
       </c>
       <c r="F217" t="n">
-        <v>1.367168580081151</v>
+        <v>1.367168580081149</v>
       </c>
       <c r="G217" t="n">
-        <v>0.3002968321451143</v>
+        <v>0.3002968321446201</v>
       </c>
       <c r="H217" t="inlineStr"/>
       <c r="I217" t="n">
@@ -7445,13 +7433,13 @@
         <v>518.4</v>
       </c>
       <c r="E218" t="n">
-        <v>24.04401673115373</v>
+        <v>24.04401673115374</v>
       </c>
       <c r="F218" t="n">
-        <v>1.367168580081151</v>
+        <v>1.367168580081149</v>
       </c>
       <c r="G218" t="n">
-        <v>0.3002968321451143</v>
+        <v>0.3002968321446201</v>
       </c>
       <c r="H218" t="inlineStr"/>
       <c r="I218" t="n">
@@ -7476,16 +7464,16 @@
         <v>518.6</v>
       </c>
       <c r="E219" t="n">
-        <v>38.62705119940595</v>
+        <v>38.62705119940681</v>
       </c>
       <c r="F219" t="n">
-        <v>1.188721162085757</v>
+        <v>1.188721162085756</v>
       </c>
       <c r="G219" t="n">
-        <v>0.3750145566047847</v>
+        <v>0.3750145566041668</v>
       </c>
       <c r="H219" t="n">
-        <v>290.394978337649</v>
+        <v>290.3949783376485</v>
       </c>
       <c r="I219" t="n">
         <v>1</v>
@@ -7509,13 +7497,13 @@
         <v>518.9</v>
       </c>
       <c r="E220" t="n">
-        <v>10.67447972308397</v>
+        <v>10.67447972308458</v>
       </c>
       <c r="F220" t="n">
-        <v>1.200750312560834</v>
+        <v>1.200750312560833</v>
       </c>
       <c r="G220" t="n">
-        <v>0.4632698966473183</v>
+        <v>0.4632698966466733</v>
       </c>
       <c r="H220" t="inlineStr"/>
       <c r="I220" t="n">
@@ -7540,13 +7528,13 @@
         <v>518.9</v>
       </c>
       <c r="E221" t="n">
-        <v>20.7297725074935</v>
+        <v>20.72977250749411</v>
       </c>
       <c r="F221" t="n">
-        <v>1.200750312560834</v>
+        <v>1.200750312560833</v>
       </c>
       <c r="G221" t="n">
-        <v>0.4632698966473183</v>
+        <v>0.4632698966466733</v>
       </c>
       <c r="H221" t="inlineStr"/>
       <c r="I221" t="n">
@@ -7571,13 +7559,13 @@
         <v>518.9</v>
       </c>
       <c r="E222" t="n">
-        <v>24.05339805956382</v>
+        <v>24.05339805956384</v>
       </c>
       <c r="F222" t="n">
-        <v>1.200750312560834</v>
+        <v>1.200750312560833</v>
       </c>
       <c r="G222" t="n">
-        <v>0.4632698966473183</v>
+        <v>0.4632698966466733</v>
       </c>
       <c r="H222" t="inlineStr"/>
       <c r="I222" t="n">
@@ -7602,16 +7590,16 @@
         <v>519</v>
       </c>
       <c r="E223" t="n">
-        <v>39.14123936028885</v>
+        <v>39.1412393602897</v>
       </c>
       <c r="F223" t="n">
         <v>1.376526252445359</v>
       </c>
       <c r="G223" t="n">
-        <v>0.4009543257895703</v>
+        <v>0.4009543257889996</v>
       </c>
       <c r="H223" t="n">
-        <v>290.0623435342031</v>
+        <v>290.0623435342026</v>
       </c>
       <c r="I223" t="n">
         <v>1</v>
@@ -7635,13 +7623,13 @@
         <v>519.4</v>
       </c>
       <c r="E224" t="n">
-        <v>11.3210045055736</v>
+        <v>11.32100450557425</v>
       </c>
       <c r="F224" t="n">
-        <v>1.705749542738054</v>
+        <v>1.705749542738053</v>
       </c>
       <c r="G224" t="n">
-        <v>0.3534672050055243</v>
+        <v>0.3534672050052625</v>
       </c>
       <c r="H224" t="inlineStr"/>
       <c r="I224" t="n">
@@ -7666,13 +7654,13 @@
         <v>519.4</v>
       </c>
       <c r="E225" t="n">
-        <v>21.37153660984988</v>
+        <v>21.37153660985053</v>
       </c>
       <c r="F225" t="n">
-        <v>1.705749542738054</v>
+        <v>1.705749542738053</v>
       </c>
       <c r="G225" t="n">
-        <v>0.3534672050055243</v>
+        <v>0.3534672050052625</v>
       </c>
       <c r="H225" t="inlineStr"/>
       <c r="I225" t="n">
@@ -7697,13 +7685,13 @@
         <v>519.4</v>
       </c>
       <c r="E226" t="n">
-        <v>24.05287269258056</v>
+        <v>24.05287269258063</v>
       </c>
       <c r="F226" t="n">
-        <v>1.705749542738054</v>
+        <v>1.705749542738053</v>
       </c>
       <c r="G226" t="n">
-        <v>0.3534672050055243</v>
+        <v>0.3534672050052625</v>
       </c>
       <c r="H226" t="inlineStr"/>
       <c r="I226" t="n">
@@ -7728,13 +7716,13 @@
         <v>519.7</v>
       </c>
       <c r="E227" t="n">
-        <v>11.88003188767539</v>
+        <v>11.88003188767606</v>
       </c>
       <c r="F227" t="n">
-        <v>1.979464004214982</v>
+        <v>1.979464004214981</v>
       </c>
       <c r="G227" t="n">
-        <v>0.1516012221968581</v>
+        <v>0.1516012221966866</v>
       </c>
       <c r="H227" t="inlineStr"/>
       <c r="I227" t="n">
@@ -7759,13 +7747,13 @@
         <v>519.7</v>
       </c>
       <c r="E228" t="n">
-        <v>21.92568813827389</v>
+        <v>21.92568813827454</v>
       </c>
       <c r="F228" t="n">
-        <v>1.979464004214982</v>
+        <v>1.979464004214981</v>
       </c>
       <c r="G228" t="n">
-        <v>0.1516012221968581</v>
+        <v>0.1516012221966866</v>
       </c>
       <c r="H228" t="inlineStr"/>
       <c r="I228" t="n">
@@ -7790,13 +7778,13 @@
         <v>519.7</v>
       </c>
       <c r="E229" t="n">
-        <v>24.37007332486704</v>
+        <v>24.37007332486712</v>
       </c>
       <c r="F229" t="n">
-        <v>1.979464004214982</v>
+        <v>1.979464004214981</v>
       </c>
       <c r="G229" t="n">
-        <v>0.1516012221968581</v>
+        <v>0.1516012221966866</v>
       </c>
       <c r="H229" t="inlineStr"/>
       <c r="I229" t="n">
@@ -7821,13 +7809,13 @@
         <v>522.3</v>
       </c>
       <c r="E230" t="n">
-        <v>14.7023996994753</v>
+        <v>14.70239969947609</v>
       </c>
       <c r="F230" t="n">
-        <v>0.4666165219531111</v>
+        <v>0.4666165219531109</v>
       </c>
       <c r="G230" t="n">
-        <v>0.6538175243378809</v>
+        <v>0.6538175243386019</v>
       </c>
       <c r="H230" t="inlineStr"/>
       <c r="I230" t="n">
@@ -7852,13 +7840,13 @@
         <v>522.3</v>
       </c>
       <c r="E231" t="n">
-        <v>24.67754501391582</v>
+        <v>24.67754501391656</v>
       </c>
       <c r="F231" t="n">
-        <v>0.4666165219531111</v>
+        <v>0.4666165219531109</v>
       </c>
       <c r="G231" t="n">
-        <v>0.6538175243378809</v>
+        <v>0.6538175243386019</v>
       </c>
       <c r="H231" t="inlineStr"/>
       <c r="I231" t="n">
@@ -7883,13 +7871,13 @@
         <v>522.3</v>
       </c>
       <c r="E232" t="n">
-        <v>25.71139633913331</v>
+        <v>25.71139633913353</v>
       </c>
       <c r="F232" t="n">
-        <v>0.4666165219531111</v>
+        <v>0.4666165219531109</v>
       </c>
       <c r="G232" t="n">
-        <v>0.6538175243378809</v>
+        <v>0.6538175243386019</v>
       </c>
       <c r="H232" t="inlineStr"/>
       <c r="I232" t="n">
@@ -7914,13 +7902,13 @@
         <v>522.8</v>
       </c>
       <c r="E233" t="n">
-        <v>15.08325353178159</v>
+        <v>15.08325353178236</v>
       </c>
       <c r="F233" t="n">
-        <v>0.5661900750877059</v>
+        <v>0.566190075087705</v>
       </c>
       <c r="G233" t="n">
-        <v>0.4818430260407764</v>
+        <v>0.4818430260415462</v>
       </c>
       <c r="H233" t="inlineStr"/>
       <c r="I233" t="n">
@@ -7945,13 +7933,13 @@
         <v>522.8</v>
       </c>
       <c r="E234" t="n">
-        <v>25.08474780780523</v>
+        <v>25.08474780780596</v>
       </c>
       <c r="F234" t="n">
-        <v>0.5661900750877059</v>
+        <v>0.566190075087705</v>
       </c>
       <c r="G234" t="n">
-        <v>0.4818430260407764</v>
+        <v>0.4818430260415462</v>
       </c>
       <c r="H234" t="inlineStr"/>
       <c r="I234" t="n">
@@ -7976,13 +7964,13 @@
         <v>522.8</v>
       </c>
       <c r="E235" t="n">
-        <v>26.28645710242918</v>
+        <v>26.28645710242941</v>
       </c>
       <c r="F235" t="n">
-        <v>0.5661900750877059</v>
+        <v>0.566190075087705</v>
       </c>
       <c r="G235" t="n">
-        <v>0.4818430260407764</v>
+        <v>0.4818430260415462</v>
       </c>
       <c r="H235" t="inlineStr"/>
       <c r="I235" t="n">
@@ -8007,13 +7995,13 @@
         <v>523.3</v>
       </c>
       <c r="E236" t="n">
-        <v>15.31135438153516</v>
+        <v>15.31135438153591</v>
       </c>
       <c r="F236" t="n">
-        <v>1.123613995734151</v>
+        <v>1.12361399573415</v>
       </c>
       <c r="G236" t="n">
-        <v>0.1188291611767064</v>
+        <v>0.1188291611774965</v>
       </c>
       <c r="H236" t="inlineStr"/>
       <c r="I236" t="n">
@@ -8038,13 +8026,13 @@
         <v>523.3</v>
       </c>
       <c r="E237" t="n">
-        <v>25.34425886068847</v>
+        <v>25.34425886068919</v>
       </c>
       <c r="F237" t="n">
-        <v>1.123613995734151</v>
+        <v>1.12361399573415</v>
       </c>
       <c r="G237" t="n">
-        <v>0.1188291611767064</v>
+        <v>0.1188291611774965</v>
       </c>
       <c r="H237" t="inlineStr"/>
       <c r="I237" t="n">
@@ -8069,13 +8057,13 @@
         <v>523.3</v>
       </c>
       <c r="E238" t="n">
-        <v>26.89096105047577</v>
+        <v>26.89096105047599</v>
       </c>
       <c r="F238" t="n">
-        <v>1.123613995734151</v>
+        <v>1.12361399573415</v>
       </c>
       <c r="G238" t="n">
-        <v>0.1188291611767064</v>
+        <v>0.1188291611774965</v>
       </c>
       <c r="H238" t="inlineStr"/>
       <c r="I238" t="n">
@@ -8100,13 +8088,13 @@
         <v>523.8</v>
       </c>
       <c r="E239" t="n">
-        <v>15.63446946844299</v>
+        <v>15.63446946844375</v>
       </c>
       <c r="F239" t="n">
-        <v>1.483573983154763</v>
+        <v>1.483573983154761</v>
       </c>
       <c r="G239" t="n">
-        <v>0.1758997118457132</v>
+        <v>0.1758997118465817</v>
       </c>
       <c r="H239" t="inlineStr"/>
       <c r="I239" t="n">
@@ -8131,13 +8119,13 @@
         <v>523.8</v>
       </c>
       <c r="E240" t="n">
-        <v>25.67328599438546</v>
+        <v>25.67328599438619</v>
       </c>
       <c r="F240" t="n">
-        <v>1.483573983154763</v>
+        <v>1.483573983154761</v>
       </c>
       <c r="G240" t="n">
-        <v>0.1758997118457132</v>
+        <v>0.1758997118465817</v>
       </c>
       <c r="H240" t="inlineStr"/>
       <c r="I240" t="n">
@@ -8162,13 +8150,13 @@
         <v>523.8</v>
       </c>
       <c r="E241" t="n">
-        <v>27.26259969389602</v>
+        <v>27.26259969389626</v>
       </c>
       <c r="F241" t="n">
-        <v>1.483573983154763</v>
+        <v>1.483573983154761</v>
       </c>
       <c r="G241" t="n">
-        <v>0.1758997118457132</v>
+        <v>0.1758997118465817</v>
       </c>
       <c r="H241" t="inlineStr"/>
       <c r="I241" t="n">
@@ -8193,13 +8181,13 @@
         <v>524.3</v>
       </c>
       <c r="E242" t="n">
-        <v>15.83360832817497</v>
+        <v>15.83360832817571</v>
       </c>
       <c r="F242" t="n">
-        <v>1.476068182383562</v>
+        <v>1.47606818238356</v>
       </c>
       <c r="G242" t="n">
-        <v>0.292742420922162</v>
+        <v>0.2927424209229702</v>
       </c>
       <c r="H242" t="inlineStr"/>
       <c r="I242" t="n">
@@ -8224,13 +8212,13 @@
         <v>524.3</v>
       </c>
       <c r="E243" t="n">
-        <v>25.87596734425303</v>
+        <v>25.87596734425375</v>
       </c>
       <c r="F243" t="n">
-        <v>1.476068182383562</v>
+        <v>1.47606818238356</v>
       </c>
       <c r="G243" t="n">
-        <v>0.292742420922162</v>
+        <v>0.2927424209229702</v>
       </c>
       <c r="H243" t="inlineStr"/>
       <c r="I243" t="n">
@@ -8255,13 +8243,13 @@
         <v>524.3</v>
       </c>
       <c r="E244" t="n">
-        <v>27.49912269590477</v>
+        <v>27.499122695905</v>
       </c>
       <c r="F244" t="n">
-        <v>1.476068182383562</v>
+        <v>1.47606818238356</v>
       </c>
       <c r="G244" t="n">
-        <v>0.292742420922162</v>
+        <v>0.2927424209229702</v>
       </c>
       <c r="H244" t="inlineStr"/>
       <c r="I244" t="n">
@@ -8286,13 +8274,13 @@
         <v>524.8</v>
       </c>
       <c r="E245" t="n">
-        <v>15.68219652834228</v>
+        <v>15.68219652834298</v>
       </c>
       <c r="F245" t="n">
-        <v>1.113956515586482</v>
+        <v>1.11395651558648</v>
       </c>
       <c r="G245" t="n">
-        <v>0.1978844505253339</v>
+        <v>0.1978844505245434</v>
       </c>
       <c r="H245" t="inlineStr"/>
       <c r="I245" t="n">
@@ -8317,13 +8305,13 @@
         <v>524.8</v>
       </c>
       <c r="E246" t="n">
-        <v>25.73788340702687</v>
+        <v>25.73788340702756</v>
       </c>
       <c r="F246" t="n">
-        <v>1.113956515586482</v>
+        <v>1.11395651558648</v>
       </c>
       <c r="G246" t="n">
-        <v>0.1978844505253339</v>
+        <v>0.1978844505245434</v>
       </c>
       <c r="H246" t="inlineStr"/>
       <c r="I246" t="n">
@@ -8348,13 +8336,13 @@
         <v>524.8</v>
       </c>
       <c r="E247" t="n">
-        <v>27.80309401385191</v>
+        <v>27.80309401385212</v>
       </c>
       <c r="F247" t="n">
-        <v>1.113956515586482</v>
+        <v>1.11395651558648</v>
       </c>
       <c r="G247" t="n">
-        <v>0.1978844505253339</v>
+        <v>0.1978844505245434</v>
       </c>
       <c r="H247" t="inlineStr"/>
       <c r="I247" t="n">
@@ -8379,13 +8367,13 @@
         <v>525.3</v>
       </c>
       <c r="E248" t="n">
-        <v>15.75826747558721</v>
+        <v>15.75826747558789</v>
       </c>
       <c r="F248" t="n">
-        <v>0.7069537076610715</v>
+        <v>0.7069537076610711</v>
       </c>
       <c r="G248" t="n">
-        <v>0.4306130132205318</v>
+        <v>0.4306130132197036</v>
       </c>
       <c r="H248" t="inlineStr"/>
       <c r="I248" t="n">
@@ -8410,13 +8398,13 @@
         <v>525.3</v>
       </c>
       <c r="E249" t="n">
-        <v>25.81423941545526</v>
+        <v>25.81423941545595</v>
       </c>
       <c r="F249" t="n">
-        <v>0.7069537076610715</v>
+        <v>0.7069537076610711</v>
       </c>
       <c r="G249" t="n">
-        <v>0.4306130132205318</v>
+        <v>0.4306130132197036</v>
       </c>
       <c r="H249" t="inlineStr"/>
       <c r="I249" t="n">
@@ -8441,13 +8429,13 @@
         <v>525.3</v>
       </c>
       <c r="E250" t="n">
-        <v>28.17226391977302</v>
+        <v>28.17226391977322</v>
       </c>
       <c r="F250" t="n">
-        <v>0.7069537076610715</v>
+        <v>0.7069537076610711</v>
       </c>
       <c r="G250" t="n">
-        <v>0.4306130132205318</v>
+        <v>0.4306130132197036</v>
       </c>
       <c r="H250" t="inlineStr"/>
       <c r="I250" t="n">
@@ -8472,13 +8460,13 @@
         <v>525.8</v>
       </c>
       <c r="E251" t="n">
-        <v>16.35953010233938</v>
+        <v>16.35953010234007</v>
       </c>
       <c r="F251" t="n">
-        <v>0.6982841779712633</v>
+        <v>0.6982841779712632</v>
       </c>
       <c r="G251" t="n">
-        <v>0.2795622436780738</v>
+        <v>0.2795622436772263</v>
       </c>
       <c r="H251" t="inlineStr"/>
       <c r="I251" t="n">
@@ -8503,13 +8491,13 @@
         <v>525.8</v>
       </c>
       <c r="E252" t="n">
-        <v>26.41142776188551</v>
+        <v>26.4114277618862</v>
       </c>
       <c r="F252" t="n">
-        <v>0.6982841779712633</v>
+        <v>0.6982841779712632</v>
       </c>
       <c r="G252" t="n">
-        <v>0.2795622436780738</v>
+        <v>0.2795622436772263</v>
       </c>
       <c r="H252" t="inlineStr"/>
       <c r="I252" t="n">
@@ -8534,13 +8522,13 @@
         <v>525.8</v>
       </c>
       <c r="E253" t="n">
-        <v>28.8781156098079</v>
+        <v>28.87811560980811</v>
       </c>
       <c r="F253" t="n">
-        <v>0.6982841779712633</v>
+        <v>0.6982841779712632</v>
       </c>
       <c r="G253" t="n">
-        <v>0.2795622436780738</v>
+        <v>0.2795622436772263</v>
       </c>
       <c r="H253" t="inlineStr"/>
       <c r="I253" t="n">
@@ -8565,13 +8553,13 @@
         <v>526.3</v>
       </c>
       <c r="E254" t="n">
-        <v>16.96321175597456</v>
+        <v>16.96321175597524</v>
       </c>
       <c r="F254" t="n">
         <v>1.094021787661149</v>
       </c>
       <c r="G254" t="n">
-        <v>0.1459625726568096</v>
+        <v>0.1459625726560889</v>
       </c>
       <c r="H254" t="inlineStr"/>
       <c r="I254" t="n">
@@ -8596,13 +8584,13 @@
         <v>526.3</v>
       </c>
       <c r="E255" t="n">
-        <v>27.01228261757338</v>
+        <v>27.01228261757407</v>
       </c>
       <c r="F255" t="n">
         <v>1.094021787661149</v>
       </c>
       <c r="G255" t="n">
-        <v>0.1459625726568096</v>
+        <v>0.1459625726560889</v>
       </c>
       <c r="H255" t="inlineStr"/>
       <c r="I255" t="n">
@@ -8627,13 +8615,13 @@
         <v>526.3</v>
       </c>
       <c r="E256" t="n">
-        <v>29.48209971236867</v>
+        <v>29.4820997123689</v>
       </c>
       <c r="F256" t="n">
         <v>1.094021787661149</v>
       </c>
       <c r="G256" t="n">
-        <v>0.1459625726568096</v>
+        <v>0.1459625726560889</v>
       </c>
       <c r="H256" t="inlineStr"/>
       <c r="I256" t="n">
@@ -8658,13 +8646,13 @@
         <v>526.8</v>
       </c>
       <c r="E257" t="n">
-        <v>17.54063127578209</v>
+        <v>17.54063127578279</v>
       </c>
       <c r="F257" t="n">
-        <v>0.9681394251237627</v>
+        <v>0.9681394251237618</v>
       </c>
       <c r="G257" t="n">
-        <v>0.2842527693307602</v>
+        <v>0.2842527693312034</v>
       </c>
       <c r="H257" t="inlineStr"/>
       <c r="I257" t="n">
@@ -8689,13 +8677,13 @@
         <v>526.8</v>
       </c>
       <c r="E258" t="n">
-        <v>27.5907422546406</v>
+        <v>27.59074225464131</v>
       </c>
       <c r="F258" t="n">
-        <v>0.9681394251237627</v>
+        <v>0.9681394251237618</v>
       </c>
       <c r="G258" t="n">
-        <v>0.2842527693307602</v>
+        <v>0.2842527693312034</v>
       </c>
       <c r="H258" t="inlineStr"/>
       <c r="I258" t="n">
@@ -8720,13 +8708,13 @@
         <v>526.8</v>
       </c>
       <c r="E259" t="n">
-        <v>29.95349355596508</v>
+        <v>29.95349355596533</v>
       </c>
       <c r="F259" t="n">
-        <v>0.9681394251237627</v>
+        <v>0.9681394251237618</v>
       </c>
       <c r="G259" t="n">
-        <v>0.2842527693307602</v>
+        <v>0.2842527693312034</v>
       </c>
       <c r="H259" t="inlineStr"/>
       <c r="I259" t="n">
@@ -8751,13 +8739,13 @@
         <v>526.9</v>
       </c>
       <c r="E260" t="n">
-        <v>29.9959654230864</v>
+        <v>29.99596542308664</v>
       </c>
       <c r="F260" t="n">
-        <v>0.906434325112457</v>
+        <v>0.906434325112456</v>
       </c>
       <c r="G260" t="n">
-        <v>0.3163297003300382</v>
+        <v>0.3163297003302901</v>
       </c>
       <c r="H260" t="inlineStr"/>
       <c r="I260" t="n">
@@ -8782,13 +8770,13 @@
         <v>527.3</v>
       </c>
       <c r="E261" t="n">
-        <v>17.90442786114227</v>
+        <v>17.90442786114294</v>
       </c>
       <c r="F261" t="n">
-        <v>0.773530107916044</v>
+        <v>0.773530107916043</v>
       </c>
       <c r="G261" t="n">
-        <v>0.3161144767603991</v>
+        <v>0.3161144767603256</v>
       </c>
       <c r="H261" t="inlineStr"/>
       <c r="I261" t="n">
@@ -8813,13 +8801,13 @@
         <v>527.3</v>
       </c>
       <c r="E262" t="n">
-        <v>27.94305372954205</v>
+        <v>27.94305372954275</v>
       </c>
       <c r="F262" t="n">
-        <v>0.773530107916044</v>
+        <v>0.773530107916043</v>
       </c>
       <c r="G262" t="n">
-        <v>0.3161144767603991</v>
+        <v>0.3161144767603256</v>
       </c>
       <c r="H262" t="inlineStr"/>
       <c r="I262" t="n">
@@ -8844,13 +8832,13 @@
         <v>527.8</v>
       </c>
       <c r="E263" t="n">
-        <v>18.35963266323564</v>
+        <v>18.3596326632363</v>
       </c>
       <c r="F263" t="n">
-        <v>1.407446343328293</v>
+        <v>1.407446343328292</v>
       </c>
       <c r="G263" t="n">
-        <v>0.5031346551089948</v>
+        <v>0.5031346551088766</v>
       </c>
       <c r="H263" t="inlineStr"/>
       <c r="I263" t="n">
@@ -8875,13 +8863,13 @@
         <v>527.8</v>
       </c>
       <c r="E264" t="n">
-        <v>28.38829964588925</v>
+        <v>28.38829964588993</v>
       </c>
       <c r="F264" t="n">
-        <v>1.407446343328293</v>
+        <v>1.407446343328292</v>
       </c>
       <c r="G264" t="n">
-        <v>0.5031346551089948</v>
+        <v>0.5031346551088766</v>
       </c>
       <c r="H264" t="inlineStr"/>
       <c r="I264" t="n">
@@ -8906,13 +8894,13 @@
         <v>528</v>
       </c>
       <c r="E265" t="n">
-        <v>18.59431317896657</v>
+        <v>18.59431317896724</v>
       </c>
       <c r="F265" t="n">
-        <v>1.88303011881511</v>
+        <v>1.883030118815109</v>
       </c>
       <c r="G265" t="n">
-        <v>0.494601999045193</v>
+        <v>0.4946019990449574</v>
       </c>
       <c r="H265" t="inlineStr"/>
       <c r="I265" t="n">
@@ -8937,13 +8925,13 @@
         <v>528</v>
       </c>
       <c r="E266" t="n">
-        <v>28.61389879764906</v>
+        <v>28.61389879764975</v>
       </c>
       <c r="F266" t="n">
-        <v>1.88303011881511</v>
+        <v>1.883030118815109</v>
       </c>
       <c r="G266" t="n">
-        <v>0.494601999045193</v>
+        <v>0.4946019990449574</v>
       </c>
       <c r="H266" t="inlineStr"/>
       <c r="I266" t="n">
@@ -8968,13 +8956,13 @@
         <v>531.4</v>
       </c>
       <c r="E267" t="n">
-        <v>23.93380059570237</v>
+        <v>23.93380059570299</v>
       </c>
       <c r="F267" t="n">
-        <v>1.340817379090371</v>
+        <v>1.34081737909037</v>
       </c>
       <c r="G267" t="n">
-        <v>0.376763423503952</v>
+        <v>0.3767634235043316</v>
       </c>
       <c r="H267" t="inlineStr"/>
       <c r="I267" t="n">
@@ -8999,13 +8987,13 @@
         <v>531.9</v>
       </c>
       <c r="E268" t="n">
-        <v>24.12509098148355</v>
+        <v>24.12509098148415</v>
       </c>
       <c r="F268" t="n">
-        <v>1.251017701666544</v>
+        <v>1.251017701666542</v>
       </c>
       <c r="G268" t="n">
-        <v>0.3709725789072579</v>
+        <v>0.3709725789070791</v>
       </c>
       <c r="H268" t="inlineStr"/>
       <c r="I268" t="n">
@@ -9030,13 +9018,13 @@
         <v>532.4</v>
       </c>
       <c r="E269" t="n">
-        <v>24.50163111205994</v>
+        <v>24.50163111206054</v>
       </c>
       <c r="F269" t="n">
-        <v>0.925311573440336</v>
+        <v>0.9253115734403341</v>
       </c>
       <c r="G269" t="n">
-        <v>0.4109597671712764</v>
+        <v>0.4109597671710672</v>
       </c>
       <c r="H269" t="inlineStr"/>
       <c r="I269" t="n">
@@ -9061,13 +9049,13 @@
         <v>532.9</v>
       </c>
       <c r="E270" t="n">
-        <v>24.59617744212643</v>
+        <v>24.59617744212701</v>
       </c>
       <c r="F270" t="n">
-        <v>0.8271686194999253</v>
+        <v>0.8271686194999235</v>
       </c>
       <c r="G270" t="n">
-        <v>0.3565896394629031</v>
+        <v>0.3565896394622471</v>
       </c>
       <c r="H270" t="inlineStr"/>
       <c r="I270" t="n">
@@ -9092,13 +9080,13 @@
         <v>533.4</v>
       </c>
       <c r="E271" t="n">
-        <v>24.69797163143195</v>
+        <v>24.69797163143253</v>
       </c>
       <c r="F271" t="n">
-        <v>0.4567031060007579</v>
+        <v>0.4567031060007572</v>
       </c>
       <c r="G271" t="n">
-        <v>0.1961124331775053</v>
+        <v>0.1961124331766551</v>
       </c>
       <c r="H271" t="inlineStr"/>
       <c r="I271" t="n">
@@ -9123,13 +9111,13 @@
         <v>533.9</v>
       </c>
       <c r="E272" t="n">
-        <v>24.54587502142991</v>
+        <v>24.54587502143048</v>
       </c>
       <c r="F272" t="n">
-        <v>0.7378191543351182</v>
+        <v>0.7378191543351178</v>
       </c>
       <c r="G272" t="n">
-        <v>0.4963991246832006</v>
+        <v>0.4963991246827748</v>
       </c>
       <c r="H272" t="inlineStr"/>
       <c r="I272" t="n">
@@ -9154,13 +9142,13 @@
         <v>534.4</v>
       </c>
       <c r="E273" t="n">
-        <v>24.89400229038622</v>
+        <v>24.8940022903868</v>
       </c>
       <c r="F273" t="n">
         <v>1.058187862805632</v>
       </c>
       <c r="G273" t="n">
-        <v>0.5574633829477794</v>
+        <v>0.5574633829475629</v>
       </c>
       <c r="H273" t="inlineStr"/>
       <c r="I273" t="n">
@@ -9185,13 +9173,13 @@
         <v>534.9</v>
       </c>
       <c r="E274" t="n">
-        <v>25.6323079299341</v>
+        <v>25.63230792993467</v>
       </c>
       <c r="F274" t="n">
-        <v>1.143556077755584</v>
+        <v>1.143556077755583</v>
       </c>
       <c r="G274" t="n">
-        <v>0.4545977833851101</v>
+        <v>0.4545977833850948</v>
       </c>
       <c r="H274" t="inlineStr"/>
       <c r="I274" t="n">
@@ -9216,13 +9204,13 @@
         <v>535.4</v>
       </c>
       <c r="E275" t="n">
-        <v>26.47171129510944</v>
+        <v>26.47171129511003</v>
       </c>
       <c r="F275" t="n">
-        <v>1.705945479586342</v>
+        <v>1.705945479586341</v>
       </c>
       <c r="G275" t="n">
-        <v>0.526313336717753</v>
+        <v>0.5263133367182699</v>
       </c>
       <c r="H275" t="inlineStr"/>
       <c r="I275" t="n">
@@ -9247,13 +9235,13 @@
         <v>535.8</v>
       </c>
       <c r="E276" t="n">
-        <v>26.95999475930734</v>
+        <v>26.95999475930792</v>
       </c>
       <c r="F276" t="n">
-        <v>1.97823809593743</v>
+        <v>1.978238095937428</v>
       </c>
       <c r="G276" t="n">
-        <v>0.4146725523521783</v>
+        <v>0.4146725523525988</v>
       </c>
       <c r="H276" t="inlineStr"/>
       <c r="I276" t="n">
@@ -9278,13 +9266,13 @@
         <v>651.6</v>
       </c>
       <c r="E277" t="n">
-        <v>11.84304703220255</v>
+        <v>11.84304703220351</v>
       </c>
       <c r="F277" t="n">
-        <v>0.9899582617095591</v>
+        <v>0.9899582617095583</v>
       </c>
       <c r="G277" t="n">
-        <v>0.3486123274259429</v>
+        <v>0.3486123274266592</v>
       </c>
       <c r="H277" t="inlineStr"/>
       <c r="I277" t="n">
@@ -9309,13 +9297,13 @@
         <v>651.6</v>
       </c>
       <c r="E278" t="n">
-        <v>20.82499671767194</v>
+        <v>20.82499671767277</v>
       </c>
       <c r="F278" t="n">
-        <v>0.9899582617095591</v>
+        <v>0.9899582617095583</v>
       </c>
       <c r="G278" t="n">
-        <v>0.3486123274259429</v>
+        <v>0.3486123274266592</v>
       </c>
       <c r="H278" t="inlineStr"/>
       <c r="I278" t="n">
@@ -9340,13 +9328,13 @@
         <v>651.6</v>
       </c>
       <c r="E279" t="n">
-        <v>19.23074969032607</v>
+        <v>19.23074969032627</v>
       </c>
       <c r="F279" t="n">
-        <v>0.9899582617095591</v>
+        <v>0.9899582617095583</v>
       </c>
       <c r="G279" t="n">
-        <v>0.3486123274259429</v>
+        <v>0.3486123274266592</v>
       </c>
       <c r="H279" t="inlineStr"/>
       <c r="I279" t="n">
@@ -9371,13 +9359,13 @@
         <v>652.1</v>
       </c>
       <c r="E280" t="n">
-        <v>12.16103783680543</v>
+        <v>12.16103783680639</v>
       </c>
       <c r="F280" t="n">
         <v>1.206932495823092</v>
       </c>
       <c r="G280" t="n">
-        <v>0.5700842473598207</v>
+        <v>0.5700842473606421</v>
       </c>
       <c r="H280" t="inlineStr"/>
       <c r="I280" t="n">
@@ -9402,13 +9390,13 @@
         <v>652.1</v>
       </c>
       <c r="E281" t="n">
-        <v>21.11505220561719</v>
+        <v>21.11505220561803</v>
       </c>
       <c r="F281" t="n">
         <v>1.206932495823092</v>
       </c>
       <c r="G281" t="n">
-        <v>0.5700842473598207</v>
+        <v>0.5700842473606421</v>
       </c>
       <c r="H281" t="inlineStr"/>
       <c r="I281" t="n">
@@ -9433,13 +9421,13 @@
         <v>652.1</v>
       </c>
       <c r="E282" t="n">
-        <v>19.34213089137282</v>
+        <v>19.34213089137304</v>
       </c>
       <c r="F282" t="n">
         <v>1.206932495823092</v>
       </c>
       <c r="G282" t="n">
-        <v>0.5700842473598207</v>
+        <v>0.5700842473606421</v>
       </c>
       <c r="H282" t="inlineStr"/>
       <c r="I282" t="n">
@@ -9464,13 +9452,13 @@
         <v>652.4</v>
       </c>
       <c r="E283" t="n">
-        <v>19.16540490026904</v>
+        <v>19.16540490026925</v>
       </c>
       <c r="F283" t="n">
-        <v>0.5983094475291147</v>
+        <v>0.5983094475291145</v>
       </c>
       <c r="G283" t="n">
-        <v>0.7722610867453404</v>
+        <v>0.772261086745857</v>
       </c>
       <c r="H283" t="inlineStr"/>
       <c r="I283" t="n">
@@ -9495,13 +9483,13 @@
         <v>652.6</v>
       </c>
       <c r="E284" t="n">
-        <v>11.97975987084937</v>
+        <v>11.97975987085034</v>
       </c>
       <c r="F284" t="n">
-        <v>0.5434802497926828</v>
+        <v>0.5434802497926826</v>
       </c>
       <c r="G284" t="n">
-        <v>0.8867402894798897</v>
+        <v>0.8867402894803255</v>
       </c>
       <c r="H284" t="inlineStr"/>
       <c r="I284" t="n">
@@ -9526,13 +9514,13 @@
         <v>652.6</v>
       </c>
       <c r="E285" t="n">
-        <v>20.94500547875356</v>
+        <v>20.9450054787544</v>
       </c>
       <c r="F285" t="n">
-        <v>0.5434802497926828</v>
+        <v>0.5434802497926826</v>
       </c>
       <c r="G285" t="n">
-        <v>0.8867402894798897</v>
+        <v>0.8867402894803255</v>
       </c>
       <c r="H285" t="inlineStr"/>
       <c r="I285" t="n">
@@ -9557,13 +9545,13 @@
         <v>652.6</v>
       </c>
       <c r="E286" t="n">
-        <v>19.26397136863424</v>
+        <v>19.26397136863445</v>
       </c>
       <c r="F286" t="n">
-        <v>0.5434802497926828</v>
+        <v>0.5434802497926826</v>
       </c>
       <c r="G286" t="n">
-        <v>0.8867402894798897</v>
+        <v>0.8867402894803255</v>
       </c>
       <c r="H286" t="inlineStr"/>
       <c r="I286" t="n">
@@ -9588,13 +9576,13 @@
         <v>653.1</v>
       </c>
       <c r="E287" t="n">
-        <v>12.37860081278891</v>
+        <v>12.37860081278987</v>
       </c>
       <c r="F287" t="n">
         <v>1.621007814464931</v>
       </c>
       <c r="G287" t="n">
-        <v>0.943695688820619</v>
+        <v>0.9436956888212015</v>
       </c>
       <c r="H287" t="inlineStr"/>
       <c r="I287" t="n">
@@ -9619,13 +9607,13 @@
         <v>653.1</v>
       </c>
       <c r="E288" t="n">
-        <v>21.5371172811258</v>
+        <v>21.53711728112664</v>
       </c>
       <c r="F288" t="n">
         <v>1.621007814464931</v>
       </c>
       <c r="G288" t="n">
-        <v>0.943695688820619</v>
+        <v>0.9436956888212015</v>
       </c>
       <c r="H288" t="inlineStr"/>
       <c r="I288" t="n">
@@ -9650,13 +9638,13 @@
         <v>653.1</v>
       </c>
       <c r="E289" t="n">
-        <v>20.13310275449394</v>
+        <v>20.13310275449416</v>
       </c>
       <c r="F289" t="n">
         <v>1.621007814464931</v>
       </c>
       <c r="G289" t="n">
-        <v>0.943695688820619</v>
+        <v>0.9436956888212015</v>
       </c>
       <c r="H289" t="inlineStr"/>
       <c r="I289" t="n">
@@ -9681,13 +9669,13 @@
         <v>653.3</v>
       </c>
       <c r="E290" t="n">
-        <v>12.40910614726563</v>
+        <v>12.40910614726656</v>
       </c>
       <c r="F290" t="n">
-        <v>1.859329606363327</v>
+        <v>1.859329606363326</v>
       </c>
       <c r="G290" t="n">
-        <v>0.8183268082045135</v>
+        <v>0.8183268082050933</v>
       </c>
       <c r="H290" t="inlineStr"/>
       <c r="I290" t="n">
@@ -9712,13 +9700,13 @@
         <v>653.3</v>
       </c>
       <c r="E291" t="n">
-        <v>21.68528467194361</v>
+        <v>21.68528467194443</v>
       </c>
       <c r="F291" t="n">
-        <v>1.859329606363327</v>
+        <v>1.859329606363326</v>
       </c>
       <c r="G291" t="n">
-        <v>0.8183268082045135</v>
+        <v>0.8183268082050933</v>
       </c>
       <c r="H291" t="inlineStr"/>
       <c r="I291" t="n">
@@ -9743,13 +9731,13 @@
         <v>653.3</v>
       </c>
       <c r="E292" t="n">
-        <v>20.55466932121856</v>
+        <v>20.55466932121877</v>
       </c>
       <c r="F292" t="n">
-        <v>1.859329606363327</v>
+        <v>1.859329606363326</v>
       </c>
       <c r="G292" t="n">
-        <v>0.8183268082045135</v>
+        <v>0.8183268082050933</v>
       </c>
       <c r="H292" t="inlineStr"/>
       <c r="I292" t="n">
@@ -9774,16 +9762,16 @@
         <v>750.8</v>
       </c>
       <c r="E293" t="n">
-        <v>37.42741317226049</v>
+        <v>37.42741317226149</v>
       </c>
       <c r="F293" t="n">
-        <v>1.374773177086003</v>
+        <v>1.374773177086002</v>
       </c>
       <c r="G293" t="n">
-        <v>0.1477724622783503</v>
+        <v>0.1477724622784411</v>
       </c>
       <c r="H293" t="n">
-        <v>227.9135905940556</v>
+        <v>227.9135905940558</v>
       </c>
       <c r="I293" t="n">
         <v>1</v>
@@ -9807,16 +9795,16 @@
         <v>750.8</v>
       </c>
       <c r="E294" t="n">
-        <v>32.45137922936761</v>
+        <v>32.45137922936853</v>
       </c>
       <c r="F294" t="n">
-        <v>1.374773177086003</v>
+        <v>1.374773177086002</v>
       </c>
       <c r="G294" t="n">
-        <v>0.1477724622783503</v>
+        <v>0.1477724622784411</v>
       </c>
       <c r="H294" t="n">
-        <v>256.6631407642616</v>
+        <v>256.6631407642609</v>
       </c>
       <c r="I294" t="n">
         <v>1</v>
@@ -9840,16 +9828,16 @@
         <v>750.8</v>
       </c>
       <c r="E295" t="n">
-        <v>22.37801193007499</v>
+        <v>22.3780119300758</v>
       </c>
       <c r="F295" t="n">
-        <v>1.374773177086003</v>
+        <v>1.374773177086002</v>
       </c>
       <c r="G295" t="n">
-        <v>0.1477724622783503</v>
+        <v>0.1477724622784411</v>
       </c>
       <c r="H295" t="n">
-        <v>269.2683666927907</v>
+        <v>269.2683666927891</v>
       </c>
       <c r="I295" t="n">
         <v>1</v>
@@ -9873,16 +9861,16 @@
         <v>750.8</v>
       </c>
       <c r="E296" t="n">
-        <v>35.3895729496723</v>
+        <v>35.3895729496727</v>
       </c>
       <c r="F296" t="n">
-        <v>1.374773177086003</v>
+        <v>1.374773177086002</v>
       </c>
       <c r="G296" t="n">
-        <v>0.1477724622783503</v>
+        <v>0.1477724622784411</v>
       </c>
       <c r="H296" t="n">
-        <v>298.9205230300088</v>
+        <v>298.9205230300073</v>
       </c>
       <c r="I296" t="n">
         <v>1</v>
@@ -9909,13 +9897,13 @@
         <v>31.42162621299427</v>
       </c>
       <c r="F297" t="n">
-        <v>1.374773177086003</v>
+        <v>1.374773177086002</v>
       </c>
       <c r="G297" t="n">
-        <v>0.1477724622783503</v>
+        <v>0.1477724622784411</v>
       </c>
       <c r="H297" t="n">
-        <v>322.1592549667104</v>
+        <v>322.1592549667086</v>
       </c>
       <c r="I297" t="n">
         <v>1</v>
@@ -9939,13 +9927,13 @@
         <v>751.1</v>
       </c>
       <c r="E298" t="n">
-        <v>23.14786527429462</v>
+        <v>23.1478652742954</v>
       </c>
       <c r="F298" t="n">
-        <v>1.296147412038318</v>
+        <v>1.296147412038316</v>
       </c>
       <c r="G298" t="n">
-        <v>0.03291068514237279</v>
+        <v>0.03291068514314721</v>
       </c>
       <c r="H298" t="inlineStr"/>
       <c r="I298" t="n">
@@ -9970,13 +9958,13 @@
         <v>751.1</v>
       </c>
       <c r="E299" t="n">
-        <v>16.05538883570373</v>
+        <v>16.05538883570392</v>
       </c>
       <c r="F299" t="n">
-        <v>1.296147412038318</v>
+        <v>1.296147412038316</v>
       </c>
       <c r="G299" t="n">
-        <v>0.03291068514237279</v>
+        <v>0.03291068514314721</v>
       </c>
       <c r="H299" t="inlineStr"/>
       <c r="I299" t="n">
@@ -10001,13 +9989,13 @@
         <v>751.1</v>
       </c>
       <c r="E300" t="n">
-        <v>11.07484435237424</v>
+        <v>11.07484435237325</v>
       </c>
       <c r="F300" t="n">
-        <v>1.296147412038318</v>
+        <v>1.296147412038316</v>
       </c>
       <c r="G300" t="n">
-        <v>0.03291068514237279</v>
+        <v>0.03291068514314721</v>
       </c>
       <c r="H300" t="inlineStr"/>
       <c r="I300" t="n">
@@ -10032,13 +10020,13 @@
         <v>751.1</v>
       </c>
       <c r="E301" t="n">
-        <v>14.6252288184861</v>
+        <v>14.62522881848545</v>
       </c>
       <c r="F301" t="n">
-        <v>1.296147412038318</v>
+        <v>1.296147412038316</v>
       </c>
       <c r="G301" t="n">
-        <v>0.03291068514237279</v>
+        <v>0.03291068514314721</v>
       </c>
       <c r="H301" t="inlineStr"/>
       <c r="I301" t="n">
@@ -10063,13 +10051,13 @@
         <v>751.1</v>
       </c>
       <c r="E302" t="n">
-        <v>23.99722965520602</v>
+        <v>23.99722965520519</v>
       </c>
       <c r="F302" t="n">
-        <v>1.296147412038318</v>
+        <v>1.296147412038316</v>
       </c>
       <c r="G302" t="n">
-        <v>0.03291068514237279</v>
+        <v>0.03291068514314721</v>
       </c>
       <c r="H302" t="inlineStr"/>
       <c r="I302" t="n">
@@ -10094,16 +10082,16 @@
         <v>751.1</v>
       </c>
       <c r="E303" t="n">
-        <v>22.5775929568108</v>
+        <v>22.57759295681159</v>
       </c>
       <c r="F303" t="n">
-        <v>1.296147412038318</v>
+        <v>1.296147412038316</v>
       </c>
       <c r="G303" t="n">
-        <v>0.03291068514237279</v>
+        <v>0.03291068514314721</v>
       </c>
       <c r="H303" t="n">
-        <v>270.0403386043821</v>
+        <v>270.0403386043805</v>
       </c>
       <c r="I303" t="n">
         <v>1</v>
@@ -10127,16 +10115,16 @@
         <v>751.2</v>
       </c>
       <c r="E304" t="n">
-        <v>37.34733695442144</v>
+        <v>37.34733695442245</v>
       </c>
       <c r="F304" t="n">
-        <v>1.422715666166499</v>
+        <v>1.422715666166497</v>
       </c>
       <c r="G304" t="n">
-        <v>0.03682616905035831</v>
+        <v>0.03682616905113705</v>
       </c>
       <c r="H304" t="n">
-        <v>228.7431169390679</v>
+        <v>228.743116939068</v>
       </c>
       <c r="I304" t="n">
         <v>1</v>
@@ -10160,16 +10148,16 @@
         <v>751.2</v>
       </c>
       <c r="E305" t="n">
-        <v>32.64186070510289</v>
+        <v>32.64186070510382</v>
       </c>
       <c r="F305" t="n">
-        <v>1.422715666166499</v>
+        <v>1.422715666166497</v>
       </c>
       <c r="G305" t="n">
-        <v>0.03682616905035831</v>
+        <v>0.03682616905113705</v>
       </c>
       <c r="H305" t="n">
-        <v>257.5661694098627</v>
+        <v>257.566169409862</v>
       </c>
       <c r="I305" t="n">
         <v>1</v>
@@ -10193,16 +10181,16 @@
         <v>751.2</v>
       </c>
       <c r="E306" t="n">
-        <v>22.67690710632537</v>
+        <v>22.67690710632618</v>
       </c>
       <c r="F306" t="n">
-        <v>1.422715666166499</v>
+        <v>1.422715666166497</v>
       </c>
       <c r="G306" t="n">
-        <v>0.03682616905035831</v>
+        <v>0.03682616905113705</v>
       </c>
       <c r="H306" t="n">
-        <v>270.4341183881015</v>
+        <v>270.4341183880999</v>
       </c>
       <c r="I306" t="n">
         <v>1</v>
@@ -10226,16 +10214,16 @@
         <v>751.2</v>
       </c>
       <c r="E307" t="n">
-        <v>35.87440510190481</v>
+        <v>35.87440510190522</v>
       </c>
       <c r="F307" t="n">
-        <v>1.422715666166499</v>
+        <v>1.422715666166497</v>
       </c>
       <c r="G307" t="n">
-        <v>0.03682616905035831</v>
+        <v>0.03682616905113705</v>
       </c>
       <c r="H307" t="n">
-        <v>299.3284134497683</v>
+        <v>299.3284134497669</v>
       </c>
       <c r="I307" t="n">
         <v>1</v>
@@ -10259,16 +10247,16 @@
         <v>751.2</v>
       </c>
       <c r="E308" t="n">
-        <v>31.96708498914314</v>
+        <v>31.96708498914316</v>
       </c>
       <c r="F308" t="n">
-        <v>1.422715666166499</v>
+        <v>1.422715666166497</v>
       </c>
       <c r="G308" t="n">
-        <v>0.03682616905035831</v>
+        <v>0.03682616905113705</v>
       </c>
       <c r="H308" t="n">
-        <v>322.2376349882749</v>
+        <v>322.2376349882731</v>
       </c>
       <c r="I308" t="n">
         <v>1</v>
@@ -10292,13 +10280,13 @@
         <v>751.6</v>
       </c>
       <c r="E309" t="n">
-        <v>22.34745182374919</v>
+        <v>22.34745182374996</v>
       </c>
       <c r="F309" t="n">
-        <v>1.52821301672404</v>
+        <v>1.528213016724039</v>
       </c>
       <c r="G309" t="n">
-        <v>0.1066025859661762</v>
+        <v>0.1066025859653081</v>
       </c>
       <c r="H309" t="inlineStr"/>
       <c r="I309" t="n">
@@ -10323,13 +10311,13 @@
         <v>751.6</v>
       </c>
       <c r="E310" t="n">
-        <v>15.12144319749427</v>
+        <v>15.12144319749441</v>
       </c>
       <c r="F310" t="n">
-        <v>1.52821301672404</v>
+        <v>1.528213016724039</v>
       </c>
       <c r="G310" t="n">
-        <v>0.1066025859661762</v>
+        <v>0.1066025859653081</v>
       </c>
       <c r="H310" t="inlineStr"/>
       <c r="I310" t="n">
@@ -10354,13 +10342,13 @@
         <v>751.6</v>
       </c>
       <c r="E311" t="n">
-        <v>11.25488207183746</v>
+        <v>11.25488207183646</v>
       </c>
       <c r="F311" t="n">
-        <v>1.52821301672404</v>
+        <v>1.528213016724039</v>
       </c>
       <c r="G311" t="n">
-        <v>0.1066025859661762</v>
+        <v>0.1066025859653081</v>
       </c>
       <c r="H311" t="inlineStr"/>
       <c r="I311" t="n">
@@ -10385,13 +10373,13 @@
         <v>751.6</v>
       </c>
       <c r="E312" t="n">
-        <v>15.51248009890714</v>
+        <v>15.51248009890653</v>
       </c>
       <c r="F312" t="n">
-        <v>1.52821301672404</v>
+        <v>1.528213016724039</v>
       </c>
       <c r="G312" t="n">
-        <v>0.1066025859661762</v>
+        <v>0.1066025859653081</v>
       </c>
       <c r="H312" t="inlineStr"/>
       <c r="I312" t="n">
@@ -10416,13 +10404,13 @@
         <v>751.6</v>
       </c>
       <c r="E313" t="n">
-        <v>24.76713570221715</v>
+        <v>24.76713570221635</v>
       </c>
       <c r="F313" t="n">
-        <v>1.52821301672404</v>
+        <v>1.528213016724039</v>
       </c>
       <c r="G313" t="n">
-        <v>0.1066025859661762</v>
+        <v>0.1066025859653081</v>
       </c>
       <c r="H313" t="inlineStr"/>
       <c r="I313" t="n">
@@ -10447,13 +10435,13 @@
         <v>752.1</v>
       </c>
       <c r="E314" t="n">
-        <v>22.33657891898262</v>
+        <v>22.33657891898341</v>
       </c>
       <c r="F314" t="n">
-        <v>1.702692040953721</v>
+        <v>1.702692040953719</v>
       </c>
       <c r="G314" t="n">
-        <v>0.4209046408603662</v>
+        <v>0.4209046408609166</v>
       </c>
       <c r="H314" t="inlineStr"/>
       <c r="I314" t="n">
@@ -10478,13 +10466,13 @@
         <v>752.1</v>
       </c>
       <c r="E315" t="n">
-        <v>14.7005860847488</v>
+        <v>14.70058608474897</v>
       </c>
       <c r="F315" t="n">
-        <v>1.702692040953721</v>
+        <v>1.702692040953719</v>
       </c>
       <c r="G315" t="n">
-        <v>0.4209046408603662</v>
+        <v>0.4209046408609166</v>
       </c>
       <c r="H315" t="inlineStr"/>
       <c r="I315" t="n">
@@ -10509,13 +10497,13 @@
         <v>752.1</v>
       </c>
       <c r="E316" t="n">
-        <v>10.85476102491779</v>
+        <v>10.85476102491678</v>
       </c>
       <c r="F316" t="n">
-        <v>1.702692040953721</v>
+        <v>1.702692040953719</v>
       </c>
       <c r="G316" t="n">
-        <v>0.4209046408603662</v>
+        <v>0.4209046408609166</v>
       </c>
       <c r="H316" t="inlineStr"/>
       <c r="I316" t="n">
@@ -10540,13 +10528,13 @@
         <v>752.1</v>
       </c>
       <c r="E317" t="n">
-        <v>15.68168174172926</v>
+        <v>15.68168174172867</v>
       </c>
       <c r="F317" t="n">
-        <v>1.702692040953721</v>
+        <v>1.702692040953719</v>
       </c>
       <c r="G317" t="n">
-        <v>0.4209046408603662</v>
+        <v>0.4209046408609166</v>
       </c>
       <c r="H317" t="inlineStr"/>
       <c r="I317" t="n">
@@ -10571,13 +10559,13 @@
         <v>752.1</v>
       </c>
       <c r="E318" t="n">
-        <v>24.77228175286634</v>
+        <v>24.77228175286555</v>
       </c>
       <c r="F318" t="n">
-        <v>1.702692040953721</v>
+        <v>1.702692040953719</v>
       </c>
       <c r="G318" t="n">
-        <v>0.4209046408603662</v>
+        <v>0.4209046408609166</v>
       </c>
       <c r="H318" t="inlineStr"/>
       <c r="I318" t="n">
@@ -10602,13 +10590,13 @@
         <v>752.5</v>
       </c>
       <c r="E319" t="n">
-        <v>21.54699595211956</v>
+        <v>21.54699595212035</v>
       </c>
       <c r="F319" t="n">
-        <v>1.905992447956873</v>
+        <v>1.905992447956871</v>
       </c>
       <c r="G319" t="n">
-        <v>0.1945147114655638</v>
+        <v>0.1945147114663569</v>
       </c>
       <c r="H319" t="inlineStr"/>
       <c r="I319" t="n">
@@ -10633,13 +10621,13 @@
         <v>752.5</v>
       </c>
       <c r="E320" t="n">
-        <v>13.63444632013236</v>
+        <v>13.63444632013251</v>
       </c>
       <c r="F320" t="n">
-        <v>1.905992447956873</v>
+        <v>1.905992447956871</v>
       </c>
       <c r="G320" t="n">
-        <v>0.1945147114655638</v>
+        <v>0.1945147114663569</v>
       </c>
       <c r="H320" t="inlineStr"/>
       <c r="I320" t="n">
@@ -10664,13 +10652,13 @@
         <v>752.5</v>
       </c>
       <c r="E321" t="n">
-        <v>11.06995835076455</v>
+        <v>11.06995835076356</v>
       </c>
       <c r="F321" t="n">
-        <v>1.905992447956873</v>
+        <v>1.905992447956871</v>
       </c>
       <c r="G321" t="n">
-        <v>0.1945147114655638</v>
+        <v>0.1945147114663569</v>
       </c>
       <c r="H321" t="inlineStr"/>
       <c r="I321" t="n">
@@ -10695,13 +10683,13 @@
         <v>752.5</v>
       </c>
       <c r="E322" t="n">
-        <v>16.65844527205111</v>
+        <v>16.65844527205057</v>
       </c>
       <c r="F322" t="n">
-        <v>1.905992447956873</v>
+        <v>1.905992447956871</v>
       </c>
       <c r="G322" t="n">
-        <v>0.1945147114655638</v>
+        <v>0.1945147114663569</v>
       </c>
       <c r="H322" t="inlineStr"/>
       <c r="I322" t="n">
@@ -10726,13 +10714,13 @@
         <v>752.5</v>
       </c>
       <c r="E323" t="n">
-        <v>25.59432867485383</v>
+        <v>25.59432867485308</v>
       </c>
       <c r="F323" t="n">
-        <v>1.905992447956873</v>
+        <v>1.905992447956871</v>
       </c>
       <c r="G323" t="n">
-        <v>0.1945147114655638</v>
+        <v>0.1945147114663569</v>
       </c>
       <c r="H323" t="inlineStr"/>
       <c r="I323" t="n">
@@ -10757,13 +10745,13 @@
         <v>763.5</v>
       </c>
       <c r="E324" t="n">
-        <v>11.11514919367791</v>
+        <v>11.11514919367892</v>
       </c>
       <c r="F324" t="n">
-        <v>0.9936591218759745</v>
+        <v>0.9936591218759739</v>
       </c>
       <c r="G324" t="n">
-        <v>0.2743797737311392</v>
+        <v>0.2743797737319775</v>
       </c>
       <c r="H324" t="inlineStr"/>
       <c r="I324" t="n">
@@ -10788,13 +10776,13 @@
         <v>763.5</v>
       </c>
       <c r="E325" t="n">
-        <v>19.02313523486334</v>
+        <v>19.02313523486422</v>
       </c>
       <c r="F325" t="n">
-        <v>0.9936591218759745</v>
+        <v>0.9936591218759739</v>
       </c>
       <c r="G325" t="n">
-        <v>0.2743797737311392</v>
+        <v>0.2743797737319775</v>
       </c>
       <c r="H325" t="inlineStr"/>
       <c r="I325" t="n">
@@ -10819,13 +10807,13 @@
         <v>763.5</v>
       </c>
       <c r="E326" t="n">
-        <v>16.00450618359402</v>
+        <v>16.00450618359421</v>
       </c>
       <c r="F326" t="n">
-        <v>0.9936591218759745</v>
+        <v>0.9936591218759739</v>
       </c>
       <c r="G326" t="n">
-        <v>0.2743797737311392</v>
+        <v>0.2743797737319775</v>
       </c>
       <c r="H326" t="inlineStr"/>
       <c r="I326" t="n">
@@ -10850,13 +10838,13 @@
         <v>763.5</v>
       </c>
       <c r="E327" t="n">
-        <v>29.75104118834951</v>
+        <v>29.75104118834986</v>
       </c>
       <c r="F327" t="n">
-        <v>0.9936591218759745</v>
+        <v>0.9936591218759739</v>
       </c>
       <c r="G327" t="n">
-        <v>0.2743797737311392</v>
+        <v>0.2743797737319775</v>
       </c>
       <c r="H327" t="inlineStr"/>
       <c r="I327" t="n">
@@ -10881,13 +10869,13 @@
         <v>763.7</v>
       </c>
       <c r="E328" t="n">
-        <v>19.00351972327389</v>
+        <v>19.00351972327476</v>
       </c>
       <c r="F328" t="n">
         <v>1.395949229701408</v>
       </c>
       <c r="G328" t="n">
-        <v>0.1857736946709881</v>
+        <v>0.1857736946718147</v>
       </c>
       <c r="H328" t="inlineStr"/>
       <c r="I328" t="n">
@@ -10912,13 +10900,13 @@
         <v>763.8</v>
       </c>
       <c r="E329" t="n">
-        <v>29.9700732815123</v>
+        <v>29.97007328151264</v>
       </c>
       <c r="F329" t="n">
-        <v>1.514815131877478</v>
+        <v>1.514815131877477</v>
       </c>
       <c r="G329" t="n">
-        <v>0.1405132604704974</v>
+        <v>0.1405132604712341</v>
       </c>
       <c r="H329" t="inlineStr"/>
       <c r="I329" t="n">
@@ -10943,13 +10931,13 @@
         <v>764</v>
       </c>
       <c r="E330" t="n">
-        <v>10.90474970160587</v>
+        <v>10.90474970160687</v>
       </c>
       <c r="F330" t="n">
-        <v>1.651259610020402</v>
+        <v>1.6512596100204</v>
       </c>
       <c r="G330" t="n">
-        <v>0.04438276035603476</v>
+        <v>0.04438276035687909</v>
       </c>
       <c r="H330" t="inlineStr"/>
       <c r="I330" t="n">
@@ -10974,13 +10962,13 @@
         <v>764</v>
       </c>
       <c r="E331" t="n">
-        <v>19.12911780159574</v>
+        <v>19.12911780159661</v>
       </c>
       <c r="F331" t="n">
-        <v>1.651259610020402</v>
+        <v>1.6512596100204</v>
       </c>
       <c r="G331" t="n">
-        <v>0.04438276035603476</v>
+        <v>0.04438276035687909</v>
       </c>
       <c r="H331" t="inlineStr"/>
       <c r="I331" t="n">
@@ -11005,13 +10993,13 @@
         <v>764</v>
       </c>
       <c r="E332" t="n">
-        <v>16.65291060626098</v>
+        <v>16.65291060626114</v>
       </c>
       <c r="F332" t="n">
-        <v>1.651259610020402</v>
+        <v>1.6512596100204</v>
       </c>
       <c r="G332" t="n">
-        <v>0.04438276035603476</v>
+        <v>0.04438276035687909</v>
       </c>
       <c r="H332" t="inlineStr"/>
       <c r="I332" t="n">
@@ -11036,13 +11024,13 @@
         <v>764.5</v>
       </c>
       <c r="E333" t="n">
-        <v>10.97903241343015</v>
+        <v>10.97903241343115</v>
       </c>
       <c r="F333" t="n">
-        <v>1.364406979694507</v>
+        <v>1.364406979694506</v>
       </c>
       <c r="G333" t="n">
-        <v>0.1027524117344432</v>
+        <v>0.1027524117349852</v>
       </c>
       <c r="H333" t="inlineStr"/>
       <c r="I333" t="n">
@@ -11067,13 +11055,13 @@
         <v>764.5</v>
       </c>
       <c r="E334" t="n">
-        <v>19.47553712558952</v>
+        <v>19.47553712559038</v>
       </c>
       <c r="F334" t="n">
-        <v>1.364406979694507</v>
+        <v>1.364406979694506</v>
       </c>
       <c r="G334" t="n">
-        <v>0.1027524117344432</v>
+        <v>0.1027524117349852</v>
       </c>
       <c r="H334" t="inlineStr"/>
       <c r="I334" t="n">
@@ -11098,13 +11086,13 @@
         <v>764.5</v>
       </c>
       <c r="E335" t="n">
-        <v>17.37285787698275</v>
+        <v>17.37285787698292</v>
       </c>
       <c r="F335" t="n">
-        <v>1.364406979694507</v>
+        <v>1.364406979694506</v>
       </c>
       <c r="G335" t="n">
-        <v>0.1027524117344432</v>
+        <v>0.1027524117349852</v>
       </c>
       <c r="H335" t="inlineStr"/>
       <c r="I335" t="n">
@@ -11129,13 +11117,13 @@
         <v>764.7</v>
       </c>
       <c r="E336" t="n">
-        <v>10.88594027831164</v>
+        <v>10.88594027831263</v>
       </c>
       <c r="F336" t="n">
-        <v>1.689251507455132</v>
+        <v>1.68925150745513</v>
       </c>
       <c r="G336" t="n">
-        <v>0.2106593647814423</v>
+        <v>0.2106593647813862</v>
       </c>
       <c r="H336" t="inlineStr"/>
       <c r="I336" t="n">
@@ -11160,13 +11148,13 @@
         <v>765</v>
       </c>
       <c r="E337" t="n">
-        <v>10.88629522791014</v>
+        <v>10.8862952279111</v>
       </c>
       <c r="F337" t="n">
-        <v>1.890849832841274</v>
+        <v>1.890849832841272</v>
       </c>
       <c r="G337" t="n">
-        <v>0.3109928395918751</v>
+        <v>0.3109928395917805</v>
       </c>
       <c r="H337" t="inlineStr"/>
       <c r="I337" t="n">
@@ -11191,13 +11179,13 @@
         <v>765</v>
       </c>
       <c r="E338" t="n">
-        <v>19.58238158698371</v>
+        <v>19.58238158698454</v>
       </c>
       <c r="F338" t="n">
-        <v>1.890849832841274</v>
+        <v>1.890849832841272</v>
       </c>
       <c r="G338" t="n">
-        <v>0.3109928395918751</v>
+        <v>0.3109928395917805</v>
       </c>
       <c r="H338" t="inlineStr"/>
       <c r="I338" t="n">
@@ -11222,13 +11210,13 @@
         <v>765</v>
       </c>
       <c r="E339" t="n">
-        <v>17.85103535375057</v>
+        <v>17.85103535375072</v>
       </c>
       <c r="F339" t="n">
-        <v>1.890849832841274</v>
+        <v>1.890849832841272</v>
       </c>
       <c r="G339" t="n">
-        <v>0.3109928395918751</v>
+        <v>0.3109928395917805</v>
       </c>
       <c r="H339" t="inlineStr"/>
       <c r="I339" t="n">
@@ -11253,13 +11241,13 @@
         <v>765.1</v>
       </c>
       <c r="E340" t="n">
-        <v>10.90137525892651</v>
+        <v>10.90137525892749</v>
       </c>
       <c r="F340" t="n">
-        <v>1.96123519602632</v>
+        <v>1.961235196026319</v>
       </c>
       <c r="G340" t="n">
-        <v>0.3163092790260462</v>
+        <v>0.3163092790259466</v>
       </c>
       <c r="H340" t="inlineStr"/>
       <c r="I340" t="n">
@@ -11284,13 +11272,13 @@
         <v>765.1</v>
       </c>
       <c r="E341" t="n">
-        <v>19.64959768808256</v>
+        <v>19.6495976880834</v>
       </c>
       <c r="F341" t="n">
-        <v>1.96123519602632</v>
+        <v>1.961235196026319</v>
       </c>
       <c r="G341" t="n">
-        <v>0.3163092790260462</v>
+        <v>0.3163092790259466</v>
       </c>
       <c r="H341" t="inlineStr"/>
       <c r="I341" t="n">
@@ -11315,13 +11303,13 @@
         <v>765.1</v>
       </c>
       <c r="E342" t="n">
-        <v>18.00160416549344</v>
+        <v>18.0016041654936</v>
       </c>
       <c r="F342" t="n">
-        <v>1.96123519602632</v>
+        <v>1.961235196026319</v>
       </c>
       <c r="G342" t="n">
-        <v>0.3163092790260462</v>
+        <v>0.3163092790259466</v>
       </c>
       <c r="H342" t="inlineStr"/>
       <c r="I342" t="n">

--- a/2026_B题/outputs/task_candidates.xlsx
+++ b/2026_B题/outputs/task_candidates.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,47 +417,47 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>target_id</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>task</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>prep_start_s</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>exec_time_s</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>distance_m</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>speed_m_s</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>accel_m_s2</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>angle_deg</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>expected_success</t>
         </is>
@@ -493,16 +481,16 @@
         <v>477</v>
       </c>
       <c r="E2" t="n">
-        <v>26.73014942483517</v>
+        <v>26.73014942483519</v>
       </c>
       <c r="F2" t="n">
         <v>1.0963632116626</v>
       </c>
       <c r="G2" t="n">
-        <v>0.3635389276737643</v>
+        <v>0.3635389276737487</v>
       </c>
       <c r="H2" t="n">
-        <v>147.5155047912844</v>
+        <v>147.5155047912845</v>
       </c>
       <c r="I2" t="n">
         <v>1</v>
@@ -532,7 +520,7 @@
         <v>1.0963632116626</v>
       </c>
       <c r="G3" t="n">
-        <v>0.3635389276737643</v>
+        <v>0.3635389276737487</v>
       </c>
       <c r="H3" t="n">
         <v>122.6641094976678</v>
@@ -565,10 +553,10 @@
         <v>1.0963632116626</v>
       </c>
       <c r="G4" t="n">
-        <v>0.3635389276737643</v>
+        <v>0.3635389276737487</v>
       </c>
       <c r="H4" t="n">
-        <v>78.50322981771842</v>
+        <v>78.50322981771848</v>
       </c>
       <c r="I4" t="n">
         <v>1</v>
@@ -592,16 +580,16 @@
         <v>477</v>
       </c>
       <c r="E5" t="n">
-        <v>29.24409414215114</v>
+        <v>29.24409414215113</v>
       </c>
       <c r="F5" t="n">
         <v>1.0963632116626</v>
       </c>
       <c r="G5" t="n">
-        <v>0.3635389276737643</v>
+        <v>0.3635389276737487</v>
       </c>
       <c r="H5" t="n">
-        <v>68.21726195687171</v>
+        <v>68.21726195687177</v>
       </c>
       <c r="I5" t="n">
         <v>1</v>
@@ -625,13 +613,13 @@
         <v>477</v>
       </c>
       <c r="E6" t="n">
-        <v>20.27576330244509</v>
+        <v>20.27576330244507</v>
       </c>
       <c r="F6" t="n">
         <v>1.0963632116626</v>
       </c>
       <c r="G6" t="n">
-        <v>0.3635389276737643</v>
+        <v>0.3635389276737487</v>
       </c>
       <c r="H6" t="n">
         <v>19.16402307633655</v>
@@ -658,16 +646,16 @@
         <v>477</v>
       </c>
       <c r="E7" t="n">
-        <v>33.80100853348428</v>
+        <v>33.80100853348426</v>
       </c>
       <c r="F7" t="n">
         <v>1.0963632116626</v>
       </c>
       <c r="G7" t="n">
-        <v>0.3635389276737643</v>
+        <v>0.3635389276737487</v>
       </c>
       <c r="H7" t="n">
-        <v>33.29690258965257</v>
+        <v>33.29690258965263</v>
       </c>
       <c r="I7" t="n">
         <v>1</v>
@@ -691,13 +679,13 @@
         <v>477</v>
       </c>
       <c r="E8" t="n">
-        <v>24.4096266559415</v>
+        <v>24.40962665594152</v>
       </c>
       <c r="F8" t="n">
         <v>1.0963632116626</v>
       </c>
       <c r="G8" t="n">
-        <v>0.3635389276737643</v>
+        <v>0.3635389276737487</v>
       </c>
       <c r="H8" t="n">
         <v>222.6692755731565</v>
@@ -724,13 +712,13 @@
         <v>477</v>
       </c>
       <c r="E9" t="n">
-        <v>19.06442508242715</v>
+        <v>19.06442508242714</v>
       </c>
       <c r="F9" t="n">
         <v>1.0963632116626</v>
       </c>
       <c r="G9" t="n">
-        <v>0.3635389276737643</v>
+        <v>0.3635389276737487</v>
       </c>
       <c r="H9" t="n">
         <v>287.8764969434181</v>
@@ -757,13 +745,13 @@
         <v>477</v>
       </c>
       <c r="E10" t="n">
-        <v>16.48436238206421</v>
+        <v>16.4843623820642</v>
       </c>
       <c r="F10" t="n">
         <v>1.0963632116626</v>
       </c>
       <c r="G10" t="n">
-        <v>0.3635389276737643</v>
+        <v>0.3635389276737487</v>
       </c>
       <c r="H10" t="n">
         <v>331.9800675777695</v>
@@ -790,13 +778,13 @@
         <v>477</v>
       </c>
       <c r="E11" t="n">
-        <v>30.58785502699282</v>
+        <v>30.58785502699281</v>
       </c>
       <c r="F11" t="n">
         <v>1.0963632116626</v>
       </c>
       <c r="G11" t="n">
-        <v>0.3635389276737643</v>
+        <v>0.3635389276737487</v>
       </c>
       <c r="H11" t="n">
         <v>318.0586209469542</v>
@@ -823,13 +811,13 @@
         <v>477</v>
       </c>
       <c r="E12" t="n">
-        <v>33.30365343076643</v>
+        <v>33.30365343076641</v>
       </c>
       <c r="F12" t="n">
         <v>1.0963632116626</v>
       </c>
       <c r="G12" t="n">
-        <v>0.3635389276737643</v>
+        <v>0.3635389276737487</v>
       </c>
       <c r="H12" t="n">
         <v>344.2427717635636</v>
@@ -862,7 +850,7 @@
         <v>1.022868112614397</v>
       </c>
       <c r="G13" t="n">
-        <v>0.3308325106365697</v>
+        <v>0.3308325106365562</v>
       </c>
       <c r="H13" t="n">
         <v>223.1676848219427</v>
@@ -889,13 +877,13 @@
         <v>477.5</v>
       </c>
       <c r="E14" t="n">
-        <v>18.26845367191012</v>
+        <v>18.26845367191013</v>
       </c>
       <c r="F14" t="n">
-        <v>0.8683134495735321</v>
+        <v>0.8683134495735332</v>
       </c>
       <c r="G14" t="n">
-        <v>0.4187514451780422</v>
+        <v>0.4187514451780406</v>
       </c>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="n">
@@ -920,13 +908,13 @@
         <v>477.5</v>
       </c>
       <c r="E15" t="n">
-        <v>10.03928385457295</v>
+        <v>10.03928385457296</v>
       </c>
       <c r="F15" t="n">
-        <v>0.8683134495735321</v>
+        <v>0.8683134495735332</v>
       </c>
       <c r="G15" t="n">
-        <v>0.4187514451780422</v>
+        <v>0.4187514451780406</v>
       </c>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="n">
@@ -954,10 +942,10 @@
         <v>13.85181735068472</v>
       </c>
       <c r="F16" t="n">
-        <v>0.8683134495735321</v>
+        <v>0.8683134495735332</v>
       </c>
       <c r="G16" t="n">
-        <v>0.4187514451780422</v>
+        <v>0.4187514451780406</v>
       </c>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="n">
@@ -982,13 +970,13 @@
         <v>477.5</v>
       </c>
       <c r="E17" t="n">
-        <v>17.53917316082145</v>
+        <v>17.53917316082144</v>
       </c>
       <c r="F17" t="n">
-        <v>0.8683134495735321</v>
+        <v>0.8683134495735332</v>
       </c>
       <c r="G17" t="n">
-        <v>0.4187514451780422</v>
+        <v>0.4187514451780406</v>
       </c>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="n">
@@ -1013,13 +1001,13 @@
         <v>477.5</v>
       </c>
       <c r="E18" t="n">
-        <v>22.32645778067443</v>
+        <v>22.32645778067442</v>
       </c>
       <c r="F18" t="n">
-        <v>0.8683134495735321</v>
+        <v>0.8683134495735332</v>
       </c>
       <c r="G18" t="n">
-        <v>0.4187514451780422</v>
+        <v>0.4187514451780406</v>
       </c>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="n">
@@ -1044,13 +1032,13 @@
         <v>477.5</v>
       </c>
       <c r="E19" t="n">
-        <v>25.80375917557321</v>
+        <v>25.80375917557323</v>
       </c>
       <c r="F19" t="n">
-        <v>0.8683134495735321</v>
+        <v>0.8683134495735332</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4187514451780422</v>
+        <v>0.4187514451780406</v>
       </c>
       <c r="H19" t="n">
         <v>148.045394783456</v>
@@ -1077,13 +1065,13 @@
         <v>477.5</v>
       </c>
       <c r="E20" t="n">
-        <v>24.90181330787541</v>
+        <v>24.90181330787542</v>
       </c>
       <c r="F20" t="n">
-        <v>0.8683134495735321</v>
+        <v>0.8683134495735332</v>
       </c>
       <c r="G20" t="n">
-        <v>0.4187514451780422</v>
+        <v>0.4187514451780406</v>
       </c>
       <c r="H20" t="n">
         <v>122.2654721509231</v>
@@ -1113,13 +1101,13 @@
         <v>17.78577284624593</v>
       </c>
       <c r="F21" t="n">
-        <v>0.8683134495735321</v>
+        <v>0.8683134495735332</v>
       </c>
       <c r="G21" t="n">
-        <v>0.4187514451780422</v>
+        <v>0.4187514451780406</v>
       </c>
       <c r="H21" t="n">
-        <v>75.98812561884358</v>
+        <v>75.98812561884364</v>
       </c>
       <c r="I21" t="n">
         <v>1</v>
@@ -1146,13 +1134,13 @@
         <v>28.8504057542612</v>
       </c>
       <c r="F22" t="n">
-        <v>0.8683134495735321</v>
+        <v>0.8683134495735332</v>
       </c>
       <c r="G22" t="n">
-        <v>0.4187514451780422</v>
+        <v>0.4187514451780406</v>
       </c>
       <c r="H22" t="n">
-        <v>66.49507991121249</v>
+        <v>66.49507991121254</v>
       </c>
       <c r="I22" t="n">
         <v>1</v>
@@ -1176,13 +1164,13 @@
         <v>477.5</v>
       </c>
       <c r="E23" t="n">
-        <v>20.68264901021444</v>
+        <v>20.68264901021443</v>
       </c>
       <c r="F23" t="n">
-        <v>0.8683134495735321</v>
+        <v>0.8683134495735332</v>
       </c>
       <c r="G23" t="n">
-        <v>0.4187514451780422</v>
+        <v>0.4187514451780406</v>
       </c>
       <c r="H23" t="n">
         <v>16.73815366121784</v>
@@ -1209,13 +1197,13 @@
         <v>477.5</v>
       </c>
       <c r="E24" t="n">
-        <v>33.9769589328986</v>
+        <v>33.97695893289858</v>
       </c>
       <c r="F24" t="n">
-        <v>0.8683134495735321</v>
+        <v>0.8683134495735332</v>
       </c>
       <c r="G24" t="n">
-        <v>0.4187514451780422</v>
+        <v>0.4187514451780406</v>
       </c>
       <c r="H24" t="n">
         <v>31.70522980077641</v>
@@ -1242,13 +1230,13 @@
         <v>477.5</v>
       </c>
       <c r="E25" t="n">
-        <v>24.42143521593184</v>
+        <v>24.42143521593185</v>
       </c>
       <c r="F25" t="n">
-        <v>0.8683134495735321</v>
+        <v>0.8683134495735332</v>
       </c>
       <c r="G25" t="n">
-        <v>0.4187514451780422</v>
+        <v>0.4187514451780406</v>
       </c>
       <c r="H25" t="n">
         <v>224.9166820391655</v>
@@ -1278,13 +1266,13 @@
         <v>19.93508148045033</v>
       </c>
       <c r="F26" t="n">
-        <v>0.8683134495735321</v>
+        <v>0.8683134495735332</v>
       </c>
       <c r="G26" t="n">
-        <v>0.4187514451780422</v>
+        <v>0.4187514451780406</v>
       </c>
       <c r="H26" t="n">
-        <v>289.0489974636978</v>
+        <v>289.0489974636977</v>
       </c>
       <c r="I26" t="n">
         <v>1</v>
@@ -1308,13 +1296,13 @@
         <v>477.5</v>
       </c>
       <c r="E27" t="n">
-        <v>17.39323042390096</v>
+        <v>17.39323042390095</v>
       </c>
       <c r="F27" t="n">
-        <v>0.8683134495735321</v>
+        <v>0.8683134495735332</v>
       </c>
       <c r="G27" t="n">
-        <v>0.4187514451780422</v>
+        <v>0.4187514451780406</v>
       </c>
       <c r="H27" t="n">
         <v>330.9584587861622</v>
@@ -1341,13 +1329,13 @@
         <v>477.5</v>
       </c>
       <c r="E28" t="n">
-        <v>31.54206244190064</v>
+        <v>31.54206244190063</v>
       </c>
       <c r="F28" t="n">
-        <v>0.8683134495735321</v>
+        <v>0.8683134495735332</v>
       </c>
       <c r="G28" t="n">
-        <v>0.4187514451780422</v>
+        <v>0.4187514451780406</v>
       </c>
       <c r="H28" t="n">
         <v>317.9078472739848</v>
@@ -1374,13 +1362,13 @@
         <v>477.5</v>
       </c>
       <c r="E29" t="n">
-        <v>34.12681411736134</v>
+        <v>34.12681411736133</v>
       </c>
       <c r="F29" t="n">
-        <v>0.8683134495735321</v>
+        <v>0.8683134495735332</v>
       </c>
       <c r="G29" t="n">
-        <v>0.4187514451780422</v>
+        <v>0.4187514451780406</v>
       </c>
       <c r="H29" t="n">
         <v>343.410863519596</v>
@@ -1407,16 +1395,16 @@
         <v>477.7</v>
       </c>
       <c r="E30" t="n">
-        <v>17.77016212315934</v>
+        <v>17.77016212315933</v>
       </c>
       <c r="F30" t="n">
-        <v>1.04548224957113</v>
+        <v>1.045482249571131</v>
       </c>
       <c r="G30" t="n">
-        <v>0.4441744183179245</v>
+        <v>0.4441744183179257</v>
       </c>
       <c r="H30" t="n">
-        <v>75.02463810216</v>
+        <v>75.02463810216005</v>
       </c>
       <c r="I30" t="n">
         <v>1</v>
@@ -1440,13 +1428,13 @@
         <v>477.9</v>
       </c>
       <c r="E31" t="n">
-        <v>25.27200155211773</v>
+        <v>25.27200155211774</v>
       </c>
       <c r="F31" t="n">
         <v>1.418202143384631</v>
       </c>
       <c r="G31" t="n">
-        <v>0.4956154509114001</v>
+        <v>0.4956154509114037</v>
       </c>
       <c r="H31" t="n">
         <v>147.7477092702189</v>
@@ -1473,16 +1461,16 @@
         <v>477.9</v>
       </c>
       <c r="E32" t="n">
-        <v>24.48227615682374</v>
+        <v>24.48227615682375</v>
       </c>
       <c r="F32" t="n">
         <v>1.418202143384631</v>
       </c>
       <c r="G32" t="n">
-        <v>0.4956154509114001</v>
+        <v>0.4956154509114037</v>
       </c>
       <c r="H32" t="n">
-        <v>121.4471548609174</v>
+        <v>121.4471548609175</v>
       </c>
       <c r="I32" t="n">
         <v>1</v>
@@ -1512,10 +1500,10 @@
         <v>1.418202143384631</v>
       </c>
       <c r="G33" t="n">
-        <v>0.4956154509114001</v>
+        <v>0.4956154509114037</v>
       </c>
       <c r="H33" t="n">
-        <v>74.223749303989</v>
+        <v>74.22374930398905</v>
       </c>
       <c r="I33" t="n">
         <v>1</v>
@@ -1539,13 +1527,13 @@
         <v>477.9</v>
       </c>
       <c r="E34" t="n">
-        <v>28.90724554108035</v>
+        <v>28.90724554108034</v>
       </c>
       <c r="F34" t="n">
         <v>1.418202143384631</v>
       </c>
       <c r="G34" t="n">
-        <v>0.4956154509114001</v>
+        <v>0.4956154509114037</v>
       </c>
       <c r="H34" t="n">
         <v>65.41357297581379</v>
@@ -1572,13 +1560,13 @@
         <v>477.9</v>
       </c>
       <c r="E35" t="n">
-        <v>21.13483570791691</v>
+        <v>21.13483570791689</v>
       </c>
       <c r="F35" t="n">
         <v>1.418202143384631</v>
       </c>
       <c r="G35" t="n">
-        <v>0.4956154509114001</v>
+        <v>0.4956154509114037</v>
       </c>
       <c r="H35" t="n">
         <v>15.88950952862376</v>
@@ -1605,16 +1593,16 @@
         <v>477.9</v>
       </c>
       <c r="E36" t="n">
-        <v>34.33327279134051</v>
+        <v>34.33327279134049</v>
       </c>
       <c r="F36" t="n">
         <v>1.418202143384631</v>
       </c>
       <c r="G36" t="n">
-        <v>0.4956154509114001</v>
+        <v>0.4956154509114037</v>
       </c>
       <c r="H36" t="n">
-        <v>31.00665599057032</v>
+        <v>31.00665599057038</v>
       </c>
       <c r="I36" t="n">
         <v>1</v>
@@ -1638,13 +1626,13 @@
         <v>477.9</v>
       </c>
       <c r="E37" t="n">
-        <v>24.1776369626777</v>
+        <v>24.17763696267771</v>
       </c>
       <c r="F37" t="n">
         <v>1.418202143384631</v>
       </c>
       <c r="G37" t="n">
-        <v>0.4956154509114001</v>
+        <v>0.4956154509114037</v>
       </c>
       <c r="H37" t="n">
         <v>226.0740848978494</v>
@@ -1671,16 +1659,16 @@
         <v>477.9</v>
       </c>
       <c r="E38" t="n">
-        <v>20.27070447692318</v>
+        <v>20.27070447692317</v>
       </c>
       <c r="F38" t="n">
         <v>1.418202143384631</v>
       </c>
       <c r="G38" t="n">
-        <v>0.4956154509114001</v>
+        <v>0.4956154509114037</v>
       </c>
       <c r="H38" t="n">
-        <v>290.2839506512402</v>
+        <v>290.2839506512401</v>
       </c>
       <c r="I38" t="n">
         <v>1</v>
@@ -1704,13 +1692,13 @@
         <v>477.9</v>
       </c>
       <c r="E39" t="n">
-        <v>17.93161656192243</v>
+        <v>17.93161656192241</v>
       </c>
       <c r="F39" t="n">
         <v>1.418202143384631</v>
       </c>
       <c r="G39" t="n">
-        <v>0.4956154509114001</v>
+        <v>0.4956154509114037</v>
       </c>
       <c r="H39" t="n">
         <v>331.2910566370913</v>
@@ -1737,16 +1725,16 @@
         <v>477.9</v>
       </c>
       <c r="E40" t="n">
-        <v>32.04351860897165</v>
+        <v>32.04351860897164</v>
       </c>
       <c r="F40" t="n">
         <v>1.418202143384631</v>
       </c>
       <c r="G40" t="n">
-        <v>0.4956154509114001</v>
+        <v>0.4956154509114037</v>
       </c>
       <c r="H40" t="n">
-        <v>318.3064240876587</v>
+        <v>318.3064240876586</v>
       </c>
       <c r="I40" t="n">
         <v>1</v>
@@ -1770,16 +1758,16 @@
         <v>477.9</v>
       </c>
       <c r="E41" t="n">
-        <v>34.67468796351898</v>
+        <v>34.67468796351897</v>
       </c>
       <c r="F41" t="n">
         <v>1.418202143384631</v>
       </c>
       <c r="G41" t="n">
-        <v>0.4956154509114001</v>
+        <v>0.4956154509114037</v>
       </c>
       <c r="H41" t="n">
-        <v>343.3870959852985</v>
+        <v>343.3870959852984</v>
       </c>
       <c r="I41" t="n">
         <v>1</v>
@@ -1803,13 +1791,13 @@
         <v>478</v>
       </c>
       <c r="E42" t="n">
-        <v>17.81294815885447</v>
+        <v>17.8129481588545</v>
       </c>
       <c r="F42" t="n">
         <v>1.623638544259858</v>
       </c>
       <c r="G42" t="n">
-        <v>0.5086029577484327</v>
+        <v>0.508602957748436</v>
       </c>
       <c r="H42" t="inlineStr"/>
       <c r="I42" t="n">
@@ -1834,13 +1822,13 @@
         <v>478</v>
       </c>
       <c r="E43" t="n">
-        <v>9.543898553853627</v>
+        <v>9.54389855385365</v>
       </c>
       <c r="F43" t="n">
         <v>1.623638544259858</v>
       </c>
       <c r="G43" t="n">
-        <v>0.5086029577484327</v>
+        <v>0.508602957748436</v>
       </c>
       <c r="H43" t="inlineStr"/>
       <c r="I43" t="n">
@@ -1871,7 +1859,7 @@
         <v>1.623638544259858</v>
       </c>
       <c r="G44" t="n">
-        <v>0.5086029577484327</v>
+        <v>0.508602957748436</v>
       </c>
       <c r="H44" t="inlineStr"/>
       <c r="I44" t="n">
@@ -1896,13 +1884,13 @@
         <v>478</v>
       </c>
       <c r="E45" t="n">
-        <v>7.43952106008578</v>
+        <v>7.439521060085759</v>
       </c>
       <c r="F45" t="n">
         <v>1.623638544259858</v>
       </c>
       <c r="G45" t="n">
-        <v>0.5086029577484327</v>
+        <v>0.508602957748436</v>
       </c>
       <c r="H45" t="inlineStr"/>
       <c r="I45" t="n">
@@ -1927,13 +1915,13 @@
         <v>478</v>
       </c>
       <c r="E46" t="n">
-        <v>18.20338548735337</v>
+        <v>18.20338548735335</v>
       </c>
       <c r="F46" t="n">
         <v>1.623638544259858</v>
       </c>
       <c r="G46" t="n">
-        <v>0.5086029577484327</v>
+        <v>0.508602957748436</v>
       </c>
       <c r="H46" t="inlineStr"/>
       <c r="I46" t="n">
@@ -1958,13 +1946,13 @@
         <v>478</v>
       </c>
       <c r="E47" t="n">
-        <v>23.04375999848842</v>
+        <v>23.0437599984884</v>
       </c>
       <c r="F47" t="n">
         <v>1.623638544259858</v>
       </c>
       <c r="G47" t="n">
-        <v>0.5086029577484327</v>
+        <v>0.508602957748436</v>
       </c>
       <c r="H47" t="inlineStr"/>
       <c r="I47" t="n">
@@ -1989,13 +1977,13 @@
         <v>478.5</v>
       </c>
       <c r="E48" t="n">
-        <v>17.02296815194612</v>
+        <v>17.02296815194614</v>
       </c>
       <c r="F48" t="n">
-        <v>1.868951035126932</v>
+        <v>1.868951035126933</v>
       </c>
       <c r="G48" t="n">
-        <v>0.4667675582714153</v>
+        <v>0.4667675582714197</v>
       </c>
       <c r="H48" t="inlineStr"/>
       <c r="I48" t="n">
@@ -2020,13 +2008,13 @@
         <v>478.5</v>
       </c>
       <c r="E49" t="n">
-        <v>8.729492783941838</v>
+        <v>8.729492783941858</v>
       </c>
       <c r="F49" t="n">
-        <v>1.868951035126932</v>
+        <v>1.868951035126933</v>
       </c>
       <c r="G49" t="n">
-        <v>0.4667675582714153</v>
+        <v>0.4667675582714197</v>
       </c>
       <c r="H49" t="inlineStr"/>
       <c r="I49" t="n">
@@ -2054,10 +2042,10 @@
         <v>13.7838154445814</v>
       </c>
       <c r="F50" t="n">
-        <v>1.868951035126932</v>
+        <v>1.868951035126933</v>
       </c>
       <c r="G50" t="n">
-        <v>0.4667675582714153</v>
+        <v>0.4667675582714197</v>
       </c>
       <c r="H50" t="inlineStr"/>
       <c r="I50" t="n">
@@ -2082,13 +2070,13 @@
         <v>478.5</v>
       </c>
       <c r="E51" t="n">
-        <v>8.234977819896942</v>
+        <v>8.234977819896919</v>
       </c>
       <c r="F51" t="n">
-        <v>1.868951035126932</v>
+        <v>1.868951035126933</v>
       </c>
       <c r="G51" t="n">
-        <v>0.4667675582714153</v>
+        <v>0.4667675582714197</v>
       </c>
       <c r="H51" t="inlineStr"/>
       <c r="I51" t="n">
@@ -2113,13 +2101,13 @@
         <v>478.5</v>
       </c>
       <c r="E52" t="n">
-        <v>18.89413146906162</v>
+        <v>18.8941314690616</v>
       </c>
       <c r="F52" t="n">
-        <v>1.868951035126932</v>
+        <v>1.868951035126933</v>
       </c>
       <c r="G52" t="n">
-        <v>0.4667675582714153</v>
+        <v>0.4667675582714197</v>
       </c>
       <c r="H52" t="inlineStr"/>
       <c r="I52" t="n">
@@ -2144,13 +2132,13 @@
         <v>478.5</v>
       </c>
       <c r="E53" t="n">
-        <v>23.90738035987672</v>
+        <v>23.9073803598767</v>
       </c>
       <c r="F53" t="n">
-        <v>1.868951035126932</v>
+        <v>1.868951035126933</v>
       </c>
       <c r="G53" t="n">
-        <v>0.4667675582714153</v>
+        <v>0.4667675582714197</v>
       </c>
       <c r="H53" t="inlineStr"/>
       <c r="I53" t="n">
@@ -2175,13 +2163,13 @@
         <v>481.5</v>
       </c>
       <c r="E54" t="n">
-        <v>20.90607911535645</v>
+        <v>20.90607911535646</v>
       </c>
       <c r="F54" t="n">
-        <v>0.8363571031746303</v>
+        <v>0.8363571031746306</v>
       </c>
       <c r="G54" t="n">
-        <v>0.3169657494272787</v>
+        <v>0.3169657494272692</v>
       </c>
       <c r="H54" t="n">
         <v>133.7901506552612</v>
@@ -2208,13 +2196,13 @@
         <v>481.5</v>
       </c>
       <c r="E55" t="n">
-        <v>23.24438395171631</v>
+        <v>23.24438395171632</v>
       </c>
       <c r="F55" t="n">
-        <v>0.8363571031746303</v>
+        <v>0.8363571031746306</v>
       </c>
       <c r="G55" t="n">
-        <v>0.3169657494272787</v>
+        <v>0.3169657494272692</v>
       </c>
       <c r="H55" t="n">
         <v>104.6209105722526</v>
@@ -2244,13 +2232,13 @@
         <v>22.06880276333557</v>
       </c>
       <c r="F56" t="n">
-        <v>0.8363571031746303</v>
+        <v>0.8363571031746306</v>
       </c>
       <c r="G56" t="n">
-        <v>0.3169657494272787</v>
+        <v>0.3169657494272692</v>
       </c>
       <c r="H56" t="n">
-        <v>57.88386653164184</v>
+        <v>57.8838665316419</v>
       </c>
       <c r="I56" t="n">
         <v>1</v>
@@ -2274,13 +2262,13 @@
         <v>481.5</v>
       </c>
       <c r="E57" t="n">
-        <v>33.71035482262113</v>
+        <v>33.71035482262112</v>
       </c>
       <c r="F57" t="n">
-        <v>0.8363571031746303</v>
+        <v>0.8363571031746306</v>
       </c>
       <c r="G57" t="n">
-        <v>0.3169657494272787</v>
+        <v>0.3169657494272692</v>
       </c>
       <c r="H57" t="n">
         <v>55.8317149165353</v>
@@ -2307,13 +2295,13 @@
         <v>481.5</v>
       </c>
       <c r="E58" t="n">
-        <v>28.21791762943959</v>
+        <v>28.21791762943958</v>
       </c>
       <c r="F58" t="n">
-        <v>0.8363571031746303</v>
+        <v>0.8363571031746306</v>
       </c>
       <c r="G58" t="n">
-        <v>0.3169657494272787</v>
+        <v>0.3169657494272692</v>
       </c>
       <c r="H58" t="n">
         <v>15.18575795195346</v>
@@ -2340,13 +2328,13 @@
         <v>481.5</v>
       </c>
       <c r="E59" t="n">
-        <v>18.63516022028481</v>
+        <v>18.63516022028482</v>
       </c>
       <c r="F59" t="n">
-        <v>0.8363571031746303</v>
+        <v>0.8363571031746306</v>
       </c>
       <c r="G59" t="n">
-        <v>0.3169657494272787</v>
+        <v>0.3169657494272692</v>
       </c>
       <c r="H59" t="n">
         <v>238.0280011047593</v>
@@ -2373,13 +2361,13 @@
         <v>481.5</v>
       </c>
       <c r="E60" t="n">
-        <v>22.29724992008123</v>
+        <v>22.29724992008122</v>
       </c>
       <c r="F60" t="n">
-        <v>0.8363571031746303</v>
+        <v>0.8363571031746306</v>
       </c>
       <c r="G60" t="n">
-        <v>0.3169657494272787</v>
+        <v>0.3169657494272692</v>
       </c>
       <c r="H60" t="n">
         <v>308.6716971776825</v>
@@ -2406,13 +2394,13 @@
         <v>481.5</v>
       </c>
       <c r="E61" t="n">
-        <v>23.69284904889784</v>
+        <v>23.69284904889783</v>
       </c>
       <c r="F61" t="n">
-        <v>0.8363571031746303</v>
+        <v>0.8363571031746306</v>
       </c>
       <c r="G61" t="n">
-        <v>0.3169657494272787</v>
+        <v>0.3169657494272692</v>
       </c>
       <c r="H61" t="n">
         <v>342.7945061999638</v>
@@ -2439,13 +2427,13 @@
         <v>481.5</v>
       </c>
       <c r="E62" t="n">
-        <v>36.59326964434836</v>
+        <v>36.59326964434835</v>
       </c>
       <c r="F62" t="n">
-        <v>0.8363571031746303</v>
+        <v>0.8363571031746306</v>
       </c>
       <c r="G62" t="n">
-        <v>0.3169657494272787</v>
+        <v>0.3169657494272692</v>
       </c>
       <c r="H62" t="n">
         <v>327.4130986474507</v>
@@ -2472,13 +2460,13 @@
         <v>481.9</v>
       </c>
       <c r="E63" t="n">
-        <v>28.30084091899367</v>
+        <v>28.30084091899366</v>
       </c>
       <c r="F63" t="n">
-        <v>0.8535811689563254</v>
+        <v>0.8535811689563259</v>
       </c>
       <c r="G63" t="n">
-        <v>0.2486059090019156</v>
+        <v>0.2486059090019244</v>
       </c>
       <c r="H63" t="n">
         <v>14.94213082913541</v>
@@ -2508,13 +2496,13 @@
         <v>20.73783426178843</v>
       </c>
       <c r="F64" t="n">
-        <v>1.032208668939235</v>
+        <v>1.032208668939236</v>
       </c>
       <c r="G64" t="n">
-        <v>0.373067563677073</v>
+        <v>0.37306756367708</v>
       </c>
       <c r="H64" t="n">
-        <v>133.7653436477757</v>
+        <v>133.7653436477758</v>
       </c>
       <c r="I64" t="n">
         <v>1</v>
@@ -2541,10 +2529,10 @@
         <v>23.10202441216586</v>
       </c>
       <c r="F65" t="n">
-        <v>1.032208668939235</v>
+        <v>1.032208668939236</v>
       </c>
       <c r="G65" t="n">
-        <v>0.373067563677073</v>
+        <v>0.37306756367708</v>
       </c>
       <c r="H65" t="n">
         <v>104.3980909908807</v>
@@ -2574,10 +2562,10 @@
         <v>22.03716215779435</v>
       </c>
       <c r="F66" t="n">
-        <v>1.032208668939235</v>
+        <v>1.032208668939236</v>
       </c>
       <c r="G66" t="n">
-        <v>0.373067563677073</v>
+        <v>0.37306756367708</v>
       </c>
       <c r="H66" t="n">
         <v>57.453910054517</v>
@@ -2604,13 +2592,13 @@
         <v>482</v>
       </c>
       <c r="E67" t="n">
-        <v>33.68444723837086</v>
+        <v>33.68444723837085</v>
       </c>
       <c r="F67" t="n">
-        <v>1.032208668939235</v>
+        <v>1.032208668939236</v>
       </c>
       <c r="G67" t="n">
-        <v>0.373067563677073</v>
+        <v>0.37306756367708</v>
       </c>
       <c r="H67" t="n">
         <v>55.54864409427717</v>
@@ -2637,16 +2625,16 @@
         <v>482</v>
       </c>
       <c r="E68" t="n">
-        <v>28.30671346860208</v>
+        <v>28.30671346860207</v>
       </c>
       <c r="F68" t="n">
-        <v>1.032208668939235</v>
+        <v>1.032208668939236</v>
       </c>
       <c r="G68" t="n">
-        <v>0.373067563677073</v>
+        <v>0.37306756367708</v>
       </c>
       <c r="H68" t="n">
-        <v>14.89547364799552</v>
+        <v>14.89547364799557</v>
       </c>
       <c r="I68" t="n">
         <v>1</v>
@@ -2670,13 +2658,13 @@
         <v>482</v>
       </c>
       <c r="E69" t="n">
-        <v>18.66856892870221</v>
+        <v>18.66856892870222</v>
       </c>
       <c r="F69" t="n">
-        <v>1.032208668939235</v>
+        <v>1.032208668939236</v>
       </c>
       <c r="G69" t="n">
-        <v>0.373067563677073</v>
+        <v>0.37306756367708</v>
       </c>
       <c r="H69" t="n">
         <v>238.5352909530305</v>
@@ -2703,16 +2691,16 @@
         <v>482</v>
       </c>
       <c r="E70" t="n">
-        <v>22.46403754543184</v>
+        <v>22.46403754543183</v>
       </c>
       <c r="F70" t="n">
-        <v>1.032208668939235</v>
+        <v>1.032208668939236</v>
       </c>
       <c r="G70" t="n">
-        <v>0.373067563677073</v>
+        <v>0.37306756367708</v>
       </c>
       <c r="H70" t="n">
-        <v>308.7327908650489</v>
+        <v>308.7327908650488</v>
       </c>
       <c r="I70" t="n">
         <v>1</v>
@@ -2736,13 +2724,13 @@
         <v>482</v>
       </c>
       <c r="E71" t="n">
-        <v>23.84446236586783</v>
+        <v>23.84446236586782</v>
       </c>
       <c r="F71" t="n">
-        <v>1.032208668939235</v>
+        <v>1.032208668939236</v>
       </c>
       <c r="G71" t="n">
-        <v>0.373067563677073</v>
+        <v>0.37306756367708</v>
       </c>
       <c r="H71" t="n">
         <v>342.6173494649419</v>
@@ -2769,13 +2757,13 @@
         <v>482</v>
       </c>
       <c r="E72" t="n">
-        <v>36.75891087370903</v>
+        <v>36.75891087370902</v>
       </c>
       <c r="F72" t="n">
-        <v>1.032208668939235</v>
+        <v>1.032208668939236</v>
       </c>
       <c r="G72" t="n">
-        <v>0.373067563677073</v>
+        <v>0.37306756367708</v>
       </c>
       <c r="H72" t="n">
         <v>327.3649331180678</v>
@@ -2805,10 +2793,10 @@
         <v>23.07067703184158</v>
       </c>
       <c r="F73" t="n">
-        <v>1.20755858531102</v>
+        <v>1.207558585311021</v>
       </c>
       <c r="G73" t="n">
-        <v>0.4708605431562736</v>
+        <v>0.4708605431562824</v>
       </c>
       <c r="H73" t="n">
         <v>104.2851528049034</v>
@@ -2835,13 +2823,13 @@
         <v>482.2</v>
       </c>
       <c r="E74" t="n">
-        <v>11.55786410938609</v>
+        <v>11.5578641093861</v>
       </c>
       <c r="F74" t="n">
-        <v>1.375716985626095</v>
+        <v>1.375716985626096</v>
       </c>
       <c r="G74" t="n">
-        <v>0.5305871504059239</v>
+        <v>0.530587150405935</v>
       </c>
       <c r="H74" t="inlineStr"/>
       <c r="I74" t="n">
@@ -2866,13 +2854,13 @@
         <v>482.2</v>
       </c>
       <c r="E75" t="n">
-        <v>13.40559926997768</v>
+        <v>13.40559926997767</v>
       </c>
       <c r="F75" t="n">
-        <v>1.375716985626095</v>
+        <v>1.375716985626096</v>
       </c>
       <c r="G75" t="n">
-        <v>0.5305871504059239</v>
+        <v>0.530587150405935</v>
       </c>
       <c r="H75" t="inlineStr"/>
       <c r="I75" t="n">
@@ -2897,13 +2885,13 @@
         <v>482.2</v>
       </c>
       <c r="E76" t="n">
-        <v>13.74803099687372</v>
+        <v>13.74803099687371</v>
       </c>
       <c r="F76" t="n">
-        <v>1.375716985626095</v>
+        <v>1.375716985626096</v>
       </c>
       <c r="G76" t="n">
-        <v>0.5305871504059239</v>
+        <v>0.530587150405935</v>
       </c>
       <c r="H76" t="inlineStr"/>
       <c r="I76" t="n">
@@ -2928,13 +2916,13 @@
         <v>482.2</v>
       </c>
       <c r="E77" t="n">
-        <v>23.47127147255535</v>
+        <v>23.47127147255534</v>
       </c>
       <c r="F77" t="n">
-        <v>1.375716985626095</v>
+        <v>1.375716985626096</v>
       </c>
       <c r="G77" t="n">
-        <v>0.5305871504059239</v>
+        <v>0.530587150405935</v>
       </c>
       <c r="H77" t="inlineStr"/>
       <c r="I77" t="n">
@@ -2959,13 +2947,13 @@
         <v>482.2</v>
       </c>
       <c r="E78" t="n">
-        <v>29.5425202105875</v>
+        <v>29.54252021058749</v>
       </c>
       <c r="F78" t="n">
-        <v>1.375716985626095</v>
+        <v>1.375716985626096</v>
       </c>
       <c r="G78" t="n">
-        <v>0.5305871504059239</v>
+        <v>0.530587150405935</v>
       </c>
       <c r="H78" t="inlineStr"/>
       <c r="I78" t="n">
@@ -2990,13 +2978,13 @@
         <v>482.2</v>
       </c>
       <c r="E79" t="n">
-        <v>20.63985779840225</v>
+        <v>20.63985779840226</v>
       </c>
       <c r="F79" t="n">
-        <v>1.375716985626095</v>
+        <v>1.375716985626096</v>
       </c>
       <c r="G79" t="n">
-        <v>0.5305871504059239</v>
+        <v>0.530587150405935</v>
       </c>
       <c r="H79" t="n">
         <v>133.4132475672204</v>
@@ -3026,13 +3014,13 @@
         <v>23.07904611964515</v>
       </c>
       <c r="F80" t="n">
-        <v>1.375716985626095</v>
+        <v>1.375716985626096</v>
       </c>
       <c r="G80" t="n">
-        <v>0.5305871504059239</v>
+        <v>0.530587150405935</v>
       </c>
       <c r="H80" t="n">
-        <v>104.0039119256677</v>
+        <v>104.0039119256678</v>
       </c>
       <c r="I80" t="n">
         <v>1</v>
@@ -3059,13 +3047,13 @@
         <v>22.13747399248892</v>
       </c>
       <c r="F81" t="n">
-        <v>1.375716985626095</v>
+        <v>1.375716985626096</v>
       </c>
       <c r="G81" t="n">
-        <v>0.5305871504059239</v>
+        <v>0.530587150405935</v>
       </c>
       <c r="H81" t="n">
-        <v>57.12886586752984</v>
+        <v>57.1288658675299</v>
       </c>
       <c r="I81" t="n">
         <v>1</v>
@@ -3092,10 +3080,10 @@
         <v>33.78874393728236</v>
       </c>
       <c r="F82" t="n">
-        <v>1.375716985626095</v>
+        <v>1.375716985626096</v>
       </c>
       <c r="G82" t="n">
-        <v>0.5305871504059239</v>
+        <v>0.530587150405935</v>
       </c>
       <c r="H82" t="n">
         <v>55.34143754606151</v>
@@ -3122,13 +3110,13 @@
         <v>482.2</v>
       </c>
       <c r="E83" t="n">
-        <v>28.46529034690224</v>
+        <v>28.46529034690223</v>
       </c>
       <c r="F83" t="n">
-        <v>1.375716985626095</v>
+        <v>1.375716985626096</v>
       </c>
       <c r="G83" t="n">
-        <v>0.5305871504059239</v>
+        <v>0.530587150405935</v>
       </c>
       <c r="H83" t="n">
         <v>14.84535038088848</v>
@@ -3155,16 +3143,16 @@
         <v>482.2</v>
       </c>
       <c r="E84" t="n">
-        <v>18.57143861973627</v>
+        <v>18.57143861973628</v>
       </c>
       <c r="F84" t="n">
-        <v>1.375716985626095</v>
+        <v>1.375716985626096</v>
       </c>
       <c r="G84" t="n">
-        <v>0.5305871504059239</v>
+        <v>0.530587150405935</v>
       </c>
       <c r="H84" t="n">
-        <v>238.9285010975935</v>
+        <v>238.9285010975934</v>
       </c>
       <c r="I84" t="n">
         <v>1</v>
@@ -3191,10 +3179,10 @@
         <v>22.55130219512326</v>
       </c>
       <c r="F85" t="n">
-        <v>1.375716985626095</v>
+        <v>1.375716985626096</v>
       </c>
       <c r="G85" t="n">
-        <v>0.5305871504059239</v>
+        <v>0.530587150405935</v>
       </c>
       <c r="H85" t="n">
         <v>309.0757242950069</v>
@@ -3221,13 +3209,13 @@
         <v>482.2</v>
       </c>
       <c r="E86" t="n">
-        <v>23.99190719369076</v>
+        <v>23.99190719369075</v>
       </c>
       <c r="F86" t="n">
-        <v>1.375716985626095</v>
+        <v>1.375716985626096</v>
       </c>
       <c r="G86" t="n">
-        <v>0.5305871504059239</v>
+        <v>0.530587150405935</v>
       </c>
       <c r="H86" t="n">
         <v>342.7692949318885</v>
@@ -3254,13 +3242,13 @@
         <v>482.2</v>
       </c>
       <c r="E87" t="n">
-        <v>36.88447870118347</v>
+        <v>36.88447870118346</v>
       </c>
       <c r="F87" t="n">
-        <v>1.375716985626095</v>
+        <v>1.375716985626096</v>
       </c>
       <c r="G87" t="n">
-        <v>0.5305871504059239</v>
+        <v>0.530587150405935</v>
       </c>
       <c r="H87" t="n">
         <v>327.5205055625799</v>
@@ -3290,10 +3278,10 @@
         <v>13.39667329560325</v>
       </c>
       <c r="F88" t="n">
-        <v>1.538291490633286</v>
+        <v>1.538291490633287</v>
       </c>
       <c r="G88" t="n">
-        <v>0.5396734574155135</v>
+        <v>0.5396734574155237</v>
       </c>
       <c r="H88" t="inlineStr"/>
       <c r="I88" t="n">
@@ -3318,13 +3306,13 @@
         <v>482.4</v>
       </c>
       <c r="E89" t="n">
-        <v>29.95834270574075</v>
+        <v>29.95834270574074</v>
       </c>
       <c r="F89" t="n">
-        <v>1.646085468121057</v>
+        <v>1.646085468121058</v>
       </c>
       <c r="G89" t="n">
-        <v>0.5053269988499057</v>
+        <v>0.5053269988499126</v>
       </c>
       <c r="H89" t="inlineStr"/>
       <c r="I89" t="n">
@@ -3349,13 +3337,13 @@
         <v>482.6</v>
       </c>
       <c r="E90" t="n">
-        <v>10.69126608630006</v>
+        <v>10.69126608630007</v>
       </c>
       <c r="F90" t="n">
-        <v>1.927836781024824</v>
+        <v>1.927836781024825</v>
       </c>
       <c r="G90" t="n">
-        <v>0.5640036702996589</v>
+        <v>0.5640036702996662</v>
       </c>
       <c r="H90" t="inlineStr"/>
       <c r="I90" t="n">
@@ -3380,13 +3368,13 @@
         <v>482.6</v>
       </c>
       <c r="E91" t="n">
-        <v>13.40914089020684</v>
+        <v>13.40914089020683</v>
       </c>
       <c r="F91" t="n">
-        <v>1.927836781024824</v>
+        <v>1.927836781024825</v>
       </c>
       <c r="G91" t="n">
-        <v>0.5640036702996589</v>
+        <v>0.5640036702996662</v>
       </c>
       <c r="H91" t="inlineStr"/>
       <c r="I91" t="n">
@@ -3411,13 +3399,13 @@
         <v>482.6</v>
       </c>
       <c r="E92" t="n">
-        <v>14.56105891840808</v>
+        <v>14.56105891840807</v>
       </c>
       <c r="F92" t="n">
-        <v>1.927836781024824</v>
+        <v>1.927836781024825</v>
       </c>
       <c r="G92" t="n">
-        <v>0.5640036702996589</v>
+        <v>0.5640036702996662</v>
       </c>
       <c r="H92" t="inlineStr"/>
       <c r="I92" t="n">
@@ -3442,13 +3430,13 @@
         <v>482.6</v>
       </c>
       <c r="E93" t="n">
-        <v>24.10752813054061</v>
+        <v>24.1075281305406</v>
       </c>
       <c r="F93" t="n">
-        <v>1.927836781024824</v>
+        <v>1.927836781024825</v>
       </c>
       <c r="G93" t="n">
-        <v>0.5640036702996589</v>
+        <v>0.5640036702996662</v>
       </c>
       <c r="H93" t="inlineStr"/>
       <c r="I93" t="n">
@@ -3473,13 +3461,13 @@
         <v>488.9</v>
       </c>
       <c r="E94" t="n">
-        <v>14.66954673566903</v>
+        <v>14.66954673566902</v>
       </c>
       <c r="F94" t="n">
-        <v>1.287848736592751</v>
+        <v>1.287848736592752</v>
       </c>
       <c r="G94" t="n">
-        <v>1.267301538357044</v>
+        <v>1.267301538357042</v>
       </c>
       <c r="H94" t="n">
         <v>71.1096553597875</v>
@@ -3509,10 +3497,10 @@
         <v>25.12012652366757</v>
       </c>
       <c r="F95" t="n">
-        <v>1.287848736592751</v>
+        <v>1.287848736592752</v>
       </c>
       <c r="G95" t="n">
-        <v>1.267301538357044</v>
+        <v>1.267301538357042</v>
       </c>
       <c r="H95" t="n">
         <v>57.8984294903189</v>
@@ -3542,10 +3530,10 @@
         <v>22.74661326445493</v>
       </c>
       <c r="F96" t="n">
-        <v>1.287848736592751</v>
+        <v>1.287848736592752</v>
       </c>
       <c r="G96" t="n">
-        <v>1.267301538357044</v>
+        <v>1.267301538357042</v>
       </c>
       <c r="H96" t="n">
         <v>17.86856123855381</v>
@@ -3575,10 +3563,10 @@
         <v>35.54427181051184</v>
       </c>
       <c r="F97" t="n">
-        <v>1.287848736592751</v>
+        <v>1.287848736592752</v>
       </c>
       <c r="G97" t="n">
-        <v>1.267301538357044</v>
+        <v>1.267301538357042</v>
       </c>
       <c r="H97" t="n">
         <v>29.45668403856541</v>
@@ -3608,10 +3596,10 @@
         <v>19.41932769318595</v>
       </c>
       <c r="F98" t="n">
-        <v>1.287848736592751</v>
+        <v>1.287848736592752</v>
       </c>
       <c r="G98" t="n">
-        <v>1.267301538357044</v>
+        <v>1.267301538357042</v>
       </c>
       <c r="H98" t="n">
         <v>298.7799700309647</v>
@@ -3641,13 +3629,13 @@
         <v>21.71549873639937</v>
       </c>
       <c r="F99" t="n">
-        <v>1.287848736592751</v>
+        <v>1.287848736592752</v>
       </c>
       <c r="G99" t="n">
-        <v>1.267301538357044</v>
+        <v>1.267301538357042</v>
       </c>
       <c r="H99" t="n">
-        <v>341.9719835904699</v>
+        <v>341.9719835904698</v>
       </c>
       <c r="I99" t="n">
         <v>1</v>
@@ -3674,10 +3662,10 @@
         <v>38.0211347879584</v>
       </c>
       <c r="F100" t="n">
-        <v>1.287848736592751</v>
+        <v>1.287848736592752</v>
       </c>
       <c r="G100" t="n">
-        <v>1.267301538357044</v>
+        <v>1.267301538357042</v>
       </c>
       <c r="H100" t="n">
         <v>330.676358241945</v>
@@ -3710,7 +3698,7 @@
         <v>1.469651081991791</v>
       </c>
       <c r="G101" t="n">
-        <v>1.349932170353145</v>
+        <v>1.349932170353143</v>
       </c>
       <c r="H101" t="n">
         <v>69.49058336901771</v>
@@ -3743,7 +3731,7 @@
         <v>1.469651081991791</v>
       </c>
       <c r="G102" t="n">
-        <v>1.349932170353145</v>
+        <v>1.349932170353143</v>
       </c>
       <c r="H102" t="n">
         <v>56.93396512547889</v>
@@ -3770,13 +3758,13 @@
         <v>489.1</v>
       </c>
       <c r="E103" t="n">
-        <v>23.02164866918861</v>
+        <v>23.0216486691886</v>
       </c>
       <c r="F103" t="n">
         <v>1.469651081991791</v>
       </c>
       <c r="G103" t="n">
-        <v>1.349932170353145</v>
+        <v>1.349932170353143</v>
       </c>
       <c r="H103" t="n">
         <v>17.06419922273255</v>
@@ -3809,7 +3797,7 @@
         <v>1.469651081991791</v>
       </c>
       <c r="G104" t="n">
-        <v>1.349932170353145</v>
+        <v>1.349932170353143</v>
       </c>
       <c r="H104" t="n">
         <v>28.86143011596533</v>
@@ -3842,7 +3830,7 @@
         <v>1.469651081991791</v>
       </c>
       <c r="G105" t="n">
-        <v>1.349932170353145</v>
+        <v>1.349932170353143</v>
       </c>
       <c r="H105" t="n">
         <v>299.3783177691982</v>
@@ -3875,7 +3863,7 @@
         <v>1.469651081991791</v>
       </c>
       <c r="G106" t="n">
-        <v>1.349932170353145</v>
+        <v>1.349932170353143</v>
       </c>
       <c r="H106" t="n">
         <v>341.7081776762602</v>
@@ -3908,7 +3896,7 @@
         <v>1.469651081991791</v>
       </c>
       <c r="G107" t="n">
-        <v>1.349932170353145</v>
+        <v>1.349932170353143</v>
       </c>
       <c r="H107" t="n">
         <v>330.6472875050372</v>
@@ -3935,13 +3923,13 @@
         <v>493.1</v>
       </c>
       <c r="E108" t="n">
-        <v>18.95471440698904</v>
+        <v>18.95471440698903</v>
       </c>
       <c r="F108" t="n">
-        <v>0.3841216179500924</v>
+        <v>0.3841216179500925</v>
       </c>
       <c r="G108" t="n">
-        <v>0.4936339235364541</v>
+        <v>0.4936339235364577</v>
       </c>
       <c r="H108" t="n">
         <v>37.36016174669368</v>
@@ -3971,10 +3959,10 @@
         <v>23.53281403354972</v>
       </c>
       <c r="F109" t="n">
-        <v>0.3841216179500924</v>
+        <v>0.3841216179500925</v>
       </c>
       <c r="G109" t="n">
-        <v>0.4936339235364541</v>
+        <v>0.4936339235364577</v>
       </c>
       <c r="H109" t="n">
         <v>353.1719032514777</v>
@@ -4004,10 +3992,10 @@
         <v>33.56165314050959</v>
       </c>
       <c r="F110" t="n">
-        <v>0.3841216179500924</v>
+        <v>0.3841216179500925</v>
       </c>
       <c r="G110" t="n">
-        <v>0.4936339235364541</v>
+        <v>0.4936339235364577</v>
       </c>
       <c r="H110" t="n">
         <v>13.26722165403316</v>
@@ -4037,13 +4025,13 @@
         <v>28.99272826013112</v>
       </c>
       <c r="F111" t="n">
-        <v>0.3841216179500924</v>
+        <v>0.3841216179500925</v>
       </c>
       <c r="G111" t="n">
-        <v>0.4936339235364541</v>
+        <v>0.4936339235364577</v>
       </c>
       <c r="H111" t="n">
-        <v>292.4376967911836</v>
+        <v>292.4376967911835</v>
       </c>
       <c r="I111" t="n">
         <v>1</v>
@@ -4067,13 +4055,13 @@
         <v>493.1</v>
       </c>
       <c r="E112" t="n">
-        <v>27.79230587376751</v>
+        <v>27.79230587376752</v>
       </c>
       <c r="F112" t="n">
-        <v>0.3841216179500924</v>
+        <v>0.3841216179500925</v>
       </c>
       <c r="G112" t="n">
-        <v>0.4936339235364541</v>
+        <v>0.4936339235364577</v>
       </c>
       <c r="H112" t="n">
         <v>323.5862756682913</v>
@@ -4103,10 +4091,10 @@
         <v>19.03579422610053</v>
       </c>
       <c r="F113" t="n">
-        <v>0.3067760547763279</v>
+        <v>0.3067760547763284</v>
       </c>
       <c r="G113" t="n">
-        <v>0.6054512777350793</v>
+        <v>0.6054512777350818</v>
       </c>
       <c r="H113" t="n">
         <v>35.1911451533897</v>
@@ -4136,13 +4124,13 @@
         <v>24.08792184815721</v>
       </c>
       <c r="F114" t="n">
-        <v>0.3067760547763279</v>
+        <v>0.3067760547763284</v>
       </c>
       <c r="G114" t="n">
-        <v>0.6054512777350793</v>
+        <v>0.6054512777350818</v>
       </c>
       <c r="H114" t="n">
-        <v>352.0548424030948</v>
+        <v>352.0548424030947</v>
       </c>
       <c r="I114" t="n">
         <v>1</v>
@@ -4169,10 +4157,10 @@
         <v>33.92317581520486</v>
       </c>
       <c r="F115" t="n">
-        <v>0.3067760547763279</v>
+        <v>0.3067760547763284</v>
       </c>
       <c r="G115" t="n">
-        <v>0.6054512777350793</v>
+        <v>0.6054512777350818</v>
       </c>
       <c r="H115" t="n">
         <v>12.20282468151788</v>
@@ -4199,16 +4187,16 @@
         <v>493.6</v>
       </c>
       <c r="E116" t="n">
-        <v>29.67257920687662</v>
+        <v>29.67257920687663</v>
       </c>
       <c r="F116" t="n">
-        <v>0.3067760547763279</v>
+        <v>0.3067760547763284</v>
       </c>
       <c r="G116" t="n">
-        <v>0.6054512777350793</v>
+        <v>0.6054512777350818</v>
       </c>
       <c r="H116" t="n">
-        <v>292.9217733735815</v>
+        <v>292.9217733735814</v>
       </c>
       <c r="I116" t="n">
         <v>1</v>
@@ -4232,13 +4220,13 @@
         <v>493.6</v>
       </c>
       <c r="E117" t="n">
-        <v>28.50323576591578</v>
+        <v>28.50323576591579</v>
       </c>
       <c r="F117" t="n">
-        <v>0.3067760547763279</v>
+        <v>0.3067760547763284</v>
       </c>
       <c r="G117" t="n">
-        <v>0.6054512777350793</v>
+        <v>0.6054512777350818</v>
       </c>
       <c r="H117" t="n">
         <v>323.3117658338113</v>
@@ -4265,13 +4253,13 @@
         <v>494</v>
       </c>
       <c r="E118" t="n">
-        <v>24.4668540662934</v>
+        <v>24.46685406629341</v>
       </c>
       <c r="F118" t="n">
-        <v>0.5435919395252031</v>
+        <v>0.5435919395252032</v>
       </c>
       <c r="G118" t="n">
-        <v>0.3514294158389075</v>
+        <v>0.3514294158389066</v>
       </c>
       <c r="H118" t="inlineStr"/>
       <c r="I118" t="n">
@@ -4299,10 +4287,10 @@
         <v>24.94375607943649</v>
       </c>
       <c r="F119" t="n">
-        <v>0.5435919395252031</v>
+        <v>0.5435919395252032</v>
       </c>
       <c r="G119" t="n">
-        <v>0.3514294158389075</v>
+        <v>0.3514294158389066</v>
       </c>
       <c r="H119" t="inlineStr"/>
       <c r="I119" t="n">
@@ -4330,10 +4318,10 @@
         <v>18.60756433081292</v>
       </c>
       <c r="F120" t="n">
-        <v>0.640356420688205</v>
+        <v>0.6403564206882054</v>
       </c>
       <c r="G120" t="n">
-        <v>0.3325233326922711</v>
+        <v>0.3325233326922695</v>
       </c>
       <c r="H120" t="n">
         <v>34.90756550742606</v>
@@ -4363,10 +4351,10 @@
         <v>23.84095350558762</v>
       </c>
       <c r="F121" t="n">
-        <v>0.640356420688205</v>
+        <v>0.6403564206882054</v>
       </c>
       <c r="G121" t="n">
-        <v>0.3325233326922711</v>
+        <v>0.3325233326922695</v>
       </c>
       <c r="H121" t="n">
         <v>351.1892615877128</v>
@@ -4396,10 +4384,10 @@
         <v>33.56565848335216</v>
       </c>
       <c r="F122" t="n">
-        <v>0.640356420688205</v>
+        <v>0.6403564206882054</v>
       </c>
       <c r="G122" t="n">
-        <v>0.3325233326922711</v>
+        <v>0.3325233326922695</v>
       </c>
       <c r="H122" t="n">
         <v>11.77246900561306</v>
@@ -4426,13 +4414,13 @@
         <v>494.1</v>
       </c>
       <c r="E123" t="n">
-        <v>29.85628987038114</v>
+        <v>29.85628987038115</v>
       </c>
       <c r="F123" t="n">
-        <v>0.640356420688205</v>
+        <v>0.6403564206882054</v>
       </c>
       <c r="G123" t="n">
-        <v>0.3325233326922711</v>
+        <v>0.3325233326922695</v>
       </c>
       <c r="H123" t="n">
         <v>292.1558560159805</v>
@@ -4459,16 +4447,16 @@
         <v>494.1</v>
       </c>
       <c r="E124" t="n">
-        <v>28.46084326420071</v>
+        <v>28.46084326420072</v>
       </c>
       <c r="F124" t="n">
-        <v>0.640356420688205</v>
+        <v>0.6403564206882054</v>
       </c>
       <c r="G124" t="n">
-        <v>0.3325233326922711</v>
+        <v>0.3325233326922695</v>
       </c>
       <c r="H124" t="n">
-        <v>322.4342997022272</v>
+        <v>322.4342997022271</v>
       </c>
       <c r="I124" t="n">
         <v>1</v>
@@ -4492,13 +4480,13 @@
         <v>494.5</v>
       </c>
       <c r="E125" t="n">
-        <v>24.58672252128206</v>
+        <v>24.58672252128207</v>
       </c>
       <c r="F125" t="n">
-        <v>0.7617148967029592</v>
+        <v>0.7617148967029593</v>
       </c>
       <c r="G125" t="n">
-        <v>0.350136699300713</v>
+        <v>0.3501366993007068</v>
       </c>
       <c r="H125" t="inlineStr"/>
       <c r="I125" t="n">
@@ -4523,13 +4511,13 @@
         <v>494.5</v>
       </c>
       <c r="E126" t="n">
-        <v>24.91605914968146</v>
+        <v>24.91605914968147</v>
       </c>
       <c r="F126" t="n">
-        <v>0.7617148967029592</v>
+        <v>0.7617148967029593</v>
       </c>
       <c r="G126" t="n">
-        <v>0.350136699300713</v>
+        <v>0.3501366993007068</v>
       </c>
       <c r="H126" t="inlineStr"/>
       <c r="I126" t="n">
@@ -4557,10 +4545,10 @@
         <v>18.18094658998797</v>
       </c>
       <c r="F127" t="n">
-        <v>0.7778113873489794</v>
+        <v>0.7778113873489795</v>
       </c>
       <c r="G127" t="n">
-        <v>0.4976135725272782</v>
+        <v>0.497613572527272</v>
       </c>
       <c r="H127" t="n">
         <v>35.20553834499077</v>
@@ -4587,13 +4575,13 @@
         <v>494.6</v>
       </c>
       <c r="E128" t="n">
-        <v>23.46818827339487</v>
+        <v>23.46818827339488</v>
       </c>
       <c r="F128" t="n">
-        <v>0.7778113873489794</v>
+        <v>0.7778113873489795</v>
       </c>
       <c r="G128" t="n">
-        <v>0.4976135725272782</v>
+        <v>0.497613572527272</v>
       </c>
       <c r="H128" t="n">
         <v>350.6358449642129</v>
@@ -4623,13 +4611,13 @@
         <v>33.13607191363835</v>
       </c>
       <c r="F129" t="n">
-        <v>0.7778113873489794</v>
+        <v>0.7778113873489795</v>
       </c>
       <c r="G129" t="n">
-        <v>0.4976135725272782</v>
+        <v>0.497613572527272</v>
       </c>
       <c r="H129" t="n">
-        <v>11.63281395716319</v>
+        <v>11.63281395716314</v>
       </c>
       <c r="I129" t="n">
         <v>1</v>
@@ -4653,13 +4641,13 @@
         <v>494.6</v>
       </c>
       <c r="E130" t="n">
-        <v>29.86149126251642</v>
+        <v>29.86149126251643</v>
       </c>
       <c r="F130" t="n">
-        <v>0.7778113873489794</v>
+        <v>0.7778113873489795</v>
       </c>
       <c r="G130" t="n">
-        <v>0.4976135725272782</v>
+        <v>0.497613572527272</v>
       </c>
       <c r="H130" t="n">
         <v>291.3169522682211</v>
@@ -4689,10 +4677,10 @@
         <v>28.24466802072088</v>
       </c>
       <c r="F131" t="n">
-        <v>0.7778113873489794</v>
+        <v>0.7778113873489795</v>
       </c>
       <c r="G131" t="n">
-        <v>0.4976135725272782</v>
+        <v>0.497613572527272</v>
       </c>
       <c r="H131" t="n">
         <v>321.6663219708577</v>
@@ -4725,7 +4713,7 @@
         <v>1.216448040112905</v>
       </c>
       <c r="G132" t="n">
-        <v>0.8094423892612015</v>
+        <v>0.8094423892611941</v>
       </c>
       <c r="H132" t="inlineStr"/>
       <c r="I132" t="n">
@@ -4756,7 +4744,7 @@
         <v>1.350099961345194</v>
       </c>
       <c r="G133" t="n">
-        <v>0.84415590848528</v>
+        <v>0.8441559084852734</v>
       </c>
       <c r="H133" t="inlineStr"/>
       <c r="I133" t="n">
@@ -4781,13 +4769,13 @@
         <v>495</v>
       </c>
       <c r="E134" t="n">
-        <v>24.500575419146</v>
+        <v>24.50057541914601</v>
       </c>
       <c r="F134" t="n">
         <v>1.350099961345194</v>
       </c>
       <c r="G134" t="n">
-        <v>0.84415590848528</v>
+        <v>0.8441559084852734</v>
       </c>
       <c r="H134" t="inlineStr"/>
       <c r="I134" t="n">
@@ -4815,13 +4803,13 @@
         <v>17.50451090525755</v>
       </c>
       <c r="F135" t="n">
-        <v>1.474287787516881</v>
+        <v>1.474287787516882</v>
       </c>
       <c r="G135" t="n">
-        <v>0.8241322598369778</v>
+        <v>0.8241322598369721</v>
       </c>
       <c r="H135" t="n">
-        <v>35.20148204067465</v>
+        <v>35.20148204067459</v>
       </c>
       <c r="I135" t="n">
         <v>1</v>
@@ -4848,10 +4836,10 @@
         <v>22.99208621713783</v>
       </c>
       <c r="F136" t="n">
-        <v>1.474287787516881</v>
+        <v>1.474287787516882</v>
       </c>
       <c r="G136" t="n">
-        <v>0.8241322598369778</v>
+        <v>0.8241322598369721</v>
       </c>
       <c r="H136" t="n">
         <v>349.4506019315439</v>
@@ -4881,10 +4869,10 @@
         <v>32.51771286355748</v>
       </c>
       <c r="F137" t="n">
-        <v>1.474287787516881</v>
+        <v>1.474287787516882</v>
       </c>
       <c r="G137" t="n">
-        <v>0.8241322598369778</v>
+        <v>0.8241322598369721</v>
       </c>
       <c r="H137" t="n">
         <v>11.15416272967161</v>
@@ -4911,13 +4899,13 @@
         <v>495.1</v>
       </c>
       <c r="E138" t="n">
-        <v>30.03223563874052</v>
+        <v>30.03223563874053</v>
       </c>
       <c r="F138" t="n">
-        <v>1.474287787516881</v>
+        <v>1.474287787516882</v>
       </c>
       <c r="G138" t="n">
-        <v>0.8241322598369778</v>
+        <v>0.8241322598369721</v>
       </c>
       <c r="H138" t="n">
         <v>290.0646386143543</v>
@@ -4944,13 +4932,13 @@
         <v>495.1</v>
       </c>
       <c r="E139" t="n">
-        <v>28.06168967739725</v>
+        <v>28.06168967739726</v>
       </c>
       <c r="F139" t="n">
-        <v>1.474287787516881</v>
+        <v>1.474287787516882</v>
       </c>
       <c r="G139" t="n">
-        <v>0.8241322598369778</v>
+        <v>0.8241322598369721</v>
       </c>
       <c r="H139" t="n">
         <v>320.3409615039532</v>
@@ -4983,7 +4971,7 @@
         <v>1.808425757148384</v>
       </c>
       <c r="G140" t="n">
-        <v>0.7102619347989289</v>
+        <v>0.7102619347989235</v>
       </c>
       <c r="H140" t="inlineStr"/>
       <c r="I140" t="n">
@@ -5014,7 +5002,7 @@
         <v>1.808425757148384</v>
       </c>
       <c r="G141" t="n">
-        <v>0.7102619347989289</v>
+        <v>0.7102619347989235</v>
       </c>
       <c r="H141" t="inlineStr"/>
       <c r="I141" t="n">
@@ -5039,13 +5027,13 @@
         <v>508.3</v>
       </c>
       <c r="E142" t="n">
-        <v>32.28036968715606</v>
+        <v>32.2803696871561</v>
       </c>
       <c r="F142" t="n">
-        <v>0.693618886047114</v>
+        <v>0.6936188860471141</v>
       </c>
       <c r="G142" t="n">
-        <v>0.3724075774265043</v>
+        <v>0.3724075774265252</v>
       </c>
       <c r="H142" t="n">
         <v>279.2192307965988</v>
@@ -5072,13 +5060,13 @@
         <v>508.3</v>
       </c>
       <c r="E143" t="n">
-        <v>28.0734334437972</v>
+        <v>28.07343344379723</v>
       </c>
       <c r="F143" t="n">
-        <v>0.693618886047114</v>
+        <v>0.6936188860471141</v>
       </c>
       <c r="G143" t="n">
-        <v>0.3724075774265043</v>
+        <v>0.3724075774265252</v>
       </c>
       <c r="H143" t="n">
         <v>299.3774311756819</v>
@@ -5105,13 +5093,13 @@
         <v>508.7</v>
       </c>
       <c r="E144" t="n">
-        <v>9.802838542534346</v>
+        <v>9.802838542534337</v>
       </c>
       <c r="F144" t="n">
-        <v>0.7624385138333061</v>
+        <v>0.7624385138333066</v>
       </c>
       <c r="G144" t="n">
-        <v>0.2357637531709909</v>
+        <v>0.2357637531709994</v>
       </c>
       <c r="H144" t="inlineStr"/>
       <c r="I144" t="n">
@@ -5139,10 +5127,10 @@
         <v>16.02941273859059</v>
       </c>
       <c r="F145" t="n">
-        <v>0.7624385138333061</v>
+        <v>0.7624385138333066</v>
       </c>
       <c r="G145" t="n">
-        <v>0.2357637531709909</v>
+        <v>0.2357637531709994</v>
       </c>
       <c r="H145" t="inlineStr"/>
       <c r="I145" t="n">
@@ -5167,13 +5155,13 @@
         <v>508.7</v>
       </c>
       <c r="E146" t="n">
-        <v>26.66308133646042</v>
+        <v>26.66308133646041</v>
       </c>
       <c r="F146" t="n">
-        <v>0.7624385138333061</v>
+        <v>0.7624385138333066</v>
       </c>
       <c r="G146" t="n">
-        <v>0.2357637531709909</v>
+        <v>0.2357637531709994</v>
       </c>
       <c r="H146" t="inlineStr"/>
       <c r="I146" t="n">
@@ -5198,13 +5186,13 @@
         <v>508.8</v>
       </c>
       <c r="E147" t="n">
-        <v>32.5811258842803</v>
+        <v>32.58112588428033</v>
       </c>
       <c r="F147" t="n">
         <v>1.041050332705881</v>
       </c>
       <c r="G147" t="n">
-        <v>0.1985587827022128</v>
+        <v>0.1985587827022239</v>
       </c>
       <c r="H147" t="n">
         <v>279.269799331768</v>
@@ -5231,16 +5219,16 @@
         <v>508.8</v>
       </c>
       <c r="E148" t="n">
-        <v>28.3657679600512</v>
+        <v>28.36576796005123</v>
       </c>
       <c r="F148" t="n">
         <v>1.041050332705881</v>
       </c>
       <c r="G148" t="n">
-        <v>0.1985587827022128</v>
+        <v>0.1985587827022239</v>
       </c>
       <c r="H148" t="n">
-        <v>299.2226143587871</v>
+        <v>299.222614358787</v>
       </c>
       <c r="I148" t="n">
         <v>1</v>
@@ -5264,13 +5252,13 @@
         <v>509.2</v>
       </c>
       <c r="E149" t="n">
-        <v>9.941706860659149</v>
+        <v>9.941706860659137</v>
       </c>
       <c r="F149" t="n">
         <v>1.18805963368034</v>
       </c>
       <c r="G149" t="n">
-        <v>0.1368536457991937</v>
+        <v>0.1368536457992151</v>
       </c>
       <c r="H149" t="inlineStr"/>
       <c r="I149" t="n">
@@ -5301,7 +5289,7 @@
         <v>1.18805963368034</v>
       </c>
       <c r="G150" t="n">
-        <v>0.1368536457991937</v>
+        <v>0.1368536457992151</v>
       </c>
       <c r="H150" t="inlineStr"/>
       <c r="I150" t="n">
@@ -5326,13 +5314,13 @@
         <v>509.2</v>
       </c>
       <c r="E151" t="n">
-        <v>26.86449274410515</v>
+        <v>26.86449274410514</v>
       </c>
       <c r="F151" t="n">
         <v>1.18805963368034</v>
       </c>
       <c r="G151" t="n">
-        <v>0.1368536457991937</v>
+        <v>0.1368536457992151</v>
       </c>
       <c r="H151" t="inlineStr"/>
       <c r="I151" t="n">
@@ -5357,13 +5345,13 @@
         <v>509.3</v>
       </c>
       <c r="E152" t="n">
-        <v>33.08959976379777</v>
+        <v>33.08959976379779</v>
       </c>
       <c r="F152" t="n">
         <v>1.106931806431469</v>
       </c>
       <c r="G152" t="n">
-        <v>0.1134330201213349</v>
+        <v>0.1134330201213506</v>
       </c>
       <c r="H152" t="n">
         <v>279.8403784151168</v>
@@ -5390,16 +5378,16 @@
         <v>509.3</v>
       </c>
       <c r="E153" t="n">
-        <v>28.95494731989802</v>
+        <v>28.95494731989805</v>
       </c>
       <c r="F153" t="n">
         <v>1.106931806431469</v>
       </c>
       <c r="G153" t="n">
-        <v>0.1134330201213349</v>
+        <v>0.1134330201213506</v>
       </c>
       <c r="H153" t="n">
-        <v>299.4932790019222</v>
+        <v>299.4932790019221</v>
       </c>
       <c r="I153" t="n">
         <v>1</v>
@@ -5423,13 +5411,13 @@
         <v>509.7</v>
       </c>
       <c r="E154" t="n">
-        <v>9.923264535508906</v>
+        <v>9.92326453550889</v>
       </c>
       <c r="F154" t="n">
-        <v>0.694609777326611</v>
+        <v>0.6946097773266113</v>
       </c>
       <c r="G154" t="n">
-        <v>0.03708754890952765</v>
+        <v>0.0370875489095473</v>
       </c>
       <c r="H154" t="inlineStr"/>
       <c r="I154" t="n">
@@ -5454,13 +5442,13 @@
         <v>509.7</v>
       </c>
       <c r="E155" t="n">
-        <v>16.74502942058774</v>
+        <v>16.74502942058775</v>
       </c>
       <c r="F155" t="n">
-        <v>0.694609777326611</v>
+        <v>0.6946097773266113</v>
       </c>
       <c r="G155" t="n">
-        <v>0.03708754890952765</v>
+        <v>0.0370875489095473</v>
       </c>
       <c r="H155" t="inlineStr"/>
       <c r="I155" t="n">
@@ -5485,13 +5473,13 @@
         <v>509.7</v>
       </c>
       <c r="E156" t="n">
-        <v>26.86744302437458</v>
+        <v>26.86744302437457</v>
       </c>
       <c r="F156" t="n">
-        <v>0.694609777326611</v>
+        <v>0.6946097773266113</v>
       </c>
       <c r="G156" t="n">
-        <v>0.03708754890952765</v>
+        <v>0.0370875489095473</v>
       </c>
       <c r="H156" t="inlineStr"/>
       <c r="I156" t="n">
@@ -5516,16 +5504,16 @@
         <v>509.8</v>
       </c>
       <c r="E157" t="n">
-        <v>33.32727092554415</v>
+        <v>33.32727092554418</v>
       </c>
       <c r="F157" t="n">
         <v>0.598639043114917</v>
       </c>
       <c r="G157" t="n">
-        <v>0.1336178658726526</v>
+        <v>0.1336178658726302</v>
       </c>
       <c r="H157" t="n">
-        <v>280.0815821922206</v>
+        <v>280.0815821922205</v>
       </c>
       <c r="I157" t="n">
         <v>1</v>
@@ -5549,13 +5537,13 @@
         <v>509.8</v>
       </c>
       <c r="E158" t="n">
-        <v>29.22572828371743</v>
+        <v>29.22572828371745</v>
       </c>
       <c r="F158" t="n">
         <v>0.598639043114917</v>
       </c>
       <c r="G158" t="n">
-        <v>0.1336178658726526</v>
+        <v>0.1336178658726302</v>
       </c>
       <c r="H158" t="n">
         <v>299.5957978327932</v>
@@ -5582,13 +5570,13 @@
         <v>510.2</v>
       </c>
       <c r="E159" t="n">
-        <v>10.09189119440125</v>
+        <v>10.09189119440123</v>
       </c>
       <c r="F159" t="n">
         <v>0.6880974848992392</v>
       </c>
       <c r="G159" t="n">
-        <v>0.2888563509935925</v>
+        <v>0.288856350993571</v>
       </c>
       <c r="H159" t="inlineStr"/>
       <c r="I159" t="n">
@@ -5613,13 +5601,13 @@
         <v>510.2</v>
       </c>
       <c r="E160" t="n">
-        <v>17.00701221364092</v>
+        <v>17.00701221364093</v>
       </c>
       <c r="F160" t="n">
         <v>0.6880974848992392</v>
       </c>
       <c r="G160" t="n">
-        <v>0.2888563509935925</v>
+        <v>0.288856350993571</v>
       </c>
       <c r="H160" t="inlineStr"/>
       <c r="I160" t="n">
@@ -5644,13 +5632,13 @@
         <v>510.2</v>
       </c>
       <c r="E161" t="n">
-        <v>27.04412191651065</v>
+        <v>27.04412191651063</v>
       </c>
       <c r="F161" t="n">
         <v>0.6880974848992392</v>
       </c>
       <c r="G161" t="n">
-        <v>0.2888563509935925</v>
+        <v>0.288856350993571</v>
       </c>
       <c r="H161" t="inlineStr"/>
       <c r="I161" t="n">
@@ -5675,13 +5663,13 @@
         <v>510.3</v>
       </c>
       <c r="E162" t="n">
-        <v>33.7429751357474</v>
+        <v>33.74297513574744</v>
       </c>
       <c r="F162" t="n">
-        <v>0.5898368486750509</v>
+        <v>0.5898368486750512</v>
       </c>
       <c r="G162" t="n">
-        <v>0.2480700076951234</v>
+        <v>0.2480700076951003</v>
       </c>
       <c r="H162" t="n">
         <v>280.1953273208402</v>
@@ -5708,13 +5696,13 @@
         <v>510.3</v>
       </c>
       <c r="E163" t="n">
-        <v>29.63996440240709</v>
+        <v>29.63996440240712</v>
       </c>
       <c r="F163" t="n">
-        <v>0.5898368486750509</v>
+        <v>0.5898368486750512</v>
       </c>
       <c r="G163" t="n">
-        <v>0.2480700076951234</v>
+        <v>0.2480700076951003</v>
       </c>
       <c r="H163" t="n">
         <v>299.4494644778874</v>
@@ -5741,13 +5729,13 @@
         <v>510.7</v>
       </c>
       <c r="E164" t="n">
-        <v>10.18180362441354</v>
+        <v>10.18180362441353</v>
       </c>
       <c r="F164" t="n">
-        <v>0.9384571308326629</v>
+        <v>0.9384571308326634</v>
       </c>
       <c r="G164" t="n">
-        <v>0.2629254130113457</v>
+        <v>0.2629254130113327</v>
       </c>
       <c r="H164" t="inlineStr"/>
       <c r="I164" t="n">
@@ -5772,13 +5760,13 @@
         <v>510.7</v>
       </c>
       <c r="E165" t="n">
-        <v>17.49710091424855</v>
+        <v>17.49710091424856</v>
       </c>
       <c r="F165" t="n">
-        <v>0.9384571308326629</v>
+        <v>0.9384571308326634</v>
       </c>
       <c r="G165" t="n">
-        <v>0.2629254130113457</v>
+        <v>0.2629254130113327</v>
       </c>
       <c r="H165" t="inlineStr"/>
       <c r="I165" t="n">
@@ -5803,13 +5791,13 @@
         <v>510.7</v>
       </c>
       <c r="E166" t="n">
-        <v>27.13805228034369</v>
+        <v>27.13805228034368</v>
       </c>
       <c r="F166" t="n">
-        <v>0.9384571308326629</v>
+        <v>0.9384571308326634</v>
       </c>
       <c r="G166" t="n">
-        <v>0.2629254130113457</v>
+        <v>0.2629254130113327</v>
       </c>
       <c r="H166" t="inlineStr"/>
       <c r="I166" t="n">
@@ -5834,13 +5822,13 @@
         <v>510.8</v>
       </c>
       <c r="E167" t="n">
-        <v>34.43859886087621</v>
+        <v>34.43859886087624</v>
       </c>
       <c r="F167" t="n">
-        <v>1.064887675165683</v>
+        <v>1.064887675165684</v>
       </c>
       <c r="G167" t="n">
-        <v>0.3407786108713514</v>
+        <v>0.3407786108713354</v>
       </c>
       <c r="H167" t="n">
         <v>280.8236934570705</v>
@@ -5867,13 +5855,13 @@
         <v>510.8</v>
       </c>
       <c r="E168" t="n">
-        <v>30.41953617708261</v>
+        <v>30.41953617708263</v>
       </c>
       <c r="F168" t="n">
-        <v>1.064887675165683</v>
+        <v>1.064887675165684</v>
       </c>
       <c r="G168" t="n">
-        <v>0.3407786108713514</v>
+        <v>0.3407786108713354</v>
       </c>
       <c r="H168" t="n">
         <v>299.6902765787503</v>
@@ -5900,13 +5888,13 @@
         <v>511.2</v>
       </c>
       <c r="E169" t="n">
-        <v>10.32304418771065</v>
+        <v>10.32304418771064</v>
       </c>
       <c r="F169" t="n">
         <v>1.330172284526002</v>
       </c>
       <c r="G169" t="n">
-        <v>0.4163370164651042</v>
+        <v>0.4163370164650882</v>
       </c>
       <c r="H169" t="inlineStr"/>
       <c r="I169" t="n">
@@ -5931,13 +5919,13 @@
         <v>511.2</v>
       </c>
       <c r="E170" t="n">
-        <v>17.88803293957966</v>
+        <v>17.88803293957967</v>
       </c>
       <c r="F170" t="n">
         <v>1.330172284526002</v>
       </c>
       <c r="G170" t="n">
-        <v>0.4163370164651042</v>
+        <v>0.4163370164650882</v>
       </c>
       <c r="H170" t="inlineStr"/>
       <c r="I170" t="n">
@@ -5962,13 +5950,13 @@
         <v>511.2</v>
       </c>
       <c r="E171" t="n">
-        <v>27.25925096404464</v>
+        <v>27.25925096404463</v>
       </c>
       <c r="F171" t="n">
         <v>1.330172284526002</v>
       </c>
       <c r="G171" t="n">
-        <v>0.4163370164651042</v>
+        <v>0.4163370164650882</v>
       </c>
       <c r="H171" t="inlineStr"/>
       <c r="I171" t="n">
@@ -5993,13 +5981,13 @@
         <v>511.3</v>
       </c>
       <c r="E172" t="n">
-        <v>34.97664658513728</v>
+        <v>34.97664658513732</v>
       </c>
       <c r="F172" t="n">
         <v>1.271885742587652</v>
       </c>
       <c r="G172" t="n">
-        <v>0.3878150816115964</v>
+        <v>0.3878150816115746</v>
       </c>
       <c r="H172" t="n">
         <v>280.898276331355</v>
@@ -6026,13 +6014,13 @@
         <v>511.3</v>
       </c>
       <c r="E173" t="n">
-        <v>30.94364834287402</v>
+        <v>30.94364834287406</v>
       </c>
       <c r="F173" t="n">
         <v>1.271885742587652</v>
       </c>
       <c r="G173" t="n">
-        <v>0.3878150816115964</v>
+        <v>0.3878150816115746</v>
       </c>
       <c r="H173" t="n">
         <v>299.4479122182499</v>
@@ -6059,13 +6047,13 @@
         <v>511.6</v>
       </c>
       <c r="E174" t="n">
-        <v>35.34373550380908</v>
+        <v>35.34373550380909</v>
       </c>
       <c r="F174" t="n">
-        <v>1.467933778324328</v>
+        <v>1.467933778324329</v>
       </c>
       <c r="G174" t="n">
-        <v>0.4907707219992246</v>
+        <v>0.4907707219992105</v>
       </c>
       <c r="H174" t="n">
         <v>281.150050823781</v>
@@ -6092,16 +6080,16 @@
         <v>511.6</v>
       </c>
       <c r="E175" t="n">
-        <v>31.34076605134889</v>
+        <v>31.34076605134891</v>
       </c>
       <c r="F175" t="n">
-        <v>1.467933778324328</v>
+        <v>1.467933778324329</v>
       </c>
       <c r="G175" t="n">
-        <v>0.4907707219992246</v>
+        <v>0.4907707219992105</v>
       </c>
       <c r="H175" t="n">
-        <v>299.5037982779102</v>
+        <v>299.5037982779101</v>
       </c>
       <c r="I175" t="n">
         <v>1</v>
@@ -6128,10 +6116,10 @@
         <v>10.42632760718104</v>
       </c>
       <c r="F176" t="n">
-        <v>1.601108585026289</v>
+        <v>1.60110858502629</v>
       </c>
       <c r="G176" t="n">
-        <v>0.5394436319247611</v>
+        <v>0.539443631924745</v>
       </c>
       <c r="H176" t="inlineStr"/>
       <c r="I176" t="n">
@@ -6159,10 +6147,10 @@
         <v>18.22731886618008</v>
       </c>
       <c r="F177" t="n">
-        <v>1.601108585026289</v>
+        <v>1.60110858502629</v>
       </c>
       <c r="G177" t="n">
-        <v>0.5394436319247611</v>
+        <v>0.539443631924745</v>
       </c>
       <c r="H177" t="inlineStr"/>
       <c r="I177" t="n">
@@ -6187,13 +6175,13 @@
         <v>511.7</v>
       </c>
       <c r="E178" t="n">
-        <v>27.32530781127085</v>
+        <v>27.32530781127084</v>
       </c>
       <c r="F178" t="n">
-        <v>1.601108585026289</v>
+        <v>1.60110858502629</v>
       </c>
       <c r="G178" t="n">
-        <v>0.5394436319247611</v>
+        <v>0.539443631924745</v>
       </c>
       <c r="H178" t="inlineStr"/>
       <c r="I178" t="n">
@@ -6218,13 +6206,13 @@
         <v>512.1</v>
       </c>
       <c r="E179" t="n">
-        <v>10.10615987508557</v>
+        <v>10.10615987508556</v>
       </c>
       <c r="F179" t="n">
-        <v>1.918208752693482</v>
+        <v>1.918208752693483</v>
       </c>
       <c r="G179" t="n">
-        <v>0.4759644820656086</v>
+        <v>0.4759644820655839</v>
       </c>
       <c r="H179" t="inlineStr"/>
       <c r="I179" t="n">
@@ -6249,13 +6237,13 @@
         <v>512.1</v>
       </c>
       <c r="E180" t="n">
-        <v>18.11913278404953</v>
+        <v>18.11913278404954</v>
       </c>
       <c r="F180" t="n">
-        <v>1.918208752693482</v>
+        <v>1.918208752693483</v>
       </c>
       <c r="G180" t="n">
-        <v>0.4759644820656086</v>
+        <v>0.4759644820655839</v>
       </c>
       <c r="H180" t="inlineStr"/>
       <c r="I180" t="n">
@@ -6280,13 +6268,13 @@
         <v>512.1</v>
       </c>
       <c r="E181" t="n">
-        <v>26.96737471065853</v>
+        <v>26.96737471065852</v>
       </c>
       <c r="F181" t="n">
-        <v>1.918208752693482</v>
+        <v>1.918208752693483</v>
       </c>
       <c r="G181" t="n">
-        <v>0.4759644820656086</v>
+        <v>0.4759644820655839</v>
       </c>
       <c r="H181" t="inlineStr"/>
       <c r="I181" t="n">
@@ -6311,13 +6299,13 @@
         <v>514.5</v>
       </c>
       <c r="E182" t="n">
-        <v>35.63247398906228</v>
+        <v>35.63247398906229</v>
       </c>
       <c r="F182" t="n">
         <v>1.246784812868127</v>
       </c>
       <c r="G182" t="n">
-        <v>0.4165842300717407</v>
+        <v>0.4165842300717582</v>
       </c>
       <c r="H182" t="n">
         <v>295.0443824501922</v>
@@ -6344,16 +6332,16 @@
         <v>514.7</v>
       </c>
       <c r="E183" t="n">
-        <v>35.7199115747288</v>
+        <v>35.71991157472885</v>
       </c>
       <c r="F183" t="n">
-        <v>1.432919305639397</v>
+        <v>1.432919305639398</v>
       </c>
       <c r="G183" t="n">
-        <v>0.3424576842780848</v>
+        <v>0.3424576842780951</v>
       </c>
       <c r="H183" t="n">
-        <v>294.8300337985546</v>
+        <v>294.8300337985545</v>
       </c>
       <c r="I183" t="n">
         <v>1</v>
@@ -6377,13 +6365,13 @@
         <v>514.9</v>
       </c>
       <c r="E184" t="n">
-        <v>10.00341585638209</v>
+        <v>10.0034158563821</v>
       </c>
       <c r="F184" t="n">
         <v>1.604412901025261</v>
       </c>
       <c r="G184" t="n">
-        <v>0.2683907458179484</v>
+        <v>0.2683907458179609</v>
       </c>
       <c r="H184" t="inlineStr"/>
       <c r="I184" t="n">
@@ -6408,13 +6396,13 @@
         <v>514.9</v>
       </c>
       <c r="E185" t="n">
-        <v>19.61096710531254</v>
+        <v>19.61096710531255</v>
       </c>
       <c r="F185" t="n">
         <v>1.604412901025261</v>
       </c>
       <c r="G185" t="n">
-        <v>0.2683907458179484</v>
+        <v>0.2683907458179609</v>
       </c>
       <c r="H185" t="inlineStr"/>
       <c r="I185" t="n">
@@ -6445,7 +6433,7 @@
         <v>1.604412901025261</v>
       </c>
       <c r="G186" t="n">
-        <v>0.2683907458179484</v>
+        <v>0.2683907458179609</v>
       </c>
       <c r="H186" t="inlineStr"/>
       <c r="I186" t="n">
@@ -6470,13 +6458,13 @@
         <v>515.3</v>
       </c>
       <c r="E187" t="n">
-        <v>9.726973239793335</v>
+        <v>9.726973239793349</v>
       </c>
       <c r="F187" t="n">
         <v>1.129932636239952</v>
       </c>
       <c r="G187" t="n">
-        <v>0.2227224652842847</v>
+        <v>0.2227224652843112</v>
       </c>
       <c r="H187" t="inlineStr"/>
       <c r="I187" t="n">
@@ -6501,13 +6489,13 @@
         <v>515.3</v>
       </c>
       <c r="E188" t="n">
-        <v>19.48204264744495</v>
+        <v>19.48204264744497</v>
       </c>
       <c r="F188" t="n">
         <v>1.129932636239952</v>
       </c>
       <c r="G188" t="n">
-        <v>0.2227224652842847</v>
+        <v>0.2227224652843112</v>
       </c>
       <c r="H188" t="inlineStr"/>
       <c r="I188" t="n">
@@ -6532,13 +6520,13 @@
         <v>515.4</v>
       </c>
       <c r="E189" t="n">
-        <v>9.743106550131611</v>
+        <v>9.743106550131621</v>
       </c>
       <c r="F189" t="n">
         <v>1.131988894599647</v>
       </c>
       <c r="G189" t="n">
-        <v>0.2119824540712907</v>
+        <v>0.2119824540713185</v>
       </c>
       <c r="H189" t="inlineStr"/>
       <c r="I189" t="n">
@@ -6563,13 +6551,13 @@
         <v>515.4</v>
       </c>
       <c r="E190" t="n">
-        <v>19.51833789523107</v>
+        <v>19.51833789523109</v>
       </c>
       <c r="F190" t="n">
         <v>1.131988894599647</v>
       </c>
       <c r="G190" t="n">
-        <v>0.2119824540712907</v>
+        <v>0.2119824540713185</v>
       </c>
       <c r="H190" t="inlineStr"/>
       <c r="I190" t="n">
@@ -6600,7 +6588,7 @@
         <v>1.131988894599647</v>
       </c>
       <c r="G191" t="n">
-        <v>0.2119824540712907</v>
+        <v>0.2119824540713185</v>
       </c>
       <c r="H191" t="inlineStr"/>
       <c r="I191" t="n">
@@ -6625,13 +6613,13 @@
         <v>515.6</v>
       </c>
       <c r="E192" t="n">
-        <v>36.62016611418344</v>
+        <v>36.62016611418347</v>
       </c>
       <c r="F192" t="n">
-        <v>1.230264802262762</v>
+        <v>1.230264802262763</v>
       </c>
       <c r="G192" t="n">
-        <v>0.3206007126666144</v>
+        <v>0.3206007126666457</v>
       </c>
       <c r="H192" t="n">
         <v>293.0276750345291</v>
@@ -6658,13 +6646,13 @@
         <v>515.9</v>
       </c>
       <c r="E193" t="n">
-        <v>9.922163722349271</v>
+        <v>9.922163722349289</v>
       </c>
       <c r="F193" t="n">
-        <v>1.146960296415411</v>
+        <v>1.146960296415412</v>
       </c>
       <c r="G193" t="n">
-        <v>0.3414076470080005</v>
+        <v>0.3414076470080241</v>
       </c>
       <c r="H193" t="inlineStr"/>
       <c r="I193" t="n">
@@ -6689,13 +6677,13 @@
         <v>515.9</v>
       </c>
       <c r="E194" t="n">
-        <v>19.80994397783455</v>
+        <v>19.80994397783457</v>
       </c>
       <c r="F194" t="n">
-        <v>1.146960296415411</v>
+        <v>1.146960296415412</v>
       </c>
       <c r="G194" t="n">
-        <v>0.3414076470080005</v>
+        <v>0.3414076470080241</v>
       </c>
       <c r="H194" t="inlineStr"/>
       <c r="I194" t="n">
@@ -6723,10 +6711,10 @@
         <v>24.79245708099291</v>
       </c>
       <c r="F195" t="n">
-        <v>1.146960296415411</v>
+        <v>1.146960296415412</v>
       </c>
       <c r="G195" t="n">
-        <v>0.3414076470080005</v>
+        <v>0.3414076470080241</v>
       </c>
       <c r="H195" t="inlineStr"/>
       <c r="I195" t="n">
@@ -6751,13 +6739,13 @@
         <v>516.1</v>
       </c>
       <c r="E196" t="n">
-        <v>36.81879072028442</v>
+        <v>36.81879072028444</v>
       </c>
       <c r="F196" t="n">
-        <v>0.9444551998036526</v>
+        <v>0.9444551998036527</v>
       </c>
       <c r="G196" t="n">
-        <v>0.2091264846009752</v>
+        <v>0.2091264846009967</v>
       </c>
       <c r="H196" t="n">
         <v>292.2989302804914</v>
@@ -6784,13 +6772,13 @@
         <v>516.4</v>
       </c>
       <c r="E197" t="n">
-        <v>9.755012154846838</v>
+        <v>9.755012154846851</v>
       </c>
       <c r="F197" t="n">
-        <v>0.7886862998960201</v>
+        <v>0.7886862998960206</v>
       </c>
       <c r="G197" t="n">
-        <v>0.07942280522209867</v>
+        <v>0.07942280522208939</v>
       </c>
       <c r="H197" t="inlineStr"/>
       <c r="I197" t="n">
@@ -6815,13 +6803,13 @@
         <v>516.4</v>
       </c>
       <c r="E198" t="n">
-        <v>19.6646603096487</v>
+        <v>19.66466030964872</v>
       </c>
       <c r="F198" t="n">
-        <v>0.7886862998960201</v>
+        <v>0.7886862998960206</v>
       </c>
       <c r="G198" t="n">
-        <v>0.07942280522209867</v>
+        <v>0.07942280522208939</v>
       </c>
       <c r="H198" t="inlineStr"/>
       <c r="I198" t="n">
@@ -6849,10 +6837,10 @@
         <v>24.56651749537098</v>
       </c>
       <c r="F199" t="n">
-        <v>0.7886862998960201</v>
+        <v>0.7886862998960206</v>
       </c>
       <c r="G199" t="n">
-        <v>0.07942280522209867</v>
+        <v>0.07942280522208939</v>
       </c>
       <c r="H199" t="inlineStr"/>
       <c r="I199" t="n">
@@ -6877,13 +6865,13 @@
         <v>516.6</v>
       </c>
       <c r="E200" t="n">
-        <v>36.96163240173752</v>
+        <v>36.96163240173757</v>
       </c>
       <c r="F200" t="n">
-        <v>0.9897355682319974</v>
+        <v>0.9897355682319978</v>
       </c>
       <c r="G200" t="n">
-        <v>0.1157850811177956</v>
+        <v>0.1157850811177677</v>
       </c>
       <c r="H200" t="n">
         <v>292.1071623426192</v>
@@ -6910,13 +6898,13 @@
         <v>516.9</v>
       </c>
       <c r="E201" t="n">
-        <v>9.856812870002852</v>
+        <v>9.856812870002864</v>
       </c>
       <c r="F201" t="n">
-        <v>0.9443705903634826</v>
+        <v>0.9443705903634828</v>
       </c>
       <c r="G201" t="n">
-        <v>0.1173810906532101</v>
+        <v>0.1173810906531871</v>
       </c>
       <c r="H201" t="inlineStr"/>
       <c r="I201" t="n">
@@ -6941,13 +6929,13 @@
         <v>516.9</v>
       </c>
       <c r="E202" t="n">
-        <v>19.81016047310003</v>
+        <v>19.81016047310004</v>
       </c>
       <c r="F202" t="n">
-        <v>0.9443705903634826</v>
+        <v>0.9443705903634828</v>
       </c>
       <c r="G202" t="n">
-        <v>0.1173810906532101</v>
+        <v>0.1173810906531871</v>
       </c>
       <c r="H202" t="inlineStr"/>
       <c r="I202" t="n">
@@ -6975,10 +6963,10 @@
         <v>24.44754815866154</v>
       </c>
       <c r="F203" t="n">
-        <v>0.9443705903634826</v>
+        <v>0.9443705903634828</v>
       </c>
       <c r="G203" t="n">
-        <v>0.1173810906532101</v>
+        <v>0.1173810906531871</v>
       </c>
       <c r="H203" t="inlineStr"/>
       <c r="I203" t="n">
@@ -7003,13 +6991,13 @@
         <v>517.1</v>
       </c>
       <c r="E204" t="n">
-        <v>37.29966591785222</v>
+        <v>37.29966591785227</v>
       </c>
       <c r="F204" t="n">
-        <v>0.6695676188099534</v>
+        <v>0.6695676188099536</v>
       </c>
       <c r="G204" t="n">
-        <v>0.1957406045421942</v>
+        <v>0.1957406045421645</v>
       </c>
       <c r="H204" t="n">
         <v>291.4595670578489</v>
@@ -7036,13 +7024,13 @@
         <v>517.4</v>
       </c>
       <c r="E205" t="n">
-        <v>9.981411981919271</v>
+        <v>9.981411981919297</v>
       </c>
       <c r="F205" t="n">
         <v>1.078540783111634</v>
       </c>
       <c r="G205" t="n">
-        <v>0.142886371987926</v>
+        <v>0.1428863719879162</v>
       </c>
       <c r="H205" t="inlineStr"/>
       <c r="I205" t="n">
@@ -7067,13 +7055,13 @@
         <v>517.4</v>
       </c>
       <c r="E206" t="n">
-        <v>19.9965737652923</v>
+        <v>19.99657376529233</v>
       </c>
       <c r="F206" t="n">
         <v>1.078540783111634</v>
       </c>
       <c r="G206" t="n">
-        <v>0.142886371987926</v>
+        <v>0.1428863719879162</v>
       </c>
       <c r="H206" t="inlineStr"/>
       <c r="I206" t="n">
@@ -7104,7 +7092,7 @@
         <v>1.078540783111634</v>
       </c>
       <c r="G207" t="n">
-        <v>0.142886371987926</v>
+        <v>0.1428863719879162</v>
       </c>
       <c r="H207" t="inlineStr"/>
       <c r="I207" t="n">
@@ -7129,13 +7117,13 @@
         <v>517.6</v>
       </c>
       <c r="E208" t="n">
-        <v>37.95515087903354</v>
+        <v>37.95515087903355</v>
       </c>
       <c r="F208" t="n">
-        <v>1.311682068010421</v>
+        <v>1.311682068010422</v>
       </c>
       <c r="G208" t="n">
-        <v>0.1311149768352878</v>
+        <v>0.131114976835274</v>
       </c>
       <c r="H208" t="n">
         <v>290.9190268931831</v>
@@ -7162,13 +7150,13 @@
         <v>517.9</v>
       </c>
       <c r="E209" t="n">
-        <v>10.04800290258433</v>
+        <v>10.04800290258434</v>
       </c>
       <c r="F209" t="n">
         <v>1.241116634959176</v>
       </c>
       <c r="G209" t="n">
-        <v>0.357459439043407</v>
+        <v>0.3574594390433974</v>
       </c>
       <c r="H209" t="inlineStr"/>
       <c r="I209" t="n">
@@ -7193,13 +7181,13 @@
         <v>517.9</v>
       </c>
       <c r="E210" t="n">
-        <v>20.09213324615944</v>
+        <v>20.09213324615946</v>
       </c>
       <c r="F210" t="n">
         <v>1.241116634959176</v>
       </c>
       <c r="G210" t="n">
-        <v>0.357459439043407</v>
+        <v>0.3574594390433974</v>
       </c>
       <c r="H210" t="inlineStr"/>
       <c r="I210" t="n">
@@ -7224,13 +7212,13 @@
         <v>517.9</v>
       </c>
       <c r="E211" t="n">
-        <v>23.85137403346109</v>
+        <v>23.8513740334611</v>
       </c>
       <c r="F211" t="n">
         <v>1.241116634959176</v>
       </c>
       <c r="G211" t="n">
-        <v>0.357459439043407</v>
+        <v>0.3574594390433974</v>
       </c>
       <c r="H211" t="inlineStr"/>
       <c r="I211" t="n">
@@ -7258,10 +7246,10 @@
         <v>23.74467429463501</v>
       </c>
       <c r="F212" t="n">
-        <v>1.304879807380613</v>
+        <v>1.304879807380614</v>
       </c>
       <c r="G212" t="n">
-        <v>0.4344780317704718</v>
+        <v>0.4344780317704656</v>
       </c>
       <c r="H212" t="inlineStr"/>
       <c r="I212" t="n">
@@ -7286,13 +7274,13 @@
         <v>518.1</v>
       </c>
       <c r="E213" t="n">
-        <v>38.269877447742</v>
+        <v>38.26987744774203</v>
       </c>
       <c r="F213" t="n">
-        <v>1.304879807380613</v>
+        <v>1.304879807380614</v>
       </c>
       <c r="G213" t="n">
-        <v>0.4344780317704718</v>
+        <v>0.4344780317704656</v>
       </c>
       <c r="H213" t="n">
         <v>290.0820247894163</v>
@@ -7319,13 +7307,13 @@
         <v>518.4</v>
       </c>
       <c r="E214" t="n">
-        <v>10.41412474303522</v>
+        <v>10.41412474303523</v>
       </c>
       <c r="F214" t="n">
         <v>1.369219943926548</v>
       </c>
       <c r="G214" t="n">
-        <v>0.3025036181089544</v>
+        <v>0.3025036181089356</v>
       </c>
       <c r="H214" t="inlineStr"/>
       <c r="I214" t="n">
@@ -7350,13 +7338,13 @@
         <v>518.4</v>
       </c>
       <c r="E215" t="n">
-        <v>20.46618198443555</v>
+        <v>20.46618198443556</v>
       </c>
       <c r="F215" t="n">
         <v>1.369219943926548</v>
       </c>
       <c r="G215" t="n">
-        <v>0.3025036181089544</v>
+        <v>0.3025036181089356</v>
       </c>
       <c r="H215" t="inlineStr"/>
       <c r="I215" t="n">
@@ -7387,7 +7375,7 @@
         <v>1.369219943926548</v>
       </c>
       <c r="G216" t="n">
-        <v>0.3025036181089544</v>
+        <v>0.3025036181089356</v>
       </c>
       <c r="H216" t="inlineStr"/>
       <c r="I216" t="n">
@@ -7412,16 +7400,16 @@
         <v>518.6</v>
       </c>
       <c r="E217" t="n">
-        <v>38.69766609447942</v>
+        <v>38.69766609447944</v>
       </c>
       <c r="F217" t="n">
         <v>1.188349102492147</v>
       </c>
       <c r="G217" t="n">
-        <v>0.3736715392675004</v>
+        <v>0.3736715392674711</v>
       </c>
       <c r="H217" t="n">
-        <v>290.2402481956462</v>
+        <v>290.2402481956461</v>
       </c>
       <c r="I217" t="n">
         <v>1</v>
@@ -7445,13 +7433,13 @@
         <v>518.9</v>
       </c>
       <c r="E218" t="n">
-        <v>10.68375353259054</v>
+        <v>10.68375353259056</v>
       </c>
       <c r="F218" t="n">
-        <v>1.198733172336673</v>
+        <v>1.198733172336674</v>
       </c>
       <c r="G218" t="n">
-        <v>0.463107917780709</v>
+        <v>0.4631079177806931</v>
       </c>
       <c r="H218" t="inlineStr"/>
       <c r="I218" t="n">
@@ -7476,13 +7464,13 @@
         <v>518.9</v>
       </c>
       <c r="E219" t="n">
-        <v>20.74018096752894</v>
+        <v>20.74018096752897</v>
       </c>
       <c r="F219" t="n">
-        <v>1.198733172336673</v>
+        <v>1.198733172336674</v>
       </c>
       <c r="G219" t="n">
-        <v>0.463107917780709</v>
+        <v>0.4631079177806931</v>
       </c>
       <c r="H219" t="inlineStr"/>
       <c r="I219" t="n">
@@ -7510,10 +7498,10 @@
         <v>23.9825705996461</v>
       </c>
       <c r="F220" t="n">
-        <v>1.198733172336673</v>
+        <v>1.198733172336674</v>
       </c>
       <c r="G220" t="n">
-        <v>0.463107917780709</v>
+        <v>0.4631079177806931</v>
       </c>
       <c r="H220" t="inlineStr"/>
       <c r="I220" t="n">
@@ -7538,13 +7526,13 @@
         <v>519</v>
       </c>
       <c r="E221" t="n">
-        <v>39.21009700113343</v>
+        <v>39.21009700113348</v>
       </c>
       <c r="F221" t="n">
-        <v>1.373070084415629</v>
+        <v>1.37307008441563</v>
       </c>
       <c r="G221" t="n">
-        <v>0.4012626261290489</v>
+        <v>0.4012626261290246</v>
       </c>
       <c r="H221" t="n">
         <v>289.9090599667561</v>
@@ -7571,13 +7559,13 @@
         <v>519.4</v>
       </c>
       <c r="E222" t="n">
-        <v>11.33728512355492</v>
+        <v>11.33728512355495</v>
       </c>
       <c r="F222" t="n">
-        <v>1.701978193407471</v>
+        <v>1.701978193407472</v>
       </c>
       <c r="G222" t="n">
-        <v>0.3552567065384867</v>
+        <v>0.3552567065384765</v>
       </c>
       <c r="H222" t="inlineStr"/>
       <c r="I222" t="n">
@@ -7602,13 +7590,13 @@
         <v>519.4</v>
       </c>
       <c r="E223" t="n">
-        <v>21.38457647077315</v>
+        <v>21.38457647077318</v>
       </c>
       <c r="F223" t="n">
-        <v>1.701978193407471</v>
+        <v>1.701978193407472</v>
       </c>
       <c r="G223" t="n">
-        <v>0.3552567065384867</v>
+        <v>0.3552567065384765</v>
       </c>
       <c r="H223" t="inlineStr"/>
       <c r="I223" t="n">
@@ -7636,10 +7624,10 @@
         <v>23.98405632017896</v>
       </c>
       <c r="F224" t="n">
-        <v>1.701978193407471</v>
+        <v>1.701978193407472</v>
       </c>
       <c r="G224" t="n">
-        <v>0.3552567065384867</v>
+        <v>0.3552567065384765</v>
       </c>
       <c r="H224" t="inlineStr"/>
       <c r="I224" t="n">
@@ -7664,13 +7652,13 @@
         <v>519.7</v>
       </c>
       <c r="E225" t="n">
-        <v>11.89716937302449</v>
+        <v>11.89716937302454</v>
       </c>
       <c r="F225" t="n">
-        <v>1.97504152330001</v>
+        <v>1.975041523300011</v>
       </c>
       <c r="G225" t="n">
-        <v>0.1538829234909377</v>
+        <v>0.1538829234909329</v>
       </c>
       <c r="H225" t="inlineStr"/>
       <c r="I225" t="n">
@@ -7695,13 +7683,13 @@
         <v>519.7</v>
       </c>
       <c r="E226" t="n">
-        <v>21.93880528481607</v>
+        <v>21.93880528481611</v>
       </c>
       <c r="F226" t="n">
-        <v>1.97504152330001</v>
+        <v>1.975041523300011</v>
       </c>
       <c r="G226" t="n">
-        <v>0.1538829234909377</v>
+        <v>0.1538829234909329</v>
       </c>
       <c r="H226" t="inlineStr"/>
       <c r="I226" t="n">
@@ -7729,10 +7717,10 @@
         <v>24.30288410315154</v>
       </c>
       <c r="F227" t="n">
-        <v>1.97504152330001</v>
+        <v>1.975041523300011</v>
       </c>
       <c r="G227" t="n">
-        <v>0.1538829234909377</v>
+        <v>0.1538829234909329</v>
       </c>
       <c r="H227" t="inlineStr"/>
       <c r="I227" t="n">
@@ -7757,13 +7745,13 @@
         <v>522.3</v>
       </c>
       <c r="E228" t="n">
-        <v>14.73439968226416</v>
+        <v>14.73439968226421</v>
       </c>
       <c r="F228" t="n">
-        <v>0.4626184202929863</v>
+        <v>0.4626184202929864</v>
       </c>
       <c r="G228" t="n">
-        <v>0.6537615808138365</v>
+        <v>0.6537615808138572</v>
       </c>
       <c r="H228" t="inlineStr"/>
       <c r="I228" t="n">
@@ -7788,13 +7776,13 @@
         <v>522.3</v>
       </c>
       <c r="E229" t="n">
-        <v>24.70087280140453</v>
+        <v>24.70087280140458</v>
       </c>
       <c r="F229" t="n">
-        <v>0.4626184202929863</v>
+        <v>0.4626184202929864</v>
       </c>
       <c r="G229" t="n">
-        <v>0.6537615808138365</v>
+        <v>0.6537615808138572</v>
       </c>
       <c r="H229" t="inlineStr"/>
       <c r="I229" t="n">
@@ -7819,13 +7807,13 @@
         <v>522.3</v>
       </c>
       <c r="E230" t="n">
-        <v>25.657907937944</v>
+        <v>25.65790793794401</v>
       </c>
       <c r="F230" t="n">
-        <v>0.4626184202929863</v>
+        <v>0.4626184202929864</v>
       </c>
       <c r="G230" t="n">
-        <v>0.6537615808138365</v>
+        <v>0.6537615808138572</v>
       </c>
       <c r="H230" t="inlineStr"/>
       <c r="I230" t="n">
@@ -7850,13 +7838,13 @@
         <v>522.8</v>
       </c>
       <c r="E231" t="n">
-        <v>15.1167214865367</v>
+        <v>15.11672148653673</v>
       </c>
       <c r="F231" t="n">
-        <v>0.5641787789230926</v>
+        <v>0.564178778923093</v>
       </c>
       <c r="G231" t="n">
-        <v>0.4844674501896218</v>
+        <v>0.4844674501896451</v>
       </c>
       <c r="H231" t="inlineStr"/>
       <c r="I231" t="n">
@@ -7881,13 +7869,13 @@
         <v>522.8</v>
       </c>
       <c r="E232" t="n">
-        <v>25.11098621072607</v>
+        <v>25.1109862107261</v>
       </c>
       <c r="F232" t="n">
-        <v>0.5641787789230926</v>
+        <v>0.564178778923093</v>
       </c>
       <c r="G232" t="n">
-        <v>0.4844674501896218</v>
+        <v>0.4844674501896451</v>
       </c>
       <c r="H232" t="inlineStr"/>
       <c r="I232" t="n">
@@ -7912,13 +7900,13 @@
         <v>522.8</v>
       </c>
       <c r="E233" t="n">
-        <v>26.23492878400018</v>
+        <v>26.23492878400019</v>
       </c>
       <c r="F233" t="n">
-        <v>0.5641787789230926</v>
+        <v>0.564178778923093</v>
       </c>
       <c r="G233" t="n">
-        <v>0.4844674501896218</v>
+        <v>0.4844674501896451</v>
       </c>
       <c r="H233" t="inlineStr"/>
       <c r="I233" t="n">
@@ -7943,13 +7931,13 @@
         <v>523.3</v>
       </c>
       <c r="E234" t="n">
-        <v>15.33295705937467</v>
+        <v>15.33295705937469</v>
       </c>
       <c r="F234" t="n">
         <v>1.116519817329047</v>
       </c>
       <c r="G234" t="n">
-        <v>0.1202038512916023</v>
+        <v>0.1202038512916272</v>
       </c>
       <c r="H234" t="inlineStr"/>
       <c r="I234" t="n">
@@ -7974,13 +7962,13 @@
         <v>523.3</v>
       </c>
       <c r="E235" t="n">
-        <v>25.36102508538065</v>
+        <v>25.36102508538067</v>
       </c>
       <c r="F235" t="n">
         <v>1.116519817329047</v>
       </c>
       <c r="G235" t="n">
-        <v>0.1202038512916023</v>
+        <v>0.1202038512916272</v>
       </c>
       <c r="H235" t="inlineStr"/>
       <c r="I235" t="n">
@@ -8005,13 +7993,13 @@
         <v>523.3</v>
       </c>
       <c r="E236" t="n">
-        <v>26.83224467428195</v>
+        <v>26.83224467428196</v>
       </c>
       <c r="F236" t="n">
         <v>1.116519817329047</v>
       </c>
       <c r="G236" t="n">
-        <v>0.1202038512916023</v>
+        <v>0.1202038512916272</v>
       </c>
       <c r="H236" t="inlineStr"/>
       <c r="I236" t="n">
@@ -8036,13 +8024,13 @@
         <v>523.8</v>
       </c>
       <c r="E237" t="n">
-        <v>15.65589331895579</v>
+        <v>15.65589331895582</v>
       </c>
       <c r="F237" t="n">
         <v>1.48090893531768</v>
       </c>
       <c r="G237" t="n">
-        <v>0.1747751081331559</v>
+        <v>0.1747751081331871</v>
       </c>
       <c r="H237" t="inlineStr"/>
       <c r="I237" t="n">
@@ -8067,13 +8055,13 @@
         <v>523.8</v>
       </c>
       <c r="E238" t="n">
-        <v>25.69066175696068</v>
+        <v>25.6906617569607</v>
       </c>
       <c r="F238" t="n">
         <v>1.48090893531768</v>
       </c>
       <c r="G238" t="n">
-        <v>0.1747751081331559</v>
+        <v>0.1747751081331871</v>
       </c>
       <c r="H238" t="inlineStr"/>
       <c r="I238" t="n">
@@ -8098,13 +8086,13 @@
         <v>523.8</v>
       </c>
       <c r="E239" t="n">
-        <v>27.20710295267127</v>
+        <v>27.20710295267128</v>
       </c>
       <c r="F239" t="n">
         <v>1.48090893531768</v>
       </c>
       <c r="G239" t="n">
-        <v>0.1747751081331559</v>
+        <v>0.1747751081331871</v>
       </c>
       <c r="H239" t="inlineStr"/>
       <c r="I239" t="n">
@@ -8129,13 +8117,13 @@
         <v>524.3</v>
       </c>
       <c r="E240" t="n">
-        <v>15.85672277189093</v>
+        <v>15.85672277189096</v>
       </c>
       <c r="F240" t="n">
         <v>1.480095338401821</v>
       </c>
       <c r="G240" t="n">
-        <v>0.2934323763092364</v>
+        <v>0.2934323763092627</v>
       </c>
       <c r="H240" t="inlineStr"/>
       <c r="I240" t="n">
@@ -8160,13 +8148,13 @@
         <v>524.3</v>
       </c>
       <c r="E241" t="n">
-        <v>25.89541844215628</v>
+        <v>25.89541844215631</v>
       </c>
       <c r="F241" t="n">
         <v>1.480095338401821</v>
       </c>
       <c r="G241" t="n">
-        <v>0.2934323763092364</v>
+        <v>0.2934323763092627</v>
       </c>
       <c r="H241" t="inlineStr"/>
       <c r="I241" t="n">
@@ -8191,13 +8179,13 @@
         <v>524.3</v>
       </c>
       <c r="E242" t="n">
-        <v>27.44500298129683</v>
+        <v>27.44500298129685</v>
       </c>
       <c r="F242" t="n">
         <v>1.480095338401821</v>
       </c>
       <c r="G242" t="n">
-        <v>0.2934323763092364</v>
+        <v>0.2934323763092627</v>
       </c>
       <c r="H242" t="inlineStr"/>
       <c r="I242" t="n">
@@ -8222,13 +8210,13 @@
         <v>524.8</v>
       </c>
       <c r="E243" t="n">
-        <v>15.69916253630921</v>
+        <v>15.69916253630925</v>
       </c>
       <c r="F243" t="n">
         <v>1.114225198433921</v>
       </c>
       <c r="G243" t="n">
-        <v>0.1967615653565812</v>
+        <v>0.196761565356556</v>
       </c>
       <c r="H243" t="inlineStr"/>
       <c r="I243" t="n">
@@ -8253,13 +8241,13 @@
         <v>524.8</v>
       </c>
       <c r="E244" t="n">
-        <v>25.7536429963853</v>
+        <v>25.75364299638533</v>
       </c>
       <c r="F244" t="n">
         <v>1.114225198433921</v>
       </c>
       <c r="G244" t="n">
-        <v>0.1967615653565812</v>
+        <v>0.196761565356556</v>
       </c>
       <c r="H244" t="inlineStr"/>
       <c r="I244" t="n">
@@ -8284,13 +8272,13 @@
         <v>524.8</v>
       </c>
       <c r="E245" t="n">
-        <v>27.74572400997583</v>
+        <v>27.74572400997584</v>
       </c>
       <c r="F245" t="n">
         <v>1.114225198433921</v>
       </c>
       <c r="G245" t="n">
-        <v>0.1967615653565812</v>
+        <v>0.196761565356556</v>
       </c>
       <c r="H245" t="inlineStr"/>
       <c r="I245" t="n">
@@ -8315,13 +8303,13 @@
         <v>525.3</v>
       </c>
       <c r="E246" t="n">
-        <v>15.76765696191977</v>
+        <v>15.7676569619198</v>
       </c>
       <c r="F246" t="n">
-        <v>0.7031466436964647</v>
+        <v>0.7031466436964651</v>
       </c>
       <c r="G246" t="n">
-        <v>0.4314701173950568</v>
+        <v>0.4314701173950263</v>
       </c>
       <c r="H246" t="inlineStr"/>
       <c r="I246" t="n">
@@ -8346,13 +8334,13 @@
         <v>525.3</v>
       </c>
       <c r="E247" t="n">
-        <v>25.82427449027422</v>
+        <v>25.82427449027425</v>
       </c>
       <c r="F247" t="n">
-        <v>0.7031466436964647</v>
+        <v>0.7031466436964651</v>
       </c>
       <c r="G247" t="n">
-        <v>0.4314701173950568</v>
+        <v>0.4314701173950263</v>
       </c>
       <c r="H247" t="inlineStr"/>
       <c r="I247" t="n">
@@ -8377,13 +8365,13 @@
         <v>525.3</v>
       </c>
       <c r="E248" t="n">
-        <v>28.11084272640639</v>
+        <v>28.1108427264064</v>
       </c>
       <c r="F248" t="n">
-        <v>0.7031466436964647</v>
+        <v>0.7031466436964651</v>
       </c>
       <c r="G248" t="n">
-        <v>0.4314701173950568</v>
+        <v>0.4314701173950263</v>
       </c>
       <c r="H248" t="inlineStr"/>
       <c r="I248" t="n">
@@ -8408,13 +8396,13 @@
         <v>525.8</v>
       </c>
       <c r="E249" t="n">
-        <v>16.36666876599842</v>
+        <v>16.36666876599844</v>
       </c>
       <c r="F249" t="n">
-        <v>0.7001311704148182</v>
+        <v>0.7001311704148183</v>
       </c>
       <c r="G249" t="n">
-        <v>0.2801156178100674</v>
+        <v>0.280115617810043</v>
       </c>
       <c r="H249" t="inlineStr"/>
       <c r="I249" t="n">
@@ -8439,13 +8427,13 @@
         <v>525.8</v>
       </c>
       <c r="E250" t="n">
-        <v>26.42033785723497</v>
+        <v>26.42033785723499</v>
       </c>
       <c r="F250" t="n">
-        <v>0.7001311704148182</v>
+        <v>0.7001311704148183</v>
       </c>
       <c r="G250" t="n">
-        <v>0.2801156178100674</v>
+        <v>0.280115617810043</v>
       </c>
       <c r="H250" t="inlineStr"/>
       <c r="I250" t="n">
@@ -8473,10 +8461,10 @@
         <v>28.81811815090392</v>
       </c>
       <c r="F251" t="n">
-        <v>0.7001311704148182</v>
+        <v>0.7001311704148183</v>
       </c>
       <c r="G251" t="n">
-        <v>0.2801156178100674</v>
+        <v>0.280115617810043</v>
       </c>
       <c r="H251" t="inlineStr"/>
       <c r="I251" t="n">
@@ -8501,13 +8489,13 @@
         <v>526.3</v>
       </c>
       <c r="E252" t="n">
-        <v>16.96801371862253</v>
+        <v>16.96801371862255</v>
       </c>
       <c r="F252" t="n">
         <v>1.096561666271024</v>
       </c>
       <c r="G252" t="n">
-        <v>0.1466863541823226</v>
+        <v>0.1466863541823004</v>
       </c>
       <c r="H252" t="inlineStr"/>
       <c r="I252" t="n">
@@ -8532,13 +8520,13 @@
         <v>526.3</v>
       </c>
       <c r="E253" t="n">
-        <v>27.01931223094348</v>
+        <v>27.0193122309435</v>
       </c>
       <c r="F253" t="n">
         <v>1.096561666271024</v>
       </c>
       <c r="G253" t="n">
-        <v>0.1466863541823226</v>
+        <v>0.1466863541823004</v>
       </c>
       <c r="H253" t="inlineStr"/>
       <c r="I253" t="n">
@@ -8563,13 +8551,13 @@
         <v>526.3</v>
       </c>
       <c r="E254" t="n">
-        <v>29.42131620397973</v>
+        <v>29.42131620397974</v>
       </c>
       <c r="F254" t="n">
         <v>1.096561666271024</v>
       </c>
       <c r="G254" t="n">
-        <v>0.1466863541823226</v>
+        <v>0.1466863541823004</v>
       </c>
       <c r="H254" t="inlineStr"/>
       <c r="I254" t="n">
@@ -8594,13 +8582,13 @@
         <v>526.8</v>
       </c>
       <c r="E255" t="n">
-        <v>17.55068619087219</v>
+        <v>17.55068619087222</v>
       </c>
       <c r="F255" t="n">
-        <v>0.9683293080969476</v>
+        <v>0.9683293080969479</v>
       </c>
       <c r="G255" t="n">
-        <v>0.2835255751000161</v>
+        <v>0.2835255751000298</v>
       </c>
       <c r="H255" t="inlineStr"/>
       <c r="I255" t="n">
@@ -8625,13 +8613,13 @@
         <v>526.8</v>
       </c>
       <c r="E256" t="n">
-        <v>27.60280568527424</v>
+        <v>27.60280568527428</v>
       </c>
       <c r="F256" t="n">
-        <v>0.9683293080969476</v>
+        <v>0.9683293080969479</v>
       </c>
       <c r="G256" t="n">
-        <v>0.2835255751000161</v>
+        <v>0.2835255751000298</v>
       </c>
       <c r="H256" t="inlineStr"/>
       <c r="I256" t="n">
@@ -8656,13 +8644,13 @@
         <v>526.8</v>
       </c>
       <c r="E257" t="n">
-        <v>29.89821502043171</v>
+        <v>29.89821502043172</v>
       </c>
       <c r="F257" t="n">
-        <v>0.9683293080969476</v>
+        <v>0.9683293080969479</v>
       </c>
       <c r="G257" t="n">
-        <v>0.2835255751000161</v>
+        <v>0.2835255751000298</v>
       </c>
       <c r="H257" t="inlineStr"/>
       <c r="I257" t="n">
@@ -8687,13 +8675,13 @@
         <v>526.9</v>
       </c>
       <c r="E258" t="n">
-        <v>29.94046727589721</v>
+        <v>29.94046727589723</v>
       </c>
       <c r="F258" t="n">
-        <v>0.907011082768659</v>
+        <v>0.9070110827686595</v>
       </c>
       <c r="G258" t="n">
-        <v>0.3149842019441956</v>
+        <v>0.3149842019442043</v>
       </c>
       <c r="H258" t="inlineStr"/>
       <c r="I258" t="n">
@@ -8718,13 +8706,13 @@
         <v>527.3</v>
       </c>
       <c r="E259" t="n">
-        <v>17.90920371677484</v>
+        <v>17.90920371677487</v>
       </c>
       <c r="F259" t="n">
-        <v>0.7730084853062542</v>
+        <v>0.773008485306255</v>
       </c>
       <c r="G259" t="n">
-        <v>0.3142905918247521</v>
+        <v>0.3142905918247493</v>
       </c>
       <c r="H259" t="inlineStr"/>
       <c r="I259" t="n">
@@ -8749,13 +8737,13 @@
         <v>527.3</v>
       </c>
       <c r="E260" t="n">
-        <v>27.9511832582507</v>
+        <v>27.95118325825074</v>
       </c>
       <c r="F260" t="n">
-        <v>0.7730084853062542</v>
+        <v>0.773008485306255</v>
       </c>
       <c r="G260" t="n">
-        <v>0.3142905918247521</v>
+        <v>0.3142905918247493</v>
       </c>
       <c r="H260" t="inlineStr"/>
       <c r="I260" t="n">
@@ -8780,13 +8768,13 @@
         <v>527.8</v>
       </c>
       <c r="E261" t="n">
-        <v>18.35932773731122</v>
+        <v>18.35932773731125</v>
       </c>
       <c r="F261" t="n">
         <v>1.405177329488421</v>
       </c>
       <c r="G261" t="n">
-        <v>0.5041967085817787</v>
+        <v>0.5041967085817756</v>
       </c>
       <c r="H261" t="inlineStr"/>
       <c r="I261" t="n">
@@ -8811,13 +8799,13 @@
         <v>527.8</v>
       </c>
       <c r="E262" t="n">
-        <v>28.39219723741407</v>
+        <v>28.3921972374141</v>
       </c>
       <c r="F262" t="n">
         <v>1.405177329488421</v>
       </c>
       <c r="G262" t="n">
-        <v>0.5041967085817787</v>
+        <v>0.5041967085817756</v>
       </c>
       <c r="H262" t="inlineStr"/>
       <c r="I262" t="n">
@@ -8842,13 +8830,13 @@
         <v>528</v>
       </c>
       <c r="E263" t="n">
-        <v>18.59233843471728</v>
+        <v>18.59233843471731</v>
       </c>
       <c r="F263" t="n">
         <v>1.880802844556056</v>
       </c>
       <c r="G263" t="n">
-        <v>0.4949702797796639</v>
+        <v>0.4949702797796565</v>
       </c>
       <c r="H263" t="inlineStr"/>
       <c r="I263" t="n">
@@ -8873,13 +8861,13 @@
         <v>528</v>
       </c>
       <c r="E264" t="n">
-        <v>28.61669928840626</v>
+        <v>28.61669928840628</v>
       </c>
       <c r="F264" t="n">
         <v>1.880802844556056</v>
       </c>
       <c r="G264" t="n">
-        <v>0.4949702797796639</v>
+        <v>0.4949702797796565</v>
       </c>
       <c r="H264" t="inlineStr"/>
       <c r="I264" t="n">
@@ -8904,13 +8892,13 @@
         <v>531.4</v>
       </c>
       <c r="E265" t="n">
-        <v>23.90850770754956</v>
+        <v>23.90850770754958</v>
       </c>
       <c r="F265" t="n">
-        <v>1.342620612324181</v>
+        <v>1.342620612324182</v>
       </c>
       <c r="G265" t="n">
-        <v>0.3750487267414306</v>
+        <v>0.3750487267414407</v>
       </c>
       <c r="H265" t="inlineStr"/>
       <c r="I265" t="n">
@@ -8935,13 +8923,13 @@
         <v>531.9</v>
       </c>
       <c r="E266" t="n">
-        <v>24.09999690153836</v>
+        <v>24.09999690153839</v>
       </c>
       <c r="F266" t="n">
         <v>1.251202870918269</v>
       </c>
       <c r="G266" t="n">
-        <v>0.3728668286126185</v>
+        <v>0.3728668286126128</v>
       </c>
       <c r="H266" t="inlineStr"/>
       <c r="I266" t="n">
@@ -8966,13 +8954,13 @@
         <v>532.4</v>
       </c>
       <c r="E267" t="n">
-        <v>24.47776237504621</v>
+        <v>24.47776237504624</v>
       </c>
       <c r="F267" t="n">
-        <v>0.925520344473855</v>
+        <v>0.9255203444738557</v>
       </c>
       <c r="G267" t="n">
-        <v>0.4133219617142912</v>
+        <v>0.4133219617142816</v>
       </c>
       <c r="H267" t="inlineStr"/>
       <c r="I267" t="n">
@@ -8997,13 +8985,13 @@
         <v>532.9</v>
       </c>
       <c r="E268" t="n">
-        <v>24.56412241867194</v>
+        <v>24.56412241867196</v>
       </c>
       <c r="F268" t="n">
-        <v>0.8281584121061147</v>
+        <v>0.8281584121061153</v>
       </c>
       <c r="G268" t="n">
-        <v>0.357640283931925</v>
+        <v>0.3576402839319019</v>
       </c>
       <c r="H268" t="inlineStr"/>
       <c r="I268" t="n">
@@ -9028,13 +9016,13 @@
         <v>533.4</v>
       </c>
       <c r="E269" t="n">
-        <v>24.66968252693294</v>
+        <v>24.66968252693296</v>
       </c>
       <c r="F269" t="n">
-        <v>0.4580375867309792</v>
+        <v>0.4580375867309796</v>
       </c>
       <c r="G269" t="n">
-        <v>0.1953526178736347</v>
+        <v>0.1953526178735995</v>
       </c>
       <c r="H269" t="inlineStr"/>
       <c r="I269" t="n">
@@ -9059,13 +9047,13 @@
         <v>533.9</v>
       </c>
       <c r="E270" t="n">
-        <v>24.51513735671215</v>
+        <v>24.51513735671218</v>
       </c>
       <c r="F270" t="n">
-        <v>0.7378325424297658</v>
+        <v>0.7378325424297659</v>
       </c>
       <c r="G270" t="n">
-        <v>0.4967556020559807</v>
+        <v>0.496755602055966</v>
       </c>
       <c r="H270" t="inlineStr"/>
       <c r="I270" t="n">
@@ -9090,13 +9078,13 @@
         <v>534.4</v>
       </c>
       <c r="E271" t="n">
-        <v>24.86073034694735</v>
+        <v>24.86073034694737</v>
       </c>
       <c r="F271" t="n">
         <v>1.061129754381722</v>
       </c>
       <c r="G271" t="n">
-        <v>0.5584944279308569</v>
+        <v>0.5584944279308489</v>
       </c>
       <c r="H271" t="inlineStr"/>
       <c r="I271" t="n">
@@ -9121,13 +9109,13 @@
         <v>534.9</v>
       </c>
       <c r="E272" t="n">
-        <v>25.59800072781904</v>
+        <v>25.59800072781906</v>
       </c>
       <c r="F272" t="n">
-        <v>1.14084536648658</v>
+        <v>1.140845366486581</v>
       </c>
       <c r="G272" t="n">
-        <v>0.4547910658071965</v>
+        <v>0.4547910658071954</v>
       </c>
       <c r="H272" t="inlineStr"/>
       <c r="I272" t="n">
@@ -9152,13 +9140,13 @@
         <v>535.4</v>
       </c>
       <c r="E273" t="n">
-        <v>26.43539844926391</v>
+        <v>26.43539844926393</v>
       </c>
       <c r="F273" t="n">
-        <v>1.712218738848167</v>
+        <v>1.712218738848168</v>
       </c>
       <c r="G273" t="n">
-        <v>0.5280201277594233</v>
+        <v>0.5280201277594411</v>
       </c>
       <c r="H273" t="inlineStr"/>
       <c r="I273" t="n">
@@ -9183,13 +9171,13 @@
         <v>535.8</v>
       </c>
       <c r="E274" t="n">
-        <v>26.92654785001888</v>
+        <v>26.9265478500189</v>
       </c>
       <c r="F274" t="n">
-        <v>1.975655383001957</v>
+        <v>1.975655383001959</v>
       </c>
       <c r="G274" t="n">
-        <v>0.4144579874077716</v>
+        <v>0.4144579874077893</v>
       </c>
       <c r="H274" t="inlineStr"/>
       <c r="I274" t="n">
@@ -9214,13 +9202,13 @@
         <v>651.6</v>
       </c>
       <c r="E275" t="n">
-        <v>11.92796601478459</v>
+        <v>11.92796601478464</v>
       </c>
       <c r="F275" t="n">
-        <v>0.9889724834258183</v>
+        <v>0.9889724834258187</v>
       </c>
       <c r="G275" t="n">
-        <v>0.3484011119854419</v>
+        <v>0.3484011119854711</v>
       </c>
       <c r="H275" t="inlineStr"/>
       <c r="I275" t="n">
@@ -9245,13 +9233,13 @@
         <v>651.6</v>
       </c>
       <c r="E276" t="n">
-        <v>20.87850686967392</v>
+        <v>20.87850686967396</v>
       </c>
       <c r="F276" t="n">
-        <v>0.9889724834258183</v>
+        <v>0.9889724834258187</v>
       </c>
       <c r="G276" t="n">
-        <v>0.3484011119854419</v>
+        <v>0.3484011119854711</v>
       </c>
       <c r="H276" t="inlineStr"/>
       <c r="I276" t="n">
@@ -9276,13 +9264,13 @@
         <v>651.6</v>
       </c>
       <c r="E277" t="n">
-        <v>19.18720310780668</v>
+        <v>19.18720310780669</v>
       </c>
       <c r="F277" t="n">
-        <v>0.9889724834258183</v>
+        <v>0.9889724834258187</v>
       </c>
       <c r="G277" t="n">
-        <v>0.3484011119854419</v>
+        <v>0.3484011119854711</v>
       </c>
       <c r="H277" t="inlineStr"/>
       <c r="I277" t="n">
@@ -9307,13 +9295,13 @@
         <v>652.1</v>
       </c>
       <c r="E278" t="n">
-        <v>12.24720869687417</v>
+        <v>12.2472086968742</v>
       </c>
       <c r="F278" t="n">
-        <v>1.2075421920659</v>
+        <v>1.207542192065901</v>
       </c>
       <c r="G278" t="n">
-        <v>0.5680913545908082</v>
+        <v>0.5680913545908371</v>
       </c>
       <c r="H278" t="inlineStr"/>
       <c r="I278" t="n">
@@ -9338,13 +9326,13 @@
         <v>652.1</v>
       </c>
       <c r="E279" t="n">
-        <v>21.17132778148415</v>
+        <v>21.17132778148417</v>
       </c>
       <c r="F279" t="n">
-        <v>1.2075421920659</v>
+        <v>1.207542192065901</v>
       </c>
       <c r="G279" t="n">
-        <v>0.5680913545908082</v>
+        <v>0.5680913545908371</v>
       </c>
       <c r="H279" t="inlineStr"/>
       <c r="I279" t="n">
@@ -9369,13 +9357,13 @@
         <v>652.1</v>
       </c>
       <c r="E280" t="n">
-        <v>19.30450410272474</v>
+        <v>19.30450410272475</v>
       </c>
       <c r="F280" t="n">
-        <v>1.2075421920659</v>
+        <v>1.207542192065901</v>
       </c>
       <c r="G280" t="n">
-        <v>0.5680913545908082</v>
+        <v>0.5680913545908371</v>
       </c>
       <c r="H280" t="inlineStr"/>
       <c r="I280" t="n">
@@ -9400,13 +9388,13 @@
         <v>652.4</v>
       </c>
       <c r="E281" t="n">
-        <v>19.12606245134535</v>
+        <v>19.12606245134536</v>
       </c>
       <c r="F281" t="n">
-        <v>0.5981028324614149</v>
+        <v>0.5981028324614152</v>
       </c>
       <c r="G281" t="n">
-        <v>0.7693180732638104</v>
+        <v>0.7693180732638264</v>
       </c>
       <c r="H281" t="inlineStr"/>
       <c r="I281" t="n">
@@ -9431,13 +9419,13 @@
         <v>652.6</v>
       </c>
       <c r="E282" t="n">
-        <v>12.06460068024579</v>
+        <v>12.06460068024583</v>
       </c>
       <c r="F282" t="n">
-        <v>0.5401087063684865</v>
+        <v>0.5401087063684862</v>
       </c>
       <c r="G282" t="n">
-        <v>0.8844653476430339</v>
+        <v>0.8844653476430504</v>
       </c>
       <c r="H282" t="inlineStr"/>
       <c r="I282" t="n">
@@ -9462,13 +9450,13 @@
         <v>652.6</v>
       </c>
       <c r="E283" t="n">
-        <v>20.99914661362366</v>
+        <v>20.9991466136237</v>
       </c>
       <c r="F283" t="n">
-        <v>0.5401087063684865</v>
+        <v>0.5401087063684862</v>
       </c>
       <c r="G283" t="n">
-        <v>0.8844653476430339</v>
+        <v>0.8844653476430504</v>
       </c>
       <c r="H283" t="inlineStr"/>
       <c r="I283" t="n">
@@ -9493,13 +9481,13 @@
         <v>652.6</v>
       </c>
       <c r="E284" t="n">
-        <v>19.22286300457577</v>
+        <v>19.22286300457578</v>
       </c>
       <c r="F284" t="n">
-        <v>0.5401087063684865</v>
+        <v>0.5401087063684862</v>
       </c>
       <c r="G284" t="n">
-        <v>0.8844653476430339</v>
+        <v>0.8844653476430504</v>
       </c>
       <c r="H284" t="inlineStr"/>
       <c r="I284" t="n">
@@ -9524,13 +9512,13 @@
         <v>653.1</v>
       </c>
       <c r="E285" t="n">
-        <v>12.4597537157031</v>
+        <v>12.45975371570316</v>
       </c>
       <c r="F285" t="n">
-        <v>1.619028076590848</v>
+        <v>1.619028076590849</v>
       </c>
       <c r="G285" t="n">
-        <v>0.9440981496388244</v>
+        <v>0.9440981496388423</v>
       </c>
       <c r="H285" t="inlineStr"/>
       <c r="I285" t="n">
@@ -9555,13 +9543,13 @@
         <v>653.1</v>
       </c>
       <c r="E286" t="n">
-        <v>21.58936475056852</v>
+        <v>21.58936475056857</v>
       </c>
       <c r="F286" t="n">
-        <v>1.619028076590848</v>
+        <v>1.619028076590849</v>
       </c>
       <c r="G286" t="n">
-        <v>0.9440981496388244</v>
+        <v>0.9440981496388423</v>
       </c>
       <c r="H286" t="inlineStr"/>
       <c r="I286" t="n">
@@ -9586,13 +9574,13 @@
         <v>653.1</v>
       </c>
       <c r="E287" t="n">
-        <v>20.09024192262879</v>
+        <v>20.09024192262881</v>
       </c>
       <c r="F287" t="n">
-        <v>1.619028076590848</v>
+        <v>1.619028076590849</v>
       </c>
       <c r="G287" t="n">
-        <v>0.9440981496388244</v>
+        <v>0.9440981496388423</v>
       </c>
       <c r="H287" t="inlineStr"/>
       <c r="I287" t="n">
@@ -9617,13 +9605,13 @@
         <v>653.3</v>
       </c>
       <c r="E288" t="n">
-        <v>12.48494428027914</v>
+        <v>12.48494428027918</v>
       </c>
       <c r="F288" t="n">
-        <v>1.854868545582641</v>
+        <v>1.854868545582642</v>
       </c>
       <c r="G288" t="n">
-        <v>0.819074136350413</v>
+        <v>0.8190741363504359</v>
       </c>
       <c r="H288" t="inlineStr"/>
       <c r="I288" t="n">
@@ -9648,13 +9636,13 @@
         <v>653.3</v>
       </c>
       <c r="E289" t="n">
-        <v>21.7335188314359</v>
+        <v>21.73351883143594</v>
       </c>
       <c r="F289" t="n">
-        <v>1.854868545582641</v>
+        <v>1.854868545582642</v>
       </c>
       <c r="G289" t="n">
-        <v>0.819074136350413</v>
+        <v>0.8190741363504359</v>
       </c>
       <c r="H289" t="inlineStr"/>
       <c r="I289" t="n">
@@ -9679,13 +9667,13 @@
         <v>653.3</v>
       </c>
       <c r="E290" t="n">
-        <v>20.50879702667061</v>
+        <v>20.50879702667062</v>
       </c>
       <c r="F290" t="n">
-        <v>1.854868545582641</v>
+        <v>1.854868545582642</v>
       </c>
       <c r="G290" t="n">
-        <v>0.819074136350413</v>
+        <v>0.8190741363504359</v>
       </c>
       <c r="H290" t="inlineStr"/>
       <c r="I290" t="n">
@@ -9710,13 +9698,13 @@
         <v>750.8</v>
       </c>
       <c r="E291" t="n">
-        <v>37.55497385351918</v>
+        <v>37.55497385351921</v>
       </c>
       <c r="F291" t="n">
         <v>1.372928021955616</v>
       </c>
       <c r="G291" t="n">
-        <v>0.1505902973488793</v>
+        <v>0.1505902973488805</v>
       </c>
       <c r="H291" t="n">
         <v>227.9350901694639</v>
@@ -9743,13 +9731,13 @@
         <v>750.8</v>
       </c>
       <c r="E292" t="n">
-        <v>32.57002814060944</v>
+        <v>32.57002814060947</v>
       </c>
       <c r="F292" t="n">
         <v>1.372928021955616</v>
       </c>
       <c r="G292" t="n">
-        <v>0.1505902973488793</v>
+        <v>0.1505902973488805</v>
       </c>
       <c r="H292" t="n">
         <v>256.5769452962618</v>
@@ -9776,13 +9764,13 @@
         <v>750.8</v>
       </c>
       <c r="E293" t="n">
-        <v>22.48319288510971</v>
+        <v>22.48319288510975</v>
       </c>
       <c r="F293" t="n">
         <v>1.372928021955616</v>
       </c>
       <c r="G293" t="n">
-        <v>0.1505902973488793</v>
+        <v>0.1505902973488805</v>
       </c>
       <c r="H293" t="n">
         <v>269.0805451334944</v>
@@ -9809,16 +9797,16 @@
         <v>750.8</v>
       </c>
       <c r="E294" t="n">
-        <v>35.44460196444977</v>
+        <v>35.4446019644498</v>
       </c>
       <c r="F294" t="n">
         <v>1.372928021955616</v>
       </c>
       <c r="G294" t="n">
-        <v>0.1505902973488793</v>
+        <v>0.1505902973488805</v>
       </c>
       <c r="H294" t="n">
-        <v>298.7329660972585</v>
+        <v>298.7329660972584</v>
       </c>
       <c r="I294" t="n">
         <v>1</v>
@@ -9842,16 +9830,16 @@
         <v>750.8</v>
       </c>
       <c r="E295" t="n">
-        <v>31.42649779819904</v>
+        <v>31.42649779819905</v>
       </c>
       <c r="F295" t="n">
         <v>1.372928021955616</v>
       </c>
       <c r="G295" t="n">
-        <v>0.1505902973488793</v>
+        <v>0.1505902973488805</v>
       </c>
       <c r="H295" t="n">
-        <v>321.9254307297865</v>
+        <v>321.9254307297864</v>
       </c>
       <c r="I295" t="n">
         <v>1</v>
@@ -9875,13 +9863,13 @@
         <v>751.1</v>
       </c>
       <c r="E296" t="n">
-        <v>23.24351631072125</v>
+        <v>23.24351631072127</v>
       </c>
       <c r="F296" t="n">
-        <v>1.293519361173363</v>
+        <v>1.293519361173364</v>
       </c>
       <c r="G296" t="n">
-        <v>0.03048836133540043</v>
+        <v>0.03048836133542235</v>
       </c>
       <c r="H296" t="inlineStr"/>
       <c r="I296" t="n">
@@ -9909,10 +9897,10 @@
         <v>16.07701967198491</v>
       </c>
       <c r="F297" t="n">
-        <v>1.293519361173363</v>
+        <v>1.293519361173364</v>
       </c>
       <c r="G297" t="n">
-        <v>0.03048836133540043</v>
+        <v>0.03048836133542235</v>
       </c>
       <c r="H297" t="inlineStr"/>
       <c r="I297" t="n">
@@ -9937,13 +9925,13 @@
         <v>751.1</v>
       </c>
       <c r="E298" t="n">
-        <v>10.95297051520534</v>
+        <v>10.95297051520531</v>
       </c>
       <c r="F298" t="n">
-        <v>1.293519361173363</v>
+        <v>1.293519361173364</v>
       </c>
       <c r="G298" t="n">
-        <v>0.03048836133540043</v>
+        <v>0.03048836133542235</v>
       </c>
       <c r="H298" t="inlineStr"/>
       <c r="I298" t="n">
@@ -9968,13 +9956,13 @@
         <v>751.1</v>
       </c>
       <c r="E299" t="n">
-        <v>14.5462032752599</v>
+        <v>14.54620327525989</v>
       </c>
       <c r="F299" t="n">
-        <v>1.293519361173363</v>
+        <v>1.293519361173364</v>
       </c>
       <c r="G299" t="n">
-        <v>0.03048836133540043</v>
+        <v>0.03048836133542235</v>
       </c>
       <c r="H299" t="inlineStr"/>
       <c r="I299" t="n">
@@ -9999,13 +9987,13 @@
         <v>751.1</v>
       </c>
       <c r="E300" t="n">
-        <v>23.8958061099</v>
+        <v>23.89580610989997</v>
       </c>
       <c r="F300" t="n">
-        <v>1.293519361173363</v>
+        <v>1.293519361173364</v>
       </c>
       <c r="G300" t="n">
-        <v>0.03048836133540043</v>
+        <v>0.03048836133542235</v>
       </c>
       <c r="H300" t="inlineStr"/>
       <c r="I300" t="n">
@@ -10030,13 +10018,13 @@
         <v>751.2</v>
       </c>
       <c r="E301" t="n">
-        <v>37.47247343638563</v>
+        <v>37.47247343638567</v>
       </c>
       <c r="F301" t="n">
-        <v>1.420309570067793</v>
+        <v>1.420309570067794</v>
       </c>
       <c r="G301" t="n">
-        <v>0.03507618127333317</v>
+        <v>0.03507618127335745</v>
       </c>
       <c r="H301" t="n">
         <v>228.7553565879416</v>
@@ -10063,16 +10051,16 @@
         <v>751.2</v>
       </c>
       <c r="E302" t="n">
-        <v>32.7553962540441</v>
+        <v>32.75539625404414</v>
       </c>
       <c r="F302" t="n">
-        <v>1.420309570067793</v>
+        <v>1.420309570067794</v>
       </c>
       <c r="G302" t="n">
-        <v>0.03507618127333317</v>
+        <v>0.03507618127335745</v>
       </c>
       <c r="H302" t="n">
-        <v>257.4729099653292</v>
+        <v>257.4729099653291</v>
       </c>
       <c r="I302" t="n">
         <v>1</v>
@@ -10096,13 +10084,13 @@
         <v>751.2</v>
       </c>
       <c r="E303" t="n">
-        <v>22.77580642653756</v>
+        <v>22.77580642653759</v>
       </c>
       <c r="F303" t="n">
-        <v>1.420309570067793</v>
+        <v>1.420309570067794</v>
       </c>
       <c r="G303" t="n">
-        <v>0.03507618127333317</v>
+        <v>0.03507618127335745</v>
       </c>
       <c r="H303" t="n">
         <v>270.2397803690155</v>
@@ -10129,13 +10117,13 @@
         <v>751.2</v>
       </c>
       <c r="E304" t="n">
-        <v>35.92373557295826</v>
+        <v>35.92373557295828</v>
       </c>
       <c r="F304" t="n">
-        <v>1.420309570067793</v>
+        <v>1.420309570067794</v>
       </c>
       <c r="G304" t="n">
-        <v>0.03507618127333317</v>
+        <v>0.03507618127335745</v>
       </c>
       <c r="H304" t="n">
         <v>299.1444234633618</v>
@@ -10165,13 +10153,13 @@
         <v>31.96769357840542</v>
       </c>
       <c r="F305" t="n">
-        <v>1.420309570067793</v>
+        <v>1.420309570067794</v>
       </c>
       <c r="G305" t="n">
-        <v>0.03507618127333317</v>
+        <v>0.03507618127335745</v>
       </c>
       <c r="H305" t="n">
-        <v>322.012896014494</v>
+        <v>322.0128960144939</v>
       </c>
       <c r="I305" t="n">
         <v>1</v>
@@ -10195,13 +10183,13 @@
         <v>751.6</v>
       </c>
       <c r="E306" t="n">
-        <v>22.44714917060569</v>
+        <v>22.44714917060572</v>
       </c>
       <c r="F306" t="n">
-        <v>1.526963109551564</v>
+        <v>1.526963109551565</v>
       </c>
       <c r="G306" t="n">
-        <v>0.1073391402630402</v>
+        <v>0.107339140263014</v>
       </c>
       <c r="H306" t="inlineStr"/>
       <c r="I306" t="n">
@@ -10229,10 +10217,10 @@
         <v>15.14130057199778</v>
       </c>
       <c r="F307" t="n">
-        <v>1.526963109551564</v>
+        <v>1.526963109551565</v>
       </c>
       <c r="G307" t="n">
-        <v>0.1073391402630402</v>
+        <v>0.107339140263014</v>
       </c>
       <c r="H307" t="inlineStr"/>
       <c r="I307" t="n">
@@ -10257,13 +10245,13 @@
         <v>751.6</v>
       </c>
       <c r="E308" t="n">
-        <v>11.1275053266274</v>
+        <v>11.12750532662736</v>
       </c>
       <c r="F308" t="n">
-        <v>1.526963109551564</v>
+        <v>1.526963109551565</v>
       </c>
       <c r="G308" t="n">
-        <v>0.1073391402630402</v>
+        <v>0.107339140263014</v>
       </c>
       <c r="H308" t="inlineStr"/>
       <c r="I308" t="n">
@@ -10288,13 +10276,13 @@
         <v>751.6</v>
       </c>
       <c r="E309" t="n">
-        <v>15.43411161944656</v>
+        <v>15.43411161944654</v>
       </c>
       <c r="F309" t="n">
-        <v>1.526963109551564</v>
+        <v>1.526963109551565</v>
       </c>
       <c r="G309" t="n">
-        <v>0.1073391402630402</v>
+        <v>0.107339140263014</v>
       </c>
       <c r="H309" t="inlineStr"/>
       <c r="I309" t="n">
@@ -10319,13 +10307,13 @@
         <v>751.6</v>
       </c>
       <c r="E310" t="n">
-        <v>24.66492235360385</v>
+        <v>24.66492235360382</v>
       </c>
       <c r="F310" t="n">
-        <v>1.526963109551564</v>
+        <v>1.526963109551565</v>
       </c>
       <c r="G310" t="n">
-        <v>0.1073391402630402</v>
+        <v>0.107339140263014</v>
       </c>
       <c r="H310" t="inlineStr"/>
       <c r="I310" t="n">
@@ -10350,13 +10338,13 @@
         <v>752.1</v>
       </c>
       <c r="E311" t="n">
-        <v>22.44042641924958</v>
+        <v>22.44042641924961</v>
       </c>
       <c r="F311" t="n">
-        <v>1.700330144654977</v>
+        <v>1.700330144654979</v>
       </c>
       <c r="G311" t="n">
-        <v>0.4215509718714996</v>
+        <v>0.4215509718715161</v>
       </c>
       <c r="H311" t="inlineStr"/>
       <c r="I311" t="n">
@@ -10384,10 +10372,10 @@
         <v>14.72537316122964</v>
       </c>
       <c r="F312" t="n">
-        <v>1.700330144654977</v>
+        <v>1.700330144654979</v>
       </c>
       <c r="G312" t="n">
-        <v>0.4215509718714996</v>
+        <v>0.4215509718715161</v>
       </c>
       <c r="H312" t="inlineStr"/>
       <c r="I312" t="n">
@@ -10412,13 +10400,13 @@
         <v>752.1</v>
       </c>
       <c r="E313" t="n">
-        <v>10.72518079997997</v>
+        <v>10.72518079997993</v>
       </c>
       <c r="F313" t="n">
-        <v>1.700330144654977</v>
+        <v>1.700330144654979</v>
       </c>
       <c r="G313" t="n">
-        <v>0.4215509718714996</v>
+        <v>0.4215509718715161</v>
       </c>
       <c r="H313" t="inlineStr"/>
       <c r="I313" t="n">
@@ -10443,13 +10431,13 @@
         <v>752.1</v>
       </c>
       <c r="E314" t="n">
-        <v>15.60542861820155</v>
+        <v>15.60542861820153</v>
       </c>
       <c r="F314" t="n">
-        <v>1.700330144654977</v>
+        <v>1.700330144654979</v>
       </c>
       <c r="G314" t="n">
-        <v>0.4215509718714996</v>
+        <v>0.4215509718715161</v>
       </c>
       <c r="H314" t="inlineStr"/>
       <c r="I314" t="n">
@@ -10474,13 +10462,13 @@
         <v>752.1</v>
       </c>
       <c r="E315" t="n">
-        <v>24.67001655204897</v>
+        <v>24.67001655204894</v>
       </c>
       <c r="F315" t="n">
-        <v>1.700330144654977</v>
+        <v>1.700330144654979</v>
       </c>
       <c r="G315" t="n">
-        <v>0.4215509718714996</v>
+        <v>0.4215509718715161</v>
       </c>
       <c r="H315" t="inlineStr"/>
       <c r="I315" t="n">
@@ -10505,13 +10493,13 @@
         <v>752.5</v>
       </c>
       <c r="E316" t="n">
-        <v>21.64944650109704</v>
+        <v>21.64944650109707</v>
       </c>
       <c r="F316" t="n">
-        <v>1.905336777270484</v>
+        <v>1.905336777270485</v>
       </c>
       <c r="G316" t="n">
-        <v>0.1917051844304302</v>
+        <v>0.1917051844304548</v>
       </c>
       <c r="H316" t="inlineStr"/>
       <c r="I316" t="n">
@@ -10536,13 +10524,13 @@
         <v>752.5</v>
       </c>
       <c r="E317" t="n">
-        <v>13.65555416083488</v>
+        <v>13.65555416083489</v>
       </c>
       <c r="F317" t="n">
-        <v>1.905336777270484</v>
+        <v>1.905336777270485</v>
       </c>
       <c r="G317" t="n">
-        <v>0.1917051844304302</v>
+        <v>0.1917051844304548</v>
       </c>
       <c r="H317" t="inlineStr"/>
       <c r="I317" t="n">
@@ -10567,13 +10555,13 @@
         <v>752.5</v>
       </c>
       <c r="E318" t="n">
-        <v>10.94305178781901</v>
+        <v>10.94305178781896</v>
       </c>
       <c r="F318" t="n">
-        <v>1.905336777270484</v>
+        <v>1.905336777270485</v>
       </c>
       <c r="G318" t="n">
-        <v>0.1917051844304302</v>
+        <v>0.1917051844304548</v>
       </c>
       <c r="H318" t="inlineStr"/>
       <c r="I318" t="n">
@@ -10598,13 +10586,13 @@
         <v>752.5</v>
       </c>
       <c r="E319" t="n">
-        <v>16.58899498636476</v>
+        <v>16.58899498636473</v>
       </c>
       <c r="F319" t="n">
-        <v>1.905336777270484</v>
+        <v>1.905336777270485</v>
       </c>
       <c r="G319" t="n">
-        <v>0.1917051844304302</v>
+        <v>0.1917051844304548</v>
       </c>
       <c r="H319" t="inlineStr"/>
       <c r="I319" t="n">
@@ -10629,13 +10617,13 @@
         <v>752.5</v>
       </c>
       <c r="E320" t="n">
-        <v>25.49821172893886</v>
+        <v>25.49821172893883</v>
       </c>
       <c r="F320" t="n">
-        <v>1.905336777270484</v>
+        <v>1.905336777270485</v>
       </c>
       <c r="G320" t="n">
-        <v>0.1917051844304302</v>
+        <v>0.1917051844304548</v>
       </c>
       <c r="H320" t="inlineStr"/>
       <c r="I320" t="n">
@@ -10660,13 +10648,13 @@
         <v>763.5</v>
       </c>
       <c r="E321" t="n">
-        <v>11.22762211741135</v>
+        <v>11.22762211741139</v>
       </c>
       <c r="F321" t="n">
-        <v>0.9916570095933905</v>
+        <v>0.9916570095933909</v>
       </c>
       <c r="G321" t="n">
-        <v>0.2767023682100468</v>
+        <v>0.276702368210072</v>
       </c>
       <c r="H321" t="inlineStr"/>
       <c r="I321" t="n">
@@ -10691,13 +10679,13 @@
         <v>763.5</v>
       </c>
       <c r="E322" t="n">
-        <v>19.09521484615123</v>
+        <v>19.09521484615126</v>
       </c>
       <c r="F322" t="n">
-        <v>0.9916570095933905</v>
+        <v>0.9916570095933909</v>
       </c>
       <c r="G322" t="n">
-        <v>0.2767023682100468</v>
+        <v>0.276702368210072</v>
       </c>
       <c r="H322" t="inlineStr"/>
       <c r="I322" t="n">
@@ -10722,13 +10710,13 @@
         <v>763.5</v>
       </c>
       <c r="E323" t="n">
-        <v>15.96406621474589</v>
+        <v>15.9640662147459</v>
       </c>
       <c r="F323" t="n">
-        <v>0.9916570095933905</v>
+        <v>0.9916570095933909</v>
       </c>
       <c r="G323" t="n">
-        <v>0.2767023682100468</v>
+        <v>0.276702368210072</v>
       </c>
       <c r="H323" t="inlineStr"/>
       <c r="I323" t="n">
@@ -10753,13 +10741,13 @@
         <v>763.5</v>
       </c>
       <c r="E324" t="n">
-        <v>29.73310582565653</v>
+        <v>29.73310582565654</v>
       </c>
       <c r="F324" t="n">
-        <v>0.9916570095933905</v>
+        <v>0.9916570095933909</v>
       </c>
       <c r="G324" t="n">
-        <v>0.2767023682100468</v>
+        <v>0.276702368210072</v>
       </c>
       <c r="H324" t="inlineStr"/>
       <c r="I324" t="n">
@@ -10784,13 +10772,13 @@
         <v>763.7</v>
       </c>
       <c r="E325" t="n">
-        <v>19.07154493529857</v>
+        <v>19.07154493529861</v>
       </c>
       <c r="F325" t="n">
-        <v>1.395763031930912</v>
+        <v>1.395763031930913</v>
       </c>
       <c r="G325" t="n">
-        <v>0.1846551444727924</v>
+        <v>0.1846551444728215</v>
       </c>
       <c r="H325" t="inlineStr"/>
       <c r="I325" t="n">
@@ -10815,13 +10803,13 @@
         <v>763.8</v>
       </c>
       <c r="E326" t="n">
-        <v>29.94983087495575</v>
+        <v>29.94983087495577</v>
       </c>
       <c r="F326" t="n">
         <v>1.515927509842519</v>
       </c>
       <c r="G326" t="n">
-        <v>0.1410284552744854</v>
+        <v>0.1410284552745128</v>
       </c>
       <c r="H326" t="inlineStr"/>
       <c r="I326" t="n">
@@ -10846,13 +10834,13 @@
         <v>764</v>
       </c>
       <c r="E327" t="n">
-        <v>11.01088858683889</v>
+        <v>11.01088858683893</v>
       </c>
       <c r="F327" t="n">
-        <v>1.64929276328804</v>
+        <v>1.649292763288041</v>
       </c>
       <c r="G327" t="n">
-        <v>0.04505304877972471</v>
+        <v>0.04505304877975524</v>
       </c>
       <c r="H327" t="inlineStr"/>
       <c r="I327" t="n">
@@ -10877,13 +10865,13 @@
         <v>764</v>
       </c>
       <c r="E328" t="n">
-        <v>19.19670933087196</v>
+        <v>19.19670933087199</v>
       </c>
       <c r="F328" t="n">
-        <v>1.64929276328804</v>
+        <v>1.649292763288041</v>
       </c>
       <c r="G328" t="n">
-        <v>0.04505304877972471</v>
+        <v>0.04505304877975524</v>
       </c>
       <c r="H328" t="inlineStr"/>
       <c r="I328" t="n">
@@ -10908,13 +10896,13 @@
         <v>764</v>
       </c>
       <c r="E329" t="n">
-        <v>16.6118618861966</v>
+        <v>16.61186188619661</v>
       </c>
       <c r="F329" t="n">
-        <v>1.64929276328804</v>
+        <v>1.649292763288041</v>
       </c>
       <c r="G329" t="n">
-        <v>0.04505304877972471</v>
+        <v>0.04505304877975524</v>
       </c>
       <c r="H329" t="inlineStr"/>
       <c r="I329" t="n">
@@ -10939,13 +10927,13 @@
         <v>764.5</v>
       </c>
       <c r="E330" t="n">
-        <v>11.08235548632518</v>
+        <v>11.08235548632522</v>
       </c>
       <c r="F330" t="n">
-        <v>1.359613288590662</v>
+        <v>1.359613288590663</v>
       </c>
       <c r="G330" t="n">
-        <v>0.1031898304907553</v>
+        <v>0.1031898304907732</v>
       </c>
       <c r="H330" t="inlineStr"/>
       <c r="I330" t="n">
@@ -10970,13 +10958,13 @@
         <v>764.5</v>
       </c>
       <c r="E331" t="n">
-        <v>19.54127907057547</v>
+        <v>19.54127907057551</v>
       </c>
       <c r="F331" t="n">
-        <v>1.359613288590662</v>
+        <v>1.359613288590663</v>
       </c>
       <c r="G331" t="n">
-        <v>0.1031898304907553</v>
+        <v>0.1031898304907732</v>
       </c>
       <c r="H331" t="inlineStr"/>
       <c r="I331" t="n">
@@ -11001,13 +10989,13 @@
         <v>764.5</v>
       </c>
       <c r="E332" t="n">
-        <v>17.33046412041753</v>
+        <v>17.33046412041754</v>
       </c>
       <c r="F332" t="n">
-        <v>1.359613288590662</v>
+        <v>1.359613288590663</v>
       </c>
       <c r="G332" t="n">
-        <v>0.1031898304907553</v>
+        <v>0.1031898304907732</v>
       </c>
       <c r="H332" t="inlineStr"/>
       <c r="I332" t="n">
@@ -11032,13 +11020,13 @@
         <v>765</v>
       </c>
       <c r="E333" t="n">
-        <v>10.97987400344702</v>
+        <v>10.97987400344705</v>
       </c>
       <c r="F333" t="n">
-        <v>1.885272226822409</v>
+        <v>1.88527222682241</v>
       </c>
       <c r="G333" t="n">
-        <v>0.3122086003172178</v>
+        <v>0.3122086003172148</v>
       </c>
       <c r="H333" t="inlineStr"/>
       <c r="I333" t="n">
@@ -11063,13 +11051,13 @@
         <v>765</v>
       </c>
       <c r="E334" t="n">
-        <v>19.63909518273976</v>
+        <v>19.63909518273978</v>
       </c>
       <c r="F334" t="n">
-        <v>1.885272226822409</v>
+        <v>1.88527222682241</v>
       </c>
       <c r="G334" t="n">
-        <v>0.3122086003172178</v>
+        <v>0.3122086003172148</v>
       </c>
       <c r="H334" t="inlineStr"/>
       <c r="I334" t="n">
@@ -11097,10 +11085,10 @@
         <v>17.80264039799376</v>
       </c>
       <c r="F335" t="n">
-        <v>1.885272226822409</v>
+        <v>1.88527222682241</v>
       </c>
       <c r="G335" t="n">
-        <v>0.3122086003172178</v>
+        <v>0.3122086003172148</v>
       </c>
       <c r="H335" t="inlineStr"/>
       <c r="I335" t="n">
@@ -11125,13 +11113,13 @@
         <v>765.1</v>
       </c>
       <c r="E336" t="n">
-        <v>10.99389254983883</v>
+        <v>10.99389254983888</v>
       </c>
       <c r="F336" t="n">
         <v>1.956639624414465</v>
       </c>
       <c r="G336" t="n">
-        <v>0.3182192259558299</v>
+        <v>0.3182192259558259</v>
       </c>
       <c r="H336" t="inlineStr"/>
       <c r="I336" t="n">
@@ -11156,13 +11144,13 @@
         <v>765.1</v>
       </c>
       <c r="E337" t="n">
-        <v>19.70538255151482</v>
+        <v>19.70538255151487</v>
       </c>
       <c r="F337" t="n">
         <v>1.956639624414465</v>
       </c>
       <c r="G337" t="n">
-        <v>0.3182192259558299</v>
+        <v>0.3182192259558259</v>
       </c>
       <c r="H337" t="inlineStr"/>
       <c r="I337" t="n">
@@ -11187,13 +11175,13 @@
         <v>765.1</v>
       </c>
       <c r="E338" t="n">
-        <v>17.95212682162249</v>
+        <v>17.9521268216225</v>
       </c>
       <c r="F338" t="n">
         <v>1.956639624414465</v>
       </c>
       <c r="G338" t="n">
-        <v>0.3182192259558299</v>
+        <v>0.3182192259558259</v>
       </c>
       <c r="H338" t="inlineStr"/>
       <c r="I338" t="n">

--- a/2026_B题/outputs/task_candidates.xlsx
+++ b/2026_B题/outputs/task_candidates.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,47 +429,47 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>target_id</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>task</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>prep_start_s</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>exec_time_s</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>distance_m</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>speed_m_s</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>accel_m_s2</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>angle_deg</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>expected_success</t>
         </is>
@@ -481,16 +493,16 @@
         <v>477</v>
       </c>
       <c r="E2" t="n">
-        <v>26.73014942483519</v>
+        <v>26.73014942483482</v>
       </c>
       <c r="F2" t="n">
-        <v>1.0963632116626</v>
+        <v>1.096363211662601</v>
       </c>
       <c r="G2" t="n">
-        <v>0.3635389276737487</v>
+        <v>0.3635389276741378</v>
       </c>
       <c r="H2" t="n">
-        <v>147.5155047912845</v>
+        <v>147.5155047912839</v>
       </c>
       <c r="I2" t="n">
         <v>1</v>
@@ -514,16 +526,16 @@
         <v>477</v>
       </c>
       <c r="E3" t="n">
-        <v>25.84311077775126</v>
+        <v>25.84311077775104</v>
       </c>
       <c r="F3" t="n">
-        <v>1.0963632116626</v>
+        <v>1.096363211662601</v>
       </c>
       <c r="G3" t="n">
-        <v>0.3635389276737487</v>
+        <v>0.3635389276741378</v>
       </c>
       <c r="H3" t="n">
-        <v>122.6641094976678</v>
+        <v>122.664109497667</v>
       </c>
       <c r="I3" t="n">
         <v>1</v>
@@ -547,16 +559,16 @@
         <v>477</v>
       </c>
       <c r="E4" t="n">
-        <v>18.32364434242325</v>
+        <v>18.32364434242335</v>
       </c>
       <c r="F4" t="n">
-        <v>1.0963632116626</v>
+        <v>1.096363211662601</v>
       </c>
       <c r="G4" t="n">
-        <v>0.3635389276737487</v>
+        <v>0.3635389276741378</v>
       </c>
       <c r="H4" t="n">
-        <v>78.50322981771848</v>
+        <v>78.50322981771711</v>
       </c>
       <c r="I4" t="n">
         <v>1</v>
@@ -580,16 +592,16 @@
         <v>477</v>
       </c>
       <c r="E5" t="n">
-        <v>29.24409414215113</v>
+        <v>29.24409414215131</v>
       </c>
       <c r="F5" t="n">
-        <v>1.0963632116626</v>
+        <v>1.096363211662601</v>
       </c>
       <c r="G5" t="n">
-        <v>0.3635389276737487</v>
+        <v>0.3635389276741378</v>
       </c>
       <c r="H5" t="n">
-        <v>68.21726195687177</v>
+        <v>68.21726195687097</v>
       </c>
       <c r="I5" t="n">
         <v>1</v>
@@ -613,16 +625,16 @@
         <v>477</v>
       </c>
       <c r="E6" t="n">
-        <v>20.27576330244507</v>
+        <v>20.27576330244549</v>
       </c>
       <c r="F6" t="n">
-        <v>1.0963632116626</v>
+        <v>1.096363211662601</v>
       </c>
       <c r="G6" t="n">
-        <v>0.3635389276737487</v>
+        <v>0.3635389276741378</v>
       </c>
       <c r="H6" t="n">
-        <v>19.16402307633655</v>
+        <v>19.16402307633621</v>
       </c>
       <c r="I6" t="n">
         <v>1</v>
@@ -646,16 +658,16 @@
         <v>477</v>
       </c>
       <c r="E7" t="n">
-        <v>33.80100853348426</v>
+        <v>33.80100853348464</v>
       </c>
       <c r="F7" t="n">
-        <v>1.0963632116626</v>
+        <v>1.096363211662601</v>
       </c>
       <c r="G7" t="n">
-        <v>0.3635389276737487</v>
+        <v>0.3635389276741378</v>
       </c>
       <c r="H7" t="n">
-        <v>33.29690258965263</v>
+        <v>33.29690258965223</v>
       </c>
       <c r="I7" t="n">
         <v>1</v>
@@ -679,16 +691,16 @@
         <v>477</v>
       </c>
       <c r="E8" t="n">
-        <v>24.40962665594152</v>
+        <v>24.40962665594118</v>
       </c>
       <c r="F8" t="n">
-        <v>1.0963632116626</v>
+        <v>1.096363211662601</v>
       </c>
       <c r="G8" t="n">
-        <v>0.3635389276737487</v>
+        <v>0.3635389276741378</v>
       </c>
       <c r="H8" t="n">
-        <v>222.6692755731565</v>
+        <v>222.6692755731572</v>
       </c>
       <c r="I8" t="n">
         <v>1</v>
@@ -712,16 +724,16 @@
         <v>477</v>
       </c>
       <c r="E9" t="n">
-        <v>19.06442508242714</v>
+        <v>19.06442508242726</v>
       </c>
       <c r="F9" t="n">
-        <v>1.0963632116626</v>
+        <v>1.096363211662601</v>
       </c>
       <c r="G9" t="n">
-        <v>0.3635389276737487</v>
+        <v>0.3635389276741378</v>
       </c>
       <c r="H9" t="n">
-        <v>287.8764969434181</v>
+        <v>287.8764969434194</v>
       </c>
       <c r="I9" t="n">
         <v>1</v>
@@ -745,16 +757,16 @@
         <v>477</v>
       </c>
       <c r="E10" t="n">
-        <v>16.4843623820642</v>
+        <v>16.48436238206458</v>
       </c>
       <c r="F10" t="n">
-        <v>1.0963632116626</v>
+        <v>1.096363211662601</v>
       </c>
       <c r="G10" t="n">
-        <v>0.3635389276737487</v>
+        <v>0.3635389276741378</v>
       </c>
       <c r="H10" t="n">
-        <v>331.9800675777695</v>
+        <v>331.9800675777703</v>
       </c>
       <c r="I10" t="n">
         <v>1</v>
@@ -778,16 +790,16 @@
         <v>477</v>
       </c>
       <c r="E11" t="n">
-        <v>30.58785502699281</v>
+        <v>30.58785502699313</v>
       </c>
       <c r="F11" t="n">
-        <v>1.0963632116626</v>
+        <v>1.096363211662601</v>
       </c>
       <c r="G11" t="n">
-        <v>0.3635389276737487</v>
+        <v>0.3635389276741378</v>
       </c>
       <c r="H11" t="n">
-        <v>318.0586209469542</v>
+        <v>318.0586209469548</v>
       </c>
       <c r="I11" t="n">
         <v>1</v>
@@ -811,16 +823,16 @@
         <v>477</v>
       </c>
       <c r="E12" t="n">
-        <v>33.30365343076641</v>
+        <v>33.30365343076684</v>
       </c>
       <c r="F12" t="n">
-        <v>1.0963632116626</v>
+        <v>1.096363211662601</v>
       </c>
       <c r="G12" t="n">
-        <v>0.3635389276737487</v>
+        <v>0.3635389276741378</v>
       </c>
       <c r="H12" t="n">
-        <v>344.2427717635636</v>
+        <v>344.2427717635638</v>
       </c>
       <c r="I12" t="n">
         <v>1</v>
@@ -844,16 +856,16 @@
         <v>477.1</v>
       </c>
       <c r="E13" t="n">
-        <v>24.39955565047384</v>
+        <v>24.39955565047352</v>
       </c>
       <c r="F13" t="n">
         <v>1.022868112614397</v>
       </c>
       <c r="G13" t="n">
-        <v>0.3308325106365562</v>
+        <v>0.3308325106369227</v>
       </c>
       <c r="H13" t="n">
-        <v>223.1676848219427</v>
+        <v>223.1676848219433</v>
       </c>
       <c r="I13" t="n">
         <v>1</v>
@@ -877,13 +889,13 @@
         <v>477.5</v>
       </c>
       <c r="E14" t="n">
-        <v>18.26845367191013</v>
+        <v>18.26845367190976</v>
       </c>
       <c r="F14" t="n">
-        <v>0.8683134495735332</v>
+        <v>0.8683134495735331</v>
       </c>
       <c r="G14" t="n">
-        <v>0.4187514451780406</v>
+        <v>0.4187514451780739</v>
       </c>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="n">
@@ -908,13 +920,13 @@
         <v>477.5</v>
       </c>
       <c r="E15" t="n">
-        <v>10.03928385457296</v>
+        <v>10.03928385457257</v>
       </c>
       <c r="F15" t="n">
-        <v>0.8683134495735332</v>
+        <v>0.8683134495735331</v>
       </c>
       <c r="G15" t="n">
-        <v>0.4187514451780406</v>
+        <v>0.4187514451780739</v>
       </c>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="n">
@@ -939,13 +951,13 @@
         <v>477.5</v>
       </c>
       <c r="E16" t="n">
-        <v>13.85181735068472</v>
+        <v>13.85181735068462</v>
       </c>
       <c r="F16" t="n">
-        <v>0.8683134495735332</v>
+        <v>0.8683134495735331</v>
       </c>
       <c r="G16" t="n">
-        <v>0.4187514451780406</v>
+        <v>0.4187514451780739</v>
       </c>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="n">
@@ -970,13 +982,13 @@
         <v>477.5</v>
       </c>
       <c r="E17" t="n">
-        <v>17.53917316082144</v>
+        <v>17.53917316082176</v>
       </c>
       <c r="F17" t="n">
-        <v>0.8683134495735332</v>
+        <v>0.8683134495735331</v>
       </c>
       <c r="G17" t="n">
-        <v>0.4187514451780406</v>
+        <v>0.4187514451780739</v>
       </c>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="n">
@@ -1001,13 +1013,13 @@
         <v>477.5</v>
       </c>
       <c r="E18" t="n">
-        <v>22.32645778067442</v>
+        <v>22.32645778067483</v>
       </c>
       <c r="F18" t="n">
-        <v>0.8683134495735332</v>
+        <v>0.8683134495735331</v>
       </c>
       <c r="G18" t="n">
-        <v>0.4187514451780406</v>
+        <v>0.4187514451780739</v>
       </c>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="n">
@@ -1032,16 +1044,16 @@
         <v>477.5</v>
       </c>
       <c r="E19" t="n">
-        <v>25.80375917557323</v>
+        <v>25.80375917557287</v>
       </c>
       <c r="F19" t="n">
-        <v>0.8683134495735332</v>
+        <v>0.8683134495735331</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4187514451780406</v>
+        <v>0.4187514451780739</v>
       </c>
       <c r="H19" t="n">
-        <v>148.045394783456</v>
+        <v>148.0453947834554</v>
       </c>
       <c r="I19" t="n">
         <v>1</v>
@@ -1065,16 +1077,16 @@
         <v>477.5</v>
       </c>
       <c r="E20" t="n">
-        <v>24.90181330787542</v>
+        <v>24.90181330787521</v>
       </c>
       <c r="F20" t="n">
-        <v>0.8683134495735332</v>
+        <v>0.8683134495735331</v>
       </c>
       <c r="G20" t="n">
-        <v>0.4187514451780406</v>
+        <v>0.4187514451780739</v>
       </c>
       <c r="H20" t="n">
-        <v>122.2654721509231</v>
+        <v>122.2654721509222</v>
       </c>
       <c r="I20" t="n">
         <v>1</v>
@@ -1098,16 +1110,16 @@
         <v>477.5</v>
       </c>
       <c r="E21" t="n">
-        <v>17.78577284624593</v>
+        <v>17.78577284624606</v>
       </c>
       <c r="F21" t="n">
-        <v>0.8683134495735332</v>
+        <v>0.8683134495735331</v>
       </c>
       <c r="G21" t="n">
-        <v>0.4187514451780406</v>
+        <v>0.4187514451780739</v>
       </c>
       <c r="H21" t="n">
-        <v>75.98812561884364</v>
+        <v>75.98812561884228</v>
       </c>
       <c r="I21" t="n">
         <v>1</v>
@@ -1131,16 +1143,16 @@
         <v>477.5</v>
       </c>
       <c r="E22" t="n">
-        <v>28.8504057542612</v>
+        <v>28.85040575426139</v>
       </c>
       <c r="F22" t="n">
-        <v>0.8683134495735332</v>
+        <v>0.8683134495735331</v>
       </c>
       <c r="G22" t="n">
-        <v>0.4187514451780406</v>
+        <v>0.4187514451780739</v>
       </c>
       <c r="H22" t="n">
-        <v>66.49507991121254</v>
+        <v>66.49507991121175</v>
       </c>
       <c r="I22" t="n">
         <v>1</v>
@@ -1164,16 +1176,16 @@
         <v>477.5</v>
       </c>
       <c r="E23" t="n">
-        <v>20.68264901021443</v>
+        <v>20.68264901021485</v>
       </c>
       <c r="F23" t="n">
-        <v>0.8683134495735332</v>
+        <v>0.8683134495735331</v>
       </c>
       <c r="G23" t="n">
-        <v>0.4187514451780406</v>
+        <v>0.4187514451780739</v>
       </c>
       <c r="H23" t="n">
-        <v>16.73815366121784</v>
+        <v>16.73815366121755</v>
       </c>
       <c r="I23" t="n">
         <v>1</v>
@@ -1197,16 +1209,16 @@
         <v>477.5</v>
       </c>
       <c r="E24" t="n">
-        <v>33.97695893289858</v>
+        <v>33.97695893289896</v>
       </c>
       <c r="F24" t="n">
-        <v>0.8683134495735332</v>
+        <v>0.8683134495735331</v>
       </c>
       <c r="G24" t="n">
-        <v>0.4187514451780406</v>
+        <v>0.4187514451780739</v>
       </c>
       <c r="H24" t="n">
-        <v>31.70522980077641</v>
+        <v>31.70522980077607</v>
       </c>
       <c r="I24" t="n">
         <v>1</v>
@@ -1230,16 +1242,16 @@
         <v>477.5</v>
       </c>
       <c r="E25" t="n">
-        <v>24.42143521593185</v>
+        <v>24.42143521593153</v>
       </c>
       <c r="F25" t="n">
-        <v>0.8683134495735332</v>
+        <v>0.8683134495735331</v>
       </c>
       <c r="G25" t="n">
-        <v>0.4187514451780406</v>
+        <v>0.4187514451780739</v>
       </c>
       <c r="H25" t="n">
-        <v>224.9166820391655</v>
+        <v>224.9166820391661</v>
       </c>
       <c r="I25" t="n">
         <v>1</v>
@@ -1263,16 +1275,16 @@
         <v>477.5</v>
       </c>
       <c r="E26" t="n">
-        <v>19.93508148045033</v>
+        <v>19.93508148045045</v>
       </c>
       <c r="F26" t="n">
-        <v>0.8683134495735332</v>
+        <v>0.8683134495735331</v>
       </c>
       <c r="G26" t="n">
-        <v>0.4187514451780406</v>
+        <v>0.4187514451780739</v>
       </c>
       <c r="H26" t="n">
-        <v>289.0489974636977</v>
+        <v>289.0489974636989</v>
       </c>
       <c r="I26" t="n">
         <v>1</v>
@@ -1296,16 +1308,16 @@
         <v>477.5</v>
       </c>
       <c r="E27" t="n">
-        <v>17.39323042390095</v>
+        <v>17.39323042390132</v>
       </c>
       <c r="F27" t="n">
-        <v>0.8683134495735332</v>
+        <v>0.8683134495735331</v>
       </c>
       <c r="G27" t="n">
-        <v>0.4187514451780406</v>
+        <v>0.4187514451780739</v>
       </c>
       <c r="H27" t="n">
-        <v>330.9584587861622</v>
+        <v>330.9584587861629</v>
       </c>
       <c r="I27" t="n">
         <v>1</v>
@@ -1329,16 +1341,16 @@
         <v>477.5</v>
       </c>
       <c r="E28" t="n">
-        <v>31.54206244190063</v>
+        <v>31.54206244190093</v>
       </c>
       <c r="F28" t="n">
-        <v>0.8683134495735332</v>
+        <v>0.8683134495735331</v>
       </c>
       <c r="G28" t="n">
-        <v>0.4187514451780406</v>
+        <v>0.4187514451780739</v>
       </c>
       <c r="H28" t="n">
-        <v>317.9078472739848</v>
+        <v>317.9078472739853</v>
       </c>
       <c r="I28" t="n">
         <v>1</v>
@@ -1362,16 +1374,16 @@
         <v>477.5</v>
       </c>
       <c r="E29" t="n">
-        <v>34.12681411736133</v>
+        <v>34.12681411736173</v>
       </c>
       <c r="F29" t="n">
-        <v>0.8683134495735332</v>
+        <v>0.8683134495735331</v>
       </c>
       <c r="G29" t="n">
-        <v>0.4187514451780406</v>
+        <v>0.4187514451780739</v>
       </c>
       <c r="H29" t="n">
-        <v>343.410863519596</v>
+        <v>343.4108635195962</v>
       </c>
       <c r="I29" t="n">
         <v>1</v>
@@ -1395,16 +1407,16 @@
         <v>477.7</v>
       </c>
       <c r="E30" t="n">
-        <v>17.77016212315933</v>
+        <v>17.77016212315947</v>
       </c>
       <c r="F30" t="n">
-        <v>1.045482249571131</v>
+        <v>1.045482249571132</v>
       </c>
       <c r="G30" t="n">
-        <v>0.4441744183179257</v>
+        <v>0.4441744183178767</v>
       </c>
       <c r="H30" t="n">
-        <v>75.02463810216005</v>
+        <v>75.02463810215875</v>
       </c>
       <c r="I30" t="n">
         <v>1</v>
@@ -1428,16 +1440,16 @@
         <v>477.9</v>
       </c>
       <c r="E31" t="n">
-        <v>25.27200155211774</v>
+        <v>25.2720015521174</v>
       </c>
       <c r="F31" t="n">
-        <v>1.418202143384631</v>
+        <v>1.418202143384633</v>
       </c>
       <c r="G31" t="n">
-        <v>0.4956154509114037</v>
+        <v>0.495615450911271</v>
       </c>
       <c r="H31" t="n">
-        <v>147.7477092702189</v>
+        <v>147.7477092702184</v>
       </c>
       <c r="I31" t="n">
         <v>1</v>
@@ -1461,16 +1473,16 @@
         <v>477.9</v>
       </c>
       <c r="E32" t="n">
-        <v>24.48227615682375</v>
+        <v>24.48227615682355</v>
       </c>
       <c r="F32" t="n">
-        <v>1.418202143384631</v>
+        <v>1.418202143384633</v>
       </c>
       <c r="G32" t="n">
-        <v>0.4956154509114037</v>
+        <v>0.495615450911271</v>
       </c>
       <c r="H32" t="n">
-        <v>121.4471548609175</v>
+        <v>121.4471548609166</v>
       </c>
       <c r="I32" t="n">
         <v>1</v>
@@ -1494,16 +1506,16 @@
         <v>477.9</v>
       </c>
       <c r="E33" t="n">
-        <v>17.75518551360726</v>
+        <v>17.7551855136074</v>
       </c>
       <c r="F33" t="n">
-        <v>1.418202143384631</v>
+        <v>1.418202143384633</v>
       </c>
       <c r="G33" t="n">
-        <v>0.4956154509114037</v>
+        <v>0.495615450911271</v>
       </c>
       <c r="H33" t="n">
-        <v>74.22374930398905</v>
+        <v>74.22374930398774</v>
       </c>
       <c r="I33" t="n">
         <v>1</v>
@@ -1527,16 +1539,16 @@
         <v>477.9</v>
       </c>
       <c r="E34" t="n">
-        <v>28.90724554108034</v>
+        <v>28.90724554108055</v>
       </c>
       <c r="F34" t="n">
-        <v>1.418202143384631</v>
+        <v>1.418202143384633</v>
       </c>
       <c r="G34" t="n">
-        <v>0.4956154509114037</v>
+        <v>0.495615450911271</v>
       </c>
       <c r="H34" t="n">
-        <v>65.41357297581379</v>
+        <v>65.41357297581305</v>
       </c>
       <c r="I34" t="n">
         <v>1</v>
@@ -1560,16 +1572,16 @@
         <v>477.9</v>
       </c>
       <c r="E35" t="n">
-        <v>21.13483570791689</v>
+        <v>21.1348357079173</v>
       </c>
       <c r="F35" t="n">
-        <v>1.418202143384631</v>
+        <v>1.418202143384633</v>
       </c>
       <c r="G35" t="n">
-        <v>0.4956154509114037</v>
+        <v>0.495615450911271</v>
       </c>
       <c r="H35" t="n">
-        <v>15.88950952862376</v>
+        <v>15.88950952862353</v>
       </c>
       <c r="I35" t="n">
         <v>1</v>
@@ -1593,16 +1605,16 @@
         <v>477.9</v>
       </c>
       <c r="E36" t="n">
-        <v>34.33327279134049</v>
+        <v>34.33327279134087</v>
       </c>
       <c r="F36" t="n">
-        <v>1.418202143384631</v>
+        <v>1.418202143384633</v>
       </c>
       <c r="G36" t="n">
-        <v>0.4956154509114037</v>
+        <v>0.495615450911271</v>
       </c>
       <c r="H36" t="n">
-        <v>31.00665599057038</v>
+        <v>31.00665599057004</v>
       </c>
       <c r="I36" t="n">
         <v>1</v>
@@ -1626,16 +1638,16 @@
         <v>477.9</v>
       </c>
       <c r="E37" t="n">
-        <v>24.17763696267771</v>
+        <v>24.17763696267739</v>
       </c>
       <c r="F37" t="n">
-        <v>1.418202143384631</v>
+        <v>1.418202143384633</v>
       </c>
       <c r="G37" t="n">
-        <v>0.4956154509114037</v>
+        <v>0.495615450911271</v>
       </c>
       <c r="H37" t="n">
-        <v>226.0740848978494</v>
+        <v>226.07408489785</v>
       </c>
       <c r="I37" t="n">
         <v>1</v>
@@ -1659,16 +1671,16 @@
         <v>477.9</v>
       </c>
       <c r="E38" t="n">
-        <v>20.27070447692317</v>
+        <v>20.27070447692329</v>
       </c>
       <c r="F38" t="n">
-        <v>1.418202143384631</v>
+        <v>1.418202143384633</v>
       </c>
       <c r="G38" t="n">
-        <v>0.4956154509114037</v>
+        <v>0.495615450911271</v>
       </c>
       <c r="H38" t="n">
-        <v>290.2839506512401</v>
+        <v>290.2839506512412</v>
       </c>
       <c r="I38" t="n">
         <v>1</v>
@@ -1692,16 +1704,16 @@
         <v>477.9</v>
       </c>
       <c r="E39" t="n">
-        <v>17.93161656192241</v>
+        <v>17.93161656192277</v>
       </c>
       <c r="F39" t="n">
-        <v>1.418202143384631</v>
+        <v>1.418202143384633</v>
       </c>
       <c r="G39" t="n">
-        <v>0.4956154509114037</v>
+        <v>0.495615450911271</v>
       </c>
       <c r="H39" t="n">
-        <v>331.2910566370913</v>
+        <v>331.291056637092</v>
       </c>
       <c r="I39" t="n">
         <v>1</v>
@@ -1725,16 +1737,16 @@
         <v>477.9</v>
       </c>
       <c r="E40" t="n">
-        <v>32.04351860897164</v>
+        <v>32.04351860897193</v>
       </c>
       <c r="F40" t="n">
-        <v>1.418202143384631</v>
+        <v>1.418202143384633</v>
       </c>
       <c r="G40" t="n">
-        <v>0.4956154509114037</v>
+        <v>0.495615450911271</v>
       </c>
       <c r="H40" t="n">
-        <v>318.3064240876586</v>
+        <v>318.3064240876592</v>
       </c>
       <c r="I40" t="n">
         <v>1</v>
@@ -1758,16 +1770,16 @@
         <v>477.9</v>
       </c>
       <c r="E41" t="n">
-        <v>34.67468796351897</v>
+        <v>34.67468796351937</v>
       </c>
       <c r="F41" t="n">
-        <v>1.418202143384631</v>
+        <v>1.418202143384633</v>
       </c>
       <c r="G41" t="n">
-        <v>0.4956154509114037</v>
+        <v>0.495615450911271</v>
       </c>
       <c r="H41" t="n">
-        <v>343.3870959852984</v>
+        <v>343.3870959852987</v>
       </c>
       <c r="I41" t="n">
         <v>1</v>
@@ -1791,13 +1803,13 @@
         <v>478</v>
       </c>
       <c r="E42" t="n">
-        <v>17.8129481588545</v>
+        <v>17.81294815885413</v>
       </c>
       <c r="F42" t="n">
-        <v>1.623638544259858</v>
+        <v>1.62363854425986</v>
       </c>
       <c r="G42" t="n">
-        <v>0.508602957748436</v>
+        <v>0.508602957748299</v>
       </c>
       <c r="H42" t="inlineStr"/>
       <c r="I42" t="n">
@@ -1822,13 +1834,13 @@
         <v>478</v>
       </c>
       <c r="E43" t="n">
-        <v>9.54389855385365</v>
+        <v>9.543898553853275</v>
       </c>
       <c r="F43" t="n">
-        <v>1.623638544259858</v>
+        <v>1.62363854425986</v>
       </c>
       <c r="G43" t="n">
-        <v>0.508602957748436</v>
+        <v>0.508602957748299</v>
       </c>
       <c r="H43" t="inlineStr"/>
       <c r="I43" t="n">
@@ -1853,13 +1865,13 @@
         <v>478</v>
       </c>
       <c r="E44" t="n">
-        <v>13.94539471714351</v>
+        <v>13.94539471714343</v>
       </c>
       <c r="F44" t="n">
-        <v>1.623638544259858</v>
+        <v>1.62363854425986</v>
       </c>
       <c r="G44" t="n">
-        <v>0.508602957748436</v>
+        <v>0.508602957748299</v>
       </c>
       <c r="H44" t="inlineStr"/>
       <c r="I44" t="n">
@@ -1884,13 +1896,13 @@
         <v>478</v>
       </c>
       <c r="E45" t="n">
-        <v>7.439521060085759</v>
+        <v>7.43952106008612</v>
       </c>
       <c r="F45" t="n">
-        <v>1.623638544259858</v>
+        <v>1.62363854425986</v>
       </c>
       <c r="G45" t="n">
-        <v>0.508602957748436</v>
+        <v>0.508602957748299</v>
       </c>
       <c r="H45" t="inlineStr"/>
       <c r="I45" t="n">
@@ -1915,13 +1927,13 @@
         <v>478</v>
       </c>
       <c r="E46" t="n">
-        <v>18.20338548735335</v>
+        <v>18.20338548735367</v>
       </c>
       <c r="F46" t="n">
-        <v>1.623638544259858</v>
+        <v>1.62363854425986</v>
       </c>
       <c r="G46" t="n">
-        <v>0.508602957748436</v>
+        <v>0.508602957748299</v>
       </c>
       <c r="H46" t="inlineStr"/>
       <c r="I46" t="n">
@@ -1946,13 +1958,13 @@
         <v>478</v>
       </c>
       <c r="E47" t="n">
-        <v>23.0437599984884</v>
+        <v>23.0437599984888</v>
       </c>
       <c r="F47" t="n">
-        <v>1.623638544259858</v>
+        <v>1.62363854425986</v>
       </c>
       <c r="G47" t="n">
-        <v>0.508602957748436</v>
+        <v>0.508602957748299</v>
       </c>
       <c r="H47" t="inlineStr"/>
       <c r="I47" t="n">
@@ -1977,13 +1989,13 @@
         <v>478.5</v>
       </c>
       <c r="E48" t="n">
-        <v>17.02296815194614</v>
+        <v>17.02296815194579</v>
       </c>
       <c r="F48" t="n">
-        <v>1.868951035126933</v>
+        <v>1.868951035126936</v>
       </c>
       <c r="G48" t="n">
-        <v>0.4667675582714197</v>
+        <v>0.4667675582712987</v>
       </c>
       <c r="H48" t="inlineStr"/>
       <c r="I48" t="n">
@@ -2008,13 +2020,13 @@
         <v>478.5</v>
       </c>
       <c r="E49" t="n">
-        <v>8.729492783941858</v>
+        <v>8.729492783941501</v>
       </c>
       <c r="F49" t="n">
-        <v>1.868951035126933</v>
+        <v>1.868951035126936</v>
       </c>
       <c r="G49" t="n">
-        <v>0.4667675582714197</v>
+        <v>0.4667675582712987</v>
       </c>
       <c r="H49" t="inlineStr"/>
       <c r="I49" t="n">
@@ -2039,13 +2051,13 @@
         <v>478.5</v>
       </c>
       <c r="E50" t="n">
-        <v>13.7838154445814</v>
+        <v>13.78381544458135</v>
       </c>
       <c r="F50" t="n">
-        <v>1.868951035126933</v>
+        <v>1.868951035126936</v>
       </c>
       <c r="G50" t="n">
-        <v>0.4667675582714197</v>
+        <v>0.4667675582712987</v>
       </c>
       <c r="H50" t="inlineStr"/>
       <c r="I50" t="n">
@@ -2070,13 +2082,13 @@
         <v>478.5</v>
       </c>
       <c r="E51" t="n">
-        <v>8.234977819896919</v>
+        <v>8.234977819897287</v>
       </c>
       <c r="F51" t="n">
-        <v>1.868951035126933</v>
+        <v>1.868951035126936</v>
       </c>
       <c r="G51" t="n">
-        <v>0.4667675582714197</v>
+        <v>0.4667675582712987</v>
       </c>
       <c r="H51" t="inlineStr"/>
       <c r="I51" t="n">
@@ -2101,13 +2113,13 @@
         <v>478.5</v>
       </c>
       <c r="E52" t="n">
-        <v>18.8941314690616</v>
+        <v>18.89413146906193</v>
       </c>
       <c r="F52" t="n">
-        <v>1.868951035126933</v>
+        <v>1.868951035126936</v>
       </c>
       <c r="G52" t="n">
-        <v>0.4667675582714197</v>
+        <v>0.4667675582712987</v>
       </c>
       <c r="H52" t="inlineStr"/>
       <c r="I52" t="n">
@@ -2132,13 +2144,13 @@
         <v>478.5</v>
       </c>
       <c r="E53" t="n">
-        <v>23.9073803598767</v>
+        <v>23.90738035987709</v>
       </c>
       <c r="F53" t="n">
-        <v>1.868951035126933</v>
+        <v>1.868951035126936</v>
       </c>
       <c r="G53" t="n">
-        <v>0.4667675582714197</v>
+        <v>0.4667675582712987</v>
       </c>
       <c r="H53" t="inlineStr"/>
       <c r="I53" t="n">
@@ -2163,16 +2175,16 @@
         <v>481.5</v>
       </c>
       <c r="E54" t="n">
-        <v>20.90607911535646</v>
+        <v>20.90607911535624</v>
       </c>
       <c r="F54" t="n">
-        <v>0.8363571031746306</v>
+        <v>0.8363571031746319</v>
       </c>
       <c r="G54" t="n">
-        <v>0.3169657494272692</v>
+        <v>0.3169657494275099</v>
       </c>
       <c r="H54" t="n">
-        <v>133.7901506552612</v>
+        <v>133.7901506552606</v>
       </c>
       <c r="I54" t="n">
         <v>1</v>
@@ -2196,16 +2208,16 @@
         <v>481.5</v>
       </c>
       <c r="E55" t="n">
-        <v>23.24438395171632</v>
+        <v>23.24438395171624</v>
       </c>
       <c r="F55" t="n">
-        <v>0.8363571031746306</v>
+        <v>0.8363571031746319</v>
       </c>
       <c r="G55" t="n">
-        <v>0.3169657494272692</v>
+        <v>0.3169657494275099</v>
       </c>
       <c r="H55" t="n">
-        <v>104.6209105722526</v>
+        <v>104.6209105722519</v>
       </c>
       <c r="I55" t="n">
         <v>1</v>
@@ -2229,16 +2241,16 @@
         <v>481.5</v>
       </c>
       <c r="E56" t="n">
-        <v>22.06880276333557</v>
+        <v>22.06880276333573</v>
       </c>
       <c r="F56" t="n">
-        <v>0.8363571031746306</v>
+        <v>0.8363571031746319</v>
       </c>
       <c r="G56" t="n">
-        <v>0.3169657494272692</v>
+        <v>0.3169657494275099</v>
       </c>
       <c r="H56" t="n">
-        <v>57.8838665316419</v>
+        <v>57.88386653164122</v>
       </c>
       <c r="I56" t="n">
         <v>1</v>
@@ -2262,16 +2274,16 @@
         <v>481.5</v>
       </c>
       <c r="E57" t="n">
-        <v>33.71035482262112</v>
+        <v>33.7103548226213</v>
       </c>
       <c r="F57" t="n">
-        <v>0.8363571031746306</v>
+        <v>0.8363571031746319</v>
       </c>
       <c r="G57" t="n">
-        <v>0.3169657494272692</v>
+        <v>0.3169657494275099</v>
       </c>
       <c r="H57" t="n">
-        <v>55.8317149165353</v>
+        <v>55.83171491653485</v>
       </c>
       <c r="I57" t="n">
         <v>1</v>
@@ -2295,16 +2307,16 @@
         <v>481.5</v>
       </c>
       <c r="E58" t="n">
-        <v>28.21791762943958</v>
+        <v>28.21791762943989</v>
       </c>
       <c r="F58" t="n">
-        <v>0.8363571031746306</v>
+        <v>0.8363571031746319</v>
       </c>
       <c r="G58" t="n">
-        <v>0.3169657494272692</v>
+        <v>0.3169657494275099</v>
       </c>
       <c r="H58" t="n">
-        <v>15.18575795195346</v>
+        <v>15.18575795195329</v>
       </c>
       <c r="I58" t="n">
         <v>1</v>
@@ -2328,16 +2340,16 @@
         <v>481.5</v>
       </c>
       <c r="E59" t="n">
-        <v>18.63516022028482</v>
+        <v>18.63516022028465</v>
       </c>
       <c r="F59" t="n">
-        <v>0.8363571031746306</v>
+        <v>0.8363571031746319</v>
       </c>
       <c r="G59" t="n">
-        <v>0.3169657494272692</v>
+        <v>0.3169657494275099</v>
       </c>
       <c r="H59" t="n">
-        <v>238.0280011047593</v>
+        <v>238.0280011047601</v>
       </c>
       <c r="I59" t="n">
         <v>1</v>
@@ -2361,16 +2373,16 @@
         <v>481.5</v>
       </c>
       <c r="E60" t="n">
-        <v>22.29724992008122</v>
+        <v>22.29724992008142</v>
       </c>
       <c r="F60" t="n">
-        <v>0.8363571031746306</v>
+        <v>0.8363571031746319</v>
       </c>
       <c r="G60" t="n">
-        <v>0.3169657494272692</v>
+        <v>0.3169657494275099</v>
       </c>
       <c r="H60" t="n">
-        <v>308.6716971776825</v>
+        <v>308.6716971776831</v>
       </c>
       <c r="I60" t="n">
         <v>1</v>
@@ -2394,16 +2406,16 @@
         <v>481.5</v>
       </c>
       <c r="E61" t="n">
-        <v>23.69284904889783</v>
+        <v>23.69284904889813</v>
       </c>
       <c r="F61" t="n">
-        <v>0.8363571031746306</v>
+        <v>0.8363571031746319</v>
       </c>
       <c r="G61" t="n">
-        <v>0.3169657494272692</v>
+        <v>0.3169657494275099</v>
       </c>
       <c r="H61" t="n">
-        <v>342.7945061999638</v>
+        <v>342.7945061999641</v>
       </c>
       <c r="I61" t="n">
         <v>1</v>
@@ -2427,16 +2439,16 @@
         <v>481.5</v>
       </c>
       <c r="E62" t="n">
-        <v>36.59326964434835</v>
+        <v>36.59326964434862</v>
       </c>
       <c r="F62" t="n">
-        <v>0.8363571031746306</v>
+        <v>0.8363571031746319</v>
       </c>
       <c r="G62" t="n">
-        <v>0.3169657494272692</v>
+        <v>0.3169657494275099</v>
       </c>
       <c r="H62" t="n">
-        <v>327.4130986474507</v>
+        <v>327.413098647451</v>
       </c>
       <c r="I62" t="n">
         <v>1</v>
@@ -2460,16 +2472,16 @@
         <v>481.9</v>
       </c>
       <c r="E63" t="n">
-        <v>28.30084091899366</v>
+        <v>28.30084091899397</v>
       </c>
       <c r="F63" t="n">
-        <v>0.8535811689563259</v>
+        <v>0.8535811689563272</v>
       </c>
       <c r="G63" t="n">
-        <v>0.2486059090019244</v>
+        <v>0.2486059090016713</v>
       </c>
       <c r="H63" t="n">
-        <v>14.94213082913541</v>
+        <v>14.94213082913524</v>
       </c>
       <c r="I63" t="n">
         <v>1</v>
@@ -2493,16 +2505,16 @@
         <v>482</v>
       </c>
       <c r="E64" t="n">
-        <v>20.73783426178843</v>
+        <v>20.73783426178822</v>
       </c>
       <c r="F64" t="n">
-        <v>1.032208668939236</v>
+        <v>1.032208668939237</v>
       </c>
       <c r="G64" t="n">
-        <v>0.37306756367708</v>
+        <v>0.3730675636768122</v>
       </c>
       <c r="H64" t="n">
-        <v>133.7653436477758</v>
+        <v>133.7653436477751</v>
       </c>
       <c r="I64" t="n">
         <v>1</v>
@@ -2526,16 +2538,16 @@
         <v>482</v>
       </c>
       <c r="E65" t="n">
-        <v>23.10202441216586</v>
+        <v>23.10202441216579</v>
       </c>
       <c r="F65" t="n">
-        <v>1.032208668939236</v>
+        <v>1.032208668939237</v>
       </c>
       <c r="G65" t="n">
-        <v>0.37306756367708</v>
+        <v>0.3730675636768122</v>
       </c>
       <c r="H65" t="n">
-        <v>104.3980909908807</v>
+        <v>104.3980909908801</v>
       </c>
       <c r="I65" t="n">
         <v>1</v>
@@ -2559,16 +2571,16 @@
         <v>482</v>
       </c>
       <c r="E66" t="n">
-        <v>22.03716215779435</v>
+        <v>22.03716215779452</v>
       </c>
       <c r="F66" t="n">
-        <v>1.032208668939236</v>
+        <v>1.032208668939237</v>
       </c>
       <c r="G66" t="n">
-        <v>0.37306756367708</v>
+        <v>0.3730675636768122</v>
       </c>
       <c r="H66" t="n">
-        <v>57.453910054517</v>
+        <v>57.45391005451631</v>
       </c>
       <c r="I66" t="n">
         <v>1</v>
@@ -2592,16 +2604,16 @@
         <v>482</v>
       </c>
       <c r="E67" t="n">
-        <v>33.68444723837085</v>
+        <v>33.68444723837103</v>
       </c>
       <c r="F67" t="n">
-        <v>1.032208668939236</v>
+        <v>1.032208668939237</v>
       </c>
       <c r="G67" t="n">
-        <v>0.37306756367708</v>
+        <v>0.3730675636768122</v>
       </c>
       <c r="H67" t="n">
-        <v>55.54864409427717</v>
+        <v>55.54864409427677</v>
       </c>
       <c r="I67" t="n">
         <v>1</v>
@@ -2625,16 +2637,16 @@
         <v>482</v>
       </c>
       <c r="E68" t="n">
-        <v>28.30671346860207</v>
+        <v>28.30671346860237</v>
       </c>
       <c r="F68" t="n">
-        <v>1.032208668939236</v>
+        <v>1.032208668939237</v>
       </c>
       <c r="G68" t="n">
-        <v>0.37306756367708</v>
+        <v>0.3730675636768122</v>
       </c>
       <c r="H68" t="n">
-        <v>14.89547364799557</v>
+        <v>14.8954736479954</v>
       </c>
       <c r="I68" t="n">
         <v>1</v>
@@ -2658,16 +2670,16 @@
         <v>482</v>
       </c>
       <c r="E69" t="n">
-        <v>18.66856892870222</v>
+        <v>18.66856892870205</v>
       </c>
       <c r="F69" t="n">
-        <v>1.032208668939236</v>
+        <v>1.032208668939237</v>
       </c>
       <c r="G69" t="n">
-        <v>0.37306756367708</v>
+        <v>0.3730675636768122</v>
       </c>
       <c r="H69" t="n">
-        <v>238.5352909530305</v>
+        <v>238.5352909530313</v>
       </c>
       <c r="I69" t="n">
         <v>1</v>
@@ -2691,16 +2703,16 @@
         <v>482</v>
       </c>
       <c r="E70" t="n">
-        <v>22.46403754543183</v>
+        <v>22.46403754543202</v>
       </c>
       <c r="F70" t="n">
-        <v>1.032208668939236</v>
+        <v>1.032208668939237</v>
       </c>
       <c r="G70" t="n">
-        <v>0.37306756367708</v>
+        <v>0.3730675636768122</v>
       </c>
       <c r="H70" t="n">
-        <v>308.7327908650488</v>
+        <v>308.7327908650494</v>
       </c>
       <c r="I70" t="n">
         <v>1</v>
@@ -2724,16 +2736,16 @@
         <v>482</v>
       </c>
       <c r="E71" t="n">
-        <v>23.84446236586782</v>
+        <v>23.84446236586811</v>
       </c>
       <c r="F71" t="n">
-        <v>1.032208668939236</v>
+        <v>1.032208668939237</v>
       </c>
       <c r="G71" t="n">
-        <v>0.37306756367708</v>
+        <v>0.3730675636768122</v>
       </c>
       <c r="H71" t="n">
-        <v>342.6173494649419</v>
+        <v>342.6173494649422</v>
       </c>
       <c r="I71" t="n">
         <v>1</v>
@@ -2757,16 +2769,16 @@
         <v>482</v>
       </c>
       <c r="E72" t="n">
-        <v>36.75891087370902</v>
+        <v>36.75891087370928</v>
       </c>
       <c r="F72" t="n">
-        <v>1.032208668939236</v>
+        <v>1.032208668939237</v>
       </c>
       <c r="G72" t="n">
-        <v>0.37306756367708</v>
+        <v>0.3730675636768122</v>
       </c>
       <c r="H72" t="n">
-        <v>327.3649331180678</v>
+        <v>327.3649331180681</v>
       </c>
       <c r="I72" t="n">
         <v>1</v>
@@ -2790,16 +2802,16 @@
         <v>482.1</v>
       </c>
       <c r="E73" t="n">
-        <v>23.07067703184158</v>
+        <v>23.07067703184151</v>
       </c>
       <c r="F73" t="n">
-        <v>1.207558585311021</v>
+        <v>1.207558585311022</v>
       </c>
       <c r="G73" t="n">
-        <v>0.4708605431562824</v>
+        <v>0.4708605431560113</v>
       </c>
       <c r="H73" t="n">
-        <v>104.2851528049034</v>
+        <v>104.2851528049026</v>
       </c>
       <c r="I73" t="n">
         <v>1</v>
@@ -2823,13 +2835,13 @@
         <v>482.2</v>
       </c>
       <c r="E74" t="n">
-        <v>11.5578641093861</v>
+        <v>11.5578641093859</v>
       </c>
       <c r="F74" t="n">
-        <v>1.375716985626096</v>
+        <v>1.375716985626097</v>
       </c>
       <c r="G74" t="n">
-        <v>0.530587150405935</v>
+        <v>0.530587150405662</v>
       </c>
       <c r="H74" t="inlineStr"/>
       <c r="I74" t="n">
@@ -2854,13 +2866,13 @@
         <v>482.2</v>
       </c>
       <c r="E75" t="n">
-        <v>13.40559926997767</v>
+        <v>13.40559926997779</v>
       </c>
       <c r="F75" t="n">
-        <v>1.375716985626096</v>
+        <v>1.375716985626097</v>
       </c>
       <c r="G75" t="n">
-        <v>0.530587150405935</v>
+        <v>0.530587150405662</v>
       </c>
       <c r="H75" t="inlineStr"/>
       <c r="I75" t="n">
@@ -2885,13 +2897,13 @@
         <v>482.2</v>
       </c>
       <c r="E76" t="n">
-        <v>13.74803099687371</v>
+        <v>13.74803099687402</v>
       </c>
       <c r="F76" t="n">
-        <v>1.375716985626096</v>
+        <v>1.375716985626097</v>
       </c>
       <c r="G76" t="n">
-        <v>0.530587150405935</v>
+        <v>0.530587150405662</v>
       </c>
       <c r="H76" t="inlineStr"/>
       <c r="I76" t="n">
@@ -2916,13 +2928,13 @@
         <v>482.2</v>
       </c>
       <c r="E77" t="n">
-        <v>23.47127147255534</v>
+        <v>23.47127147255562</v>
       </c>
       <c r="F77" t="n">
-        <v>1.375716985626096</v>
+        <v>1.375716985626097</v>
       </c>
       <c r="G77" t="n">
-        <v>0.530587150405935</v>
+        <v>0.530587150405662</v>
       </c>
       <c r="H77" t="inlineStr"/>
       <c r="I77" t="n">
@@ -2947,13 +2959,13 @@
         <v>482.2</v>
       </c>
       <c r="E78" t="n">
-        <v>29.54252021058749</v>
+        <v>29.5425202105878</v>
       </c>
       <c r="F78" t="n">
-        <v>1.375716985626096</v>
+        <v>1.375716985626097</v>
       </c>
       <c r="G78" t="n">
-        <v>0.530587150405935</v>
+        <v>0.530587150405662</v>
       </c>
       <c r="H78" t="inlineStr"/>
       <c r="I78" t="n">
@@ -2978,16 +2990,16 @@
         <v>482.2</v>
       </c>
       <c r="E79" t="n">
-        <v>20.63985779840226</v>
+        <v>20.63985779840205</v>
       </c>
       <c r="F79" t="n">
-        <v>1.375716985626096</v>
+        <v>1.375716985626097</v>
       </c>
       <c r="G79" t="n">
-        <v>0.530587150405935</v>
+        <v>0.530587150405662</v>
       </c>
       <c r="H79" t="n">
-        <v>133.4132475672204</v>
+        <v>133.4132475672197</v>
       </c>
       <c r="I79" t="n">
         <v>1</v>
@@ -3011,16 +3023,16 @@
         <v>482.2</v>
       </c>
       <c r="E80" t="n">
-        <v>23.07904611964515</v>
+        <v>23.07904611964508</v>
       </c>
       <c r="F80" t="n">
-        <v>1.375716985626096</v>
+        <v>1.375716985626097</v>
       </c>
       <c r="G80" t="n">
-        <v>0.530587150405935</v>
+        <v>0.530587150405662</v>
       </c>
       <c r="H80" t="n">
-        <v>104.0039119256678</v>
+        <v>104.003911925667</v>
       </c>
       <c r="I80" t="n">
         <v>1</v>
@@ -3044,16 +3056,16 @@
         <v>482.2</v>
       </c>
       <c r="E81" t="n">
-        <v>22.13747399248892</v>
+        <v>22.13747399248909</v>
       </c>
       <c r="F81" t="n">
-        <v>1.375716985626096</v>
+        <v>1.375716985626097</v>
       </c>
       <c r="G81" t="n">
-        <v>0.530587150405935</v>
+        <v>0.530587150405662</v>
       </c>
       <c r="H81" t="n">
-        <v>57.1288658675299</v>
+        <v>57.12886586752921</v>
       </c>
       <c r="I81" t="n">
         <v>1</v>
@@ -3077,16 +3089,16 @@
         <v>482.2</v>
       </c>
       <c r="E82" t="n">
-        <v>33.78874393728236</v>
+        <v>33.78874393728254</v>
       </c>
       <c r="F82" t="n">
-        <v>1.375716985626096</v>
+        <v>1.375716985626097</v>
       </c>
       <c r="G82" t="n">
-        <v>0.530587150405935</v>
+        <v>0.530587150405662</v>
       </c>
       <c r="H82" t="n">
-        <v>55.34143754606151</v>
+        <v>55.34143754606106</v>
       </c>
       <c r="I82" t="n">
         <v>1</v>
@@ -3110,16 +3122,16 @@
         <v>482.2</v>
       </c>
       <c r="E83" t="n">
-        <v>28.46529034690223</v>
+        <v>28.46529034690253</v>
       </c>
       <c r="F83" t="n">
-        <v>1.375716985626096</v>
+        <v>1.375716985626097</v>
       </c>
       <c r="G83" t="n">
-        <v>0.530587150405935</v>
+        <v>0.530587150405662</v>
       </c>
       <c r="H83" t="n">
-        <v>14.84535038088848</v>
+        <v>14.84535038088831</v>
       </c>
       <c r="I83" t="n">
         <v>1</v>
@@ -3143,16 +3155,16 @@
         <v>482.2</v>
       </c>
       <c r="E84" t="n">
-        <v>18.57143861973628</v>
+        <v>18.57143861973612</v>
       </c>
       <c r="F84" t="n">
-        <v>1.375716985626096</v>
+        <v>1.375716985626097</v>
       </c>
       <c r="G84" t="n">
-        <v>0.530587150405935</v>
+        <v>0.530587150405662</v>
       </c>
       <c r="H84" t="n">
-        <v>238.9285010975934</v>
+        <v>238.9285010975942</v>
       </c>
       <c r="I84" t="n">
         <v>1</v>
@@ -3176,16 +3188,16 @@
         <v>482.2</v>
       </c>
       <c r="E85" t="n">
-        <v>22.55130219512326</v>
+        <v>22.55130219512344</v>
       </c>
       <c r="F85" t="n">
-        <v>1.375716985626096</v>
+        <v>1.375716985626097</v>
       </c>
       <c r="G85" t="n">
-        <v>0.530587150405935</v>
+        <v>0.530587150405662</v>
       </c>
       <c r="H85" t="n">
-        <v>309.0757242950069</v>
+        <v>309.0757242950075</v>
       </c>
       <c r="I85" t="n">
         <v>1</v>
@@ -3209,16 +3221,16 @@
         <v>482.2</v>
       </c>
       <c r="E86" t="n">
-        <v>23.99190719369075</v>
+        <v>23.99190719369104</v>
       </c>
       <c r="F86" t="n">
-        <v>1.375716985626096</v>
+        <v>1.375716985626097</v>
       </c>
       <c r="G86" t="n">
-        <v>0.530587150405935</v>
+        <v>0.530587150405662</v>
       </c>
       <c r="H86" t="n">
-        <v>342.7692949318885</v>
+        <v>342.7692949318887</v>
       </c>
       <c r="I86" t="n">
         <v>1</v>
@@ -3242,16 +3254,16 @@
         <v>482.2</v>
       </c>
       <c r="E87" t="n">
-        <v>36.88447870118346</v>
+        <v>36.88447870118372</v>
       </c>
       <c r="F87" t="n">
-        <v>1.375716985626096</v>
+        <v>1.375716985626097</v>
       </c>
       <c r="G87" t="n">
-        <v>0.530587150405935</v>
+        <v>0.530587150405662</v>
       </c>
       <c r="H87" t="n">
-        <v>327.5205055625799</v>
+        <v>327.5205055625801</v>
       </c>
       <c r="I87" t="n">
         <v>1</v>
@@ -3275,13 +3287,13 @@
         <v>482.3</v>
       </c>
       <c r="E88" t="n">
-        <v>13.39667329560325</v>
+        <v>13.39667329560337</v>
       </c>
       <c r="F88" t="n">
-        <v>1.538291490633287</v>
+        <v>1.538291490633289</v>
       </c>
       <c r="G88" t="n">
-        <v>0.5396734574155237</v>
+        <v>0.5396734574152625</v>
       </c>
       <c r="H88" t="inlineStr"/>
       <c r="I88" t="n">
@@ -3306,13 +3318,13 @@
         <v>482.4</v>
       </c>
       <c r="E89" t="n">
-        <v>29.95834270574074</v>
+        <v>29.95834270574105</v>
       </c>
       <c r="F89" t="n">
-        <v>1.646085468121058</v>
+        <v>1.646085468121059</v>
       </c>
       <c r="G89" t="n">
-        <v>0.5053269988499126</v>
+        <v>0.5053269988496767</v>
       </c>
       <c r="H89" t="inlineStr"/>
       <c r="I89" t="n">
@@ -3337,13 +3349,13 @@
         <v>482.6</v>
       </c>
       <c r="E90" t="n">
-        <v>10.69126608630007</v>
+        <v>10.69126608629989</v>
       </c>
       <c r="F90" t="n">
-        <v>1.927836781024825</v>
+        <v>1.927836781024827</v>
       </c>
       <c r="G90" t="n">
-        <v>0.5640036702996662</v>
+        <v>0.5640036702994704</v>
       </c>
       <c r="H90" t="inlineStr"/>
       <c r="I90" t="n">
@@ -3368,13 +3380,13 @@
         <v>482.6</v>
       </c>
       <c r="E91" t="n">
-        <v>13.40914089020683</v>
+        <v>13.40914089020697</v>
       </c>
       <c r="F91" t="n">
-        <v>1.927836781024825</v>
+        <v>1.927836781024827</v>
       </c>
       <c r="G91" t="n">
-        <v>0.5640036702996662</v>
+        <v>0.5640036702994704</v>
       </c>
       <c r="H91" t="inlineStr"/>
       <c r="I91" t="n">
@@ -3399,13 +3411,13 @@
         <v>482.6</v>
       </c>
       <c r="E92" t="n">
-        <v>14.56105891840807</v>
+        <v>14.56105891840837</v>
       </c>
       <c r="F92" t="n">
-        <v>1.927836781024825</v>
+        <v>1.927836781024827</v>
       </c>
       <c r="G92" t="n">
-        <v>0.5640036702996662</v>
+        <v>0.5640036702994704</v>
       </c>
       <c r="H92" t="inlineStr"/>
       <c r="I92" t="n">
@@ -3430,13 +3442,13 @@
         <v>482.6</v>
       </c>
       <c r="E93" t="n">
-        <v>24.1075281305406</v>
+        <v>24.10752813054088</v>
       </c>
       <c r="F93" t="n">
-        <v>1.927836781024825</v>
+        <v>1.927836781024827</v>
       </c>
       <c r="G93" t="n">
-        <v>0.5640036702996662</v>
+        <v>0.5640036702994704</v>
       </c>
       <c r="H93" t="inlineStr"/>
       <c r="I93" t="n">
@@ -3461,13 +3473,13 @@
         <v>488.9</v>
       </c>
       <c r="E94" t="n">
-        <v>14.66954673566902</v>
+        <v>14.66954673566905</v>
       </c>
       <c r="F94" t="n">
         <v>1.287848736592752</v>
       </c>
       <c r="G94" t="n">
-        <v>1.267301538357042</v>
+        <v>1.267301538357066</v>
       </c>
       <c r="H94" t="n">
         <v>71.1096553597875</v>
@@ -3494,13 +3506,13 @@
         <v>488.9</v>
       </c>
       <c r="E95" t="n">
-        <v>25.12012652366757</v>
+        <v>25.1201265236676</v>
       </c>
       <c r="F95" t="n">
         <v>1.287848736592752</v>
       </c>
       <c r="G95" t="n">
-        <v>1.267301538357042</v>
+        <v>1.267301538357066</v>
       </c>
       <c r="H95" t="n">
         <v>57.8984294903189</v>
@@ -3527,16 +3539,16 @@
         <v>488.9</v>
       </c>
       <c r="E96" t="n">
-        <v>22.74661326445493</v>
+        <v>22.74661326445495</v>
       </c>
       <c r="F96" t="n">
         <v>1.287848736592752</v>
       </c>
       <c r="G96" t="n">
-        <v>1.267301538357042</v>
+        <v>1.267301538357066</v>
       </c>
       <c r="H96" t="n">
-        <v>17.86856123855381</v>
+        <v>17.86856123855387</v>
       </c>
       <c r="I96" t="n">
         <v>1</v>
@@ -3560,13 +3572,13 @@
         <v>488.9</v>
       </c>
       <c r="E97" t="n">
-        <v>35.54427181051184</v>
+        <v>35.54427181051186</v>
       </c>
       <c r="F97" t="n">
         <v>1.287848736592752</v>
       </c>
       <c r="G97" t="n">
-        <v>1.267301538357042</v>
+        <v>1.267301538357066</v>
       </c>
       <c r="H97" t="n">
         <v>29.45668403856541</v>
@@ -3593,16 +3605,16 @@
         <v>488.9</v>
       </c>
       <c r="E98" t="n">
-        <v>19.41932769318595</v>
+        <v>19.41932769318594</v>
       </c>
       <c r="F98" t="n">
         <v>1.287848736592752</v>
       </c>
       <c r="G98" t="n">
-        <v>1.267301538357042</v>
+        <v>1.267301538357066</v>
       </c>
       <c r="H98" t="n">
-        <v>298.7799700309647</v>
+        <v>298.7799700309648</v>
       </c>
       <c r="I98" t="n">
         <v>1</v>
@@ -3626,16 +3638,16 @@
         <v>488.9</v>
       </c>
       <c r="E99" t="n">
-        <v>21.71549873639937</v>
+        <v>21.71549873639938</v>
       </c>
       <c r="F99" t="n">
         <v>1.287848736592752</v>
       </c>
       <c r="G99" t="n">
-        <v>1.267301538357042</v>
+        <v>1.267301538357066</v>
       </c>
       <c r="H99" t="n">
-        <v>341.9719835904698</v>
+        <v>341.97198359047</v>
       </c>
       <c r="I99" t="n">
         <v>1</v>
@@ -3665,10 +3677,10 @@
         <v>1.287848736592752</v>
       </c>
       <c r="G100" t="n">
-        <v>1.267301538357042</v>
+        <v>1.267301538357066</v>
       </c>
       <c r="H100" t="n">
-        <v>330.676358241945</v>
+        <v>330.6763582419451</v>
       </c>
       <c r="I100" t="n">
         <v>1</v>
@@ -3692,13 +3704,13 @@
         <v>489.1</v>
       </c>
       <c r="E101" t="n">
-        <v>14.57968142715013</v>
+        <v>14.57968142715015</v>
       </c>
       <c r="F101" t="n">
-        <v>1.469651081991791</v>
+        <v>1.469651081991792</v>
       </c>
       <c r="G101" t="n">
-        <v>1.349932170353143</v>
+        <v>1.349932170353165</v>
       </c>
       <c r="H101" t="n">
         <v>69.49058336901771</v>
@@ -3725,13 +3737,13 @@
         <v>489.1</v>
       </c>
       <c r="E102" t="n">
-        <v>25.12467779092843</v>
+        <v>25.12467779092845</v>
       </c>
       <c r="F102" t="n">
-        <v>1.469651081991791</v>
+        <v>1.469651081991792</v>
       </c>
       <c r="G102" t="n">
-        <v>1.349932170353143</v>
+        <v>1.349932170353165</v>
       </c>
       <c r="H102" t="n">
         <v>56.93396512547889</v>
@@ -3758,16 +3770,16 @@
         <v>489.1</v>
       </c>
       <c r="E103" t="n">
-        <v>23.0216486691886</v>
+        <v>23.02164866918862</v>
       </c>
       <c r="F103" t="n">
-        <v>1.469651081991791</v>
+        <v>1.469651081991792</v>
       </c>
       <c r="G103" t="n">
-        <v>1.349932170353143</v>
+        <v>1.349932170353165</v>
       </c>
       <c r="H103" t="n">
-        <v>17.06419922273255</v>
+        <v>17.06419922273261</v>
       </c>
       <c r="I103" t="n">
         <v>1</v>
@@ -3791,13 +3803,13 @@
         <v>489.1</v>
       </c>
       <c r="E104" t="n">
-        <v>35.74848829281528</v>
+        <v>35.7484882928153</v>
       </c>
       <c r="F104" t="n">
-        <v>1.469651081991791</v>
+        <v>1.469651081991792</v>
       </c>
       <c r="G104" t="n">
-        <v>1.349932170353143</v>
+        <v>1.349932170353165</v>
       </c>
       <c r="H104" t="n">
         <v>28.86143011596533</v>
@@ -3824,16 +3836,16 @@
         <v>489.1</v>
       </c>
       <c r="E105" t="n">
-        <v>19.78938114818741</v>
+        <v>19.78938114818739</v>
       </c>
       <c r="F105" t="n">
-        <v>1.469651081991791</v>
+        <v>1.469651081991792</v>
       </c>
       <c r="G105" t="n">
-        <v>1.349932170353143</v>
+        <v>1.349932170353165</v>
       </c>
       <c r="H105" t="n">
-        <v>299.3783177691982</v>
+        <v>299.3783177691983</v>
       </c>
       <c r="I105" t="n">
         <v>1</v>
@@ -3860,13 +3872,13 @@
         <v>22.12618635458189</v>
       </c>
       <c r="F106" t="n">
-        <v>1.469651081991791</v>
+        <v>1.469651081991792</v>
       </c>
       <c r="G106" t="n">
-        <v>1.349932170353143</v>
+        <v>1.349932170353165</v>
       </c>
       <c r="H106" t="n">
-        <v>341.7081776762602</v>
+        <v>341.7081776762603</v>
       </c>
       <c r="I106" t="n">
         <v>1</v>
@@ -3893,10 +3905,10 @@
         <v>38.44359654404074</v>
       </c>
       <c r="F107" t="n">
-        <v>1.469651081991791</v>
+        <v>1.469651081991792</v>
       </c>
       <c r="G107" t="n">
-        <v>1.349932170353143</v>
+        <v>1.349932170353165</v>
       </c>
       <c r="H107" t="n">
         <v>330.6472875050372</v>
@@ -3923,16 +3935,16 @@
         <v>493.1</v>
       </c>
       <c r="E108" t="n">
-        <v>18.95471440698903</v>
+        <v>18.95471440698913</v>
       </c>
       <c r="F108" t="n">
-        <v>0.3841216179500925</v>
+        <v>0.3841216179500923</v>
       </c>
       <c r="G108" t="n">
-        <v>0.4936339235364577</v>
+        <v>0.4936339235363214</v>
       </c>
       <c r="H108" t="n">
-        <v>37.36016174669368</v>
+        <v>37.36016174669413</v>
       </c>
       <c r="I108" t="n">
         <v>1</v>
@@ -3956,16 +3968,16 @@
         <v>493.1</v>
       </c>
       <c r="E109" t="n">
-        <v>23.53281403354972</v>
+        <v>23.53281403354969</v>
       </c>
       <c r="F109" t="n">
-        <v>0.3841216179500925</v>
+        <v>0.3841216179500923</v>
       </c>
       <c r="G109" t="n">
-        <v>0.4936339235364577</v>
+        <v>0.4936339235363214</v>
       </c>
       <c r="H109" t="n">
-        <v>353.1719032514777</v>
+        <v>353.1719032514781</v>
       </c>
       <c r="I109" t="n">
         <v>1</v>
@@ -3989,16 +4001,16 @@
         <v>493.1</v>
       </c>
       <c r="E110" t="n">
-        <v>33.56165314050959</v>
+        <v>33.56165314050962</v>
       </c>
       <c r="F110" t="n">
-        <v>0.3841216179500925</v>
+        <v>0.3841216179500923</v>
       </c>
       <c r="G110" t="n">
-        <v>0.4936339235364577</v>
+        <v>0.4936339235363214</v>
       </c>
       <c r="H110" t="n">
-        <v>13.26722165403316</v>
+        <v>13.26722165403345</v>
       </c>
       <c r="I110" t="n">
         <v>1</v>
@@ -4022,16 +4034,16 @@
         <v>493.1</v>
       </c>
       <c r="E111" t="n">
-        <v>28.99272826013112</v>
+        <v>28.99272826013096</v>
       </c>
       <c r="F111" t="n">
-        <v>0.3841216179500925</v>
+        <v>0.3841216179500923</v>
       </c>
       <c r="G111" t="n">
-        <v>0.4936339235364577</v>
+        <v>0.4936339235363214</v>
       </c>
       <c r="H111" t="n">
-        <v>292.4376967911835</v>
+        <v>292.4376967911836</v>
       </c>
       <c r="I111" t="n">
         <v>1</v>
@@ -4055,16 +4067,16 @@
         <v>493.1</v>
       </c>
       <c r="E112" t="n">
-        <v>27.79230587376752</v>
+        <v>27.7923058737674</v>
       </c>
       <c r="F112" t="n">
-        <v>0.3841216179500925</v>
+        <v>0.3841216179500923</v>
       </c>
       <c r="G112" t="n">
-        <v>0.4936339235364577</v>
+        <v>0.4936339235363214</v>
       </c>
       <c r="H112" t="n">
-        <v>323.5862756682913</v>
+        <v>323.5862756682916</v>
       </c>
       <c r="I112" t="n">
         <v>1</v>
@@ -4088,16 +4100,16 @@
         <v>493.6</v>
       </c>
       <c r="E113" t="n">
-        <v>19.03579422610053</v>
+        <v>19.03579422610062</v>
       </c>
       <c r="F113" t="n">
-        <v>0.3067760547763284</v>
+        <v>0.3067760547763293</v>
       </c>
       <c r="G113" t="n">
-        <v>0.6054512777350818</v>
+        <v>0.605451277735005</v>
       </c>
       <c r="H113" t="n">
-        <v>35.1911451533897</v>
+        <v>35.19114515339015</v>
       </c>
       <c r="I113" t="n">
         <v>1</v>
@@ -4121,16 +4133,16 @@
         <v>493.6</v>
       </c>
       <c r="E114" t="n">
-        <v>24.08792184815721</v>
+        <v>24.08792184815716</v>
       </c>
       <c r="F114" t="n">
-        <v>0.3067760547763284</v>
+        <v>0.3067760547763293</v>
       </c>
       <c r="G114" t="n">
-        <v>0.6054512777350818</v>
+        <v>0.605451277735005</v>
       </c>
       <c r="H114" t="n">
-        <v>352.0548424030947</v>
+        <v>352.0548424030952</v>
       </c>
       <c r="I114" t="n">
         <v>1</v>
@@ -4154,16 +4166,16 @@
         <v>493.6</v>
       </c>
       <c r="E115" t="n">
-        <v>33.92317581520486</v>
+        <v>33.92317581520488</v>
       </c>
       <c r="F115" t="n">
-        <v>0.3067760547763284</v>
+        <v>0.3067760547763293</v>
       </c>
       <c r="G115" t="n">
-        <v>0.6054512777350818</v>
+        <v>0.605451277735005</v>
       </c>
       <c r="H115" t="n">
-        <v>12.20282468151788</v>
+        <v>12.20282468151822</v>
       </c>
       <c r="I115" t="n">
         <v>1</v>
@@ -4187,16 +4199,16 @@
         <v>493.6</v>
       </c>
       <c r="E116" t="n">
-        <v>29.67257920687663</v>
+        <v>29.67257920687645</v>
       </c>
       <c r="F116" t="n">
-        <v>0.3067760547763284</v>
+        <v>0.3067760547763293</v>
       </c>
       <c r="G116" t="n">
-        <v>0.6054512777350818</v>
+        <v>0.605451277735005</v>
       </c>
       <c r="H116" t="n">
-        <v>292.9217733735814</v>
+        <v>292.9217733735815</v>
       </c>
       <c r="I116" t="n">
         <v>1</v>
@@ -4220,16 +4232,16 @@
         <v>493.6</v>
       </c>
       <c r="E117" t="n">
-        <v>28.50323576591579</v>
+        <v>28.50323576591566</v>
       </c>
       <c r="F117" t="n">
-        <v>0.3067760547763284</v>
+        <v>0.3067760547763293</v>
       </c>
       <c r="G117" t="n">
-        <v>0.6054512777350818</v>
+        <v>0.605451277735005</v>
       </c>
       <c r="H117" t="n">
-        <v>323.3117658338113</v>
+        <v>323.3117658338116</v>
       </c>
       <c r="I117" t="n">
         <v>1</v>
@@ -4253,13 +4265,13 @@
         <v>494</v>
       </c>
       <c r="E118" t="n">
-        <v>24.46685406629341</v>
+        <v>24.46685406629324</v>
       </c>
       <c r="F118" t="n">
-        <v>0.5435919395252032</v>
+        <v>0.5435919395252038</v>
       </c>
       <c r="G118" t="n">
-        <v>0.3514294158389066</v>
+        <v>0.3514294158389191</v>
       </c>
       <c r="H118" t="inlineStr"/>
       <c r="I118" t="n">
@@ -4284,13 +4296,13 @@
         <v>494</v>
       </c>
       <c r="E119" t="n">
-        <v>24.94375607943649</v>
+        <v>24.94375607943637</v>
       </c>
       <c r="F119" t="n">
-        <v>0.5435919395252032</v>
+        <v>0.5435919395252038</v>
       </c>
       <c r="G119" t="n">
-        <v>0.3514294158389066</v>
+        <v>0.3514294158389191</v>
       </c>
       <c r="H119" t="inlineStr"/>
       <c r="I119" t="n">
@@ -4315,16 +4327,16 @@
         <v>494.1</v>
       </c>
       <c r="E120" t="n">
-        <v>18.60756433081292</v>
+        <v>18.60756433081302</v>
       </c>
       <c r="F120" t="n">
-        <v>0.6403564206882054</v>
+        <v>0.6403564206882053</v>
       </c>
       <c r="G120" t="n">
-        <v>0.3325233326922695</v>
+        <v>0.3325233326923064</v>
       </c>
       <c r="H120" t="n">
-        <v>34.90756550742606</v>
+        <v>34.90756550742657</v>
       </c>
       <c r="I120" t="n">
         <v>1</v>
@@ -4348,16 +4360,16 @@
         <v>494.1</v>
       </c>
       <c r="E121" t="n">
-        <v>23.84095350558762</v>
+        <v>23.84095350558757</v>
       </c>
       <c r="F121" t="n">
-        <v>0.6403564206882054</v>
+        <v>0.6403564206882053</v>
       </c>
       <c r="G121" t="n">
-        <v>0.3325233326922695</v>
+        <v>0.3325233326923064</v>
       </c>
       <c r="H121" t="n">
-        <v>351.1892615877128</v>
+        <v>351.1892615877132</v>
       </c>
       <c r="I121" t="n">
         <v>1</v>
@@ -4381,16 +4393,16 @@
         <v>494.1</v>
       </c>
       <c r="E122" t="n">
-        <v>33.56565848335216</v>
+        <v>33.56565848335218</v>
       </c>
       <c r="F122" t="n">
-        <v>0.6403564206882054</v>
+        <v>0.6403564206882053</v>
       </c>
       <c r="G122" t="n">
-        <v>0.3325233326922695</v>
+        <v>0.3325233326923064</v>
       </c>
       <c r="H122" t="n">
-        <v>11.77246900561306</v>
+        <v>11.7724690056134</v>
       </c>
       <c r="I122" t="n">
         <v>1</v>
@@ -4414,16 +4426,16 @@
         <v>494.1</v>
       </c>
       <c r="E123" t="n">
-        <v>29.85628987038115</v>
+        <v>29.85628987038097</v>
       </c>
       <c r="F123" t="n">
-        <v>0.6403564206882054</v>
+        <v>0.6403564206882053</v>
       </c>
       <c r="G123" t="n">
-        <v>0.3325233326922695</v>
+        <v>0.3325233326923064</v>
       </c>
       <c r="H123" t="n">
-        <v>292.1558560159805</v>
+        <v>292.1558560159806</v>
       </c>
       <c r="I123" t="n">
         <v>1</v>
@@ -4447,16 +4459,16 @@
         <v>494.1</v>
       </c>
       <c r="E124" t="n">
-        <v>28.46084326420072</v>
+        <v>28.46084326420059</v>
       </c>
       <c r="F124" t="n">
-        <v>0.6403564206882054</v>
+        <v>0.6403564206882053</v>
       </c>
       <c r="G124" t="n">
-        <v>0.3325233326922695</v>
+        <v>0.3325233326923064</v>
       </c>
       <c r="H124" t="n">
-        <v>322.4342997022271</v>
+        <v>322.4342997022275</v>
       </c>
       <c r="I124" t="n">
         <v>1</v>
@@ -4480,13 +4492,13 @@
         <v>494.5</v>
       </c>
       <c r="E125" t="n">
-        <v>24.58672252128207</v>
+        <v>24.58672252128189</v>
       </c>
       <c r="F125" t="n">
-        <v>0.7617148967029593</v>
+        <v>0.7617148967029598</v>
       </c>
       <c r="G125" t="n">
-        <v>0.3501366993007068</v>
+        <v>0.3501366993008572</v>
       </c>
       <c r="H125" t="inlineStr"/>
       <c r="I125" t="n">
@@ -4511,13 +4523,13 @@
         <v>494.5</v>
       </c>
       <c r="E126" t="n">
-        <v>24.91605914968147</v>
+        <v>24.91605914968134</v>
       </c>
       <c r="F126" t="n">
-        <v>0.7617148967029593</v>
+        <v>0.7617148967029598</v>
       </c>
       <c r="G126" t="n">
-        <v>0.3501366993007068</v>
+        <v>0.3501366993008572</v>
       </c>
       <c r="H126" t="inlineStr"/>
       <c r="I126" t="n">
@@ -4542,16 +4554,16 @@
         <v>494.6</v>
       </c>
       <c r="E127" t="n">
-        <v>18.18094658998797</v>
+        <v>18.18094658998807</v>
       </c>
       <c r="F127" t="n">
-        <v>0.7778113873489795</v>
+        <v>0.7778113873489796</v>
       </c>
       <c r="G127" t="n">
-        <v>0.497613572527272</v>
+        <v>0.4976135725274385</v>
       </c>
       <c r="H127" t="n">
-        <v>35.20553834499077</v>
+        <v>35.20553834499128</v>
       </c>
       <c r="I127" t="n">
         <v>1</v>
@@ -4575,16 +4587,16 @@
         <v>494.6</v>
       </c>
       <c r="E128" t="n">
-        <v>23.46818827339488</v>
+        <v>23.46818827339483</v>
       </c>
       <c r="F128" t="n">
-        <v>0.7778113873489795</v>
+        <v>0.7778113873489796</v>
       </c>
       <c r="G128" t="n">
-        <v>0.497613572527272</v>
+        <v>0.4976135725274385</v>
       </c>
       <c r="H128" t="n">
-        <v>350.6358449642129</v>
+        <v>350.6358449642133</v>
       </c>
       <c r="I128" t="n">
         <v>1</v>
@@ -4608,16 +4620,16 @@
         <v>494.6</v>
       </c>
       <c r="E129" t="n">
-        <v>33.13607191363835</v>
+        <v>33.13607191363838</v>
       </c>
       <c r="F129" t="n">
-        <v>0.7778113873489795</v>
+        <v>0.7778113873489796</v>
       </c>
       <c r="G129" t="n">
-        <v>0.497613572527272</v>
+        <v>0.4976135725274385</v>
       </c>
       <c r="H129" t="n">
-        <v>11.63281395716314</v>
+        <v>11.63281395716348</v>
       </c>
       <c r="I129" t="n">
         <v>1</v>
@@ -4641,16 +4653,16 @@
         <v>494.6</v>
       </c>
       <c r="E130" t="n">
-        <v>29.86149126251643</v>
+        <v>29.86149126251624</v>
       </c>
       <c r="F130" t="n">
-        <v>0.7778113873489795</v>
+        <v>0.7778113873489796</v>
       </c>
       <c r="G130" t="n">
-        <v>0.497613572527272</v>
+        <v>0.4976135725274385</v>
       </c>
       <c r="H130" t="n">
-        <v>291.3169522682211</v>
+        <v>291.3169522682213</v>
       </c>
       <c r="I130" t="n">
         <v>1</v>
@@ -4674,16 +4686,16 @@
         <v>494.6</v>
       </c>
       <c r="E131" t="n">
-        <v>28.24466802072088</v>
+        <v>28.24466802072075</v>
       </c>
       <c r="F131" t="n">
-        <v>0.7778113873489795</v>
+        <v>0.7778113873489796</v>
       </c>
       <c r="G131" t="n">
-        <v>0.497613572527272</v>
+        <v>0.4976135725274385</v>
       </c>
       <c r="H131" t="n">
-        <v>321.6663219708577</v>
+        <v>321.666321970858</v>
       </c>
       <c r="I131" t="n">
         <v>1</v>
@@ -4707,13 +4719,13 @@
         <v>494.9</v>
       </c>
       <c r="E132" t="n">
-        <v>24.30339230624596</v>
+        <v>24.3033923062458</v>
       </c>
       <c r="F132" t="n">
-        <v>1.216448040112905</v>
+        <v>1.216448040112907</v>
       </c>
       <c r="G132" t="n">
-        <v>0.8094423892611941</v>
+        <v>0.8094423892613594</v>
       </c>
       <c r="H132" t="inlineStr"/>
       <c r="I132" t="n">
@@ -4738,13 +4750,13 @@
         <v>495</v>
       </c>
       <c r="E133" t="n">
-        <v>24.35267159006401</v>
+        <v>24.35267159006384</v>
       </c>
       <c r="F133" t="n">
-        <v>1.350099961345194</v>
+        <v>1.350099961345196</v>
       </c>
       <c r="G133" t="n">
-        <v>0.8441559084852734</v>
+        <v>0.8441559084854369</v>
       </c>
       <c r="H133" t="inlineStr"/>
       <c r="I133" t="n">
@@ -4769,13 +4781,13 @@
         <v>495</v>
       </c>
       <c r="E134" t="n">
-        <v>24.50057541914601</v>
+        <v>24.50057541914588</v>
       </c>
       <c r="F134" t="n">
-        <v>1.350099961345194</v>
+        <v>1.350099961345196</v>
       </c>
       <c r="G134" t="n">
-        <v>0.8441559084852734</v>
+        <v>0.8441559084854369</v>
       </c>
       <c r="H134" t="inlineStr"/>
       <c r="I134" t="n">
@@ -4800,16 +4812,16 @@
         <v>495.1</v>
       </c>
       <c r="E135" t="n">
-        <v>17.50451090525755</v>
+        <v>17.50451090525766</v>
       </c>
       <c r="F135" t="n">
-        <v>1.474287787516882</v>
+        <v>1.474287787516883</v>
       </c>
       <c r="G135" t="n">
-        <v>0.8241322598369721</v>
+        <v>0.8241322598371309</v>
       </c>
       <c r="H135" t="n">
-        <v>35.20148204067459</v>
+        <v>35.20148204067516</v>
       </c>
       <c r="I135" t="n">
         <v>1</v>
@@ -4833,16 +4845,16 @@
         <v>495.1</v>
       </c>
       <c r="E136" t="n">
-        <v>22.99208621713783</v>
+        <v>22.99208621713779</v>
       </c>
       <c r="F136" t="n">
-        <v>1.474287787516882</v>
+        <v>1.474287787516883</v>
       </c>
       <c r="G136" t="n">
-        <v>0.8241322598369721</v>
+        <v>0.8241322598371309</v>
       </c>
       <c r="H136" t="n">
-        <v>349.4506019315439</v>
+        <v>349.4506019315444</v>
       </c>
       <c r="I136" t="n">
         <v>1</v>
@@ -4866,16 +4878,16 @@
         <v>495.1</v>
       </c>
       <c r="E137" t="n">
-        <v>32.51771286355748</v>
+        <v>32.51771286355752</v>
       </c>
       <c r="F137" t="n">
-        <v>1.474287787516882</v>
+        <v>1.474287787516883</v>
       </c>
       <c r="G137" t="n">
-        <v>0.8241322598369721</v>
+        <v>0.8241322598371309</v>
       </c>
       <c r="H137" t="n">
-        <v>11.15416272967161</v>
+        <v>11.15416272967195</v>
       </c>
       <c r="I137" t="n">
         <v>1</v>
@@ -4899,16 +4911,16 @@
         <v>495.1</v>
       </c>
       <c r="E138" t="n">
-        <v>30.03223563874053</v>
+        <v>30.03223563874034</v>
       </c>
       <c r="F138" t="n">
-        <v>1.474287787516882</v>
+        <v>1.474287787516883</v>
       </c>
       <c r="G138" t="n">
-        <v>0.8241322598369721</v>
+        <v>0.8241322598371309</v>
       </c>
       <c r="H138" t="n">
-        <v>290.0646386143543</v>
+        <v>290.0646386143544</v>
       </c>
       <c r="I138" t="n">
         <v>1</v>
@@ -4932,16 +4944,16 @@
         <v>495.1</v>
       </c>
       <c r="E139" t="n">
-        <v>28.06168967739726</v>
+        <v>28.06168967739713</v>
       </c>
       <c r="F139" t="n">
-        <v>1.474287787516882</v>
+        <v>1.474287787516883</v>
       </c>
       <c r="G139" t="n">
-        <v>0.8241322598369721</v>
+        <v>0.8241322598371309</v>
       </c>
       <c r="H139" t="n">
-        <v>320.3409615039532</v>
+        <v>320.3409615039535</v>
       </c>
       <c r="I139" t="n">
         <v>1</v>
@@ -4965,13 +4977,13 @@
         <v>495.3</v>
       </c>
       <c r="E140" t="n">
-        <v>24.87293646094129</v>
+        <v>24.87293646094112</v>
       </c>
       <c r="F140" t="n">
-        <v>1.808425757148384</v>
+        <v>1.808425757148386</v>
       </c>
       <c r="G140" t="n">
-        <v>0.7102619347989235</v>
+        <v>0.7102619347990865</v>
       </c>
       <c r="H140" t="inlineStr"/>
       <c r="I140" t="n">
@@ -4996,13 +5008,13 @@
         <v>495.3</v>
       </c>
       <c r="E141" t="n">
-        <v>24.86082035561912</v>
+        <v>24.86082035561899</v>
       </c>
       <c r="F141" t="n">
-        <v>1.808425757148384</v>
+        <v>1.808425757148386</v>
       </c>
       <c r="G141" t="n">
-        <v>0.7102619347989235</v>
+        <v>0.7102619347990865</v>
       </c>
       <c r="H141" t="inlineStr"/>
       <c r="I141" t="n">
@@ -5027,16 +5039,16 @@
         <v>508.3</v>
       </c>
       <c r="E142" t="n">
-        <v>32.2803696871561</v>
+        <v>32.28036968715536</v>
       </c>
       <c r="F142" t="n">
-        <v>0.6936188860471141</v>
+        <v>0.6936188860471145</v>
       </c>
       <c r="G142" t="n">
-        <v>0.3724075774265252</v>
+        <v>0.3724075774258854</v>
       </c>
       <c r="H142" t="n">
-        <v>279.2192307965988</v>
+        <v>279.219230796599</v>
       </c>
       <c r="I142" t="n">
         <v>1</v>
@@ -5060,16 +5072,16 @@
         <v>508.3</v>
       </c>
       <c r="E143" t="n">
-        <v>28.07343344379723</v>
+        <v>28.07343344379659</v>
       </c>
       <c r="F143" t="n">
-        <v>0.6936188860471141</v>
+        <v>0.6936188860471145</v>
       </c>
       <c r="G143" t="n">
-        <v>0.3724075774265252</v>
+        <v>0.3724075774258854</v>
       </c>
       <c r="H143" t="n">
-        <v>299.3774311756819</v>
+        <v>299.3774311756827</v>
       </c>
       <c r="I143" t="n">
         <v>1</v>
@@ -5093,13 +5105,13 @@
         <v>508.7</v>
       </c>
       <c r="E144" t="n">
-        <v>9.802838542534337</v>
+        <v>9.802838542534722</v>
       </c>
       <c r="F144" t="n">
-        <v>0.7624385138333066</v>
+        <v>0.7624385138333071</v>
       </c>
       <c r="G144" t="n">
-        <v>0.2357637531709994</v>
+        <v>0.2357637531707255</v>
       </c>
       <c r="H144" t="inlineStr"/>
       <c r="I144" t="n">
@@ -5124,13 +5136,13 @@
         <v>508.7</v>
       </c>
       <c r="E145" t="n">
-        <v>16.02941273859059</v>
+        <v>16.02941273859052</v>
       </c>
       <c r="F145" t="n">
-        <v>0.7624385138333066</v>
+        <v>0.7624385138333071</v>
       </c>
       <c r="G145" t="n">
-        <v>0.2357637531709994</v>
+        <v>0.2357637531707255</v>
       </c>
       <c r="H145" t="inlineStr"/>
       <c r="I145" t="n">
@@ -5155,13 +5167,13 @@
         <v>508.7</v>
       </c>
       <c r="E146" t="n">
-        <v>26.66308133646041</v>
+        <v>26.66308133646072</v>
       </c>
       <c r="F146" t="n">
-        <v>0.7624385138333066</v>
+        <v>0.7624385138333071</v>
       </c>
       <c r="G146" t="n">
-        <v>0.2357637531709994</v>
+        <v>0.2357637531707255</v>
       </c>
       <c r="H146" t="inlineStr"/>
       <c r="I146" t="n">
@@ -5186,16 +5198,16 @@
         <v>508.8</v>
       </c>
       <c r="E147" t="n">
-        <v>32.58112588428033</v>
+        <v>32.58112588427958</v>
       </c>
       <c r="F147" t="n">
-        <v>1.041050332705881</v>
+        <v>1.041050332705882</v>
       </c>
       <c r="G147" t="n">
-        <v>0.1985587827022239</v>
+        <v>0.198558782701811</v>
       </c>
       <c r="H147" t="n">
-        <v>279.269799331768</v>
+        <v>279.2697993317682</v>
       </c>
       <c r="I147" t="n">
         <v>1</v>
@@ -5219,16 +5231,16 @@
         <v>508.8</v>
       </c>
       <c r="E148" t="n">
-        <v>28.36576796005123</v>
+        <v>28.36576796005058</v>
       </c>
       <c r="F148" t="n">
-        <v>1.041050332705881</v>
+        <v>1.041050332705882</v>
       </c>
       <c r="G148" t="n">
-        <v>0.1985587827022239</v>
+        <v>0.198558782701811</v>
       </c>
       <c r="H148" t="n">
-        <v>299.222614358787</v>
+        <v>299.2226143587878</v>
       </c>
       <c r="I148" t="n">
         <v>1</v>
@@ -5252,13 +5264,13 @@
         <v>509.2</v>
       </c>
       <c r="E149" t="n">
-        <v>9.941706860659137</v>
+        <v>9.94170686065948</v>
       </c>
       <c r="F149" t="n">
         <v>1.18805963368034</v>
       </c>
       <c r="G149" t="n">
-        <v>0.1368536457992151</v>
+        <v>0.1368536457985831</v>
       </c>
       <c r="H149" t="inlineStr"/>
       <c r="I149" t="n">
@@ -5283,13 +5295,13 @@
         <v>509.2</v>
       </c>
       <c r="E150" t="n">
-        <v>16.54791209219983</v>
+        <v>16.54791209219973</v>
       </c>
       <c r="F150" t="n">
         <v>1.18805963368034</v>
       </c>
       <c r="G150" t="n">
-        <v>0.1368536457992151</v>
+        <v>0.1368536457985831</v>
       </c>
       <c r="H150" t="inlineStr"/>
       <c r="I150" t="n">
@@ -5314,13 +5326,13 @@
         <v>509.2</v>
       </c>
       <c r="E151" t="n">
-        <v>26.86449274410514</v>
+        <v>26.86449274410543</v>
       </c>
       <c r="F151" t="n">
         <v>1.18805963368034</v>
       </c>
       <c r="G151" t="n">
-        <v>0.1368536457992151</v>
+        <v>0.1368536457985831</v>
       </c>
       <c r="H151" t="inlineStr"/>
       <c r="I151" t="n">
@@ -5345,16 +5357,16 @@
         <v>509.3</v>
       </c>
       <c r="E152" t="n">
-        <v>33.08959976379779</v>
+        <v>33.08959976379705</v>
       </c>
       <c r="F152" t="n">
-        <v>1.106931806431469</v>
+        <v>1.10693180643147</v>
       </c>
       <c r="G152" t="n">
-        <v>0.1134330201213506</v>
+        <v>0.1134330201208114</v>
       </c>
       <c r="H152" t="n">
-        <v>279.8403784151168</v>
+        <v>279.840378415117</v>
       </c>
       <c r="I152" t="n">
         <v>1</v>
@@ -5378,16 +5390,16 @@
         <v>509.3</v>
       </c>
       <c r="E153" t="n">
-        <v>28.95494731989805</v>
+        <v>28.95494731989739</v>
       </c>
       <c r="F153" t="n">
-        <v>1.106931806431469</v>
+        <v>1.10693180643147</v>
       </c>
       <c r="G153" t="n">
-        <v>0.1134330201213506</v>
+        <v>0.1134330201208114</v>
       </c>
       <c r="H153" t="n">
-        <v>299.4932790019221</v>
+        <v>299.4932790019229</v>
       </c>
       <c r="I153" t="n">
         <v>1</v>
@@ -5411,13 +5423,13 @@
         <v>509.7</v>
       </c>
       <c r="E154" t="n">
-        <v>9.92326453550889</v>
+        <v>9.923264535509206</v>
       </c>
       <c r="F154" t="n">
-        <v>0.6946097773266113</v>
+        <v>0.6946097773266117</v>
       </c>
       <c r="G154" t="n">
-        <v>0.0370875489095473</v>
+        <v>0.03708754890893045</v>
       </c>
       <c r="H154" t="inlineStr"/>
       <c r="I154" t="n">
@@ -5442,13 +5454,13 @@
         <v>509.7</v>
       </c>
       <c r="E155" t="n">
-        <v>16.74502942058775</v>
+        <v>16.74502942058762</v>
       </c>
       <c r="F155" t="n">
-        <v>0.6946097773266113</v>
+        <v>0.6946097773266117</v>
       </c>
       <c r="G155" t="n">
-        <v>0.0370875489095473</v>
+        <v>0.03708754890893045</v>
       </c>
       <c r="H155" t="inlineStr"/>
       <c r="I155" t="n">
@@ -5473,13 +5485,13 @@
         <v>509.7</v>
       </c>
       <c r="E156" t="n">
-        <v>26.86744302437457</v>
+        <v>26.86744302437485</v>
       </c>
       <c r="F156" t="n">
-        <v>0.6946097773266113</v>
+        <v>0.6946097773266117</v>
       </c>
       <c r="G156" t="n">
-        <v>0.0370875489095473</v>
+        <v>0.03708754890893045</v>
       </c>
       <c r="H156" t="inlineStr"/>
       <c r="I156" t="n">
@@ -5504,16 +5516,16 @@
         <v>509.8</v>
       </c>
       <c r="E157" t="n">
-        <v>33.32727092554418</v>
+        <v>33.32727092554342</v>
       </c>
       <c r="F157" t="n">
-        <v>0.598639043114917</v>
+        <v>0.5986390431149172</v>
       </c>
       <c r="G157" t="n">
-        <v>0.1336178658726302</v>
+        <v>0.133617865873239</v>
       </c>
       <c r="H157" t="n">
-        <v>280.0815821922205</v>
+        <v>280.0815821922208</v>
       </c>
       <c r="I157" t="n">
         <v>1</v>
@@ -5537,16 +5549,16 @@
         <v>509.8</v>
       </c>
       <c r="E158" t="n">
-        <v>29.22572828371745</v>
+        <v>29.22572828371679</v>
       </c>
       <c r="F158" t="n">
-        <v>0.598639043114917</v>
+        <v>0.5986390431149172</v>
       </c>
       <c r="G158" t="n">
-        <v>0.1336178658726302</v>
+        <v>0.133617865873239</v>
       </c>
       <c r="H158" t="n">
-        <v>299.5957978327932</v>
+        <v>299.5957978327939</v>
       </c>
       <c r="I158" t="n">
         <v>1</v>
@@ -5570,13 +5582,13 @@
         <v>510.2</v>
       </c>
       <c r="E159" t="n">
-        <v>10.09189119440123</v>
+        <v>10.09189119440153</v>
       </c>
       <c r="F159" t="n">
-        <v>0.6880974848992392</v>
+        <v>0.6880974848992393</v>
       </c>
       <c r="G159" t="n">
-        <v>0.288856350993571</v>
+        <v>0.2888563509942299</v>
       </c>
       <c r="H159" t="inlineStr"/>
       <c r="I159" t="n">
@@ -5601,13 +5613,13 @@
         <v>510.2</v>
       </c>
       <c r="E160" t="n">
-        <v>17.00701221364093</v>
+        <v>17.0070122136408</v>
       </c>
       <c r="F160" t="n">
-        <v>0.6880974848992392</v>
+        <v>0.6880974848992393</v>
       </c>
       <c r="G160" t="n">
-        <v>0.288856350993571</v>
+        <v>0.2888563509942299</v>
       </c>
       <c r="H160" t="inlineStr"/>
       <c r="I160" t="n">
@@ -5632,13 +5644,13 @@
         <v>510.2</v>
       </c>
       <c r="E161" t="n">
-        <v>27.04412191651063</v>
+        <v>27.04412191651091</v>
       </c>
       <c r="F161" t="n">
-        <v>0.6880974848992392</v>
+        <v>0.6880974848992393</v>
       </c>
       <c r="G161" t="n">
-        <v>0.288856350993571</v>
+        <v>0.2888563509942299</v>
       </c>
       <c r="H161" t="inlineStr"/>
       <c r="I161" t="n">
@@ -5663,16 +5675,16 @@
         <v>510.3</v>
       </c>
       <c r="E162" t="n">
-        <v>33.74297513574744</v>
+        <v>33.7429751357467</v>
       </c>
       <c r="F162" t="n">
-        <v>0.5898368486750512</v>
+        <v>0.5898368486750513</v>
       </c>
       <c r="G162" t="n">
-        <v>0.2480700076951003</v>
+        <v>0.248070007695768</v>
       </c>
       <c r="H162" t="n">
-        <v>280.1953273208402</v>
+        <v>280.1953273208404</v>
       </c>
       <c r="I162" t="n">
         <v>1</v>
@@ -5696,16 +5708,16 @@
         <v>510.3</v>
       </c>
       <c r="E163" t="n">
-        <v>29.63996440240712</v>
+        <v>29.63996440240646</v>
       </c>
       <c r="F163" t="n">
-        <v>0.5898368486750512</v>
+        <v>0.5898368486750513</v>
       </c>
       <c r="G163" t="n">
-        <v>0.2480700076951003</v>
+        <v>0.248070007695768</v>
       </c>
       <c r="H163" t="n">
-        <v>299.4494644778874</v>
+        <v>299.4494644778881</v>
       </c>
       <c r="I163" t="n">
         <v>1</v>
@@ -5729,13 +5741,13 @@
         <v>510.7</v>
       </c>
       <c r="E164" t="n">
-        <v>10.18180362441353</v>
+        <v>10.18180362441377</v>
       </c>
       <c r="F164" t="n">
-        <v>0.9384571308326634</v>
+        <v>0.9384571308326635</v>
       </c>
       <c r="G164" t="n">
-        <v>0.2629254130113327</v>
+        <v>0.2629254130118261</v>
       </c>
       <c r="H164" t="inlineStr"/>
       <c r="I164" t="n">
@@ -5760,13 +5772,13 @@
         <v>510.7</v>
       </c>
       <c r="E165" t="n">
-        <v>17.49710091424856</v>
+        <v>17.49710091424839</v>
       </c>
       <c r="F165" t="n">
-        <v>0.9384571308326634</v>
+        <v>0.9384571308326635</v>
       </c>
       <c r="G165" t="n">
-        <v>0.2629254130113327</v>
+        <v>0.2629254130118261</v>
       </c>
       <c r="H165" t="inlineStr"/>
       <c r="I165" t="n">
@@ -5791,13 +5803,13 @@
         <v>510.7</v>
       </c>
       <c r="E166" t="n">
-        <v>27.13805228034368</v>
+        <v>27.13805228034392</v>
       </c>
       <c r="F166" t="n">
-        <v>0.9384571308326634</v>
+        <v>0.9384571308326635</v>
       </c>
       <c r="G166" t="n">
-        <v>0.2629254130113327</v>
+        <v>0.2629254130118261</v>
       </c>
       <c r="H166" t="inlineStr"/>
       <c r="I166" t="n">
@@ -5822,16 +5834,16 @@
         <v>510.8</v>
       </c>
       <c r="E167" t="n">
-        <v>34.43859886087624</v>
+        <v>34.43859886087547</v>
       </c>
       <c r="F167" t="n">
         <v>1.064887675165684</v>
       </c>
       <c r="G167" t="n">
-        <v>0.3407786108713354</v>
+        <v>0.3407786108717917</v>
       </c>
       <c r="H167" t="n">
-        <v>280.8236934570705</v>
+        <v>280.8236934570707</v>
       </c>
       <c r="I167" t="n">
         <v>1</v>
@@ -5855,16 +5867,16 @@
         <v>510.8</v>
       </c>
       <c r="E168" t="n">
-        <v>30.41953617708263</v>
+        <v>30.41953617708195</v>
       </c>
       <c r="F168" t="n">
         <v>1.064887675165684</v>
       </c>
       <c r="G168" t="n">
-        <v>0.3407786108713354</v>
+        <v>0.3407786108717917</v>
       </c>
       <c r="H168" t="n">
-        <v>299.6902765787503</v>
+        <v>299.690276578751</v>
       </c>
       <c r="I168" t="n">
         <v>1</v>
@@ -5888,13 +5900,13 @@
         <v>511.2</v>
       </c>
       <c r="E169" t="n">
-        <v>10.32304418771064</v>
+        <v>10.32304418771084</v>
       </c>
       <c r="F169" t="n">
-        <v>1.330172284526002</v>
+        <v>1.330172284526003</v>
       </c>
       <c r="G169" t="n">
-        <v>0.4163370164650882</v>
+        <v>0.4163370164655184</v>
       </c>
       <c r="H169" t="inlineStr"/>
       <c r="I169" t="n">
@@ -5919,13 +5931,13 @@
         <v>511.2</v>
       </c>
       <c r="E170" t="n">
-        <v>17.88803293957967</v>
+        <v>17.88803293957948</v>
       </c>
       <c r="F170" t="n">
-        <v>1.330172284526002</v>
+        <v>1.330172284526003</v>
       </c>
       <c r="G170" t="n">
-        <v>0.4163370164650882</v>
+        <v>0.4163370164655184</v>
       </c>
       <c r="H170" t="inlineStr"/>
       <c r="I170" t="n">
@@ -5950,13 +5962,13 @@
         <v>511.2</v>
       </c>
       <c r="E171" t="n">
-        <v>27.25925096404463</v>
+        <v>27.25925096404486</v>
       </c>
       <c r="F171" t="n">
-        <v>1.330172284526002</v>
+        <v>1.330172284526003</v>
       </c>
       <c r="G171" t="n">
-        <v>0.4163370164650882</v>
+        <v>0.4163370164655184</v>
       </c>
       <c r="H171" t="inlineStr"/>
       <c r="I171" t="n">
@@ -5981,16 +5993,16 @@
         <v>511.3</v>
       </c>
       <c r="E172" t="n">
-        <v>34.97664658513732</v>
+        <v>34.97664658513654</v>
       </c>
       <c r="F172" t="n">
-        <v>1.271885742587652</v>
+        <v>1.271885742587654</v>
       </c>
       <c r="G172" t="n">
-        <v>0.3878150816115746</v>
+        <v>0.3878150816120629</v>
       </c>
       <c r="H172" t="n">
-        <v>280.898276331355</v>
+        <v>280.8982763313552</v>
       </c>
       <c r="I172" t="n">
         <v>1</v>
@@ -6014,16 +6026,16 @@
         <v>511.3</v>
       </c>
       <c r="E173" t="n">
-        <v>30.94364834287406</v>
+        <v>30.94364834287336</v>
       </c>
       <c r="F173" t="n">
-        <v>1.271885742587652</v>
+        <v>1.271885742587654</v>
       </c>
       <c r="G173" t="n">
-        <v>0.3878150816115746</v>
+        <v>0.3878150816120629</v>
       </c>
       <c r="H173" t="n">
-        <v>299.4479122182499</v>
+        <v>299.4479122182506</v>
       </c>
       <c r="I173" t="n">
         <v>1</v>
@@ -6047,16 +6059,16 @@
         <v>511.6</v>
       </c>
       <c r="E174" t="n">
-        <v>35.34373550380909</v>
+        <v>35.34373550380833</v>
       </c>
       <c r="F174" t="n">
-        <v>1.467933778324329</v>
+        <v>1.46793377832433</v>
       </c>
       <c r="G174" t="n">
-        <v>0.4907707219992105</v>
+        <v>0.4907707219996489</v>
       </c>
       <c r="H174" t="n">
-        <v>281.150050823781</v>
+        <v>281.1500508237812</v>
       </c>
       <c r="I174" t="n">
         <v>1</v>
@@ -6080,16 +6092,16 @@
         <v>511.6</v>
       </c>
       <c r="E175" t="n">
-        <v>31.34076605134891</v>
+        <v>31.34076605134822</v>
       </c>
       <c r="F175" t="n">
-        <v>1.467933778324329</v>
+        <v>1.46793377832433</v>
       </c>
       <c r="G175" t="n">
-        <v>0.4907707219992105</v>
+        <v>0.4907707219996489</v>
       </c>
       <c r="H175" t="n">
-        <v>299.5037982779101</v>
+        <v>299.5037982779108</v>
       </c>
       <c r="I175" t="n">
         <v>1</v>
@@ -6113,13 +6125,13 @@
         <v>511.7</v>
       </c>
       <c r="E176" t="n">
-        <v>10.42632760718104</v>
+        <v>10.42632760718119</v>
       </c>
       <c r="F176" t="n">
-        <v>1.60110858502629</v>
+        <v>1.601108585026291</v>
       </c>
       <c r="G176" t="n">
-        <v>0.539443631924745</v>
+        <v>0.5394436319252088</v>
       </c>
       <c r="H176" t="inlineStr"/>
       <c r="I176" t="n">
@@ -6144,13 +6156,13 @@
         <v>511.7</v>
       </c>
       <c r="E177" t="n">
-        <v>18.22731886618008</v>
+        <v>18.22731886617987</v>
       </c>
       <c r="F177" t="n">
-        <v>1.60110858502629</v>
+        <v>1.601108585026291</v>
       </c>
       <c r="G177" t="n">
-        <v>0.539443631924745</v>
+        <v>0.5394436319252088</v>
       </c>
       <c r="H177" t="inlineStr"/>
       <c r="I177" t="n">
@@ -6175,13 +6187,13 @@
         <v>511.7</v>
       </c>
       <c r="E178" t="n">
-        <v>27.32530781127084</v>
+        <v>27.32530781127106</v>
       </c>
       <c r="F178" t="n">
-        <v>1.60110858502629</v>
+        <v>1.601108585026291</v>
       </c>
       <c r="G178" t="n">
-        <v>0.539443631924745</v>
+        <v>0.5394436319252088</v>
       </c>
       <c r="H178" t="inlineStr"/>
       <c r="I178" t="n">
@@ -6206,13 +6218,13 @@
         <v>512.1</v>
       </c>
       <c r="E179" t="n">
-        <v>10.10615987508556</v>
+        <v>10.10615987508569</v>
       </c>
       <c r="F179" t="n">
-        <v>1.918208752693483</v>
+        <v>1.918208752693484</v>
       </c>
       <c r="G179" t="n">
-        <v>0.4759644820655839</v>
+        <v>0.4759644820662102</v>
       </c>
       <c r="H179" t="inlineStr"/>
       <c r="I179" t="n">
@@ -6237,13 +6249,13 @@
         <v>512.1</v>
       </c>
       <c r="E180" t="n">
-        <v>18.11913278404954</v>
+        <v>18.11913278404931</v>
       </c>
       <c r="F180" t="n">
-        <v>1.918208752693483</v>
+        <v>1.918208752693484</v>
       </c>
       <c r="G180" t="n">
-        <v>0.4759644820655839</v>
+        <v>0.4759644820662102</v>
       </c>
       <c r="H180" t="inlineStr"/>
       <c r="I180" t="n">
@@ -6268,13 +6280,13 @@
         <v>512.1</v>
       </c>
       <c r="E181" t="n">
-        <v>26.96737471065852</v>
+        <v>26.96737471065873</v>
       </c>
       <c r="F181" t="n">
-        <v>1.918208752693483</v>
+        <v>1.918208752693484</v>
       </c>
       <c r="G181" t="n">
-        <v>0.4759644820655839</v>
+        <v>0.4759644820662102</v>
       </c>
       <c r="H181" t="inlineStr"/>
       <c r="I181" t="n">
@@ -6299,16 +6311,16 @@
         <v>514.5</v>
       </c>
       <c r="E182" t="n">
-        <v>35.63247398906229</v>
+        <v>35.63247398906151</v>
       </c>
       <c r="F182" t="n">
-        <v>1.246784812868127</v>
+        <v>1.246784812868128</v>
       </c>
       <c r="G182" t="n">
-        <v>0.4165842300717582</v>
+        <v>0.4165842300712299</v>
       </c>
       <c r="H182" t="n">
-        <v>295.0443824501922</v>
+        <v>295.0443824501927</v>
       </c>
       <c r="I182" t="n">
         <v>1</v>
@@ -6332,16 +6344,16 @@
         <v>514.7</v>
       </c>
       <c r="E183" t="n">
-        <v>35.71991157472885</v>
+        <v>35.71991157472804</v>
       </c>
       <c r="F183" t="n">
         <v>1.432919305639398</v>
       </c>
       <c r="G183" t="n">
-        <v>0.3424576842780951</v>
+        <v>0.3424576842776932</v>
       </c>
       <c r="H183" t="n">
-        <v>294.8300337985545</v>
+        <v>294.8300337985551</v>
       </c>
       <c r="I183" t="n">
         <v>1</v>
@@ -6365,13 +6377,13 @@
         <v>514.9</v>
       </c>
       <c r="E184" t="n">
-        <v>10.0034158563821</v>
+        <v>10.00341585638183</v>
       </c>
       <c r="F184" t="n">
-        <v>1.604412901025261</v>
+        <v>1.604412901025263</v>
       </c>
       <c r="G184" t="n">
-        <v>0.2683907458179609</v>
+        <v>0.2683907458175703</v>
       </c>
       <c r="H184" t="inlineStr"/>
       <c r="I184" t="n">
@@ -6396,13 +6408,13 @@
         <v>514.9</v>
       </c>
       <c r="E185" t="n">
-        <v>19.61096710531255</v>
+        <v>19.61096710531211</v>
       </c>
       <c r="F185" t="n">
-        <v>1.604412901025261</v>
+        <v>1.604412901025263</v>
       </c>
       <c r="G185" t="n">
-        <v>0.2683907458179609</v>
+        <v>0.2683907458175703</v>
       </c>
       <c r="H185" t="inlineStr"/>
       <c r="I185" t="n">
@@ -6427,13 +6439,13 @@
         <v>514.9</v>
       </c>
       <c r="E186" t="n">
-        <v>25.6058908416445</v>
+        <v>25.60589084164459</v>
       </c>
       <c r="F186" t="n">
-        <v>1.604412901025261</v>
+        <v>1.604412901025263</v>
       </c>
       <c r="G186" t="n">
-        <v>0.2683907458179609</v>
+        <v>0.2683907458175703</v>
       </c>
       <c r="H186" t="inlineStr"/>
       <c r="I186" t="n">
@@ -6458,13 +6470,13 @@
         <v>515.3</v>
       </c>
       <c r="E187" t="n">
-        <v>9.726973239793349</v>
+        <v>9.726973239793022</v>
       </c>
       <c r="F187" t="n">
         <v>1.129932636239952</v>
       </c>
       <c r="G187" t="n">
-        <v>0.2227224652843112</v>
+        <v>0.2227224652835454</v>
       </c>
       <c r="H187" t="inlineStr"/>
       <c r="I187" t="n">
@@ -6489,13 +6501,13 @@
         <v>515.3</v>
       </c>
       <c r="E188" t="n">
-        <v>19.48204264744497</v>
+        <v>19.4820426474445</v>
       </c>
       <c r="F188" t="n">
         <v>1.129932636239952</v>
       </c>
       <c r="G188" t="n">
-        <v>0.2227224652843112</v>
+        <v>0.2227224652835454</v>
       </c>
       <c r="H188" t="inlineStr"/>
       <c r="I188" t="n">
@@ -6520,13 +6532,13 @@
         <v>515.4</v>
       </c>
       <c r="E189" t="n">
-        <v>9.743106550131621</v>
+        <v>9.743106550131289</v>
       </c>
       <c r="F189" t="n">
         <v>1.131988894599647</v>
       </c>
       <c r="G189" t="n">
-        <v>0.2119824540713185</v>
+        <v>0.2119824540705489</v>
       </c>
       <c r="H189" t="inlineStr"/>
       <c r="I189" t="n">
@@ -6551,13 +6563,13 @@
         <v>515.4</v>
       </c>
       <c r="E190" t="n">
-        <v>19.51833789523109</v>
+        <v>19.51833789523063</v>
       </c>
       <c r="F190" t="n">
         <v>1.131988894599647</v>
       </c>
       <c r="G190" t="n">
-        <v>0.2119824540713185</v>
+        <v>0.2119824540705489</v>
       </c>
       <c r="H190" t="inlineStr"/>
       <c r="I190" t="n">
@@ -6582,13 +6594,13 @@
         <v>515.4</v>
       </c>
       <c r="E191" t="n">
-        <v>25.00196640849416</v>
+        <v>25.00196640849423</v>
       </c>
       <c r="F191" t="n">
         <v>1.131988894599647</v>
       </c>
       <c r="G191" t="n">
-        <v>0.2119824540713185</v>
+        <v>0.2119824540705489</v>
       </c>
       <c r="H191" t="inlineStr"/>
       <c r="I191" t="n">
@@ -6613,16 +6625,16 @@
         <v>515.6</v>
       </c>
       <c r="E192" t="n">
-        <v>36.62016611418347</v>
+        <v>36.62016611418266</v>
       </c>
       <c r="F192" t="n">
-        <v>1.230264802262763</v>
+        <v>1.230264802262762</v>
       </c>
       <c r="G192" t="n">
-        <v>0.3206007126666457</v>
+        <v>0.3206007126658693</v>
       </c>
       <c r="H192" t="n">
-        <v>293.0276750345291</v>
+        <v>293.0276750345296</v>
       </c>
       <c r="I192" t="n">
         <v>1</v>
@@ -6646,13 +6658,13 @@
         <v>515.9</v>
       </c>
       <c r="E193" t="n">
-        <v>9.922163722349289</v>
+        <v>9.922163722348889</v>
       </c>
       <c r="F193" t="n">
         <v>1.146960296415412</v>
       </c>
       <c r="G193" t="n">
-        <v>0.3414076470080241</v>
+        <v>0.3414076470072479</v>
       </c>
       <c r="H193" t="inlineStr"/>
       <c r="I193" t="n">
@@ -6677,13 +6689,13 @@
         <v>515.9</v>
       </c>
       <c r="E194" t="n">
-        <v>19.80994397783457</v>
+        <v>19.80994397783407</v>
       </c>
       <c r="F194" t="n">
         <v>1.146960296415412</v>
       </c>
       <c r="G194" t="n">
-        <v>0.3414076470080241</v>
+        <v>0.3414076470072479</v>
       </c>
       <c r="H194" t="inlineStr"/>
       <c r="I194" t="n">
@@ -6708,13 +6720,13 @@
         <v>515.9</v>
       </c>
       <c r="E195" t="n">
-        <v>24.79245708099291</v>
+        <v>24.79245708099296</v>
       </c>
       <c r="F195" t="n">
         <v>1.146960296415412</v>
       </c>
       <c r="G195" t="n">
-        <v>0.3414076470080241</v>
+        <v>0.3414076470072479</v>
       </c>
       <c r="H195" t="inlineStr"/>
       <c r="I195" t="n">
@@ -6739,16 +6751,16 @@
         <v>516.1</v>
       </c>
       <c r="E196" t="n">
-        <v>36.81879072028444</v>
+        <v>36.81879072028363</v>
       </c>
       <c r="F196" t="n">
-        <v>0.9444551998036527</v>
+        <v>0.9444551998036534</v>
       </c>
       <c r="G196" t="n">
-        <v>0.2091264846009967</v>
+        <v>0.2091264846004115</v>
       </c>
       <c r="H196" t="n">
-        <v>292.2989302804914</v>
+        <v>292.298930280492</v>
       </c>
       <c r="I196" t="n">
         <v>1</v>
@@ -6772,13 +6784,13 @@
         <v>516.4</v>
       </c>
       <c r="E197" t="n">
-        <v>9.755012154846851</v>
+        <v>9.755012154846447</v>
       </c>
       <c r="F197" t="n">
-        <v>0.7886862998960206</v>
+        <v>0.7886862998960202</v>
       </c>
       <c r="G197" t="n">
-        <v>0.07942280522208939</v>
+        <v>0.07942280522234769</v>
       </c>
       <c r="H197" t="inlineStr"/>
       <c r="I197" t="n">
@@ -6803,13 +6815,13 @@
         <v>516.4</v>
       </c>
       <c r="E198" t="n">
-        <v>19.66466030964872</v>
+        <v>19.66466030964822</v>
       </c>
       <c r="F198" t="n">
-        <v>0.7886862998960206</v>
+        <v>0.7886862998960202</v>
       </c>
       <c r="G198" t="n">
-        <v>0.07942280522208939</v>
+        <v>0.07942280522234769</v>
       </c>
       <c r="H198" t="inlineStr"/>
       <c r="I198" t="n">
@@ -6834,13 +6846,13 @@
         <v>516.4</v>
       </c>
       <c r="E199" t="n">
-        <v>24.56651749537098</v>
+        <v>24.56651749537103</v>
       </c>
       <c r="F199" t="n">
-        <v>0.7886862998960206</v>
+        <v>0.7886862998960202</v>
       </c>
       <c r="G199" t="n">
-        <v>0.07942280522208939</v>
+        <v>0.07942280522234769</v>
       </c>
       <c r="H199" t="inlineStr"/>
       <c r="I199" t="n">
@@ -6865,16 +6877,16 @@
         <v>516.6</v>
       </c>
       <c r="E200" t="n">
-        <v>36.96163240173757</v>
+        <v>36.96163240173673</v>
       </c>
       <c r="F200" t="n">
-        <v>0.9897355682319978</v>
+        <v>0.9897355682319979</v>
       </c>
       <c r="G200" t="n">
-        <v>0.1157850811177677</v>
+        <v>0.1157850811185366</v>
       </c>
       <c r="H200" t="n">
-        <v>292.1071623426192</v>
+        <v>292.1071623426197</v>
       </c>
       <c r="I200" t="n">
         <v>1</v>
@@ -6898,13 +6910,13 @@
         <v>516.9</v>
       </c>
       <c r="E201" t="n">
-        <v>9.856812870002864</v>
+        <v>9.856812870002418</v>
       </c>
       <c r="F201" t="n">
-        <v>0.9443705903634828</v>
+        <v>0.9443705903634829</v>
       </c>
       <c r="G201" t="n">
-        <v>0.1173810906531871</v>
+        <v>0.1173810906539691</v>
       </c>
       <c r="H201" t="inlineStr"/>
       <c r="I201" t="n">
@@ -6929,13 +6941,13 @@
         <v>516.9</v>
       </c>
       <c r="E202" t="n">
-        <v>19.81016047310004</v>
+        <v>19.81016047309952</v>
       </c>
       <c r="F202" t="n">
-        <v>0.9443705903634828</v>
+        <v>0.9443705903634829</v>
       </c>
       <c r="G202" t="n">
-        <v>0.1173810906531871</v>
+        <v>0.1173810906539691</v>
       </c>
       <c r="H202" t="inlineStr"/>
       <c r="I202" t="n">
@@ -6960,13 +6972,13 @@
         <v>516.9</v>
       </c>
       <c r="E203" t="n">
-        <v>24.44754815866154</v>
+        <v>24.44754815866158</v>
       </c>
       <c r="F203" t="n">
-        <v>0.9443705903634828</v>
+        <v>0.9443705903634829</v>
       </c>
       <c r="G203" t="n">
-        <v>0.1173810906531871</v>
+        <v>0.1173810906539691</v>
       </c>
       <c r="H203" t="inlineStr"/>
       <c r="I203" t="n">
@@ -6991,16 +7003,16 @@
         <v>517.1</v>
       </c>
       <c r="E204" t="n">
-        <v>37.29966591785227</v>
+        <v>37.29966591785143</v>
       </c>
       <c r="F204" t="n">
-        <v>0.6695676188099536</v>
+        <v>0.669567618809954</v>
       </c>
       <c r="G204" t="n">
-        <v>0.1957406045421645</v>
+        <v>0.1957406045428467</v>
       </c>
       <c r="H204" t="n">
-        <v>291.4595670578489</v>
+        <v>291.4595670578494</v>
       </c>
       <c r="I204" t="n">
         <v>1</v>
@@ -7024,13 +7036,13 @@
         <v>517.4</v>
       </c>
       <c r="E205" t="n">
-        <v>9.981411981919297</v>
+        <v>9.981411981918786</v>
       </c>
       <c r="F205" t="n">
-        <v>1.078540783111634</v>
+        <v>1.078540783111635</v>
       </c>
       <c r="G205" t="n">
-        <v>0.1428863719879162</v>
+        <v>0.1428863719881995</v>
       </c>
       <c r="H205" t="inlineStr"/>
       <c r="I205" t="n">
@@ -7055,13 +7067,13 @@
         <v>517.4</v>
       </c>
       <c r="E206" t="n">
-        <v>19.99657376529233</v>
+        <v>19.99657376529177</v>
       </c>
       <c r="F206" t="n">
-        <v>1.078540783111634</v>
+        <v>1.078540783111635</v>
       </c>
       <c r="G206" t="n">
-        <v>0.1428863719879162</v>
+        <v>0.1428863719881995</v>
       </c>
       <c r="H206" t="inlineStr"/>
       <c r="I206" t="n">
@@ -7086,13 +7098,13 @@
         <v>517.4</v>
       </c>
       <c r="E207" t="n">
-        <v>24.13885988967415</v>
+        <v>24.13885988967418</v>
       </c>
       <c r="F207" t="n">
-        <v>1.078540783111634</v>
+        <v>1.078540783111635</v>
       </c>
       <c r="G207" t="n">
-        <v>0.1428863719879162</v>
+        <v>0.1428863719881995</v>
       </c>
       <c r="H207" t="inlineStr"/>
       <c r="I207" t="n">
@@ -7117,16 +7129,16 @@
         <v>517.6</v>
       </c>
       <c r="E208" t="n">
-        <v>37.95515087903355</v>
+        <v>37.95515087903271</v>
       </c>
       <c r="F208" t="n">
         <v>1.311682068010422</v>
       </c>
       <c r="G208" t="n">
-        <v>0.131114976835274</v>
+        <v>0.1311149768356811</v>
       </c>
       <c r="H208" t="n">
-        <v>290.9190268931831</v>
+        <v>290.9190268931836</v>
       </c>
       <c r="I208" t="n">
         <v>1</v>
@@ -7150,13 +7162,13 @@
         <v>517.9</v>
       </c>
       <c r="E209" t="n">
-        <v>10.04800290258434</v>
+        <v>10.04800290258379</v>
       </c>
       <c r="F209" t="n">
-        <v>1.241116634959176</v>
+        <v>1.241116634959177</v>
       </c>
       <c r="G209" t="n">
-        <v>0.3574594390433974</v>
+        <v>0.3574594390436244</v>
       </c>
       <c r="H209" t="inlineStr"/>
       <c r="I209" t="n">
@@ -7181,13 +7193,13 @@
         <v>517.9</v>
       </c>
       <c r="E210" t="n">
-        <v>20.09213324615946</v>
+        <v>20.09213324615888</v>
       </c>
       <c r="F210" t="n">
-        <v>1.241116634959176</v>
+        <v>1.241116634959177</v>
       </c>
       <c r="G210" t="n">
-        <v>0.3574594390433974</v>
+        <v>0.3574594390436244</v>
       </c>
       <c r="H210" t="inlineStr"/>
       <c r="I210" t="n">
@@ -7215,10 +7227,10 @@
         <v>23.8513740334611</v>
       </c>
       <c r="F211" t="n">
-        <v>1.241116634959176</v>
+        <v>1.241116634959177</v>
       </c>
       <c r="G211" t="n">
-        <v>0.3574594390433974</v>
+        <v>0.3574594390436244</v>
       </c>
       <c r="H211" t="inlineStr"/>
       <c r="I211" t="n">
@@ -7246,10 +7258,10 @@
         <v>23.74467429463501</v>
       </c>
       <c r="F212" t="n">
-        <v>1.304879807380614</v>
+        <v>1.304879807380615</v>
       </c>
       <c r="G212" t="n">
-        <v>0.4344780317704656</v>
+        <v>0.4344780317706834</v>
       </c>
       <c r="H212" t="inlineStr"/>
       <c r="I212" t="n">
@@ -7274,16 +7286,16 @@
         <v>518.1</v>
       </c>
       <c r="E213" t="n">
-        <v>38.26987744774203</v>
+        <v>38.26987744774117</v>
       </c>
       <c r="F213" t="n">
-        <v>1.304879807380614</v>
+        <v>1.304879807380615</v>
       </c>
       <c r="G213" t="n">
-        <v>0.4344780317704656</v>
+        <v>0.4344780317706834</v>
       </c>
       <c r="H213" t="n">
-        <v>290.0820247894163</v>
+        <v>290.0820247894168</v>
       </c>
       <c r="I213" t="n">
         <v>1</v>
@@ -7307,13 +7319,13 @@
         <v>518.4</v>
       </c>
       <c r="E214" t="n">
-        <v>10.41412474303523</v>
+        <v>10.41412474303466</v>
       </c>
       <c r="F214" t="n">
-        <v>1.369219943926548</v>
+        <v>1.369219943926549</v>
       </c>
       <c r="G214" t="n">
-        <v>0.3025036181089356</v>
+        <v>0.3025036181094297</v>
       </c>
       <c r="H214" t="inlineStr"/>
       <c r="I214" t="n">
@@ -7338,13 +7350,13 @@
         <v>518.4</v>
       </c>
       <c r="E215" t="n">
-        <v>20.46618198443556</v>
+        <v>20.46618198443498</v>
       </c>
       <c r="F215" t="n">
-        <v>1.369219943926548</v>
+        <v>1.369219943926549</v>
       </c>
       <c r="G215" t="n">
-        <v>0.3025036181089356</v>
+        <v>0.3025036181094297</v>
       </c>
       <c r="H215" t="inlineStr"/>
       <c r="I215" t="n">
@@ -7369,13 +7381,13 @@
         <v>518.4</v>
       </c>
       <c r="E216" t="n">
-        <v>23.96915843429319</v>
+        <v>23.96915843429318</v>
       </c>
       <c r="F216" t="n">
-        <v>1.369219943926548</v>
+        <v>1.369219943926549</v>
       </c>
       <c r="G216" t="n">
-        <v>0.3025036181089356</v>
+        <v>0.3025036181094297</v>
       </c>
       <c r="H216" t="inlineStr"/>
       <c r="I216" t="n">
@@ -7400,16 +7412,16 @@
         <v>518.6</v>
       </c>
       <c r="E217" t="n">
-        <v>38.69766609447944</v>
+        <v>38.69766609447858</v>
       </c>
       <c r="F217" t="n">
-        <v>1.188349102492147</v>
+        <v>1.188349102492148</v>
       </c>
       <c r="G217" t="n">
-        <v>0.3736715392674711</v>
+        <v>0.3736715392681085</v>
       </c>
       <c r="H217" t="n">
-        <v>290.2402481956461</v>
+        <v>290.2402481956466</v>
       </c>
       <c r="I217" t="n">
         <v>1</v>
@@ -7433,13 +7445,13 @@
         <v>518.9</v>
       </c>
       <c r="E218" t="n">
-        <v>10.68375353259056</v>
+        <v>10.68375353258994</v>
       </c>
       <c r="F218" t="n">
-        <v>1.198733172336674</v>
+        <v>1.198733172336675</v>
       </c>
       <c r="G218" t="n">
-        <v>0.4631079177806931</v>
+        <v>0.4631079177813391</v>
       </c>
       <c r="H218" t="inlineStr"/>
       <c r="I218" t="n">
@@ -7464,13 +7476,13 @@
         <v>518.9</v>
       </c>
       <c r="E219" t="n">
-        <v>20.74018096752897</v>
+        <v>20.74018096752835</v>
       </c>
       <c r="F219" t="n">
-        <v>1.198733172336674</v>
+        <v>1.198733172336675</v>
       </c>
       <c r="G219" t="n">
-        <v>0.4631079177806931</v>
+        <v>0.4631079177813391</v>
       </c>
       <c r="H219" t="inlineStr"/>
       <c r="I219" t="n">
@@ -7495,13 +7507,13 @@
         <v>518.9</v>
       </c>
       <c r="E220" t="n">
-        <v>23.9825705996461</v>
+        <v>23.98257059964607</v>
       </c>
       <c r="F220" t="n">
-        <v>1.198733172336674</v>
+        <v>1.198733172336675</v>
       </c>
       <c r="G220" t="n">
-        <v>0.4631079177806931</v>
+        <v>0.4631079177813391</v>
       </c>
       <c r="H220" t="inlineStr"/>
       <c r="I220" t="n">
@@ -7526,16 +7538,16 @@
         <v>519</v>
       </c>
       <c r="E221" t="n">
-        <v>39.21009700113348</v>
+        <v>39.21009700113259</v>
       </c>
       <c r="F221" t="n">
         <v>1.37307008441563</v>
       </c>
       <c r="G221" t="n">
-        <v>0.4012626261290246</v>
+        <v>0.4012626261296032</v>
       </c>
       <c r="H221" t="n">
-        <v>289.9090599667561</v>
+        <v>289.9090599667566</v>
       </c>
       <c r="I221" t="n">
         <v>1</v>
@@ -7559,13 +7571,13 @@
         <v>519.4</v>
       </c>
       <c r="E222" t="n">
-        <v>11.33728512355495</v>
+        <v>11.3372851235543</v>
       </c>
       <c r="F222" t="n">
         <v>1.701978193407472</v>
       </c>
       <c r="G222" t="n">
-        <v>0.3552567065384765</v>
+        <v>0.3552567065387378</v>
       </c>
       <c r="H222" t="inlineStr"/>
       <c r="I222" t="n">
@@ -7590,13 +7602,13 @@
         <v>519.4</v>
       </c>
       <c r="E223" t="n">
-        <v>21.38457647077318</v>
+        <v>21.38457647077254</v>
       </c>
       <c r="F223" t="n">
         <v>1.701978193407472</v>
       </c>
       <c r="G223" t="n">
-        <v>0.3552567065384765</v>
+        <v>0.3552567065387378</v>
       </c>
       <c r="H223" t="inlineStr"/>
       <c r="I223" t="n">
@@ -7621,13 +7633,13 @@
         <v>519.4</v>
       </c>
       <c r="E224" t="n">
-        <v>23.98405632017896</v>
+        <v>23.98405632017889</v>
       </c>
       <c r="F224" t="n">
         <v>1.701978193407472</v>
       </c>
       <c r="G224" t="n">
-        <v>0.3552567065384765</v>
+        <v>0.3552567065387378</v>
       </c>
       <c r="H224" t="inlineStr"/>
       <c r="I224" t="n">
@@ -7652,13 +7664,13 @@
         <v>519.7</v>
       </c>
       <c r="E225" t="n">
-        <v>11.89716937302454</v>
+        <v>11.89716937302385</v>
       </c>
       <c r="F225" t="n">
-        <v>1.975041523300011</v>
+        <v>1.975041523300013</v>
       </c>
       <c r="G225" t="n">
-        <v>0.1538829234909329</v>
+        <v>0.1538829234911094</v>
       </c>
       <c r="H225" t="inlineStr"/>
       <c r="I225" t="n">
@@ -7683,13 +7695,13 @@
         <v>519.7</v>
       </c>
       <c r="E226" t="n">
-        <v>21.93880528481611</v>
+        <v>21.93880528481544</v>
       </c>
       <c r="F226" t="n">
-        <v>1.975041523300011</v>
+        <v>1.975041523300013</v>
       </c>
       <c r="G226" t="n">
-        <v>0.1538829234909329</v>
+        <v>0.1538829234911094</v>
       </c>
       <c r="H226" t="inlineStr"/>
       <c r="I226" t="n">
@@ -7714,13 +7726,13 @@
         <v>519.7</v>
       </c>
       <c r="E227" t="n">
-        <v>24.30288410315154</v>
+        <v>24.30288410315145</v>
       </c>
       <c r="F227" t="n">
-        <v>1.975041523300011</v>
+        <v>1.975041523300013</v>
       </c>
       <c r="G227" t="n">
-        <v>0.1538829234909329</v>
+        <v>0.1538829234911094</v>
       </c>
       <c r="H227" t="inlineStr"/>
       <c r="I227" t="n">
@@ -7745,13 +7757,13 @@
         <v>522.3</v>
       </c>
       <c r="E228" t="n">
-        <v>14.73439968226421</v>
+        <v>14.73439968226341</v>
       </c>
       <c r="F228" t="n">
-        <v>0.4626184202929864</v>
+        <v>0.4626184202929866</v>
       </c>
       <c r="G228" t="n">
-        <v>0.6537615808138572</v>
+        <v>0.6537615808131367</v>
       </c>
       <c r="H228" t="inlineStr"/>
       <c r="I228" t="n">
@@ -7776,13 +7788,13 @@
         <v>522.3</v>
       </c>
       <c r="E229" t="n">
-        <v>24.70087280140458</v>
+        <v>24.70087280140383</v>
       </c>
       <c r="F229" t="n">
-        <v>0.4626184202929864</v>
+        <v>0.4626184202929866</v>
       </c>
       <c r="G229" t="n">
-        <v>0.6537615808138572</v>
+        <v>0.6537615808131367</v>
       </c>
       <c r="H229" t="inlineStr"/>
       <c r="I229" t="n">
@@ -7807,13 +7819,13 @@
         <v>522.3</v>
       </c>
       <c r="E230" t="n">
-        <v>25.65790793794401</v>
+        <v>25.65790793794378</v>
       </c>
       <c r="F230" t="n">
-        <v>0.4626184202929864</v>
+        <v>0.4626184202929866</v>
       </c>
       <c r="G230" t="n">
-        <v>0.6537615808138572</v>
+        <v>0.6537615808131367</v>
       </c>
       <c r="H230" t="inlineStr"/>
       <c r="I230" t="n">
@@ -7838,13 +7850,13 @@
         <v>522.8</v>
       </c>
       <c r="E231" t="n">
-        <v>15.11672148653673</v>
+        <v>15.11672148653595</v>
       </c>
       <c r="F231" t="n">
-        <v>0.564178778923093</v>
+        <v>0.564178778923094</v>
       </c>
       <c r="G231" t="n">
-        <v>0.4844674501896451</v>
+        <v>0.4844674501888714</v>
       </c>
       <c r="H231" t="inlineStr"/>
       <c r="I231" t="n">
@@ -7869,13 +7881,13 @@
         <v>522.8</v>
       </c>
       <c r="E232" t="n">
-        <v>25.1109862107261</v>
+        <v>25.11098621072537</v>
       </c>
       <c r="F232" t="n">
-        <v>0.564178778923093</v>
+        <v>0.564178778923094</v>
       </c>
       <c r="G232" t="n">
-        <v>0.4844674501896451</v>
+        <v>0.4844674501888714</v>
       </c>
       <c r="H232" t="inlineStr"/>
       <c r="I232" t="n">
@@ -7900,13 +7912,13 @@
         <v>522.8</v>
       </c>
       <c r="E233" t="n">
-        <v>26.23492878400019</v>
+        <v>26.23492878399996</v>
       </c>
       <c r="F233" t="n">
-        <v>0.564178778923093</v>
+        <v>0.564178778923094</v>
       </c>
       <c r="G233" t="n">
-        <v>0.4844674501896451</v>
+        <v>0.4844674501888714</v>
       </c>
       <c r="H233" t="inlineStr"/>
       <c r="I233" t="n">
@@ -7931,13 +7943,13 @@
         <v>523.3</v>
       </c>
       <c r="E234" t="n">
-        <v>15.33295705937469</v>
+        <v>15.33295705937393</v>
       </c>
       <c r="F234" t="n">
-        <v>1.116519817329047</v>
+        <v>1.116519817329049</v>
       </c>
       <c r="G234" t="n">
-        <v>0.1202038512916272</v>
+        <v>0.1202038512908442</v>
       </c>
       <c r="H234" t="inlineStr"/>
       <c r="I234" t="n">
@@ -7962,13 +7974,13 @@
         <v>523.3</v>
       </c>
       <c r="E235" t="n">
-        <v>25.36102508538067</v>
+        <v>25.36102508537994</v>
       </c>
       <c r="F235" t="n">
-        <v>1.116519817329047</v>
+        <v>1.116519817329049</v>
       </c>
       <c r="G235" t="n">
-        <v>0.1202038512916272</v>
+        <v>0.1202038512908442</v>
       </c>
       <c r="H235" t="inlineStr"/>
       <c r="I235" t="n">
@@ -7993,13 +8005,13 @@
         <v>523.3</v>
       </c>
       <c r="E236" t="n">
-        <v>26.83224467428196</v>
+        <v>26.83224467428173</v>
       </c>
       <c r="F236" t="n">
-        <v>1.116519817329047</v>
+        <v>1.116519817329049</v>
       </c>
       <c r="G236" t="n">
-        <v>0.1202038512916272</v>
+        <v>0.1202038512908442</v>
       </c>
       <c r="H236" t="inlineStr"/>
       <c r="I236" t="n">
@@ -8024,13 +8036,13 @@
         <v>523.8</v>
       </c>
       <c r="E237" t="n">
-        <v>15.65589331895582</v>
+        <v>15.65589331895508</v>
       </c>
       <c r="F237" t="n">
-        <v>1.48090893531768</v>
+        <v>1.480908935317681</v>
       </c>
       <c r="G237" t="n">
-        <v>0.1747751081331871</v>
+        <v>0.1747751081323227</v>
       </c>
       <c r="H237" t="inlineStr"/>
       <c r="I237" t="n">
@@ -8055,13 +8067,13 @@
         <v>523.8</v>
       </c>
       <c r="E238" t="n">
-        <v>25.6906617569607</v>
+        <v>25.69066175695999</v>
       </c>
       <c r="F238" t="n">
-        <v>1.48090893531768</v>
+        <v>1.480908935317681</v>
       </c>
       <c r="G238" t="n">
-        <v>0.1747751081331871</v>
+        <v>0.1747751081323227</v>
       </c>
       <c r="H238" t="inlineStr"/>
       <c r="I238" t="n">
@@ -8086,13 +8098,13 @@
         <v>523.8</v>
       </c>
       <c r="E239" t="n">
-        <v>27.20710295267128</v>
+        <v>27.20710295267105</v>
       </c>
       <c r="F239" t="n">
-        <v>1.48090893531768</v>
+        <v>1.480908935317681</v>
       </c>
       <c r="G239" t="n">
-        <v>0.1747751081331871</v>
+        <v>0.1747751081323227</v>
       </c>
       <c r="H239" t="inlineStr"/>
       <c r="I239" t="n">
@@ -8117,13 +8129,13 @@
         <v>524.3</v>
       </c>
       <c r="E240" t="n">
-        <v>15.85672277189096</v>
+        <v>15.85672277189022</v>
       </c>
       <c r="F240" t="n">
-        <v>1.480095338401821</v>
+        <v>1.480095338401824</v>
       </c>
       <c r="G240" t="n">
-        <v>0.2934323763092627</v>
+        <v>0.2934323763084577</v>
       </c>
       <c r="H240" t="inlineStr"/>
       <c r="I240" t="n">
@@ -8148,13 +8160,13 @@
         <v>524.3</v>
       </c>
       <c r="E241" t="n">
-        <v>25.89541844215631</v>
+        <v>25.89541844215559</v>
       </c>
       <c r="F241" t="n">
-        <v>1.480095338401821</v>
+        <v>1.480095338401824</v>
       </c>
       <c r="G241" t="n">
-        <v>0.2934323763092627</v>
+        <v>0.2934323763084577</v>
       </c>
       <c r="H241" t="inlineStr"/>
       <c r="I241" t="n">
@@ -8179,13 +8191,13 @@
         <v>524.3</v>
       </c>
       <c r="E242" t="n">
-        <v>27.44500298129685</v>
+        <v>27.44500298129661</v>
       </c>
       <c r="F242" t="n">
-        <v>1.480095338401821</v>
+        <v>1.480095338401824</v>
       </c>
       <c r="G242" t="n">
-        <v>0.2934323763092627</v>
+        <v>0.2934323763084577</v>
       </c>
       <c r="H242" t="inlineStr"/>
       <c r="I242" t="n">
@@ -8210,13 +8222,13 @@
         <v>524.8</v>
       </c>
       <c r="E243" t="n">
-        <v>15.69916253630925</v>
+        <v>15.69916253630853</v>
       </c>
       <c r="F243" t="n">
-        <v>1.114225198433921</v>
+        <v>1.114225198433923</v>
       </c>
       <c r="G243" t="n">
-        <v>0.196761565356556</v>
+        <v>0.196761565357338</v>
       </c>
       <c r="H243" t="inlineStr"/>
       <c r="I243" t="n">
@@ -8241,13 +8253,13 @@
         <v>524.8</v>
       </c>
       <c r="E244" t="n">
-        <v>25.75364299638533</v>
+        <v>25.75364299638461</v>
       </c>
       <c r="F244" t="n">
-        <v>1.114225198433921</v>
+        <v>1.114225198433923</v>
       </c>
       <c r="G244" t="n">
-        <v>0.196761565356556</v>
+        <v>0.196761565357338</v>
       </c>
       <c r="H244" t="inlineStr"/>
       <c r="I244" t="n">
@@ -8272,13 +8284,13 @@
         <v>524.8</v>
       </c>
       <c r="E245" t="n">
-        <v>27.74572400997584</v>
+        <v>27.74572400997562</v>
       </c>
       <c r="F245" t="n">
-        <v>1.114225198433921</v>
+        <v>1.114225198433923</v>
       </c>
       <c r="G245" t="n">
-        <v>0.196761565356556</v>
+        <v>0.196761565357338</v>
       </c>
       <c r="H245" t="inlineStr"/>
       <c r="I245" t="n">
@@ -8303,13 +8315,13 @@
         <v>525.3</v>
       </c>
       <c r="E246" t="n">
-        <v>15.7676569619198</v>
+        <v>15.76765696191912</v>
       </c>
       <c r="F246" t="n">
-        <v>0.7031466436964651</v>
+        <v>0.7031466436964653</v>
       </c>
       <c r="G246" t="n">
-        <v>0.4314701173950263</v>
+        <v>0.431470117395847</v>
       </c>
       <c r="H246" t="inlineStr"/>
       <c r="I246" t="n">
@@ -8334,13 +8346,13 @@
         <v>525.3</v>
       </c>
       <c r="E247" t="n">
-        <v>25.82427449027425</v>
+        <v>25.82427449027356</v>
       </c>
       <c r="F247" t="n">
-        <v>0.7031466436964651</v>
+        <v>0.7031466436964653</v>
       </c>
       <c r="G247" t="n">
-        <v>0.4314701173950263</v>
+        <v>0.431470117395847</v>
       </c>
       <c r="H247" t="inlineStr"/>
       <c r="I247" t="n">
@@ -8365,13 +8377,13 @@
         <v>525.3</v>
       </c>
       <c r="E248" t="n">
-        <v>28.1108427264064</v>
+        <v>28.1108427264062</v>
       </c>
       <c r="F248" t="n">
-        <v>0.7031466436964651</v>
+        <v>0.7031466436964653</v>
       </c>
       <c r="G248" t="n">
-        <v>0.4314701173950263</v>
+        <v>0.431470117395847</v>
       </c>
       <c r="H248" t="inlineStr"/>
       <c r="I248" t="n">
@@ -8396,13 +8408,13 @@
         <v>525.8</v>
       </c>
       <c r="E249" t="n">
-        <v>16.36666876599844</v>
+        <v>16.36666876599777</v>
       </c>
       <c r="F249" t="n">
-        <v>0.7001311704148183</v>
+        <v>0.7001311704148188</v>
       </c>
       <c r="G249" t="n">
-        <v>0.280115617810043</v>
+        <v>0.2801156178108868</v>
       </c>
       <c r="H249" t="inlineStr"/>
       <c r="I249" t="n">
@@ -8427,13 +8439,13 @@
         <v>525.8</v>
       </c>
       <c r="E250" t="n">
-        <v>26.42033785723499</v>
+        <v>26.4203378572343</v>
       </c>
       <c r="F250" t="n">
-        <v>0.7001311704148183</v>
+        <v>0.7001311704148188</v>
       </c>
       <c r="G250" t="n">
-        <v>0.280115617810043</v>
+        <v>0.2801156178108868</v>
       </c>
       <c r="H250" t="inlineStr"/>
       <c r="I250" t="n">
@@ -8458,13 +8470,13 @@
         <v>525.8</v>
       </c>
       <c r="E251" t="n">
-        <v>28.81811815090392</v>
+        <v>28.81811815090371</v>
       </c>
       <c r="F251" t="n">
-        <v>0.7001311704148183</v>
+        <v>0.7001311704148188</v>
       </c>
       <c r="G251" t="n">
-        <v>0.280115617810043</v>
+        <v>0.2801156178108868</v>
       </c>
       <c r="H251" t="inlineStr"/>
       <c r="I251" t="n">
@@ -8489,13 +8501,13 @@
         <v>526.3</v>
       </c>
       <c r="E252" t="n">
-        <v>16.96801371862255</v>
+        <v>16.96801371862187</v>
       </c>
       <c r="F252" t="n">
         <v>1.096561666271024</v>
       </c>
       <c r="G252" t="n">
-        <v>0.1466863541823004</v>
+        <v>0.1466863541830201</v>
       </c>
       <c r="H252" t="inlineStr"/>
       <c r="I252" t="n">
@@ -8520,13 +8532,13 @@
         <v>526.3</v>
       </c>
       <c r="E253" t="n">
-        <v>27.0193122309435</v>
+        <v>27.01931223094281</v>
       </c>
       <c r="F253" t="n">
         <v>1.096561666271024</v>
       </c>
       <c r="G253" t="n">
-        <v>0.1466863541823004</v>
+        <v>0.1466863541830201</v>
       </c>
       <c r="H253" t="inlineStr"/>
       <c r="I253" t="n">
@@ -8551,13 +8563,13 @@
         <v>526.3</v>
       </c>
       <c r="E254" t="n">
-        <v>29.42131620397974</v>
+        <v>29.42131620397951</v>
       </c>
       <c r="F254" t="n">
         <v>1.096561666271024</v>
       </c>
       <c r="G254" t="n">
-        <v>0.1466863541823004</v>
+        <v>0.1466863541830201</v>
       </c>
       <c r="H254" t="inlineStr"/>
       <c r="I254" t="n">
@@ -8582,13 +8594,13 @@
         <v>526.8</v>
       </c>
       <c r="E255" t="n">
-        <v>17.55068619087222</v>
+        <v>17.55068619087152</v>
       </c>
       <c r="F255" t="n">
-        <v>0.9683293080969479</v>
+        <v>0.9683293080969486</v>
       </c>
       <c r="G255" t="n">
-        <v>0.2835255751000298</v>
+        <v>0.283525575099573</v>
       </c>
       <c r="H255" t="inlineStr"/>
       <c r="I255" t="n">
@@ -8613,13 +8625,13 @@
         <v>526.8</v>
       </c>
       <c r="E256" t="n">
-        <v>27.60280568527428</v>
+        <v>27.60280568527357</v>
       </c>
       <c r="F256" t="n">
-        <v>0.9683293080969479</v>
+        <v>0.9683293080969486</v>
       </c>
       <c r="G256" t="n">
-        <v>0.2835255751000298</v>
+        <v>0.283525575099573</v>
       </c>
       <c r="H256" t="inlineStr"/>
       <c r="I256" t="n">
@@ -8644,13 +8656,13 @@
         <v>526.8</v>
       </c>
       <c r="E257" t="n">
-        <v>29.89821502043172</v>
+        <v>29.89821502043147</v>
       </c>
       <c r="F257" t="n">
-        <v>0.9683293080969479</v>
+        <v>0.9683293080969486</v>
       </c>
       <c r="G257" t="n">
-        <v>0.2835255751000298</v>
+        <v>0.283525575099573</v>
       </c>
       <c r="H257" t="inlineStr"/>
       <c r="I257" t="n">
@@ -8675,13 +8687,13 @@
         <v>526.9</v>
       </c>
       <c r="E258" t="n">
-        <v>29.94046727589723</v>
+        <v>29.94046727589697</v>
       </c>
       <c r="F258" t="n">
-        <v>0.9070110827686595</v>
+        <v>0.9070110827686603</v>
       </c>
       <c r="G258" t="n">
-        <v>0.3149842019442043</v>
+        <v>0.3149842019439437</v>
       </c>
       <c r="H258" t="inlineStr"/>
       <c r="I258" t="n">
@@ -8706,13 +8718,13 @@
         <v>527.3</v>
       </c>
       <c r="E259" t="n">
-        <v>17.90920371677487</v>
+        <v>17.90920371677419</v>
       </c>
       <c r="F259" t="n">
-        <v>0.773008485306255</v>
+        <v>0.773008485306256</v>
       </c>
       <c r="G259" t="n">
-        <v>0.3142905918247493</v>
+        <v>0.3142905918248202</v>
       </c>
       <c r="H259" t="inlineStr"/>
       <c r="I259" t="n">
@@ -8737,13 +8749,13 @@
         <v>527.3</v>
       </c>
       <c r="E260" t="n">
-        <v>27.95118325825074</v>
+        <v>27.95118325825004</v>
       </c>
       <c r="F260" t="n">
-        <v>0.773008485306255</v>
+        <v>0.773008485306256</v>
       </c>
       <c r="G260" t="n">
-        <v>0.3142905918247493</v>
+        <v>0.3142905918248202</v>
       </c>
       <c r="H260" t="inlineStr"/>
       <c r="I260" t="n">
@@ -8768,13 +8780,13 @@
         <v>527.8</v>
       </c>
       <c r="E261" t="n">
-        <v>18.35932773731125</v>
+        <v>18.35932773731058</v>
       </c>
       <c r="F261" t="n">
-        <v>1.405177329488421</v>
+        <v>1.405177329488423</v>
       </c>
       <c r="G261" t="n">
-        <v>0.5041967085817756</v>
+        <v>0.5041967085818887</v>
       </c>
       <c r="H261" t="inlineStr"/>
       <c r="I261" t="n">
@@ -8799,13 +8811,13 @@
         <v>527.8</v>
       </c>
       <c r="E262" t="n">
-        <v>28.3921972374141</v>
+        <v>28.39219723741341</v>
       </c>
       <c r="F262" t="n">
-        <v>1.405177329488421</v>
+        <v>1.405177329488423</v>
       </c>
       <c r="G262" t="n">
-        <v>0.5041967085817756</v>
+        <v>0.5041967085818887</v>
       </c>
       <c r="H262" t="inlineStr"/>
       <c r="I262" t="n">
@@ -8830,13 +8842,13 @@
         <v>528</v>
       </c>
       <c r="E263" t="n">
-        <v>18.59233843471731</v>
+        <v>18.59233843471664</v>
       </c>
       <c r="F263" t="n">
-        <v>1.880802844556056</v>
+        <v>1.880802844556058</v>
       </c>
       <c r="G263" t="n">
-        <v>0.4949702797796565</v>
+        <v>0.4949702797798886</v>
       </c>
       <c r="H263" t="inlineStr"/>
       <c r="I263" t="n">
@@ -8861,13 +8873,13 @@
         <v>528</v>
       </c>
       <c r="E264" t="n">
-        <v>28.61669928840628</v>
+        <v>28.61669928840559</v>
       </c>
       <c r="F264" t="n">
-        <v>1.880802844556056</v>
+        <v>1.880802844556058</v>
       </c>
       <c r="G264" t="n">
-        <v>0.4949702797796565</v>
+        <v>0.4949702797798886</v>
       </c>
       <c r="H264" t="inlineStr"/>
       <c r="I264" t="n">
@@ -8892,13 +8904,13 @@
         <v>531.4</v>
       </c>
       <c r="E265" t="n">
-        <v>23.90850770754958</v>
+        <v>23.90850770754896</v>
       </c>
       <c r="F265" t="n">
-        <v>1.342620612324182</v>
+        <v>1.342620612324183</v>
       </c>
       <c r="G265" t="n">
-        <v>0.3750487267414407</v>
+        <v>0.3750487267410605</v>
       </c>
       <c r="H265" t="inlineStr"/>
       <c r="I265" t="n">
@@ -8923,13 +8935,13 @@
         <v>531.9</v>
       </c>
       <c r="E266" t="n">
-        <v>24.09999690153839</v>
+        <v>24.09999690153779</v>
       </c>
       <c r="F266" t="n">
-        <v>1.251202870918269</v>
+        <v>1.251202870918271</v>
       </c>
       <c r="G266" t="n">
-        <v>0.3728668286126128</v>
+        <v>0.3728668286127885</v>
       </c>
       <c r="H266" t="inlineStr"/>
       <c r="I266" t="n">
@@ -8954,13 +8966,13 @@
         <v>532.4</v>
       </c>
       <c r="E267" t="n">
-        <v>24.47776237504624</v>
+        <v>24.47776237504565</v>
       </c>
       <c r="F267" t="n">
-        <v>0.9255203444738557</v>
+        <v>0.9255203444738573</v>
       </c>
       <c r="G267" t="n">
-        <v>0.4133219617142816</v>
+        <v>0.4133219617144845</v>
       </c>
       <c r="H267" t="inlineStr"/>
       <c r="I267" t="n">
@@ -8985,13 +8997,13 @@
         <v>532.9</v>
       </c>
       <c r="E268" t="n">
-        <v>24.56412241867196</v>
+        <v>24.56412241867138</v>
       </c>
       <c r="F268" t="n">
-        <v>0.8281584121061153</v>
+        <v>0.8281584121061165</v>
       </c>
       <c r="G268" t="n">
-        <v>0.3576402839319019</v>
+        <v>0.3576402839325678</v>
       </c>
       <c r="H268" t="inlineStr"/>
       <c r="I268" t="n">
@@ -9016,13 +9028,13 @@
         <v>533.4</v>
       </c>
       <c r="E269" t="n">
-        <v>24.66968252693296</v>
+        <v>24.66968252693238</v>
       </c>
       <c r="F269" t="n">
-        <v>0.4580375867309796</v>
+        <v>0.4580375867309799</v>
       </c>
       <c r="G269" t="n">
-        <v>0.1953526178735995</v>
+        <v>0.1953526178744607</v>
       </c>
       <c r="H269" t="inlineStr"/>
       <c r="I269" t="n">
@@ -9047,13 +9059,13 @@
         <v>533.9</v>
       </c>
       <c r="E270" t="n">
-        <v>24.51513735671218</v>
+        <v>24.5151373567116</v>
       </c>
       <c r="F270" t="n">
         <v>0.7378325424297659</v>
       </c>
       <c r="G270" t="n">
-        <v>0.496755602055966</v>
+        <v>0.4967556020563897</v>
       </c>
       <c r="H270" t="inlineStr"/>
       <c r="I270" t="n">
@@ -9078,13 +9090,13 @@
         <v>534.4</v>
       </c>
       <c r="E271" t="n">
-        <v>24.86073034694737</v>
+        <v>24.8607303469468</v>
       </c>
       <c r="F271" t="n">
-        <v>1.061129754381722</v>
+        <v>1.061129754381723</v>
       </c>
       <c r="G271" t="n">
-        <v>0.5584944279308489</v>
+        <v>0.5584944279310682</v>
       </c>
       <c r="H271" t="inlineStr"/>
       <c r="I271" t="n">
@@ -9109,13 +9121,13 @@
         <v>534.9</v>
       </c>
       <c r="E272" t="n">
-        <v>25.59800072781906</v>
+        <v>25.59800072781849</v>
       </c>
       <c r="F272" t="n">
         <v>1.140845366486581</v>
       </c>
       <c r="G272" t="n">
-        <v>0.4547910658071954</v>
+        <v>0.4547910658072119</v>
       </c>
       <c r="H272" t="inlineStr"/>
       <c r="I272" t="n">
@@ -9140,13 +9152,13 @@
         <v>535.4</v>
       </c>
       <c r="E273" t="n">
-        <v>26.43539844926393</v>
+        <v>26.43539844926335</v>
       </c>
       <c r="F273" t="n">
-        <v>1.712218738848168</v>
+        <v>1.71221873884817</v>
       </c>
       <c r="G273" t="n">
-        <v>0.5280201277594411</v>
+        <v>0.5280201277589204</v>
       </c>
       <c r="H273" t="inlineStr"/>
       <c r="I273" t="n">
@@ -9171,13 +9183,13 @@
         <v>535.8</v>
       </c>
       <c r="E274" t="n">
-        <v>26.9265478500189</v>
+        <v>26.92654785001831</v>
       </c>
       <c r="F274" t="n">
-        <v>1.975655383001959</v>
+        <v>1.975655383001961</v>
       </c>
       <c r="G274" t="n">
-        <v>0.4144579874077893</v>
+        <v>0.4144579874073563</v>
       </c>
       <c r="H274" t="inlineStr"/>
       <c r="I274" t="n">
@@ -9202,13 +9214,13 @@
         <v>651.6</v>
       </c>
       <c r="E275" t="n">
-        <v>11.92796601478464</v>
+        <v>11.92796601478367</v>
       </c>
       <c r="F275" t="n">
-        <v>0.9889724834258187</v>
+        <v>0.9889724834258193</v>
       </c>
       <c r="G275" t="n">
-        <v>0.3484011119854711</v>
+        <v>0.3484011119847545</v>
       </c>
       <c r="H275" t="inlineStr"/>
       <c r="I275" t="n">
@@ -9233,13 +9245,13 @@
         <v>651.6</v>
       </c>
       <c r="E276" t="n">
-        <v>20.87850686967396</v>
+        <v>20.87850686967312</v>
       </c>
       <c r="F276" t="n">
-        <v>0.9889724834258187</v>
+        <v>0.9889724834258193</v>
       </c>
       <c r="G276" t="n">
-        <v>0.3484011119854711</v>
+        <v>0.3484011119847545</v>
       </c>
       <c r="H276" t="inlineStr"/>
       <c r="I276" t="n">
@@ -9264,13 +9276,13 @@
         <v>651.6</v>
       </c>
       <c r="E277" t="n">
-        <v>19.18720310780669</v>
+        <v>19.18720310780648</v>
       </c>
       <c r="F277" t="n">
-        <v>0.9889724834258187</v>
+        <v>0.9889724834258193</v>
       </c>
       <c r="G277" t="n">
-        <v>0.3484011119854711</v>
+        <v>0.3484011119847545</v>
       </c>
       <c r="H277" t="inlineStr"/>
       <c r="I277" t="n">
@@ -9295,13 +9307,13 @@
         <v>652.1</v>
       </c>
       <c r="E278" t="n">
-        <v>12.2472086968742</v>
+        <v>12.24720869687323</v>
       </c>
       <c r="F278" t="n">
-        <v>1.207542192065901</v>
+        <v>1.207542192065902</v>
       </c>
       <c r="G278" t="n">
-        <v>0.5680913545908371</v>
+        <v>0.5680913545900071</v>
       </c>
       <c r="H278" t="inlineStr"/>
       <c r="I278" t="n">
@@ -9326,13 +9338,13 @@
         <v>652.1</v>
       </c>
       <c r="E279" t="n">
-        <v>21.17132778148417</v>
+        <v>21.17132778148333</v>
       </c>
       <c r="F279" t="n">
-        <v>1.207542192065901</v>
+        <v>1.207542192065902</v>
       </c>
       <c r="G279" t="n">
-        <v>0.5680913545908371</v>
+        <v>0.5680913545900071</v>
       </c>
       <c r="H279" t="inlineStr"/>
       <c r="I279" t="n">
@@ -9357,13 +9369,13 @@
         <v>652.1</v>
       </c>
       <c r="E280" t="n">
-        <v>19.30450410272475</v>
+        <v>19.30450410272452</v>
       </c>
       <c r="F280" t="n">
-        <v>1.207542192065901</v>
+        <v>1.207542192065902</v>
       </c>
       <c r="G280" t="n">
-        <v>0.5680913545908371</v>
+        <v>0.5680913545900071</v>
       </c>
       <c r="H280" t="inlineStr"/>
       <c r="I280" t="n">
@@ -9388,13 +9400,13 @@
         <v>652.4</v>
       </c>
       <c r="E281" t="n">
-        <v>19.12606245134536</v>
+        <v>19.12606245134514</v>
       </c>
       <c r="F281" t="n">
-        <v>0.5981028324614152</v>
+        <v>0.5981028324614156</v>
       </c>
       <c r="G281" t="n">
-        <v>0.7693180732638264</v>
+        <v>0.7693180732633064</v>
       </c>
       <c r="H281" t="inlineStr"/>
       <c r="I281" t="n">
@@ -9419,13 +9431,13 @@
         <v>652.6</v>
       </c>
       <c r="E282" t="n">
-        <v>12.06460068024583</v>
+        <v>12.06460068024486</v>
       </c>
       <c r="F282" t="n">
-        <v>0.5401087063684862</v>
+        <v>0.5401087063684866</v>
       </c>
       <c r="G282" t="n">
-        <v>0.8844653476430504</v>
+        <v>0.8844653476426152</v>
       </c>
       <c r="H282" t="inlineStr"/>
       <c r="I282" t="n">
@@ -9450,13 +9462,13 @@
         <v>652.6</v>
       </c>
       <c r="E283" t="n">
-        <v>20.9991466136237</v>
+        <v>20.99914661362286</v>
       </c>
       <c r="F283" t="n">
-        <v>0.5401087063684862</v>
+        <v>0.5401087063684866</v>
       </c>
       <c r="G283" t="n">
-        <v>0.8844653476430504</v>
+        <v>0.8844653476426152</v>
       </c>
       <c r="H283" t="inlineStr"/>
       <c r="I283" t="n">
@@ -9481,13 +9493,13 @@
         <v>652.6</v>
       </c>
       <c r="E284" t="n">
-        <v>19.22286300457578</v>
+        <v>19.22286300457557</v>
       </c>
       <c r="F284" t="n">
-        <v>0.5401087063684862</v>
+        <v>0.5401087063684866</v>
       </c>
       <c r="G284" t="n">
-        <v>0.8844653476430504</v>
+        <v>0.8844653476426152</v>
       </c>
       <c r="H284" t="inlineStr"/>
       <c r="I284" t="n">
@@ -9512,13 +9524,13 @@
         <v>653.1</v>
       </c>
       <c r="E285" t="n">
-        <v>12.45975371570316</v>
+        <v>12.45975371570219</v>
       </c>
       <c r="F285" t="n">
-        <v>1.619028076590849</v>
+        <v>1.619028076590851</v>
       </c>
       <c r="G285" t="n">
-        <v>0.9440981496388423</v>
+        <v>0.9440981496382583</v>
       </c>
       <c r="H285" t="inlineStr"/>
       <c r="I285" t="n">
@@ -9543,13 +9555,13 @@
         <v>653.1</v>
       </c>
       <c r="E286" t="n">
-        <v>21.58936475056857</v>
+        <v>21.58936475056773</v>
       </c>
       <c r="F286" t="n">
-        <v>1.619028076590849</v>
+        <v>1.619028076590851</v>
       </c>
       <c r="G286" t="n">
-        <v>0.9440981496388423</v>
+        <v>0.9440981496382583</v>
       </c>
       <c r="H286" t="inlineStr"/>
       <c r="I286" t="n">
@@ -9574,13 +9586,13 @@
         <v>653.1</v>
       </c>
       <c r="E287" t="n">
-        <v>20.09024192262881</v>
+        <v>20.09024192262858</v>
       </c>
       <c r="F287" t="n">
-        <v>1.619028076590849</v>
+        <v>1.619028076590851</v>
       </c>
       <c r="G287" t="n">
-        <v>0.9440981496388423</v>
+        <v>0.9440981496382583</v>
       </c>
       <c r="H287" t="inlineStr"/>
       <c r="I287" t="n">
@@ -9605,13 +9617,13 @@
         <v>653.3</v>
       </c>
       <c r="E288" t="n">
-        <v>12.48494428027918</v>
+        <v>12.48494428027823</v>
       </c>
       <c r="F288" t="n">
-        <v>1.854868545582642</v>
+        <v>1.854868545582644</v>
       </c>
       <c r="G288" t="n">
-        <v>0.8190741363504359</v>
+        <v>0.8190741363498528</v>
       </c>
       <c r="H288" t="inlineStr"/>
       <c r="I288" t="n">
@@ -9636,13 +9648,13 @@
         <v>653.3</v>
       </c>
       <c r="E289" t="n">
-        <v>21.73351883143594</v>
+        <v>21.7335188314351</v>
       </c>
       <c r="F289" t="n">
-        <v>1.854868545582642</v>
+        <v>1.854868545582644</v>
       </c>
       <c r="G289" t="n">
-        <v>0.8190741363504359</v>
+        <v>0.8190741363498528</v>
       </c>
       <c r="H289" t="inlineStr"/>
       <c r="I289" t="n">
@@ -9667,13 +9679,13 @@
         <v>653.3</v>
       </c>
       <c r="E290" t="n">
-        <v>20.50879702667062</v>
+        <v>20.5087970266704</v>
       </c>
       <c r="F290" t="n">
-        <v>1.854868545582642</v>
+        <v>1.854868545582644</v>
       </c>
       <c r="G290" t="n">
-        <v>0.8190741363504359</v>
+        <v>0.8190741363498528</v>
       </c>
       <c r="H290" t="inlineStr"/>
       <c r="I290" t="n">
@@ -9698,16 +9710,16 @@
         <v>750.8</v>
       </c>
       <c r="E291" t="n">
-        <v>37.55497385351921</v>
+        <v>37.55497385351821</v>
       </c>
       <c r="F291" t="n">
-        <v>1.372928021955616</v>
+        <v>1.372928021955617</v>
       </c>
       <c r="G291" t="n">
-        <v>0.1505902973488805</v>
+        <v>0.1505902973487885</v>
       </c>
       <c r="H291" t="n">
-        <v>227.9350901694639</v>
+        <v>227.9350901694638</v>
       </c>
       <c r="I291" t="n">
         <v>1</v>
@@ -9731,16 +9743,16 @@
         <v>750.8</v>
       </c>
       <c r="E292" t="n">
-        <v>32.57002814060947</v>
+        <v>32.57002814060856</v>
       </c>
       <c r="F292" t="n">
-        <v>1.372928021955616</v>
+        <v>1.372928021955617</v>
       </c>
       <c r="G292" t="n">
-        <v>0.1505902973488805</v>
+        <v>0.1505902973487885</v>
       </c>
       <c r="H292" t="n">
-        <v>256.5769452962618</v>
+        <v>256.5769452962625</v>
       </c>
       <c r="I292" t="n">
         <v>1</v>
@@ -9764,16 +9776,16 @@
         <v>750.8</v>
       </c>
       <c r="E293" t="n">
-        <v>22.48319288510975</v>
+        <v>22.48319288510894</v>
       </c>
       <c r="F293" t="n">
-        <v>1.372928021955616</v>
+        <v>1.372928021955617</v>
       </c>
       <c r="G293" t="n">
-        <v>0.1505902973488805</v>
+        <v>0.1505902973487885</v>
       </c>
       <c r="H293" t="n">
-        <v>269.0805451334944</v>
+        <v>269.0805451334959</v>
       </c>
       <c r="I293" t="n">
         <v>1</v>
@@ -9797,16 +9809,16 @@
         <v>750.8</v>
       </c>
       <c r="E294" t="n">
-        <v>35.4446019644498</v>
+        <v>35.4446019644494</v>
       </c>
       <c r="F294" t="n">
-        <v>1.372928021955616</v>
+        <v>1.372928021955617</v>
       </c>
       <c r="G294" t="n">
-        <v>0.1505902973488805</v>
+        <v>0.1505902973487885</v>
       </c>
       <c r="H294" t="n">
-        <v>298.7329660972584</v>
+        <v>298.7329660972599</v>
       </c>
       <c r="I294" t="n">
         <v>1</v>
@@ -9830,16 +9842,16 @@
         <v>750.8</v>
       </c>
       <c r="E295" t="n">
-        <v>31.42649779819905</v>
+        <v>31.42649779819904</v>
       </c>
       <c r="F295" t="n">
-        <v>1.372928021955616</v>
+        <v>1.372928021955617</v>
       </c>
       <c r="G295" t="n">
-        <v>0.1505902973488805</v>
+        <v>0.1505902973487885</v>
       </c>
       <c r="H295" t="n">
-        <v>321.9254307297864</v>
+        <v>321.9254307297882</v>
       </c>
       <c r="I295" t="n">
         <v>1</v>
@@ -9863,13 +9875,13 @@
         <v>751.1</v>
       </c>
       <c r="E296" t="n">
-        <v>23.24351631072127</v>
+        <v>23.24351631072049</v>
       </c>
       <c r="F296" t="n">
-        <v>1.293519361173364</v>
+        <v>1.293519361173365</v>
       </c>
       <c r="G296" t="n">
-        <v>0.03048836133542235</v>
+        <v>0.03048836133468722</v>
       </c>
       <c r="H296" t="inlineStr"/>
       <c r="I296" t="n">
@@ -9894,13 +9906,13 @@
         <v>751.1</v>
       </c>
       <c r="E297" t="n">
-        <v>16.07701967198491</v>
+        <v>16.07701967198473</v>
       </c>
       <c r="F297" t="n">
-        <v>1.293519361173364</v>
+        <v>1.293519361173365</v>
       </c>
       <c r="G297" t="n">
-        <v>0.03048836133542235</v>
+        <v>0.03048836133468722</v>
       </c>
       <c r="H297" t="inlineStr"/>
       <c r="I297" t="n">
@@ -9925,13 +9937,13 @@
         <v>751.1</v>
       </c>
       <c r="E298" t="n">
-        <v>10.95297051520531</v>
+        <v>10.9529705152063</v>
       </c>
       <c r="F298" t="n">
-        <v>1.293519361173364</v>
+        <v>1.293519361173365</v>
       </c>
       <c r="G298" t="n">
-        <v>0.03048836133542235</v>
+        <v>0.03048836133468722</v>
       </c>
       <c r="H298" t="inlineStr"/>
       <c r="I298" t="n">
@@ -9956,13 +9968,13 @@
         <v>751.1</v>
       </c>
       <c r="E299" t="n">
-        <v>14.54620327525989</v>
+        <v>14.54620327526052</v>
       </c>
       <c r="F299" t="n">
-        <v>1.293519361173364</v>
+        <v>1.293519361173365</v>
       </c>
       <c r="G299" t="n">
-        <v>0.03048836133542235</v>
+        <v>0.03048836133468722</v>
       </c>
       <c r="H299" t="inlineStr"/>
       <c r="I299" t="n">
@@ -9987,13 +9999,13 @@
         <v>751.1</v>
       </c>
       <c r="E300" t="n">
-        <v>23.89580610989997</v>
+        <v>23.89580610990079</v>
       </c>
       <c r="F300" t="n">
-        <v>1.293519361173364</v>
+        <v>1.293519361173365</v>
       </c>
       <c r="G300" t="n">
-        <v>0.03048836133542235</v>
+        <v>0.03048836133468722</v>
       </c>
       <c r="H300" t="inlineStr"/>
       <c r="I300" t="n">
@@ -10018,16 +10030,16 @@
         <v>751.2</v>
       </c>
       <c r="E301" t="n">
-        <v>37.47247343638567</v>
+        <v>37.47247343638466</v>
       </c>
       <c r="F301" t="n">
-        <v>1.420309570067794</v>
+        <v>1.420309570067795</v>
       </c>
       <c r="G301" t="n">
-        <v>0.03507618127335745</v>
+        <v>0.03507618127259821</v>
       </c>
       <c r="H301" t="n">
-        <v>228.7553565879416</v>
+        <v>228.7553565879415</v>
       </c>
       <c r="I301" t="n">
         <v>1</v>
@@ -10051,16 +10063,16 @@
         <v>751.2</v>
       </c>
       <c r="E302" t="n">
-        <v>32.75539625404414</v>
+        <v>32.75539625404322</v>
       </c>
       <c r="F302" t="n">
-        <v>1.420309570067794</v>
+        <v>1.420309570067795</v>
       </c>
       <c r="G302" t="n">
-        <v>0.03507618127335745</v>
+        <v>0.03507618127259821</v>
       </c>
       <c r="H302" t="n">
-        <v>257.4729099653291</v>
+        <v>257.4729099653298</v>
       </c>
       <c r="I302" t="n">
         <v>1</v>
@@ -10084,16 +10096,16 @@
         <v>751.2</v>
       </c>
       <c r="E303" t="n">
-        <v>22.77580642653759</v>
+        <v>22.77580642653679</v>
       </c>
       <c r="F303" t="n">
-        <v>1.420309570067794</v>
+        <v>1.420309570067795</v>
       </c>
       <c r="G303" t="n">
-        <v>0.03507618127335745</v>
+        <v>0.03507618127259821</v>
       </c>
       <c r="H303" t="n">
-        <v>270.2397803690155</v>
+        <v>270.239780369017</v>
       </c>
       <c r="I303" t="n">
         <v>1</v>
@@ -10117,16 +10129,16 @@
         <v>751.2</v>
       </c>
       <c r="E304" t="n">
-        <v>35.92373557295828</v>
+        <v>35.92373557295787</v>
       </c>
       <c r="F304" t="n">
-        <v>1.420309570067794</v>
+        <v>1.420309570067795</v>
       </c>
       <c r="G304" t="n">
-        <v>0.03507618127335745</v>
+        <v>0.03507618127259821</v>
       </c>
       <c r="H304" t="n">
-        <v>299.1444234633618</v>
+        <v>299.1444234633632</v>
       </c>
       <c r="I304" t="n">
         <v>1</v>
@@ -10150,16 +10162,16 @@
         <v>751.2</v>
       </c>
       <c r="E305" t="n">
-        <v>31.96769357840542</v>
+        <v>31.9676935784054</v>
       </c>
       <c r="F305" t="n">
-        <v>1.420309570067794</v>
+        <v>1.420309570067795</v>
       </c>
       <c r="G305" t="n">
-        <v>0.03507618127335745</v>
+        <v>0.03507618127259821</v>
       </c>
       <c r="H305" t="n">
-        <v>322.0128960144939</v>
+        <v>322.0128960144958</v>
       </c>
       <c r="I305" t="n">
         <v>1</v>
@@ -10183,13 +10195,13 @@
         <v>751.6</v>
       </c>
       <c r="E306" t="n">
-        <v>22.44714917060572</v>
+        <v>22.44714917060494</v>
       </c>
       <c r="F306" t="n">
-        <v>1.526963109551565</v>
+        <v>1.526963109551566</v>
       </c>
       <c r="G306" t="n">
-        <v>0.107339140263014</v>
+        <v>0.1073391402638918</v>
       </c>
       <c r="H306" t="inlineStr"/>
       <c r="I306" t="n">
@@ -10214,13 +10226,13 @@
         <v>751.6</v>
       </c>
       <c r="E307" t="n">
-        <v>15.14130057199778</v>
+        <v>15.14130057199764</v>
       </c>
       <c r="F307" t="n">
-        <v>1.526963109551565</v>
+        <v>1.526963109551566</v>
       </c>
       <c r="G307" t="n">
-        <v>0.107339140263014</v>
+        <v>0.1073391402638918</v>
       </c>
       <c r="H307" t="inlineStr"/>
       <c r="I307" t="n">
@@ -10245,13 +10257,13 @@
         <v>751.6</v>
       </c>
       <c r="E308" t="n">
-        <v>11.12750532662736</v>
+        <v>11.12750532662837</v>
       </c>
       <c r="F308" t="n">
-        <v>1.526963109551565</v>
+        <v>1.526963109551566</v>
       </c>
       <c r="G308" t="n">
-        <v>0.107339140263014</v>
+        <v>0.1073391402638918</v>
       </c>
       <c r="H308" t="inlineStr"/>
       <c r="I308" t="n">
@@ -10276,13 +10288,13 @@
         <v>751.6</v>
       </c>
       <c r="E309" t="n">
-        <v>15.43411161944654</v>
+        <v>15.43411161944714</v>
       </c>
       <c r="F309" t="n">
-        <v>1.526963109551565</v>
+        <v>1.526963109551566</v>
       </c>
       <c r="G309" t="n">
-        <v>0.107339140263014</v>
+        <v>0.1073391402638918</v>
       </c>
       <c r="H309" t="inlineStr"/>
       <c r="I309" t="n">
@@ -10307,13 +10319,13 @@
         <v>751.6</v>
       </c>
       <c r="E310" t="n">
-        <v>24.66492235360382</v>
+        <v>24.66492235360462</v>
       </c>
       <c r="F310" t="n">
-        <v>1.526963109551565</v>
+        <v>1.526963109551566</v>
       </c>
       <c r="G310" t="n">
-        <v>0.107339140263014</v>
+        <v>0.1073391402638918</v>
       </c>
       <c r="H310" t="inlineStr"/>
       <c r="I310" t="n">
@@ -10338,13 +10350,13 @@
         <v>752.1</v>
       </c>
       <c r="E311" t="n">
-        <v>22.44042641924961</v>
+        <v>22.44042641924881</v>
       </c>
       <c r="F311" t="n">
-        <v>1.700330144654979</v>
+        <v>1.70033014465498</v>
       </c>
       <c r="G311" t="n">
-        <v>0.4215509718715161</v>
+        <v>0.4215509718709702</v>
       </c>
       <c r="H311" t="inlineStr"/>
       <c r="I311" t="n">
@@ -10369,13 +10381,13 @@
         <v>752.1</v>
       </c>
       <c r="E312" t="n">
-        <v>14.72537316122964</v>
+        <v>14.72537316122946</v>
       </c>
       <c r="F312" t="n">
-        <v>1.700330144654979</v>
+        <v>1.70033014465498</v>
       </c>
       <c r="G312" t="n">
-        <v>0.4215509718715161</v>
+        <v>0.4215509718709702</v>
       </c>
       <c r="H312" t="inlineStr"/>
       <c r="I312" t="n">
@@ -10400,13 +10412,13 @@
         <v>752.1</v>
       </c>
       <c r="E313" t="n">
-        <v>10.72518079997993</v>
+        <v>10.72518079998094</v>
       </c>
       <c r="F313" t="n">
-        <v>1.700330144654979</v>
+        <v>1.70033014465498</v>
       </c>
       <c r="G313" t="n">
-        <v>0.4215509718715161</v>
+        <v>0.4215509718709702</v>
       </c>
       <c r="H313" t="inlineStr"/>
       <c r="I313" t="n">
@@ -10431,13 +10443,13 @@
         <v>752.1</v>
       </c>
       <c r="E314" t="n">
-        <v>15.60542861820153</v>
+        <v>15.60542861820211</v>
       </c>
       <c r="F314" t="n">
-        <v>1.700330144654979</v>
+        <v>1.70033014465498</v>
       </c>
       <c r="G314" t="n">
-        <v>0.4215509718715161</v>
+        <v>0.4215509718709702</v>
       </c>
       <c r="H314" t="inlineStr"/>
       <c r="I314" t="n">
@@ -10462,13 +10474,13 @@
         <v>752.1</v>
       </c>
       <c r="E315" t="n">
-        <v>24.67001655204894</v>
+        <v>24.67001655204972</v>
       </c>
       <c r="F315" t="n">
-        <v>1.700330144654979</v>
+        <v>1.70033014465498</v>
       </c>
       <c r="G315" t="n">
-        <v>0.4215509718715161</v>
+        <v>0.4215509718709702</v>
       </c>
       <c r="H315" t="inlineStr"/>
       <c r="I315" t="n">
@@ -10493,13 +10505,13 @@
         <v>752.5</v>
       </c>
       <c r="E316" t="n">
-        <v>21.64944650109707</v>
+        <v>21.64944650109626</v>
       </c>
       <c r="F316" t="n">
-        <v>1.905336777270485</v>
+        <v>1.905336777270486</v>
       </c>
       <c r="G316" t="n">
-        <v>0.1917051844304548</v>
+        <v>0.1917051844296607</v>
       </c>
       <c r="H316" t="inlineStr"/>
       <c r="I316" t="n">
@@ -10524,13 +10536,13 @@
         <v>752.5</v>
       </c>
       <c r="E317" t="n">
-        <v>13.65555416083489</v>
+        <v>13.65555416083473</v>
       </c>
       <c r="F317" t="n">
-        <v>1.905336777270485</v>
+        <v>1.905336777270486</v>
       </c>
       <c r="G317" t="n">
-        <v>0.1917051844304548</v>
+        <v>0.1917051844296607</v>
       </c>
       <c r="H317" t="inlineStr"/>
       <c r="I317" t="n">
@@ -10555,13 +10567,13 @@
         <v>752.5</v>
       </c>
       <c r="E318" t="n">
-        <v>10.94305178781896</v>
+        <v>10.94305178781997</v>
       </c>
       <c r="F318" t="n">
-        <v>1.905336777270485</v>
+        <v>1.905336777270486</v>
       </c>
       <c r="G318" t="n">
-        <v>0.1917051844304548</v>
+        <v>0.1917051844296607</v>
       </c>
       <c r="H318" t="inlineStr"/>
       <c r="I318" t="n">
@@ -10586,13 +10598,13 @@
         <v>752.5</v>
       </c>
       <c r="E319" t="n">
-        <v>16.58899498636473</v>
+        <v>16.58899498636527</v>
       </c>
       <c r="F319" t="n">
-        <v>1.905336777270485</v>
+        <v>1.905336777270486</v>
       </c>
       <c r="G319" t="n">
-        <v>0.1917051844304548</v>
+        <v>0.1917051844296607</v>
       </c>
       <c r="H319" t="inlineStr"/>
       <c r="I319" t="n">
@@ -10617,13 +10629,13 @@
         <v>752.5</v>
       </c>
       <c r="E320" t="n">
-        <v>25.49821172893883</v>
+        <v>25.49821172893958</v>
       </c>
       <c r="F320" t="n">
-        <v>1.905336777270485</v>
+        <v>1.905336777270486</v>
       </c>
       <c r="G320" t="n">
-        <v>0.1917051844304548</v>
+        <v>0.1917051844296607</v>
       </c>
       <c r="H320" t="inlineStr"/>
       <c r="I320" t="n">
@@ -10648,13 +10660,13 @@
         <v>763.5</v>
       </c>
       <c r="E321" t="n">
-        <v>11.22762211741139</v>
+        <v>11.22762211741037</v>
       </c>
       <c r="F321" t="n">
-        <v>0.9916570095933909</v>
+        <v>0.9916570095933919</v>
       </c>
       <c r="G321" t="n">
-        <v>0.276702368210072</v>
+        <v>0.2767023682092388</v>
       </c>
       <c r="H321" t="inlineStr"/>
       <c r="I321" t="n">
@@ -10679,13 +10691,13 @@
         <v>763.5</v>
       </c>
       <c r="E322" t="n">
-        <v>19.09521484615126</v>
+        <v>19.09521484615037</v>
       </c>
       <c r="F322" t="n">
-        <v>0.9916570095933909</v>
+        <v>0.9916570095933919</v>
       </c>
       <c r="G322" t="n">
-        <v>0.276702368210072</v>
+        <v>0.2767023682092388</v>
       </c>
       <c r="H322" t="inlineStr"/>
       <c r="I322" t="n">
@@ -10710,13 +10722,13 @@
         <v>763.5</v>
       </c>
       <c r="E323" t="n">
-        <v>15.9640662147459</v>
+        <v>15.96406621474571</v>
       </c>
       <c r="F323" t="n">
-        <v>0.9916570095933909</v>
+        <v>0.9916570095933919</v>
       </c>
       <c r="G323" t="n">
-        <v>0.276702368210072</v>
+        <v>0.2767023682092388</v>
       </c>
       <c r="H323" t="inlineStr"/>
       <c r="I323" t="n">
@@ -10741,13 +10753,13 @@
         <v>763.5</v>
       </c>
       <c r="E324" t="n">
-        <v>29.73310582565654</v>
+        <v>29.73310582565619</v>
       </c>
       <c r="F324" t="n">
-        <v>0.9916570095933909</v>
+        <v>0.9916570095933919</v>
       </c>
       <c r="G324" t="n">
-        <v>0.276702368210072</v>
+        <v>0.2767023682092388</v>
       </c>
       <c r="H324" t="inlineStr"/>
       <c r="I324" t="n">
@@ -10772,13 +10784,13 @@
         <v>763.7</v>
       </c>
       <c r="E325" t="n">
-        <v>19.07154493529861</v>
+        <v>19.07154493529772</v>
       </c>
       <c r="F325" t="n">
-        <v>1.395763031930913</v>
+        <v>1.395763031930914</v>
       </c>
       <c r="G325" t="n">
-        <v>0.1846551444728215</v>
+        <v>0.1846551444719783</v>
       </c>
       <c r="H325" t="inlineStr"/>
       <c r="I325" t="n">
@@ -10803,13 +10815,13 @@
         <v>763.8</v>
       </c>
       <c r="E326" t="n">
-        <v>29.94983087495577</v>
+        <v>29.94983087495542</v>
       </c>
       <c r="F326" t="n">
-        <v>1.515927509842519</v>
+        <v>1.515927509842521</v>
       </c>
       <c r="G326" t="n">
-        <v>0.1410284552745128</v>
+        <v>0.1410284552737679</v>
       </c>
       <c r="H326" t="inlineStr"/>
       <c r="I326" t="n">
@@ -10834,13 +10846,13 @@
         <v>764</v>
       </c>
       <c r="E327" t="n">
-        <v>11.01088858683893</v>
+        <v>11.01088858683793</v>
       </c>
       <c r="F327" t="n">
-        <v>1.649292763288041</v>
+        <v>1.649292763288043</v>
       </c>
       <c r="G327" t="n">
-        <v>0.04505304877975524</v>
+        <v>0.04505304877889495</v>
       </c>
       <c r="H327" t="inlineStr"/>
       <c r="I327" t="n">
@@ -10865,13 +10877,13 @@
         <v>764</v>
       </c>
       <c r="E328" t="n">
-        <v>19.19670933087199</v>
+        <v>19.19670933087112</v>
       </c>
       <c r="F328" t="n">
-        <v>1.649292763288041</v>
+        <v>1.649292763288043</v>
       </c>
       <c r="G328" t="n">
-        <v>0.04505304877975524</v>
+        <v>0.04505304877889495</v>
       </c>
       <c r="H328" t="inlineStr"/>
       <c r="I328" t="n">
@@ -10896,13 +10908,13 @@
         <v>764</v>
       </c>
       <c r="E329" t="n">
-        <v>16.61186188619661</v>
+        <v>16.61186188619644</v>
       </c>
       <c r="F329" t="n">
-        <v>1.649292763288041</v>
+        <v>1.649292763288043</v>
       </c>
       <c r="G329" t="n">
-        <v>0.04505304877975524</v>
+        <v>0.04505304877889495</v>
       </c>
       <c r="H329" t="inlineStr"/>
       <c r="I329" t="n">
@@ -10927,13 +10939,13 @@
         <v>764.5</v>
       </c>
       <c r="E330" t="n">
-        <v>11.08235548632522</v>
+        <v>11.08235548632424</v>
       </c>
       <c r="F330" t="n">
-        <v>1.359613288590663</v>
+        <v>1.359613288590665</v>
       </c>
       <c r="G330" t="n">
-        <v>0.1031898304907732</v>
+        <v>0.1031898304902059</v>
       </c>
       <c r="H330" t="inlineStr"/>
       <c r="I330" t="n">
@@ -10958,13 +10970,13 @@
         <v>764.5</v>
       </c>
       <c r="E331" t="n">
-        <v>19.54127907057551</v>
+        <v>19.54127907057466</v>
       </c>
       <c r="F331" t="n">
-        <v>1.359613288590663</v>
+        <v>1.359613288590665</v>
       </c>
       <c r="G331" t="n">
-        <v>0.1031898304907732</v>
+        <v>0.1031898304902059</v>
       </c>
       <c r="H331" t="inlineStr"/>
       <c r="I331" t="n">
@@ -10989,13 +11001,13 @@
         <v>764.5</v>
       </c>
       <c r="E332" t="n">
-        <v>17.33046412041754</v>
+        <v>17.33046412041737</v>
       </c>
       <c r="F332" t="n">
-        <v>1.359613288590663</v>
+        <v>1.359613288590665</v>
       </c>
       <c r="G332" t="n">
-        <v>0.1031898304907732</v>
+        <v>0.1031898304902059</v>
       </c>
       <c r="H332" t="inlineStr"/>
       <c r="I332" t="n">
@@ -11020,13 +11032,13 @@
         <v>765</v>
       </c>
       <c r="E333" t="n">
-        <v>10.97987400344705</v>
+        <v>10.97987400344607</v>
       </c>
       <c r="F333" t="n">
-        <v>1.88527222682241</v>
+        <v>1.885272226822412</v>
       </c>
       <c r="G333" t="n">
-        <v>0.3122086003172148</v>
+        <v>0.3122086003173097</v>
       </c>
       <c r="H333" t="inlineStr"/>
       <c r="I333" t="n">
@@ -11051,13 +11063,13 @@
         <v>765</v>
       </c>
       <c r="E334" t="n">
-        <v>19.63909518273978</v>
+        <v>19.63909518273894</v>
       </c>
       <c r="F334" t="n">
-        <v>1.88527222682241</v>
+        <v>1.885272226822412</v>
       </c>
       <c r="G334" t="n">
-        <v>0.3122086003172148</v>
+        <v>0.3122086003173097</v>
       </c>
       <c r="H334" t="inlineStr"/>
       <c r="I334" t="n">
@@ -11082,13 +11094,13 @@
         <v>765</v>
       </c>
       <c r="E335" t="n">
-        <v>17.80264039799376</v>
+        <v>17.80264039799359</v>
       </c>
       <c r="F335" t="n">
-        <v>1.88527222682241</v>
+        <v>1.885272226822412</v>
       </c>
       <c r="G335" t="n">
-        <v>0.3122086003172148</v>
+        <v>0.3122086003173097</v>
       </c>
       <c r="H335" t="inlineStr"/>
       <c r="I335" t="n">
@@ -11113,13 +11125,13 @@
         <v>765.1</v>
       </c>
       <c r="E336" t="n">
-        <v>10.99389254983888</v>
+        <v>10.9938925498379</v>
       </c>
       <c r="F336" t="n">
-        <v>1.956639624414465</v>
+        <v>1.956639624414467</v>
       </c>
       <c r="G336" t="n">
-        <v>0.3182192259558259</v>
+        <v>0.3182192259559275</v>
       </c>
       <c r="H336" t="inlineStr"/>
       <c r="I336" t="n">
@@ -11144,13 +11156,13 @@
         <v>765.1</v>
       </c>
       <c r="E337" t="n">
-        <v>19.70538255151487</v>
+        <v>19.70538255151402</v>
       </c>
       <c r="F337" t="n">
-        <v>1.956639624414465</v>
+        <v>1.956639624414467</v>
       </c>
       <c r="G337" t="n">
-        <v>0.3182192259558259</v>
+        <v>0.3182192259559275</v>
       </c>
       <c r="H337" t="inlineStr"/>
       <c r="I337" t="n">
@@ -11175,13 +11187,13 @@
         <v>765.1</v>
       </c>
       <c r="E338" t="n">
-        <v>17.9521268216225</v>
+        <v>17.95212682162234</v>
       </c>
       <c r="F338" t="n">
-        <v>1.956639624414465</v>
+        <v>1.956639624414467</v>
       </c>
       <c r="G338" t="n">
-        <v>0.3182192259558259</v>
+        <v>0.3182192259559275</v>
       </c>
       <c r="H338" t="inlineStr"/>
       <c r="I338" t="n">
